--- a/docs/00_构建与版本/故障码/LTD故障代码统一表.xlsx
+++ b/docs/00_构建与版本/故障码/LTD故障代码统一表.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文档简介" sheetId="1" r:id="R7d599b03e23a4104"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="故障代码" sheetId="2" r:id="R97d376c868394b28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备参数" sheetId="3" r:id="Ra34ba6fdacfb4982"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测量结果" sheetId="4" r:id="R8e202b2776824443"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文档简介" sheetId="1" r:id="Ra5e44b3574f94f17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="故障代码" sheetId="2" r:id="R7e91e1199543411f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="设备参数" sheetId="3" r:id="R391592786a9e49d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测量结果" sheetId="4" r:id="R4008947f72144251"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -49,8 +49,45 @@
       <x:color rgb="FF44546A"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF222222"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF222222"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF44546A"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF666666"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF375623"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF375623"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF666666"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -75,6 +112,26 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF8F8F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2EAF2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE7E6E6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -196,7 +253,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="46">
+  <x:cellXfs count="78">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -317,6 +374,98 @@
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -327,7 +476,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -337,7 +486,7 @@
         <x:color rgb="FF666666"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -347,7 +496,7 @@
         <x:color rgb="FF666666"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE7E6E6"/>
         </x:patternFill>
       </x:fill>
@@ -567,7 +716,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="9" t="str">
-        <x:v>正式版本｜2026-07-11</x:v>
+        <x:v>正式版本｜2026-07-12</x:v>
       </x:c>
       <x:c r="B2" s="9"/>
       <x:c r="C2" s="9"/>
@@ -688,12 +837,12 @@
         <x:v>状态</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="72" customHeight="1">
-      <x:c r="A5" s="25" t="n">
+    <x:row r="5" ht="36" hidden="0" customHeight="1">
+      <x:c r="A5" s="61" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B5" s="30" t="str">
-        <x:v>电机与驱动</x:v>
+      <x:c r="B5" s="66" t="str">
+        <x:v>电机驱动</x:v>
       </x:c>
       <x:c r="C5" s="22" t="n">
         <x:v>1</x:v>
@@ -710,16 +859,16 @@
       <x:c r="G5" s="18" t="str">
         <x:v>停止运动，检查机构、驱动供电和连接；排除异常后重新运行。</x:v>
       </x:c>
-      <x:c r="H5" s="22" t="str">
+      <x:c r="H5" s="71" t="str">
         <x:v>保留</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="72" customHeight="1">
-      <x:c r="A6" s="26" t="n">
+    <x:row r="6" ht="36" hidden="0" customHeight="1">
+      <x:c r="A6" s="61" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
-        <x:v>电机与驱动</x:v>
+      <x:c r="B6" s="66" t="str">
+        <x:v>电机驱动</x:v>
       </x:c>
       <x:c r="C6" s="22" t="n">
         <x:v>2</x:v>
@@ -736,16 +885,16 @@
       <x:c r="G6" s="18" t="str">
         <x:v>停止运动，检查机构、驱动供电和连接；排除异常后重新运行。</x:v>
       </x:c>
-      <x:c r="H6" s="22" t="str">
+      <x:c r="H6" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="72" customHeight="1">
-      <x:c r="A7" s="26" t="n">
+    <x:row r="7" ht="36" hidden="0" customHeight="1">
+      <x:c r="A7" s="61" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B7" s="31" t="str">
-        <x:v>电机与驱动</x:v>
+      <x:c r="B7" s="66" t="str">
+        <x:v>电机驱动</x:v>
       </x:c>
       <x:c r="C7" s="22" t="n">
         <x:v>3</x:v>
@@ -762,16 +911,16 @@
       <x:c r="G7" s="18" t="str">
         <x:v>停止运动，检查机构、驱动供电和连接；排除异常后重新运行。</x:v>
       </x:c>
-      <x:c r="H7" s="22" t="str">
+      <x:c r="H7" s="71" t="str">
         <x:v>保留</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="72" customHeight="1">
-      <x:c r="A8" s="26" t="n">
+    <x:row r="8" ht="36" hidden="0" customHeight="1">
+      <x:c r="A8" s="61" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B8" s="31" t="str">
-        <x:v>电机与驱动</x:v>
+      <x:c r="B8" s="66" t="str">
+        <x:v>电机驱动</x:v>
       </x:c>
       <x:c r="C8" s="22" t="n">
         <x:v>4</x:v>
@@ -788,16 +937,16 @@
       <x:c r="G8" s="18" t="str">
         <x:v>停止运动，检查机构、驱动供电和连接；排除异常后重新运行。</x:v>
       </x:c>
-      <x:c r="H8" s="22" t="str">
+      <x:c r="H8" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="72" customHeight="1">
-      <x:c r="A9" s="26" t="n">
+    <x:row r="9" ht="24" hidden="0" customHeight="1">
+      <x:c r="A9" s="61" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
-        <x:v>电机与驱动</x:v>
+      <x:c r="B9" s="66" t="str">
+        <x:v>电机驱动</x:v>
       </x:c>
       <x:c r="C9" s="22" t="n">
         <x:v>5</x:v>
@@ -814,16 +963,16 @@
       <x:c r="G9" s="18" t="str">
         <x:v>停止运动，检查机构、驱动供电和连接；排除异常后重新运行。</x:v>
       </x:c>
-      <x:c r="H9" s="22" t="str">
+      <x:c r="H9" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="72" customHeight="1">
-      <x:c r="A10" s="26" t="n">
+    <x:row r="10" ht="24" hidden="0" customHeight="1">
+      <x:c r="A10" s="61" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B10" s="31" t="str">
-        <x:v>电机与驱动</x:v>
+      <x:c r="B10" s="66" t="str">
+        <x:v>电机驱动</x:v>
       </x:c>
       <x:c r="C10" s="22" t="n">
         <x:v>6</x:v>
@@ -840,16 +989,16 @@
       <x:c r="G10" s="18" t="str">
         <x:v>停止运动，检查机构、驱动供电和连接；排除异常后重新运行。</x:v>
       </x:c>
-      <x:c r="H10" s="22" t="str">
+      <x:c r="H10" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="72" customHeight="1">
-      <x:c r="A11" s="26" t="n">
+    <x:row r="11" ht="24" hidden="0" customHeight="1">
+      <x:c r="A11" s="61" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B11" s="31" t="str">
-        <x:v>电机与驱动</x:v>
+      <x:c r="B11" s="66" t="str">
+        <x:v>电机驱动</x:v>
       </x:c>
       <x:c r="C11" s="22" t="n">
         <x:v>7</x:v>
@@ -866,16 +1015,16 @@
       <x:c r="G11" s="18" t="str">
         <x:v>停止运动，检查机构、驱动供电和连接；排除异常后重新运行。</x:v>
       </x:c>
-      <x:c r="H11" s="22" t="str">
+      <x:c r="H11" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="72" customHeight="1">
-      <x:c r="A12" s="26" t="n">
+    <x:row r="12" ht="24" hidden="0" customHeight="1">
+      <x:c r="A12" s="61" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B12" s="31" t="str">
-        <x:v>电机与驱动</x:v>
+      <x:c r="B12" s="66" t="str">
+        <x:v>电机驱动</x:v>
       </x:c>
       <x:c r="C12" s="22" t="n">
         <x:v>8</x:v>
@@ -892,16 +1041,16 @@
       <x:c r="G12" s="18" t="str">
         <x:v>停止运动，检查机构、驱动供电和连接；排除异常后重新运行。</x:v>
       </x:c>
-      <x:c r="H12" s="22" t="str">
+      <x:c r="H12" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="72" customHeight="1">
-      <x:c r="A13" s="26" t="n">
+    <x:row r="13" ht="24" hidden="0" customHeight="1">
+      <x:c r="A13" s="61" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B13" s="31" t="str">
-        <x:v>电机与驱动</x:v>
+      <x:c r="B13" s="66" t="str">
+        <x:v>电机驱动</x:v>
       </x:c>
       <x:c r="C13" s="22" t="n">
         <x:v>9</x:v>
@@ -918,334 +1067,334 @@
       <x:c r="G13" s="18" t="str">
         <x:v>停止运动，检查机构、驱动供电和连接；排除异常后重新运行。</x:v>
       </x:c>
-      <x:c r="H13" s="22" t="str">
+      <x:c r="H13" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="72" customHeight="1">
-      <x:c r="A14" s="27" t="n">
+    <x:row r="14" ht="24" hidden="0" customHeight="1">
+      <x:c r="A14" s="61" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B14" s="32" t="str">
-        <x:v>电机与驱动</x:v>
-      </x:c>
-      <x:c r="C14" s="34" t="n">
+      <x:c r="B14" s="66" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="C14" s="22" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D14" s="34" t="str">
+      <x:c r="D14" s="22" t="str">
         <x:v>11-10</x:v>
       </x:c>
-      <x:c r="E14" s="35" t="str">
-        <x:v>电机驱动通信失败</x:v>
-      </x:c>
-      <x:c r="F14" s="35" t="str">
-        <x:v>主控单元读写电机驱动器状态或配置失败，或发现驱动配置丢失，无法确认当前位置、目标位置和运行状态。</x:v>
-      </x:c>
-      <x:c r="G14" s="35" t="str">
-        <x:v>停止运动，检查机构、驱动供电和连接；排除异常后重新运行。</x:v>
-      </x:c>
-      <x:c r="H14" s="36" t="str">
+      <x:c r="E14" s="18" t="str">
+        <x:v>电机驱动通信异常</x:v>
+      </x:c>
+      <x:c r="F14" s="18" t="str">
+        <x:v>主控单元读取或写入电机驱动寄存器时通信失败，当前驱动状态和运动参数无法确认。</x:v>
+      </x:c>
+      <x:c r="G14" s="18" t="str">
+        <x:v>停止运动，检查电机驱动供电、通信连接和驱动状态；重新上电后复核。</x:v>
+      </x:c>
+      <x:c r="H14" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="72" customHeight="1">
-      <x:c r="A15" s="25" t="n">
+    <x:row r="15" ht="36" hidden="0" customHeight="1">
+      <x:c r="A15" s="61" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B15" s="66" t="str">
+        <x:v>电机驱动</x:v>
+      </x:c>
+      <x:c r="C15" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D15" s="22" t="str">
+        <x:v>11-11</x:v>
+      </x:c>
+      <x:c r="E15" s="18" t="str">
+        <x:v>电机驱动配置丢失</x:v>
+      </x:c>
+      <x:c r="F15" s="18" t="str">
+        <x:v>设备能够读取电机驱动器，但关键运动配置为空或未保持，不能确认电流、速度和运动控制参数有效。</x:v>
+      </x:c>
+      <x:c r="G15" s="18" t="str">
+        <x:v>停止运动并重新上电；检查电机驱动供电是否中断。若重复出现，记录故障码和发生动作。</x:v>
+      </x:c>
+      <x:c r="H15" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="24" hidden="0" customHeight="1">
+      <x:c r="A16" s="61" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B15" s="30" t="str">
-        <x:v>位置检测</x:v>
-      </x:c>
-      <x:c r="C15" s="22" t="n">
+      <x:c r="B16" s="66" t="str">
+        <x:v>编码器</x:v>
+      </x:c>
+      <x:c r="C16" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D15" s="22" t="str">
+      <x:c r="D16" s="22" t="str">
         <x:v>12-1</x:v>
       </x:c>
-      <x:c r="E15" s="18" t="str">
+      <x:c r="E16" s="18" t="str">
         <x:v>编码器通信无响应</x:v>
       </x:c>
-      <x:c r="F15" s="18" t="str">
+      <x:c r="F16" s="18" t="str">
         <x:v>位置编码器通信接口未就绪、接收启动失败，或等待期间始终没有取得一帧有效位置数据。</x:v>
-      </x:c>
-      <x:c r="G15" s="18" t="str">
-        <x:v>停止运动，检查编码器安装、连接和位置反馈；确认正常后重试。</x:v>
-      </x:c>
-      <x:c r="H15" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="72" customHeight="1">
-      <x:c r="A16" s="26" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B16" s="31" t="str">
-        <x:v>位置检测</x:v>
-      </x:c>
-      <x:c r="C16" s="22" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="22" t="str">
-        <x:v>12-2</x:v>
-      </x:c>
-      <x:c r="E16" s="18" t="str">
-        <x:v>编码器校验位错误</x:v>
-      </x:c>
-      <x:c r="F16" s="18" t="str">
-        <x:v>编码器返回的位置数据未通过奇偶校验，说明本次位置数据在传输过程中发生错误。</x:v>
       </x:c>
       <x:c r="G16" s="18" t="str">
         <x:v>停止运动，检查编码器安装、连接和位置反馈；确认正常后重试。</x:v>
       </x:c>
-      <x:c r="H16" s="22" t="str">
+      <x:c r="H16" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="72" customHeight="1">
-      <x:c r="A17" s="26" t="n">
+    <x:row r="17" ht="24" hidden="0" customHeight="1">
+      <x:c r="A17" s="61" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B17" s="31" t="str">
-        <x:v>位置检测</x:v>
+      <x:c r="B17" s="66" t="str">
+        <x:v>编码器</x:v>
       </x:c>
       <x:c r="C17" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D17" s="22" t="str">
-        <x:v>12-3</x:v>
+        <x:v>12-2</x:v>
       </x:c>
       <x:c r="E17" s="18" t="str">
-        <x:v>编码器检测到丢步</x:v>
+        <x:v>编码器校验位错误</x:v>
       </x:c>
       <x:c r="F17" s="18" t="str">
-        <x:v>电机已产生明显位移，但编码轮的位移变化小于跟随要求，或标定得到的卷筒周长低于允许下限。</x:v>
+        <x:v>编码器返回的位置数据未通过奇偶校验，说明本次位置数据在传输过程中发生错误。</x:v>
       </x:c>
       <x:c r="G17" s="18" t="str">
         <x:v>停止运动，检查编码器安装、连接和位置反馈；确认正常后重试。</x:v>
       </x:c>
-      <x:c r="H17" s="22" t="str">
+      <x:c r="H17" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="72" customHeight="1">
-      <x:c r="A18" s="26" t="n">
+    <x:row r="18" ht="24" hidden="0" customHeight="1">
+      <x:c r="A18" s="61" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B18" s="31" t="str">
-        <x:v>位置检测</x:v>
+      <x:c r="B18" s="66" t="str">
+        <x:v>编码器</x:v>
       </x:c>
       <x:c r="C18" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D18" s="22" t="str">
-        <x:v>12-4</x:v>
+        <x:v>12-3</x:v>
       </x:c>
       <x:c r="E18" s="18" t="str">
-        <x:v>编码器多次无效数据</x:v>
+        <x:v>编码器检测到丢步</x:v>
       </x:c>
       <x:c r="F18" s="18" t="str">
-        <x:v>编码器连续返回无效数据，且数据中没有可归类为校验、未完成、运算溢出或线性报警的明确状态。</x:v>
+        <x:v>电机已产生明显位移，但编码轮的位移变化小于跟随要求，或标定得到的卷筒周长低于允许下限。</x:v>
       </x:c>
       <x:c r="G18" s="18" t="str">
         <x:v>停止运动，检查编码器安装、连接和位置反馈；确认正常后重试。</x:v>
       </x:c>
-      <x:c r="H18" s="22" t="str">
+      <x:c r="H18" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="72" customHeight="1">
-      <x:c r="A19" s="26" t="n">
+    <x:row r="19" ht="24" hidden="0" customHeight="1">
+      <x:c r="A19" s="61" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B19" s="31" t="str">
-        <x:v>位置检测</x:v>
+      <x:c r="B19" s="66" t="str">
+        <x:v>编码器</x:v>
       </x:c>
       <x:c r="C19" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D19" s="22" t="str">
-        <x:v>12-5</x:v>
+        <x:v>12-4</x:v>
       </x:c>
       <x:c r="E19" s="18" t="str">
-        <x:v>编码器初始化失败</x:v>
+        <x:v>编码器多次无效数据</x:v>
       </x:c>
       <x:c r="F19" s="18" t="str">
-        <x:v>上电读取编码器位置记录时，两个备份区均无有效数据，设备已将位置回退为默认值。</x:v>
+        <x:v>编码器连续返回无效数据，且数据中没有可归类为校验、未完成、运算溢出或线性报警的明确状态。</x:v>
       </x:c>
       <x:c r="G19" s="18" t="str">
         <x:v>停止运动，检查编码器安装、连接和位置反馈；确认正常后重试。</x:v>
       </x:c>
-      <x:c r="H19" s="22" t="str">
+      <x:c r="H19" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="72" customHeight="1">
-      <x:c r="A20" s="26" t="n">
+    <x:row r="20" ht="24" hidden="0" customHeight="1">
+      <x:c r="A20" s="61" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B20" s="31" t="str">
-        <x:v>位置检测</x:v>
+      <x:c r="B20" s="66" t="str">
+        <x:v>编码器</x:v>
       </x:c>
       <x:c r="C20" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D20" s="22" t="str">
-        <x:v>12-6</x:v>
+        <x:v>12-5</x:v>
       </x:c>
       <x:c r="E20" s="18" t="str">
-        <x:v>编码器上电变化</x:v>
+        <x:v>编码器初始化失败</x:v>
       </x:c>
       <x:c r="F20" s="18" t="str">
-        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于上电前后编码器位置记录发生异常变化的情况。</x:v>
+        <x:v>上电读取编码器位置记录时，两个备份区均无有效数据，设备已将位置回退为默认值。</x:v>
       </x:c>
       <x:c r="G20" s="18" t="str">
         <x:v>停止运动，检查编码器安装、连接和位置反馈；确认正常后重试。</x:v>
       </x:c>
-      <x:c r="H20" s="22" t="str">
-        <x:v>保留</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="72" customHeight="1">
-      <x:c r="A21" s="26" t="n">
+      <x:c r="H20" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="36" hidden="0" customHeight="1">
+      <x:c r="A21" s="61" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B21" s="31" t="str">
-        <x:v>位置检测</x:v>
+      <x:c r="B21" s="66" t="str">
+        <x:v>编码器</x:v>
       </x:c>
       <x:c r="C21" s="22" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D21" s="22" t="str">
-        <x:v>12-7</x:v>
+        <x:v>12-6</x:v>
       </x:c>
       <x:c r="E21" s="18" t="str">
-        <x:v>编码器计算溢出</x:v>
+        <x:v>编码器上电变化</x:v>
       </x:c>
       <x:c r="F21" s="18" t="str">
-        <x:v>编码器状态表明内部角度运算超出有效范围，本次角度值不能作为可靠位置使用。</x:v>
+        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于上电前后编码器位置记录发生异常变化的情况。</x:v>
       </x:c>
       <x:c r="G21" s="18" t="str">
         <x:v>停止运动，检查编码器安装、连接和位置反馈；确认正常后重试。</x:v>
       </x:c>
-      <x:c r="H21" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="72" customHeight="1">
-      <x:c r="A22" s="26" t="n">
+      <x:c r="H21" s="71" t="str">
+        <x:v>保留</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="24" hidden="0" customHeight="1">
+      <x:c r="A22" s="61" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B22" s="31" t="str">
-        <x:v>位置检测</x:v>
+      <x:c r="B22" s="66" t="str">
+        <x:v>编码器</x:v>
       </x:c>
       <x:c r="C22" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D22" s="22" t="str">
-        <x:v>12-8</x:v>
+        <x:v>12-7</x:v>
       </x:c>
       <x:c r="E22" s="18" t="str">
-        <x:v>编码器线性报警</x:v>
+        <x:v>编码器计算溢出</x:v>
       </x:c>
       <x:c r="F22" s="18" t="str">
-        <x:v>编码器状态表明磁场或安装条件导致线性度超差，本次位置值可能存在明显偏差。</x:v>
+        <x:v>编码器状态表明内部角度运算超出有效范围，本次角度值不能作为可靠位置使用。</x:v>
       </x:c>
       <x:c r="G22" s="18" t="str">
         <x:v>停止运动，检查编码器安装、连接和位置反馈；确认正常后重试。</x:v>
       </x:c>
-      <x:c r="H22" s="22" t="str">
+      <x:c r="H22" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="72" customHeight="1">
-      <x:c r="A23" s="26" t="n">
+    <x:row r="23" ht="24" hidden="0" customHeight="1">
+      <x:c r="A23" s="61" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B23" s="31" t="str">
-        <x:v>位置检测</x:v>
+      <x:c r="B23" s="66" t="str">
+        <x:v>编码器</x:v>
       </x:c>
       <x:c r="C23" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D23" s="22" t="str">
-        <x:v>12-9</x:v>
+        <x:v>12-8</x:v>
       </x:c>
       <x:c r="E23" s="18" t="str">
-        <x:v>编码器差值过大</x:v>
+        <x:v>编码器线性报警</x:v>
       </x:c>
       <x:c r="F23" s="18" t="str">
-        <x:v>相邻位置值变化超过允许范围，或卷筒周长标定结果高于允许上限，位置变化与实际运动不一致。</x:v>
+        <x:v>编码器状态表明磁场或安装条件导致线性度超差，本次位置值可能存在明显偏差。</x:v>
       </x:c>
       <x:c r="G23" s="18" t="str">
         <x:v>停止运动，检查编码器安装、连接和位置反馈；确认正常后重试。</x:v>
       </x:c>
-      <x:c r="H23" s="22" t="str">
+      <x:c r="H23" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="72" customHeight="1">
-      <x:c r="A24" s="27" t="n">
+    <x:row r="24" ht="24" hidden="0" customHeight="1">
+      <x:c r="A24" s="61" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B24" s="32" t="str">
-        <x:v>位置检测</x:v>
-      </x:c>
-      <x:c r="C24" s="34" t="n">
+      <x:c r="B24" s="66" t="str">
+        <x:v>编码器</x:v>
+      </x:c>
+      <x:c r="C24" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D24" s="22" t="str">
+        <x:v>12-9</x:v>
+      </x:c>
+      <x:c r="E24" s="18" t="str">
+        <x:v>编码器差值过大</x:v>
+      </x:c>
+      <x:c r="F24" s="18" t="str">
+        <x:v>相邻位置值变化超过允许范围，或卷筒周长标定结果高于允许上限，位置变化与实际运动不一致。</x:v>
+      </x:c>
+      <x:c r="G24" s="18" t="str">
+        <x:v>停止运动，检查编码器安装、连接和位置反馈；确认正常后重试。</x:v>
+      </x:c>
+      <x:c r="H24" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="24" hidden="0" customHeight="1">
+      <x:c r="A25" s="61" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B25" s="66" t="str">
+        <x:v>编码器</x:v>
+      </x:c>
+      <x:c r="C25" s="22" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D24" s="34" t="str">
+      <x:c r="D25" s="22" t="str">
         <x:v>12-10</x:v>
       </x:c>
-      <x:c r="E24" s="35" t="str">
+      <x:c r="E25" s="18" t="str">
         <x:v>编码器状态未完成</x:v>
       </x:c>
-      <x:c r="F24" s="35" t="str">
+      <x:c r="F25" s="18" t="str">
         <x:v>编码器尚未完成内部角度计算，返回帧中的位置数据未达到可用状态。</x:v>
       </x:c>
-      <x:c r="G24" s="35" t="str">
+      <x:c r="G25" s="18" t="str">
         <x:v>停止运动，检查编码器安装、连接和位置反馈；确认正常后重试。</x:v>
       </x:c>
-      <x:c r="H24" s="36" t="str">
+      <x:c r="H25" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="72" customHeight="1">
-      <x:c r="A25" s="25" t="n">
+    <x:row r="26" ht="24" hidden="0" customHeight="1">
+      <x:c r="A26" s="61" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B25" s="30" t="str">
+      <x:c r="B26" s="66" t="str">
         <x:v>传感器与密度</x:v>
       </x:c>
-      <x:c r="C25" s="22" t="n">
+      <x:c r="C26" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D25" s="22" t="str">
+      <x:c r="D26" s="22" t="str">
         <x:v>13-1</x:v>
-      </x:c>
-      <x:c r="E25" s="18" t="str">
-        <x:v>传感器数据校验失败</x:v>
-      </x:c>
-      <x:c r="F25" s="18" t="str">
-        <x:v>传感器已返回完整数据，但接收端计算的校验值与数据中携带的校验值不一致。</x:v>
-      </x:c>
-      <x:c r="G25" s="18" t="str">
-        <x:v>检查传感器供电、连接和工作状态；数据稳定后重新测量。</x:v>
-      </x:c>
-      <x:c r="H25" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="72" customHeight="1">
-      <x:c r="A26" s="26" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B26" s="31" t="str">
-        <x:v>传感器与密度</x:v>
-      </x:c>
-      <x:c r="C26" s="22" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D26" s="22" t="str">
-        <x:v>13-2</x:v>
       </x:c>
       <x:c r="E26" s="18" t="str">
         <x:v>声波频率异常</x:v>
@@ -1256,1307 +1405,1411 @@
       <x:c r="G26" s="18" t="str">
         <x:v>检查传感器供电、连接和工作状态；数据稳定后重新测量。</x:v>
       </x:c>
-      <x:c r="H26" s="22" t="str">
+      <x:c r="H26" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="72" customHeight="1">
-      <x:c r="A27" s="26" t="n">
+    <x:row r="27" ht="24" hidden="0" customHeight="1">
+      <x:c r="A27" s="61" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B27" s="31" t="str">
+      <x:c r="B27" s="66" t="str">
         <x:v>传感器与密度</x:v>
       </x:c>
       <x:c r="C27" s="22" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D27" s="22" t="str">
-        <x:v>13-3</x:v>
+        <x:v>13-2</x:v>
       </x:c>
       <x:c r="E27" s="18" t="str">
-        <x:v>传感器通信超时</x:v>
+        <x:v>密度值异常无效</x:v>
       </x:c>
       <x:c r="F27" s="18" t="str">
-        <x:v>向传感器发送指令后，在规定时间和重试次数内没有收到任何有效响应数据。</x:v>
+        <x:v>传感器返回的密度小于等于零或大于二千千克每立方米，连续无效时终止当前液位或密度判断。</x:v>
       </x:c>
       <x:c r="G27" s="18" t="str">
         <x:v>检查传感器供电、连接和工作状态；数据稳定后重新测量。</x:v>
       </x:c>
-      <x:c r="H27" s="22" t="str">
+      <x:c r="H27" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="72" customHeight="1">
-      <x:c r="A28" s="26" t="n">
+    <x:row r="28" ht="36" hidden="0" customHeight="1">
+      <x:c r="A28" s="61" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B28" s="31" t="str">
+      <x:c r="B28" s="66" t="str">
         <x:v>传感器与密度</x:v>
       </x:c>
       <x:c r="C28" s="22" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D28" s="22" t="str">
-        <x:v>13-4</x:v>
+        <x:v>13-3</x:v>
       </x:c>
       <x:c r="E28" s="18" t="str">
-        <x:v>密度值异常无效</x:v>
+        <x:v>传感器温度异常</x:v>
       </x:c>
       <x:c r="F28" s="18" t="str">
-        <x:v>传感器返回的密度小于等于零或大于二千千克每立方米，连续无效时终止当前液位或密度判断。</x:v>
+        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于传感器温度超出可测范围或温度数据无效的情况。</x:v>
       </x:c>
       <x:c r="G28" s="18" t="str">
         <x:v>检查传感器供电、连接和工作状态；数据稳定后重新测量。</x:v>
       </x:c>
-      <x:c r="H28" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="72" customHeight="1">
-      <x:c r="A29" s="26" t="n">
+      <x:c r="H28" s="71" t="str">
+        <x:v>保留</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="24" hidden="0" customHeight="1">
+      <x:c r="A29" s="61" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B29" s="31" t="str">
+      <x:c r="B29" s="66" t="str">
         <x:v>传感器与密度</x:v>
       </x:c>
       <x:c r="C29" s="22" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D29" s="22" t="str">
-        <x:v>13-5</x:v>
+        <x:v>13-4</x:v>
       </x:c>
       <x:c r="E29" s="18" t="str">
-        <x:v>传感器温度异常</x:v>
+        <x:v>传感器电压异常</x:v>
       </x:c>
       <x:c r="F29" s="18" t="str">
-        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于传感器温度超出可测范围或温度数据无效的情况。</x:v>
+        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于传感器供电电压超出正常范围的情况。</x:v>
       </x:c>
       <x:c r="G29" s="18" t="str">
         <x:v>检查传感器供电、连接和工作状态；数据稳定后重新测量。</x:v>
       </x:c>
-      <x:c r="H29" s="22" t="str">
+      <x:c r="H29" s="71" t="str">
         <x:v>保留</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="72" customHeight="1">
-      <x:c r="A30" s="26" t="n">
+    <x:row r="30" ht="24" hidden="0" customHeight="1">
+      <x:c r="A30" s="61" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B30" s="32" t="str">
+      <x:c r="B30" s="66" t="str">
         <x:v>传感器与密度</x:v>
       </x:c>
       <x:c r="C30" s="22" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D30" s="22" t="str">
-        <x:v>13-6</x:v>
+        <x:v>13-5</x:v>
       </x:c>
       <x:c r="E30" s="18" t="str">
-        <x:v>传感器电压异常</x:v>
+        <x:v>密度不稳定</x:v>
       </x:c>
       <x:c r="F30" s="18" t="str">
-        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于传感器供电电压超出正常范围的情况。</x:v>
+        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于连续密度样本波动超过稳定判定范围的情况。</x:v>
       </x:c>
       <x:c r="G30" s="18" t="str">
         <x:v>检查传感器供电、连接和工作状态；数据稳定后重新测量。</x:v>
       </x:c>
-      <x:c r="H30" s="22" t="str">
+      <x:c r="H30" s="71" t="str">
         <x:v>保留</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="72" customHeight="1">
-      <x:c r="A31" s="26" t="n">
+    <x:row r="31" ht="24" hidden="0" customHeight="1">
+      <x:c r="A31" s="61" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B31" s="30" t="str">
+      <x:c r="B31" s="66" t="str">
+        <x:v>传感器与密度</x:v>
+      </x:c>
+      <x:c r="C31" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D31" s="22" t="str">
+        <x:v>13-6</x:v>
+      </x:c>
+      <x:c r="E31" s="18" t="str">
+        <x:v>传感器设备内部错误</x:v>
+      </x:c>
+      <x:c r="F31" s="18" t="str">
+        <x:v>通信和数据格式正常，但传感器在响应中明确返回设备内部错误状态。</x:v>
+      </x:c>
+      <x:c r="G31" s="18" t="str">
+        <x:v>检查传感器供电、连接和工作状态；数据稳定后重新测量。</x:v>
+      </x:c>
+      <x:c r="H31" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="24" hidden="0" customHeight="1">
+      <x:c r="A32" s="61" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B32" s="66" t="str">
+        <x:v>传感器通信</x:v>
+      </x:c>
+      <x:c r="C32" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D32" s="22" t="str">
+        <x:v>14-1</x:v>
+      </x:c>
+      <x:c r="E32" s="18" t="str">
+        <x:v>传感器数据校验失败</x:v>
+      </x:c>
+      <x:c r="F32" s="18" t="str">
+        <x:v>传感器已返回完整数据，但接收端计算的校验值与数据中携带的校验值不一致。</x:v>
+      </x:c>
+      <x:c r="G32" s="18" t="str">
+        <x:v>检查传感器供电、连接和工作状态；数据稳定后重新测量。</x:v>
+      </x:c>
+      <x:c r="H32" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="36" hidden="0" customHeight="1">
+      <x:c r="A33" s="61" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B33" s="66" t="str">
+        <x:v>传感器通信</x:v>
+      </x:c>
+      <x:c r="C33" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D33" s="22" t="str">
+        <x:v>14-2</x:v>
+      </x:c>
+      <x:c r="E33" s="18" t="str">
+        <x:v>传感器通信超时</x:v>
+      </x:c>
+      <x:c r="F33" s="18" t="str">
+        <x:v>主控单元向传感器发送指令失败、接收启动失败，或在规定时间和重试次数内没有收到有效响应，当前测量数据无法取得。</x:v>
+      </x:c>
+      <x:c r="G33" s="18" t="str">
+        <x:v>检查传感器供电、通信连接和滑环链路；确认指令能够发出、接收能够启动并能收到完整响应后重新测量。</x:v>
+      </x:c>
+      <x:c r="H33" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="36" hidden="0" customHeight="1">
+      <x:c r="A34" s="61" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B34" s="66" t="str">
+        <x:v>传感器通信</x:v>
+      </x:c>
+      <x:c r="C34" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D34" s="22" t="str">
+        <x:v>14-3</x:v>
+      </x:c>
+      <x:c r="E34" s="18" t="str">
+        <x:v>传感器响应格式异常</x:v>
+      </x:c>
+      <x:c r="F34" s="18" t="str">
+        <x:v>传感器已经返回数据，但应答长度、起始标志、结束标志、功能码、参数码或数值格式不符合当前指令要求。</x:v>
+      </x:c>
+      <x:c r="G34" s="18" t="str">
+        <x:v>检查传感器供电和通信连接，记录原始应答后重新操作；重复出现时检查传感器型号和通信设置。</x:v>
+      </x:c>
+      <x:c r="H34" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="36" hidden="0" customHeight="1">
+      <x:c r="A35" s="61" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B35" s="66" t="str">
+        <x:v>传感器通信</x:v>
+      </x:c>
+      <x:c r="C35" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D35" s="22" t="str">
+        <x:v>14-4</x:v>
+      </x:c>
+      <x:c r="E35" s="18" t="str">
+        <x:v>串口传输异常</x:v>
+      </x:c>
+      <x:c r="F35" s="18" t="str">
+        <x:v>主控单元与传感器或无线模块通信时，串口或数据传输启动失败、传输过程中出现硬件错误，或发送未在允许时间内完成。</x:v>
+      </x:c>
+      <x:c r="G35" s="18" t="str">
+        <x:v>检查模块供电、通信线和接插件，重新上电后复测；若重复出现，记录发生模块和操作步骤。</x:v>
+      </x:c>
+      <x:c r="H35" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="24" hidden="0" customHeight="1">
+      <x:c r="A36" s="61" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B36" s="66" t="str">
         <x:v>无线与滑环</x:v>
       </x:c>
-      <x:c r="C31" s="22" t="n">
+      <x:c r="C36" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D36" s="22" t="str">
+        <x:v>14-5</x:v>
+      </x:c>
+      <x:c r="E36" s="18" t="str">
+        <x:v>滑环通信失败</x:v>
+      </x:c>
+      <x:c r="F36" s="18" t="str">
+        <x:v>主控单元与无线滑环模块之间的指令发送或状态查询未完成，无法继续执行无线链路操作。</x:v>
+      </x:c>
+      <x:c r="G36" s="18" t="str">
+        <x:v>检查无线模块和滑环链路的供电、连接及信号条件。</x:v>
+      </x:c>
+      <x:c r="H36" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="24" hidden="0" customHeight="1">
+      <x:c r="A37" s="61" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B37" s="66" t="str">
+        <x:v>无线与滑环</x:v>
+      </x:c>
+      <x:c r="C37" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D37" s="22" t="str">
+        <x:v>14-6</x:v>
+      </x:c>
+      <x:c r="E37" s="18" t="str">
+        <x:v>滑环数据校验失败</x:v>
+      </x:c>
+      <x:c r="F37" s="18" t="str">
+        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于滑环链路收到数据但校验不通过的情况。</x:v>
+      </x:c>
+      <x:c r="G37" s="18" t="str">
+        <x:v>检查无线模块和滑环链路的供电、连接及信号条件。</x:v>
+      </x:c>
+      <x:c r="H37" s="71" t="str">
+        <x:v>保留</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="36" hidden="0" customHeight="1">
+      <x:c r="A38" s="61" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B38" s="66" t="str">
+        <x:v>无线与滑环</x:v>
+      </x:c>
+      <x:c r="C38" s="22" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D31" s="22" t="str">
-        <x:v>13-7</x:v>
-      </x:c>
-      <x:c r="E31" s="18" t="str">
-        <x:v>滑环通信失败</x:v>
-      </x:c>
-      <x:c r="F31" s="18" t="str">
-        <x:v>主控单元与无线滑环模块之间的指令发送或状态查询未完成，无法继续执行无线链路操作。</x:v>
-      </x:c>
-      <x:c r="G31" s="18" t="str">
-        <x:v>检查无线模块和滑环链路的供电、连接及信号条件。</x:v>
-      </x:c>
-      <x:c r="H31" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="72" customHeight="1">
-      <x:c r="A32" s="26" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B32" s="31" t="str">
-        <x:v>无线与滑环</x:v>
-      </x:c>
-      <x:c r="C32" s="22" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D32" s="22" t="str">
-        <x:v>13-8</x:v>
-      </x:c>
-      <x:c r="E32" s="18" t="str">
-        <x:v>滑环数据校验失败</x:v>
-      </x:c>
-      <x:c r="F32" s="18" t="str">
-        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于滑环链路收到数据但校验不通过的情况。</x:v>
-      </x:c>
-      <x:c r="G32" s="18" t="str">
-        <x:v>检查无线模块和滑环链路的供电、连接及信号条件。</x:v>
-      </x:c>
-      <x:c r="H32" s="22" t="str">
-        <x:v>保留</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="72" customHeight="1">
-      <x:c r="A33" s="26" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B33" s="31" t="str">
-        <x:v>无线与滑环</x:v>
-      </x:c>
-      <x:c r="C33" s="22" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D33" s="22" t="str">
-        <x:v>13-9</x:v>
-      </x:c>
-      <x:c r="E33" s="18" t="str">
+      <x:c r="D38" s="22" t="str">
+        <x:v>14-7</x:v>
+      </x:c>
+      <x:c r="E38" s="18" t="str">
         <x:v>滑环数据包丢失</x:v>
       </x:c>
-      <x:c r="F33" s="18" t="str">
+      <x:c r="F38" s="18" t="str">
         <x:v>当前版本未发现运行流程主动产生此码；该码保留用于滑环链路数据序列不连续或数据包缺失的情况。</x:v>
-      </x:c>
-      <x:c r="G33" s="18" t="str">
-        <x:v>检查无线模块和滑环链路的供电、连接及信号条件。</x:v>
-      </x:c>
-      <x:c r="H33" s="22" t="str">
-        <x:v>保留</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="72" customHeight="1">
-      <x:c r="A34" s="26" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B34" s="32" t="str">
-        <x:v>无线与滑环</x:v>
-      </x:c>
-      <x:c r="C34" s="22" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D34" s="22" t="str">
-        <x:v>13-10</x:v>
-      </x:c>
-      <x:c r="E34" s="18" t="str">
-        <x:v>信号弱</x:v>
-      </x:c>
-      <x:c r="F34" s="18" t="str">
-        <x:v>无线配对或链路检查时读取到的信号强度低于设置要求，连接可能不稳定。</x:v>
-      </x:c>
-      <x:c r="G34" s="18" t="str">
-        <x:v>检查无线模块和滑环链路的供电、连接及信号条件。</x:v>
-      </x:c>
-      <x:c r="H34" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="72" customHeight="1">
-      <x:c r="A35" s="26" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B35" s="30" t="str">
-        <x:v>传感器与密度</x:v>
-      </x:c>
-      <x:c r="C35" s="22" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D35" s="22" t="str">
-        <x:v>13-11</x:v>
-      </x:c>
-      <x:c r="E35" s="18" t="str">
-        <x:v>传感器响应格式错误</x:v>
-      </x:c>
-      <x:c r="F35" s="18" t="str">
-        <x:v>已经收到传感器或无线模块响应，但长度、起始标志、结束标志、字段标签或数值格式不符合约定。</x:v>
-      </x:c>
-      <x:c r="G35" s="18" t="str">
-        <x:v>检查传感器供电、连接和工作状态；数据稳定后重新测量。</x:v>
-      </x:c>
-      <x:c r="H35" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="72" customHeight="1">
-      <x:c r="A36" s="26" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B36" s="31" t="str">
-        <x:v>传感器与密度</x:v>
-      </x:c>
-      <x:c r="C36" s="22" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D36" s="22" t="str">
-        <x:v>13-12</x:v>
-      </x:c>
-      <x:c r="E36" s="18" t="str">
-        <x:v>密度不稳定</x:v>
-      </x:c>
-      <x:c r="F36" s="18" t="str">
-        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于连续密度样本波动超过稳定判定范围的情况。</x:v>
-      </x:c>
-      <x:c r="G36" s="18" t="str">
-        <x:v>检查传感器供电、连接和工作状态；数据稳定后重新测量。</x:v>
-      </x:c>
-      <x:c r="H36" s="22" t="str">
-        <x:v>保留</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="72" customHeight="1">
-      <x:c r="A37" s="26" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B37" s="32" t="str">
-        <x:v>传感器与密度</x:v>
-      </x:c>
-      <x:c r="C37" s="22" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D37" s="22" t="str">
-        <x:v>13-13</x:v>
-      </x:c>
-      <x:c r="E37" s="18" t="str">
-        <x:v>传感器设备内部错误</x:v>
-      </x:c>
-      <x:c r="F37" s="18" t="str">
-        <x:v>通信和数据格式正常，但传感器在响应中明确返回设备内部错误状态。</x:v>
-      </x:c>
-      <x:c r="G37" s="18" t="str">
-        <x:v>检查传感器供电、连接和工作状态；数据稳定后重新测量。</x:v>
-      </x:c>
-      <x:c r="H37" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="72" customHeight="1">
-      <x:c r="A38" s="26" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B38" s="30" t="str">
-        <x:v>无线与滑环</x:v>
-      </x:c>
-      <x:c r="C38" s="22" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D38" s="22" t="str">
-        <x:v>13-16</x:v>
-      </x:c>
-      <x:c r="E38" s="18" t="str">
-        <x:v>无线主机通信超时</x:v>
-      </x:c>
-      <x:c r="F38" s="18" t="str">
-        <x:v>无线主机模块状态查询失败，或模块当前没有处于主机工作模式，无法建立后续连接。</x:v>
       </x:c>
       <x:c r="G38" s="18" t="str">
         <x:v>检查无线模块和滑环链路的供电、连接及信号条件。</x:v>
       </x:c>
-      <x:c r="H38" s="22" t="str">
+      <x:c r="H38" s="71" t="str">
+        <x:v>保留</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="24" hidden="0" customHeight="1">
+      <x:c r="A39" s="61" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B39" s="66" t="str">
+        <x:v>无线与滑环</x:v>
+      </x:c>
+      <x:c r="C39" s="22" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D39" s="22" t="str">
+        <x:v>14-8</x:v>
+      </x:c>
+      <x:c r="E39" s="18" t="str">
+        <x:v>信号弱</x:v>
+      </x:c>
+      <x:c r="F39" s="18" t="str">
+        <x:v>无线配对或链路检查时读取到的信号强度低于设置要求，连接可能不稳定。</x:v>
+      </x:c>
+      <x:c r="G39" s="18" t="str">
+        <x:v>检查无线模块和滑环链路的供电、连接及信号条件。</x:v>
+      </x:c>
+      <x:c r="H39" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="72" customHeight="1">
-      <x:c r="A39" s="27" t="n">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B39" s="32" t="str">
+    <x:row r="40" ht="36" hidden="0" customHeight="1">
+      <x:c r="A40" s="61" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B40" s="66" t="str">
         <x:v>无线与滑环</x:v>
       </x:c>
-      <x:c r="C39" s="34" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D39" s="34" t="str">
-        <x:v>13-17</x:v>
-      </x:c>
-      <x:c r="E39" s="35" t="str">
+      <x:c r="C40" s="22" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D40" s="22" t="str">
+        <x:v>14-9</x:v>
+      </x:c>
+      <x:c r="E40" s="18" t="str">
+        <x:v>无线主机通信超时</x:v>
+      </x:c>
+      <x:c r="F40" s="18" t="str">
+        <x:v>无线主机指令未能发出、状态查询没有响应，或模块未处于主机工作模式，后续扫描、配对和连接无法继续。</x:v>
+      </x:c>
+      <x:c r="G40" s="18" t="str">
+        <x:v>检查无线主机供电和通信连接，确认模块处于主机模式并能响应状态查询，再重新建立连接。</x:v>
+      </x:c>
+      <x:c r="H40" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="24" hidden="0" customHeight="1">
+      <x:c r="A41" s="61" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B41" s="66" t="str">
+        <x:v>无线与滑环</x:v>
+      </x:c>
+      <x:c r="C41" s="22" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D41" s="22" t="str">
+        <x:v>14-10</x:v>
+      </x:c>
+      <x:c r="E41" s="18" t="str">
         <x:v>无线从机未连接</x:v>
       </x:c>
-      <x:c r="F39" s="35" t="str">
+      <x:c r="F41" s="18" t="str">
         <x:v>无线主机模块能够正常响应，但没有连接到从机，或扫描完成后没有找到可连接设备。</x:v>
       </x:c>
-      <x:c r="G39" s="35" t="str">
+      <x:c r="G41" s="18" t="str">
         <x:v>检查无线模块和滑环链路的供电、连接及信号条件。</x:v>
       </x:c>
-      <x:c r="H39" s="36" t="str">
+      <x:c r="H41" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="72" customHeight="1">
-      <x:c r="A40" s="25" t="n">
+    <x:row r="42" ht="36" hidden="0" customHeight="1">
+      <x:c r="A42" s="61" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B42" s="66" t="str">
+        <x:v>无线与滑环</x:v>
+      </x:c>
+      <x:c r="C42" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D42" s="22" t="str">
+        <x:v>14-11</x:v>
+      </x:c>
+      <x:c r="E42" s="18" t="str">
+        <x:v>无线响应格式异常</x:v>
+      </x:c>
+      <x:c r="F42" s="18" t="str">
+        <x:v>无线模块已经应答，但工作模式、连接状态、设备地址、信号强度或扫描结果字段缺失，设备无法确认无线链路状态。</x:v>
+      </x:c>
+      <x:c r="G42" s="18" t="str">
+        <x:v>检查无线模块供电和连接，重新执行查询或配对；记录模块应答内容和发生步骤。</x:v>
+      </x:c>
+      <x:c r="H42" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="24" hidden="0" customHeight="1">
+      <x:c r="A43" s="61" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B43" s="66" t="str">
+        <x:v>主控通信</x:v>
+      </x:c>
+      <x:c r="C43" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D43" s="22" t="str">
+        <x:v>14-12</x:v>
+      </x:c>
+      <x:c r="E43" s="18" t="str">
+        <x:v>主控单元通信超时</x:v>
+      </x:c>
+      <x:c r="F43" s="18" t="str">
+        <x:v>显示单元连续十次未收到主控单元的有效响应，设备状态、测量结果和参数同步被判定中断。</x:v>
+      </x:c>
+      <x:c r="G43" s="18" t="str">
+        <x:v>检查主控单元与显示单元的供电和内部通信连接。</x:v>
+      </x:c>
+      <x:c r="H43" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="36" hidden="0" customHeight="1">
+      <x:c r="A44" s="61" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B40" s="30" t="str">
-        <x:v>测量过程</x:v>
-      </x:c>
-      <x:c r="C40" s="22" t="n">
+      <x:c r="B44" s="66" t="str">
+        <x:v>位置与标定</x:v>
+      </x:c>
+      <x:c r="C44" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D40" s="22" t="str">
+      <x:c r="D44" s="22" t="str">
         <x:v>15-1</x:v>
       </x:c>
-      <x:c r="E40" s="18" t="str">
-        <x:v>位置测量值异常</x:v>
-      </x:c>
-      <x:c r="F40" s="18" t="str">
-        <x:v>当前或目标位置值无效、运动越过目标位置超过允许量，或到位后的实际位置偏差超过规定范围。</x:v>
-      </x:c>
-      <x:c r="G40" s="18" t="str">
-        <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
-      </x:c>
-      <x:c r="H40" s="22" t="str">
+      <x:c r="E44" s="18" t="str">
+        <x:v>定位结果异常</x:v>
+      </x:c>
+      <x:c r="F44" s="18" t="str">
+        <x:v>位置反馈无效、移动过程中越过目标、停止后的实际位置偏差超过允许值，或罐高标定未取得有效实高，设备无法确认当前位置是否可靠。</x:v>
+      </x:c>
+      <x:c r="G44" s="18" t="str">
+        <x:v>停止运动，检查位置检测、尺带状态和目标位置；确认当前位置能够正常读取后重新执行。若重复出现，记录目标位置、实际位置和偏差。</x:v>
+      </x:c>
+      <x:c r="H44" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="72" customHeight="1">
-      <x:c r="A41" s="26" t="n">
+    <x:row r="45" ht="24" hidden="0" customHeight="1">
+      <x:c r="A45" s="61" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B41" s="31" t="str">
-        <x:v>测量过程</x:v>
-      </x:c>
-      <x:c r="C41" s="22" t="n">
+      <x:c r="B45" s="66" t="str">
+        <x:v>测量流程</x:v>
+      </x:c>
+      <x:c r="C45" s="22" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D41" s="22" t="str">
+      <x:c r="D45" s="22" t="str">
         <x:v>15-2</x:v>
       </x:c>
-      <x:c r="E41" s="18" t="str">
+      <x:c r="E45" s="18" t="str">
         <x:v>测量流程超时</x:v>
       </x:c>
-      <x:c r="F41" s="18" t="str">
+      <x:c r="F45" s="18" t="str">
         <x:v>液位频率闭环或密度闭环搜索持续超过规定时间，仍未形成满足条件的测量结果。</x:v>
-      </x:c>
-      <x:c r="G41" s="18" t="str">
-        <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
-      </x:c>
-      <x:c r="H41" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="72" customHeight="1">
-      <x:c r="A42" s="26" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B42" s="31" t="str">
-        <x:v>测量过程</x:v>
-      </x:c>
-      <x:c r="C42" s="22" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D42" s="22" t="str">
-        <x:v>15-3</x:v>
-      </x:c>
-      <x:c r="E42" s="18" t="str">
-        <x:v>零点超出范围</x:v>
-      </x:c>
-      <x:c r="F42" s="18" t="str">
-        <x:v>粗找、精找或完成回零后，尺带位置与零点的偏差仍大于设备参数中规定的最大零点偏差。</x:v>
-      </x:c>
-      <x:c r="G42" s="18" t="str">
-        <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
-      </x:c>
-      <x:c r="H42" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" ht="72" customHeight="1">
-      <x:c r="A43" s="26" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B43" s="31" t="str">
-        <x:v>测量过程</x:v>
-      </x:c>
-      <x:c r="C43" s="22" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D43" s="22" t="str">
-        <x:v>15-5</x:v>
-      </x:c>
-      <x:c r="E43" s="18" t="str">
-        <x:v>零点重复性差</x:v>
-      </x:c>
-      <x:c r="F43" s="18" t="str">
-        <x:v>罐底检测建立姿态基准时，多次采集的横向或纵向角度离散程度超过允许值，基准不稳定。</x:v>
-      </x:c>
-      <x:c r="G43" s="18" t="str">
-        <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
-      </x:c>
-      <x:c r="H43" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" ht="72" customHeight="1">
-      <x:c r="A44" s="26" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B44" s="31" t="str">
-        <x:v>测量过程</x:v>
-      </x:c>
-      <x:c r="C44" s="22" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D44" s="22" t="str">
-        <x:v>15-6</x:v>
-      </x:c>
-      <x:c r="E44" s="18" t="str">
-        <x:v>实高偏差过大</x:v>
-      </x:c>
-      <x:c r="F44" s="18" t="str">
-        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于实高测量结果与设定罐高的偏差超过允许值。</x:v>
-      </x:c>
-      <x:c r="G44" s="18" t="str">
-        <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
-      </x:c>
-      <x:c r="H44" s="22" t="str">
-        <x:v>保留</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="72" customHeight="1">
-      <x:c r="A45" s="26" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B45" s="31" t="str">
-        <x:v>测量过程</x:v>
-      </x:c>
-      <x:c r="C45" s="22" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D45" s="22" t="str">
-        <x:v>15-7</x:v>
-      </x:c>
-      <x:c r="E45" s="18" t="str">
-        <x:v>液位超过罐高</x:v>
-      </x:c>
-      <x:c r="F45" s="18" t="str">
-        <x:v>液位搜索位置已经到达罐高对应的上限位置，仍未在允许范围内完成液位识别。</x:v>
       </x:c>
       <x:c r="G45" s="18" t="str">
         <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
       </x:c>
-      <x:c r="H45" s="22" t="str">
+      <x:c r="H45" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="72" customHeight="1">
-      <x:c r="A46" s="26" t="n">
+    <x:row r="46" ht="24" hidden="0" customHeight="1">
+      <x:c r="A46" s="61" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B46" s="31" t="str">
-        <x:v>测量过程</x:v>
+      <x:c r="B46" s="66" t="str">
+        <x:v>零点与标定</x:v>
       </x:c>
       <x:c r="C46" s="22" t="n">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D46" s="22" t="str">
-        <x:v>15-8</x:v>
+        <x:v>15-3</x:v>
       </x:c>
       <x:c r="E46" s="18" t="str">
-        <x:v>下行未找到液位</x:v>
+        <x:v>零点超出范围</x:v>
       </x:c>
       <x:c r="F46" s="18" t="str">
-        <x:v>向下搜索液位时已经进入盲区或到达下限位置，仍未识别到有效的液位分界。</x:v>
+        <x:v>粗找、精找或完成回零后，尺带位置与零点的偏差仍大于设备参数中规定的最大零点偏差。</x:v>
       </x:c>
       <x:c r="G46" s="18" t="str">
         <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
       </x:c>
-      <x:c r="H46" s="22" t="str">
+      <x:c r="H46" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="72" customHeight="1">
-      <x:c r="A47" s="26" t="n">
+    <x:row r="47" ht="36" hidden="0" customHeight="1">
+      <x:c r="A47" s="61" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B47" s="31" t="str">
-        <x:v>测量过程</x:v>
+      <x:c r="B47" s="66" t="str">
+        <x:v>零点与标定</x:v>
       </x:c>
       <x:c r="C47" s="22" t="n">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D47" s="22" t="str">
-        <x:v>15-9</x:v>
+        <x:v>15-4</x:v>
       </x:c>
       <x:c r="E47" s="18" t="str">
-        <x:v>上行未找到液位</x:v>
+        <x:v>零点重复性差</x:v>
       </x:c>
       <x:c r="F47" s="18" t="str">
-        <x:v>向上搜索液位或重新启用液位测量模式后，仍未识别到满足条件的液位分界。</x:v>
+        <x:v>罐底检测所需的姿态基准未建立或已经失效，或建立基准时多次角度采样的离散程度超过允许值，无法可靠判断罐底。</x:v>
       </x:c>
       <x:c r="G47" s="18" t="str">
-        <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
-      </x:c>
-      <x:c r="H47" s="22" t="str">
+        <x:v>保持设备静止，检查姿态传感器和连接；重新回零建立基准，并确认多次角度采样差值在允许范围内。</x:v>
+      </x:c>
+      <x:c r="H47" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="72" customHeight="1">
-      <x:c r="A48" s="26" t="n">
+    <x:row r="48" ht="24" hidden="0" customHeight="1">
+      <x:c r="A48" s="61" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B48" s="31" t="str">
-        <x:v>测量过程</x:v>
+      <x:c r="B48" s="66" t="str">
+        <x:v>零点与标定</x:v>
       </x:c>
       <x:c r="C48" s="22" t="n">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D48" s="22" t="str">
-        <x:v>15-10</x:v>
+        <x:v>15-5</x:v>
       </x:c>
       <x:c r="E48" s="18" t="str">
-        <x:v>下行寻重失败</x:v>
+        <x:v>实高偏差过大</x:v>
       </x:c>
       <x:c r="F48" s="18" t="str">
-        <x:v>罐底搜索达到最大下行位置、精找越过预期范围，或粗找前上移后仍未离开罐底，未能可靠识别罐底。</x:v>
+        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于实高测量结果与设定罐高的偏差超过允许值。</x:v>
       </x:c>
       <x:c r="G48" s="18" t="str">
         <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
       </x:c>
-      <x:c r="H48" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" ht="72" customHeight="1">
-      <x:c r="A49" s="26" t="n">
+      <x:c r="H48" s="71" t="str">
+        <x:v>保留</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="24" hidden="0" customHeight="1">
+      <x:c r="A49" s="61" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B49" s="31" t="str">
-        <x:v>测量过程</x:v>
+      <x:c r="B49" s="66" t="str">
+        <x:v>液位测量</x:v>
       </x:c>
       <x:c r="C49" s="22" t="n">
-        <x:v>11</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D49" s="22" t="str">
-        <x:v>15-11</x:v>
+        <x:v>15-6</x:v>
       </x:c>
       <x:c r="E49" s="18" t="str">
-        <x:v>上行寻重失败</x:v>
+        <x:v>液位超过罐高</x:v>
       </x:c>
       <x:c r="F49" s="18" t="str">
-        <x:v>精确回零过程中向上移动超过允许的零点偏差范围，仍未检测到零点受力特征。</x:v>
+        <x:v>液位搜索位置已经到达罐高对应的上限位置，仍未在允许范围内完成液位识别。</x:v>
       </x:c>
       <x:c r="G49" s="18" t="str">
         <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
       </x:c>
-      <x:c r="H49" s="22" t="str">
+      <x:c r="H49" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="72" customHeight="1">
-      <x:c r="A50" s="26" t="n">
+    <x:row r="50" ht="24" hidden="0" customHeight="1">
+      <x:c r="A50" s="61" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B50" s="31" t="str">
-        <x:v>测量过程</x:v>
+      <x:c r="B50" s="66" t="str">
+        <x:v>液位测量</x:v>
       </x:c>
       <x:c r="C50" s="22" t="n">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D50" s="22" t="str">
-        <x:v>15-12</x:v>
+        <x:v>15-7</x:v>
       </x:c>
       <x:c r="E50" s="18" t="str">
-        <x:v>下行未找到水位</x:v>
+        <x:v>下行未找到液位</x:v>
       </x:c>
       <x:c r="F50" s="18" t="str">
-        <x:v>水位搜索到达零点附近仍处于水区，或粗找、精找重试后仍未找到水油分界。</x:v>
+        <x:v>向下搜索液位时已经进入盲区或到达下限位置，仍未识别到有效的液位分界。</x:v>
       </x:c>
       <x:c r="G50" s="18" t="str">
         <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
       </x:c>
-      <x:c r="H50" s="22" t="str">
+      <x:c r="H50" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="72" customHeight="1">
-      <x:c r="A51" s="26" t="n">
+    <x:row r="51" ht="24" hidden="0" customHeight="1">
+      <x:c r="A51" s="61" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B51" s="31" t="str">
-        <x:v>测量过程</x:v>
+      <x:c r="B51" s="66" t="str">
+        <x:v>液位测量</x:v>
       </x:c>
       <x:c r="C51" s="22" t="n">
-        <x:v>15</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D51" s="22" t="str">
-        <x:v>15-15</x:v>
+        <x:v>15-8</x:v>
       </x:c>
       <x:c r="E51" s="18" t="str">
-        <x:v>液位变化过快</x:v>
+        <x:v>上行未找到液位</x:v>
       </x:c>
       <x:c r="F51" s="18" t="str">
-        <x:v>液位跟随过程中，传感器频率连续高于或低于目标区间的次数超过上限，无法保持稳定跟随。</x:v>
+        <x:v>向上搜索液位或重新启用液位测量模式后，仍未识别到满足条件的液位分界。</x:v>
       </x:c>
       <x:c r="G51" s="18" t="str">
         <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
       </x:c>
-      <x:c r="H51" s="22" t="str">
+      <x:c r="H51" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="72" customHeight="1">
-      <x:c r="A52" s="26" t="n">
+    <x:row r="52" ht="36" hidden="0" customHeight="1">
+      <x:c r="A52" s="61" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B52" s="31" t="str">
-        <x:v>测量过程</x:v>
+      <x:c r="B52" s="66" t="str">
+        <x:v>寻重测量</x:v>
       </x:c>
       <x:c r="C52" s="22" t="n">
-        <x:v>16</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D52" s="22" t="str">
-        <x:v>15-16</x:v>
+        <x:v>15-9</x:v>
       </x:c>
       <x:c r="E52" s="18" t="str">
-        <x:v>密度测量无有效点</x:v>
+        <x:v>下行寻重失败</x:v>
       </x:c>
       <x:c r="F52" s="18" t="str">
-        <x:v>分布测量计划没有生成可用测点，或全部测点完成后仍没有取得一组有效密度数据。</x:v>
+        <x:v>罐底搜索达到最大下行位置、精找越过预期范围，或粗找前上移后仍未离开罐底，未能可靠识别罐底。</x:v>
       </x:c>
       <x:c r="G52" s="18" t="str">
         <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
       </x:c>
-      <x:c r="H52" s="22" t="str">
+      <x:c r="H52" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="72" customHeight="1">
-      <x:c r="A53" s="26" t="n">
+    <x:row r="53" ht="24" hidden="0" customHeight="1">
+      <x:c r="A53" s="61" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B53" s="31" t="str">
-        <x:v>测量过程</x:v>
+      <x:c r="B53" s="66" t="str">
+        <x:v>寻重测量</x:v>
       </x:c>
       <x:c r="C53" s="22" t="n">
-        <x:v>17</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D53" s="22" t="str">
-        <x:v>15-17</x:v>
+        <x:v>15-10</x:v>
       </x:c>
       <x:c r="E53" s="18" t="str">
-        <x:v>密度测量未找到油面</x:v>
+        <x:v>上行寻重失败</x:v>
       </x:c>
       <x:c r="F53" s="18" t="str">
-        <x:v>分布测量移动到最高测点后仍未识别到空气区，或整个过程没有形成可用于确认液面的有效液体点。</x:v>
+        <x:v>精确回零过程中向上移动超过允许的零点偏差范围，仍未检测到零点受力特征。</x:v>
       </x:c>
       <x:c r="G53" s="18" t="str">
         <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
       </x:c>
-      <x:c r="H53" s="22" t="str">
+      <x:c r="H53" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="72" customHeight="1">
-      <x:c r="A54" s="27" t="n">
+    <x:row r="54" ht="24" hidden="0" customHeight="1">
+      <x:c r="A54" s="61" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B54" s="32" t="str">
-        <x:v>测量过程</x:v>
-      </x:c>
-      <x:c r="C54" s="34" t="n">
+      <x:c r="B54" s="66" t="str">
+        <x:v>水位测量</x:v>
+      </x:c>
+      <x:c r="C54" s="22" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="D54" s="22" t="str">
+        <x:v>15-11</x:v>
+      </x:c>
+      <x:c r="E54" s="18" t="str">
+        <x:v>下行未找到水位</x:v>
+      </x:c>
+      <x:c r="F54" s="18" t="str">
+        <x:v>水位搜索到达零点附近仍处于水区，或粗找、精找重试后仍未找到水油分界。</x:v>
+      </x:c>
+      <x:c r="G54" s="18" t="str">
+        <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
+      </x:c>
+      <x:c r="H54" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="24" hidden="0" customHeight="1">
+      <x:c r="A55" s="61" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B55" s="66" t="str">
+        <x:v>液位跟随</x:v>
+      </x:c>
+      <x:c r="C55" s="22" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D55" s="22" t="str">
+        <x:v>15-12</x:v>
+      </x:c>
+      <x:c r="E55" s="18" t="str">
+        <x:v>液位变化过快</x:v>
+      </x:c>
+      <x:c r="F55" s="18" t="str">
+        <x:v>液位跟随过程中，传感器频率连续高于或低于目标区间的次数超过上限，无法保持稳定跟随。</x:v>
+      </x:c>
+      <x:c r="G55" s="18" t="str">
+        <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
+      </x:c>
+      <x:c r="H55" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="24" hidden="0" customHeight="1">
+      <x:c r="A56" s="61" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B56" s="66" t="str">
+        <x:v>密度分布</x:v>
+      </x:c>
+      <x:c r="C56" s="22" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D56" s="22" t="str">
+        <x:v>15-13</x:v>
+      </x:c>
+      <x:c r="E56" s="18" t="str">
+        <x:v>密度测量无有效点</x:v>
+      </x:c>
+      <x:c r="F56" s="18" t="str">
+        <x:v>分布测量计划没有生成可用测点，或全部测点完成后仍没有取得一组有效密度数据。</x:v>
+      </x:c>
+      <x:c r="G56" s="18" t="str">
+        <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
+      </x:c>
+      <x:c r="H56" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="24" hidden="0" customHeight="1">
+      <x:c r="A57" s="61" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B57" s="66" t="str">
+        <x:v>密度分布</x:v>
+      </x:c>
+      <x:c r="C57" s="22" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D57" s="22" t="str">
+        <x:v>15-14</x:v>
+      </x:c>
+      <x:c r="E57" s="18" t="str">
+        <x:v>密度测量未找到油面</x:v>
+      </x:c>
+      <x:c r="F57" s="18" t="str">
+        <x:v>分布测量移动到最高测点后仍未识别到空气区，或整个过程没有形成可用于确认液面的有效液体点。</x:v>
+      </x:c>
+      <x:c r="G57" s="18" t="str">
+        <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
+      </x:c>
+      <x:c r="H57" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="36" hidden="0" customHeight="1">
+      <x:c r="A58" s="61" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B58" s="66" t="str">
+        <x:v>密度分布</x:v>
+      </x:c>
+      <x:c r="C58" s="22" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D58" s="22" t="str">
+        <x:v>15-15</x:v>
+      </x:c>
+      <x:c r="E58" s="18" t="str">
+        <x:v>密度范围异常</x:v>
+      </x:c>
+      <x:c r="F58" s="18" t="str">
+        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于密度测量起点、终点或测点范围不符合罐体有效区间。</x:v>
+      </x:c>
+      <x:c r="G58" s="18" t="str">
+        <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
+      </x:c>
+      <x:c r="H58" s="71" t="str">
+        <x:v>保留</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="36" hidden="0" customHeight="1">
+      <x:c r="A59" s="61" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B59" s="66" t="str">
+        <x:v>模拟量输出</x:v>
+      </x:c>
+      <x:c r="C59" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D59" s="22" t="str">
+        <x:v>16-1</x:v>
+      </x:c>
+      <x:c r="E59" s="18" t="str">
+        <x:v>模拟量输出初始化失败</x:v>
+      </x:c>
+      <x:c r="F59" s="18" t="str">
+        <x:v>模拟量输出芯片启动时，复位指令未完成、控制配置写入或读取失败，或启动过程被其他访问占用，设备无法建立稳定的模拟量输出状态。</x:v>
+      </x:c>
+      <x:c r="G59" s="18" t="str">
+        <x:v>检查模拟量输出芯片供电、通信连接和回路负载；重新上电后确认初始化完成，并结合故障日志定位失败阶段。</x:v>
+      </x:c>
+      <x:c r="H59" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="24" hidden="0" customHeight="1">
+      <x:c r="A60" s="61" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B60" s="66" t="str">
+        <x:v>模拟量输出</x:v>
+      </x:c>
+      <x:c r="C60" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D60" s="22" t="str">
+        <x:v>16-2</x:v>
+      </x:c>
+      <x:c r="E60" s="18" t="str">
+        <x:v>模拟量输出电流设置失败</x:v>
+      </x:c>
+      <x:c r="F60" s="18" t="str">
+        <x:v>目标输出电流已经计算完成，但电流值未能写入模拟量输出芯片。</x:v>
+      </x:c>
+      <x:c r="G60" s="18" t="str">
+        <x:v>检查模拟量回路供电、接线和负载，确认输出恢复正常。</x:v>
+      </x:c>
+      <x:c r="H60" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="36" hidden="0" customHeight="1">
+      <x:c r="A61" s="61" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B61" s="66" t="str">
+        <x:v>模拟量输出</x:v>
+      </x:c>
+      <x:c r="C61" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D61" s="22" t="str">
+        <x:v>16-3</x:v>
+      </x:c>
+      <x:c r="E61" s="18" t="str">
+        <x:v>模拟量输出硬件报警</x:v>
+      </x:c>
+      <x:c r="F61" s="18" t="str">
+        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于模拟量输出芯片的硬件故障引脚出现报警电平。</x:v>
+      </x:c>
+      <x:c r="G61" s="18" t="str">
+        <x:v>检查模拟量回路供电、接线和负载，确认输出恢复正常。</x:v>
+      </x:c>
+      <x:c r="H61" s="71" t="str">
+        <x:v>保留</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="24" hidden="0" customHeight="1">
+      <x:c r="A62" s="61" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B62" s="66" t="str">
+        <x:v>模拟量输出</x:v>
+      </x:c>
+      <x:c r="C62" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D62" s="22" t="str">
+        <x:v>16-4</x:v>
+      </x:c>
+      <x:c r="E62" s="18" t="str">
+        <x:v>模拟量输出故障信息读取失败</x:v>
+      </x:c>
+      <x:c r="F62" s="18" t="str">
+        <x:v>主控单元无法读取模拟量输出芯片的故障信息，当前输出回路状态不能确认。</x:v>
+      </x:c>
+      <x:c r="G62" s="18" t="str">
+        <x:v>检查模拟量回路供电、接线和负载；重新上电后复核输出，重复出现时交由技术人员检查。</x:v>
+      </x:c>
+      <x:c r="H62" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="24" hidden="0" customHeight="1">
+      <x:c r="A63" s="61" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B63" s="66" t="str">
+        <x:v>模拟量输出</x:v>
+      </x:c>
+      <x:c r="C63" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D63" s="22" t="str">
+        <x:v>16-5</x:v>
+      </x:c>
+      <x:c r="E63" s="18" t="str">
+        <x:v>模拟量输出芯片报警</x:v>
+      </x:c>
+      <x:c r="F63" s="18" t="str">
+        <x:v>模拟量输出芯片已经返回故障状态，表示输出回路、芯片温度、供电或负载存在异常。</x:v>
+      </x:c>
+      <x:c r="G63" s="18" t="str">
+        <x:v>检查模拟量回路供电、接线、负载和回路是否开路；排除异常后重新上电复测。</x:v>
+      </x:c>
+      <x:c r="H63" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="24" hidden="0" customHeight="1">
+      <x:c r="A64" s="61" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B64" s="66" t="str">
+        <x:v>模拟量输出</x:v>
+      </x:c>
+      <x:c r="C64" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D64" s="22" t="str">
+        <x:v>16-6</x:v>
+      </x:c>
+      <x:c r="E64" s="18" t="str">
+        <x:v>模拟量输出配置校验失败</x:v>
+      </x:c>
+      <x:c r="F64" s="18" t="str">
+        <x:v>控制配置写入模拟量输出芯片后，回读值与写入值不一致，配置结果无法确认。</x:v>
+      </x:c>
+      <x:c r="G64" s="18" t="str">
+        <x:v>检查模拟量回路供电、接线和负载；重新上电后复核输出配置。</x:v>
+      </x:c>
+      <x:c r="H64" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="48" hidden="0" customHeight="1">
+      <x:c r="A65" s="61" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B65" s="66" t="str">
+        <x:v>参数存储</x:v>
+      </x:c>
+      <x:c r="C65" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D65" s="22" t="str">
+        <x:v>17-1</x:v>
+      </x:c>
+      <x:c r="E65" s="18" t="str">
+        <x:v>参数存储读写失败</x:v>
+      </x:c>
+      <x:c r="F65" s="18" t="str">
+        <x:v>两份设备参数存储区均无法提供可用参数，且原因不能明确归为未初始化或完整性校验失败；可能存在存储内容不兼容、读写异常或严重损坏，设备将改用出厂参数继续启动。</x:v>
+      </x:c>
+      <x:c r="G65" s="18" t="str">
+        <x:v>记录并备份现场参数，检查存储器供电和连接；重新下发设备参数并断电复查，仍重复出现时进行技术检修。</x:v>
+      </x:c>
+      <x:c r="H65" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="36" hidden="0" customHeight="1">
+      <x:c r="A66" s="61" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B66" s="66" t="str">
+        <x:v>参数存储</x:v>
+      </x:c>
+      <x:c r="C66" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D66" s="22" t="str">
+        <x:v>17-2</x:v>
+      </x:c>
+      <x:c r="E66" s="18" t="str">
+        <x:v>参数未初始化</x:v>
+      </x:c>
+      <x:c r="F66" s="18" t="str">
+        <x:v>两份设备参数存储区都没有有效的初始化标志，常见于首次装机、更换存储器、存储区被清空或内容全零，设备将改用出厂参数继续启动。</x:v>
+      </x:c>
+      <x:c r="G66" s="18" t="str">
+        <x:v>确认是否为首次使用或更换存储器；重新设置并保存设备参数，断电重启后复查参数是否完整保留。</x:v>
+      </x:c>
+      <x:c r="H66" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="24" hidden="0" customHeight="1">
+      <x:c r="A67" s="61" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B67" s="66" t="str">
+        <x:v>参数设置</x:v>
+      </x:c>
+      <x:c r="C67" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D67" s="22" t="str">
+        <x:v>17-3</x:v>
+      </x:c>
+      <x:c r="E67" s="18" t="str">
+        <x:v>参数值超出范围</x:v>
+      </x:c>
+      <x:c r="F67" s="18" t="str">
+        <x:v>当前设置值、目标位置或测量范围超出设备允许范围，继续执行可能得到无效结果或触发保护。</x:v>
+      </x:c>
+      <x:c r="G67" s="18" t="str">
+        <x:v>核对参数名称、单位和允许范围，修正并保存后重新执行。</x:v>
+      </x:c>
+      <x:c r="H67" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="36" hidden="0" customHeight="1">
+      <x:c r="A68" s="61" t="n">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B68" s="66" t="str">
+        <x:v>参数存储</x:v>
+      </x:c>
+      <x:c r="C68" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D68" s="22" t="str">
+        <x:v>17-4</x:v>
+      </x:c>
+      <x:c r="E68" s="18" t="str">
+        <x:v>参数完整性校验失败</x:v>
+      </x:c>
+      <x:c r="F68" s="18" t="str">
+        <x:v>参数存储区的基本标志、结构和版本有效，但保存内容与完整性校验结果不一致，另一份存储区也无法提供有效备份，设备将改用出厂参数继续启动。</x:v>
+      </x:c>
+      <x:c r="G68" s="18" t="str">
+        <x:v>记录并备份现场参数，重新设置并保存设备参数；断电重启后复查，仍重复出现时检查存储器和供电。</x:v>
+      </x:c>
+      <x:c r="H68" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="24" hidden="0" customHeight="1">
+      <x:c r="A69" s="61" t="n">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D54" s="34" t="str">
-        <x:v>15-18</x:v>
-      </x:c>
-      <x:c r="E54" s="35" t="str">
-        <x:v>密度范围异常</x:v>
-      </x:c>
-      <x:c r="F54" s="35" t="str">
-        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于密度测量起点、终点或测点范围不符合罐体有效区间。</x:v>
-      </x:c>
-      <x:c r="G54" s="35" t="str">
-        <x:v>核对现场条件和测量参数，确认设备状态正常后重新测量。</x:v>
-      </x:c>
-      <x:c r="H54" s="36" t="str">
+      <x:c r="B69" s="66" t="str">
+        <x:v>扭力检测</x:v>
+      </x:c>
+      <x:c r="C69" s="22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D69" s="22" t="str">
+        <x:v>18-1</x:v>
+      </x:c>
+      <x:c r="E69" s="18" t="str">
+        <x:v>扭力超过上限</x:v>
+      </x:c>
+      <x:c r="F69" s="18" t="str">
+        <x:v>满载扭力标定值高于允许上限，当前载荷、传感器安装或标定条件不符合要求。</x:v>
+      </x:c>
+      <x:c r="G69" s="18" t="str">
+        <x:v>停止运动，检查浮子、钢丝、导向机构和称重部件。</x:v>
+      </x:c>
+      <x:c r="H69" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="24" hidden="0" customHeight="1">
+      <x:c r="A70" s="61" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B70" s="66" t="str">
+        <x:v>扭力检测</x:v>
+      </x:c>
+      <x:c r="C70" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D70" s="22" t="str">
+        <x:v>18-2</x:v>
+      </x:c>
+      <x:c r="E70" s="18" t="str">
+        <x:v>扭力低于下限</x:v>
+      </x:c>
+      <x:c r="F70" s="18" t="str">
+        <x:v>满载扭力标定值低于允许下限，可能未正确加载、传感器未受力或标定条件不足。</x:v>
+      </x:c>
+      <x:c r="G70" s="18" t="str">
+        <x:v>停止运动，检查浮子、钢丝、导向机构和称重部件。</x:v>
+      </x:c>
+      <x:c r="H70" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="36" hidden="0" customHeight="1">
+      <x:c r="A71" s="61" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B71" s="66" t="str">
+        <x:v>扭力检测</x:v>
+      </x:c>
+      <x:c r="C71" s="22" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D71" s="22" t="str">
+        <x:v>18-3</x:v>
+      </x:c>
+      <x:c r="E71" s="18" t="str">
+        <x:v>扭力检测到碰撞</x:v>
+      </x:c>
+      <x:c r="F71" s="18" t="str">
+        <x:v>运动过程中当前扭力相对稳定基准的上升或下降量超过保护阈值，设备判断浮子、尺带或运动机构可能受阻。</x:v>
+      </x:c>
+      <x:c r="G71" s="18" t="str">
+        <x:v>停止运动，检查浮子、钢丝、导向机构和称重部件。</x:v>
+      </x:c>
+      <x:c r="H71" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="24" hidden="0" customHeight="1">
+      <x:c r="A72" s="61" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B72" s="66" t="str">
+        <x:v>扭力检测</x:v>
+      </x:c>
+      <x:c r="C72" s="22" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D72" s="22" t="str">
+        <x:v>18-4</x:v>
+      </x:c>
+      <x:c r="E72" s="18" t="str">
+        <x:v>扭力数据漂移异常</x:v>
+      </x:c>
+      <x:c r="F72" s="18" t="str">
+        <x:v>空载标定时扭力绝对值超过允许范围，说明零点漂移、传感器预紧或安装受力异常。</x:v>
+      </x:c>
+      <x:c r="G72" s="18" t="str">
+        <x:v>停止运动，检查浮子、钢丝、导向机构和称重部件。</x:v>
+      </x:c>
+      <x:c r="H72" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="36" hidden="0" customHeight="1">
+      <x:c r="A73" s="61" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B73" s="66" t="str">
+        <x:v>扭力检测</x:v>
+      </x:c>
+      <x:c r="C73" s="22" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D73" s="22" t="str">
+        <x:v>18-5</x:v>
+      </x:c>
+      <x:c r="E73" s="18" t="str">
+        <x:v>扭力传感器饱和</x:v>
+      </x:c>
+      <x:c r="F73" s="18" t="str">
+        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于扭力传感器输出达到量程极限、无法继续区分载荷变化。</x:v>
+      </x:c>
+      <x:c r="G73" s="18" t="str">
+        <x:v>停止运动，检查浮子、钢丝、导向机构和称重部件。</x:v>
+      </x:c>
+      <x:c r="H73" s="71" t="str">
         <x:v>保留</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="72" customHeight="1">
-      <x:c r="A55" s="25" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B55" s="30" t="str">
-        <x:v>参数存储</x:v>
-      </x:c>
-      <x:c r="C55" s="22" t="n">
+    <x:row r="74" ht="24" hidden="0" customHeight="1">
+      <x:c r="A74" s="61" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B74" s="66" t="str">
+        <x:v>扭力检测</x:v>
+      </x:c>
+      <x:c r="C74" s="22" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D74" s="22" t="str">
+        <x:v>18-6</x:v>
+      </x:c>
+      <x:c r="E74" s="18" t="str">
+        <x:v>扭力通信无响应</x:v>
+      </x:c>
+      <x:c r="F74" s="18" t="str">
+        <x:v>连续一秒没有收到新的有效扭力数据，称重通信被判定中断。</x:v>
+      </x:c>
+      <x:c r="G74" s="18" t="str">
+        <x:v>停止运动，检查浮子、钢丝、导向机构和称重部件。</x:v>
+      </x:c>
+      <x:c r="H74" s="73" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="24" hidden="0" customHeight="1">
+      <x:c r="A75" s="61" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B75" s="66" t="str">
+        <x:v>系统兜底</x:v>
+      </x:c>
+      <x:c r="C75" s="22" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D55" s="22" t="str">
-        <x:v>17-1</x:v>
-      </x:c>
-      <x:c r="E55" s="18" t="str">
-        <x:v>参数存储读写失败</x:v>
-      </x:c>
-      <x:c r="F55" s="18" t="str">
-        <x:v>设备参数的两个存储备份区均无法通过读取和完整性检查，连续重试失败后已改用出厂参数。</x:v>
-      </x:c>
-      <x:c r="G55" s="18" t="str">
-        <x:v>保留当前参数，核对参数内容和版本；必要时由技术人员恢复。</x:v>
-      </x:c>
-      <x:c r="H55" s="22" t="str">
+      <x:c r="D75" s="22" t="str">
+        <x:v>19-1</x:v>
+      </x:c>
+      <x:c r="E75" s="18" t="str">
+        <x:v>未知故障</x:v>
+      </x:c>
+      <x:c r="F75" s="18" t="str">
+        <x:v>当前版本未发现运行流程主动产生此码；该码仅作为无法归入现有类别的历史兜底故障保留。</x:v>
+      </x:c>
+      <x:c r="G75" s="18" t="str">
+        <x:v>检查设备供电和连接，记录故障状态并进行技术处理。</x:v>
+      </x:c>
+      <x:c r="H75" s="71" t="str">
+        <x:v>保留</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="36" hidden="0" customHeight="1">
+      <x:c r="A76" s="61" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B76" s="66" t="str">
+        <x:v>软件内部</x:v>
+      </x:c>
+      <x:c r="C76" s="22" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D76" s="22" t="str">
+        <x:v>19-2</x:v>
+      </x:c>
+      <x:c r="E76" s="18" t="str">
+        <x:v>数据位置异常</x:v>
+      </x:c>
+      <x:c r="F76" s="18" t="str">
+        <x:v>设备内部读取状态或写入结果时，没有取得有效的数据位置、输出位置或缓存空间，当前操作不能继续。</x:v>
+      </x:c>
+      <x:c r="G76" s="18" t="str">
+        <x:v>停止重复操作，记录发生功能和故障码；重新上电后复核。若再次出现，交由技术人员检查软件版本和故障日志。</x:v>
+      </x:c>
+      <x:c r="H76" s="73" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="72" customHeight="1">
-      <x:c r="A56" s="26" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B56" s="32" t="str">
-        <x:v>参数存储</x:v>
-      </x:c>
-      <x:c r="C56" s="22" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D56" s="22" t="str">
-        <x:v>17-2</x:v>
-      </x:c>
-      <x:c r="E56" s="18" t="str">
-        <x:v>参数未初始化</x:v>
-      </x:c>
-      <x:c r="F56" s="18" t="str">
-        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于设备参数尚未建立有效初始值的情况。</x:v>
-      </x:c>
-      <x:c r="G56" s="18" t="str">
-        <x:v>保留当前参数，核对参数内容和版本；必要时由技术人员恢复。</x:v>
-      </x:c>
-      <x:c r="H56" s="22" t="str">
+    <x:row r="77" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A77" s="63" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B77" s="68" t="str">
+        <x:v>软件内部</x:v>
+      </x:c>
+      <x:c r="C77" s="69" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D77" s="69" t="str">
+        <x:v>19-3</x:v>
+      </x:c>
+      <x:c r="E77" s="58" t="str">
+        <x:v>调用条件异常</x:v>
+      </x:c>
+      <x:c r="F77" s="58" t="str">
+        <x:v>当前操作所需的方向、速度、测量方法、设备状态或计算条件不完整或不符合要求，程序已中止本次操作以避免产生错误结果。</x:v>
+      </x:c>
+      <x:c r="G77" s="58" t="str">
+        <x:v>核对当前操作、设置参数和设备状态；修正不符合要求的条件后重试。若重复出现，记录操作步骤和故障日志。</x:v>
+      </x:c>
+      <x:c r="H77" s="75" t="str">
+        <x:v>使用中</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A78" s="63" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B78" s="68" t="str">
+        <x:v>数据访问</x:v>
+      </x:c>
+      <x:c r="C78" s="69" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D78" s="69" t="str">
+        <x:v>19-4</x:v>
+      </x:c>
+      <x:c r="E78" s="58" t="str">
+        <x:v>地址读取错误</x:v>
+      </x:c>
+      <x:c r="F78" s="58" t="str">
+        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于读取外部地址时未取得有效数据的情况。</x:v>
+      </x:c>
+      <x:c r="G78" s="58" t="str">
+        <x:v>检查设备供电和连接，记录故障状态并进行技术处理。</x:v>
+      </x:c>
+      <x:c r="H78" s="77" t="str">
         <x:v>保留</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="72" customHeight="1">
-      <x:c r="A57" s="26" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B57" s="30" t="str">
-        <x:v>参数设置</x:v>
-      </x:c>
-      <x:c r="C57" s="22" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D57" s="22" t="str">
-        <x:v>17-3</x:v>
-      </x:c>
-      <x:c r="E57" s="18" t="str">
-        <x:v>参数超出范围</x:v>
-      </x:c>
-      <x:c r="F57" s="18" t="str">
-        <x:v>测点数量、测点间距、起始位置或其他设置值为零、超限，不能用于当前测量或控制计算。</x:v>
-      </x:c>
-      <x:c r="G57" s="18" t="str">
-        <x:v>核对参数值、单位和范围，修正后重新设置。</x:v>
-      </x:c>
-      <x:c r="H57" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" ht="72" customHeight="1">
-      <x:c r="A58" s="26" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B58" s="32" t="str">
-        <x:v>参数设置</x:v>
-      </x:c>
-      <x:c r="C58" s="22" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D58" s="22" t="str">
-        <x:v>17-4</x:v>
-      </x:c>
-      <x:c r="E58" s="18" t="str">
-        <x:v>参数地址越界</x:v>
-      </x:c>
-      <x:c r="F58" s="18" t="str">
-        <x:v>调用过程没有提供有效的数据存放位置，或参数、测点及寄存器地址超出允许范围。</x:v>
-      </x:c>
-      <x:c r="G58" s="18" t="str">
-        <x:v>核对参数值、单位和范围，修正后重新设置。</x:v>
-      </x:c>
-      <x:c r="H58" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" ht="72" customHeight="1">
-      <x:c r="A59" s="26" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B59" s="33" t="str">
-        <x:v>参数存储</x:v>
-      </x:c>
-      <x:c r="C59" s="22" t="n">
+    <x:row r="79" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A79" s="63" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B79" s="68" t="str">
+        <x:v>供电</x:v>
+      </x:c>
+      <x:c r="C79" s="69" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D59" s="22" t="str">
-        <x:v>17-5</x:v>
-      </x:c>
-      <x:c r="E59" s="18" t="str">
-        <x:v>参数完整性校验失败</x:v>
-      </x:c>
-      <x:c r="F59" s="18" t="str">
-        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于参数内容与其完整性校验结果不一致的情况。</x:v>
-      </x:c>
-      <x:c r="G59" s="18" t="str">
-        <x:v>保留当前参数，核对参数内容和版本；必要时由技术人员恢复。</x:v>
-      </x:c>
-      <x:c r="H59" s="22" t="str">
+      <x:c r="D79" s="69" t="str">
+        <x:v>19-5</x:v>
+      </x:c>
+      <x:c r="E79" s="58" t="str">
+        <x:v>电源波动异常</x:v>
+      </x:c>
+      <x:c r="F79" s="58" t="str">
+        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于设备供电波动超过允许范围的情况。</x:v>
+      </x:c>
+      <x:c r="G79" s="58" t="str">
+        <x:v>检查设备供电和连接，记录故障状态并进行技术处理。</x:v>
+      </x:c>
+      <x:c r="H79" s="77" t="str">
         <x:v>保留</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="72" customHeight="1">
-      <x:c r="A60" s="27" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B60" s="32" t="str">
-        <x:v>参数设置</x:v>
-      </x:c>
-      <x:c r="C60" s="34" t="n">
+    <x:row r="80" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A80" s="63" t="n">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B80" s="68" t="str">
+        <x:v>外设配置</x:v>
+      </x:c>
+      <x:c r="C80" s="69" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D60" s="34" t="str">
-        <x:v>17-6</x:v>
-      </x:c>
-      <x:c r="E60" s="35" t="str">
-        <x:v>程序参数调用错误</x:v>
-      </x:c>
-      <x:c r="F60" s="35" t="str">
-        <x:v>运行前参数组合无法使用，例如运动方向无效、标定值为零、拟合样本不足或计算结果不合法。</x:v>
-      </x:c>
-      <x:c r="G60" s="35" t="str">
-        <x:v>核对参数值、单位和范围，修正后重新设置。</x:v>
-      </x:c>
-      <x:c r="H60" s="36" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" ht="72" customHeight="1">
-      <x:c r="A61" s="25" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B61" s="30" t="str">
-        <x:v>称重与保护</x:v>
-      </x:c>
-      <x:c r="C61" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D61" s="22" t="str">
-        <x:v>18-1</x:v>
-      </x:c>
-      <x:c r="E61" s="18" t="str">
-        <x:v>扭力超过上限</x:v>
-      </x:c>
-      <x:c r="F61" s="18" t="str">
-        <x:v>满载扭力标定值高于允许上限，当前载荷、传感器安装或标定条件不符合要求。</x:v>
-      </x:c>
-      <x:c r="G61" s="18" t="str">
-        <x:v>停止运动，检查浮子、钢丝、导向机构和称重部件。</x:v>
-      </x:c>
-      <x:c r="H61" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" ht="72" customHeight="1">
-      <x:c r="A62" s="26" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B62" s="31" t="str">
-        <x:v>称重与保护</x:v>
-      </x:c>
-      <x:c r="C62" s="22" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D62" s="22" t="str">
-        <x:v>18-2</x:v>
-      </x:c>
-      <x:c r="E62" s="18" t="str">
-        <x:v>扭力低于下限</x:v>
-      </x:c>
-      <x:c r="F62" s="18" t="str">
-        <x:v>满载扭力标定值低于允许下限，可能未正确加载、传感器未受力或标定条件不足。</x:v>
-      </x:c>
-      <x:c r="G62" s="18" t="str">
-        <x:v>停止运动，检查浮子、钢丝、导向机构和称重部件。</x:v>
-      </x:c>
-      <x:c r="H62" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" ht="72" customHeight="1">
-      <x:c r="A63" s="26" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B63" s="31" t="str">
-        <x:v>称重与保护</x:v>
-      </x:c>
-      <x:c r="C63" s="22" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D63" s="22" t="str">
-        <x:v>18-3</x:v>
-      </x:c>
-      <x:c r="E63" s="18" t="str">
-        <x:v>扭力检测到碰撞</x:v>
-      </x:c>
-      <x:c r="F63" s="18" t="str">
-        <x:v>运动过程中当前扭力相对稳定基准的上升或下降量超过保护阈值，设备判断浮子、尺带或运动机构可能受阻。</x:v>
-      </x:c>
-      <x:c r="G63" s="18" t="str">
-        <x:v>停止运动，检查浮子、钢丝、导向机构和称重部件。</x:v>
-      </x:c>
-      <x:c r="H63" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" ht="72" customHeight="1">
-      <x:c r="A64" s="26" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B64" s="31" t="str">
-        <x:v>称重与保护</x:v>
-      </x:c>
-      <x:c r="C64" s="22" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D64" s="22" t="str">
-        <x:v>18-4</x:v>
-      </x:c>
-      <x:c r="E64" s="18" t="str">
-        <x:v>扭力数据漂移异常</x:v>
-      </x:c>
-      <x:c r="F64" s="18" t="str">
-        <x:v>空载标定时扭力绝对值超过允许范围，说明零点漂移、传感器预紧或安装受力异常。</x:v>
-      </x:c>
-      <x:c r="G64" s="18" t="str">
-        <x:v>停止运动，检查浮子、钢丝、导向机构和称重部件。</x:v>
-      </x:c>
-      <x:c r="H64" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="72" customHeight="1">
-      <x:c r="A65" s="26" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B65" s="31" t="str">
-        <x:v>称重与保护</x:v>
-      </x:c>
-      <x:c r="C65" s="22" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D65" s="22" t="str">
-        <x:v>18-5</x:v>
-      </x:c>
-      <x:c r="E65" s="18" t="str">
-        <x:v>扭力传感器饱和</x:v>
-      </x:c>
-      <x:c r="F65" s="18" t="str">
-        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于扭力传感器输出达到量程极限、无法继续区分载荷变化。</x:v>
-      </x:c>
-      <x:c r="G65" s="18" t="str">
-        <x:v>停止运动，检查浮子、钢丝、导向机构和称重部件。</x:v>
-      </x:c>
-      <x:c r="H65" s="22" t="str">
-        <x:v>保留</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" ht="72" customHeight="1">
-      <x:c r="A66" s="27" t="n">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B66" s="32" t="str">
-        <x:v>称重与保护</x:v>
-      </x:c>
-      <x:c r="C66" s="34" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D66" s="34" t="str">
-        <x:v>18-6</x:v>
-      </x:c>
-      <x:c r="E66" s="35" t="str">
-        <x:v>扭力通信无响应</x:v>
-      </x:c>
-      <x:c r="F66" s="35" t="str">
-        <x:v>连续一秒没有收到新的有效扭力数据，称重通信被判定中断。</x:v>
-      </x:c>
-      <x:c r="G66" s="35" t="str">
-        <x:v>停止运动，检查浮子、钢丝、导向机构和称重部件。</x:v>
-      </x:c>
-      <x:c r="H66" s="36" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" ht="72" customHeight="1">
-      <x:c r="A67" s="25" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B67" s="30" t="str">
-        <x:v>系统与电源</x:v>
-      </x:c>
-      <x:c r="C67" s="22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D67" s="22" t="str">
-        <x:v>19-1</x:v>
-      </x:c>
-      <x:c r="E67" s="18" t="str">
-        <x:v>未知故障</x:v>
-      </x:c>
-      <x:c r="F67" s="18" t="str">
-        <x:v>当前版本未发现运行流程主动产生此码；该码仅作为无法归入现有类别的历史兜底故障保留。</x:v>
-      </x:c>
-      <x:c r="G67" s="18" t="str">
-        <x:v>检查设备供电和连接，记录故障状态并进行技术处理。</x:v>
-      </x:c>
-      <x:c r="H67" s="22" t="str">
-        <x:v>保留</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" ht="72" customHeight="1">
-      <x:c r="A68" s="26" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B68" s="31" t="str">
-        <x:v>系统与电源</x:v>
-      </x:c>
-      <x:c r="C68" s="22" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D68" s="22" t="str">
-        <x:v>19-2</x:v>
-      </x:c>
-      <x:c r="E68" s="18" t="str">
-        <x:v>地址读取错误</x:v>
-      </x:c>
-      <x:c r="F68" s="18" t="str">
-        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于读取外部地址时未取得有效数据的情况。</x:v>
-      </x:c>
-      <x:c r="G68" s="18" t="str">
-        <x:v>检查设备供电和连接，记录故障状态并进行技术处理。</x:v>
-      </x:c>
-      <x:c r="H68" s="22" t="str">
-        <x:v>保留</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" ht="72" customHeight="1">
-      <x:c r="A69" s="26" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B69" s="31" t="str">
-        <x:v>系统与电源</x:v>
-      </x:c>
-      <x:c r="C69" s="22" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D69" s="22" t="str">
-        <x:v>19-3</x:v>
-      </x:c>
-      <x:c r="E69" s="18" t="str">
-        <x:v>电源波动异常</x:v>
-      </x:c>
-      <x:c r="F69" s="18" t="str">
-        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于设备供电波动超过允许范围的情况。</x:v>
-      </x:c>
-      <x:c r="G69" s="18" t="str">
-        <x:v>检查设备供电和连接，记录故障状态并进行技术处理。</x:v>
-      </x:c>
-      <x:c r="H69" s="22" t="str">
-        <x:v>保留</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" ht="72" customHeight="1">
-      <x:c r="A70" s="26" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B70" s="32" t="str">
-        <x:v>系统与电源</x:v>
-      </x:c>
-      <x:c r="C70" s="22" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D70" s="22" t="str">
-        <x:v>19-4</x:v>
-      </x:c>
-      <x:c r="E70" s="18" t="str">
+      <x:c r="D80" s="69" t="str">
+        <x:v>19-6</x:v>
+      </x:c>
+      <x:c r="E80" s="58" t="str">
         <x:v>外部设备配置失败</x:v>
       </x:c>
-      <x:c r="F70" s="18" t="str">
-        <x:v>外部设备访问未完成，或罐底检测需要的姿态基准无效；当前主要触发点包括模拟量输出读写失败、访问被占用和姿态基准未建立。</x:v>
-      </x:c>
-      <x:c r="G70" s="18" t="str">
-        <x:v>检查设备供电和连接，记录故障状态并进行技术处理。</x:v>
-      </x:c>
-      <x:c r="H70" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" ht="72" customHeight="1">
-      <x:c r="A71" s="26" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B71" s="30" t="str">
-        <x:v>模拟量输出</x:v>
-      </x:c>
-      <x:c r="C71" s="22" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D71" s="22" t="str">
-        <x:v>19-5</x:v>
-      </x:c>
-      <x:c r="E71" s="18" t="str">
-        <x:v>模拟量输出初始化失败</x:v>
-      </x:c>
-      <x:c r="F71" s="18" t="str">
-        <x:v>模拟量输出芯片的启动顺序未完成，初始化访问无法开始，或控制配置写入失败。</x:v>
-      </x:c>
-      <x:c r="G71" s="18" t="str">
-        <x:v>检查模拟量回路供电、接线和负载，确认输出恢复正常。</x:v>
-      </x:c>
-      <x:c r="H71" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" ht="72" customHeight="1">
-      <x:c r="A72" s="26" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B72" s="31" t="str">
-        <x:v>模拟量输出</x:v>
-      </x:c>
-      <x:c r="C72" s="22" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D72" s="22" t="str">
-        <x:v>19-6</x:v>
-      </x:c>
-      <x:c r="E72" s="18" t="str">
-        <x:v>模拟量输出电流设置失败</x:v>
-      </x:c>
-      <x:c r="F72" s="18" t="str">
-        <x:v>目标输出电流已经计算完成，但电流值未能写入模拟量输出芯片。</x:v>
-      </x:c>
-      <x:c r="G72" s="18" t="str">
-        <x:v>检查模拟量回路供电、接线和负载，确认输出恢复正常。</x:v>
-      </x:c>
-      <x:c r="H72" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" ht="72" customHeight="1">
-      <x:c r="A73" s="26" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B73" s="31" t="str">
-        <x:v>模拟量输出</x:v>
-      </x:c>
-      <x:c r="C73" s="22" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D73" s="22" t="str">
-        <x:v>19-7</x:v>
-      </x:c>
-      <x:c r="E73" s="18" t="str">
-        <x:v>模拟量输出硬件报警</x:v>
-      </x:c>
-      <x:c r="F73" s="18" t="str">
-        <x:v>当前版本未发现运行流程主动产生此码；该码保留用于模拟量输出芯片的硬件故障引脚出现报警电平。</x:v>
-      </x:c>
-      <x:c r="G73" s="18" t="str">
-        <x:v>检查模拟量回路供电、接线和负载，确认输出恢复正常。</x:v>
-      </x:c>
-      <x:c r="H73" s="22" t="str">
-        <x:v>保留</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" ht="72" customHeight="1">
-      <x:c r="A74" s="26" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B74" s="31" t="str">
-        <x:v>模拟量输出</x:v>
-      </x:c>
-      <x:c r="C74" s="22" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D74" s="22" t="str">
-        <x:v>19-8</x:v>
-      </x:c>
-      <x:c r="E74" s="18" t="str">
-        <x:v>模拟量输出状态异常</x:v>
-      </x:c>
-      <x:c r="F74" s="18" t="str">
-        <x:v>模拟量输出芯片的诊断状态读取失败，或读取到的诊断状态表明输出回路存在内部故障。</x:v>
-      </x:c>
-      <x:c r="G74" s="18" t="str">
-        <x:v>检查模拟量回路供电、接线和负载，确认输出恢复正常。</x:v>
-      </x:c>
-      <x:c r="H74" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" ht="72" customHeight="1">
-      <x:c r="A75" s="26" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B75" s="32" t="str">
-        <x:v>模拟量输出</x:v>
-      </x:c>
-      <x:c r="C75" s="22" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D75" s="22" t="str">
-        <x:v>19-9</x:v>
-      </x:c>
-      <x:c r="E75" s="18" t="str">
-        <x:v>模拟量输出配置校验失败</x:v>
-      </x:c>
-      <x:c r="F75" s="18" t="str">
-        <x:v>控制配置写入模拟量输出芯片后，回读值与写入值不一致，配置结果无法确认。</x:v>
-      </x:c>
-      <x:c r="G75" s="18" t="str">
-        <x:v>检查模拟量回路供电、接线和负载，确认输出恢复正常。</x:v>
-      </x:c>
-      <x:c r="H75" s="22" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" ht="72" customHeight="1">
-      <x:c r="A76" s="27" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B76" s="32" t="str">
-        <x:v>主控通信</x:v>
-      </x:c>
-      <x:c r="C76" s="34" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D76" s="34" t="str">
-        <x:v>19-10</x:v>
-      </x:c>
-      <x:c r="E76" s="35" t="str">
-        <x:v>主控单元通信超时</x:v>
-      </x:c>
-      <x:c r="F76" s="35" t="str">
-        <x:v>显示单元连续十次未收到主控单元的有效响应，设备状态、测量结果和参数同步被判定中断。</x:v>
-      </x:c>
-      <x:c r="G76" s="35" t="str">
-        <x:v>检查主控单元与显示单元的供电和内部通信连接。</x:v>
-      </x:c>
-      <x:c r="H76" s="36" t="str">
+      <x:c r="F80" s="58" t="str">
+        <x:v>主控单元访问模拟量输出芯片时，写入、读取指令或读取数据未完成，或同一时刻已有一次访问尚未结束，当前操作无法执行。</x:v>
+      </x:c>
+      <x:c r="G80" s="58" t="str">
+        <x:v>检查模拟量输出芯片供电和通信连接；根据日志中的访问阶段、读写方向、寄存器和底层状态定位失败环节。</x:v>
+      </x:c>
+      <x:c r="H80" s="75" t="str">
         <x:v>使用中</x:v>
       </x:c>
     </x:row>
@@ -2564,25 +2817,28 @@
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>
     <x:mergeCell ref="A2:H2"/>
-    <x:mergeCell ref="A5:A14"/>
-    <x:mergeCell ref="A15:A24"/>
-    <x:mergeCell ref="A25:A39"/>
-    <x:mergeCell ref="A40:A54"/>
-    <x:mergeCell ref="A55:A60"/>
-    <x:mergeCell ref="A61:A66"/>
-    <x:mergeCell ref="A67:A76"/>
-    <x:mergeCell ref="B5:B14"/>
-    <x:mergeCell ref="B15:B24"/>
-    <x:mergeCell ref="B25:B30"/>
-    <x:mergeCell ref="B31:B34"/>
-    <x:mergeCell ref="B35:B37"/>
-    <x:mergeCell ref="B38:B39"/>
-    <x:mergeCell ref="B40:B54"/>
-    <x:mergeCell ref="B55:B56"/>
-    <x:mergeCell ref="B57:B58"/>
-    <x:mergeCell ref="B61:B66"/>
-    <x:mergeCell ref="B67:B70"/>
-    <x:mergeCell ref="B71:B75"/>
+    <x:mergeCell ref="A5:A15"/>
+    <x:mergeCell ref="A16:A25"/>
+    <x:mergeCell ref="A26:A31"/>
+    <x:mergeCell ref="A32:A43"/>
+    <x:mergeCell ref="A44:A58"/>
+    <x:mergeCell ref="A59:A64"/>
+    <x:mergeCell ref="A65:A68"/>
+    <x:mergeCell ref="A69:A74"/>
+    <x:mergeCell ref="A75:A80"/>
+    <x:mergeCell ref="B5:B15"/>
+    <x:mergeCell ref="B16:B25"/>
+    <x:mergeCell ref="B26:B31"/>
+    <x:mergeCell ref="B32:B35"/>
+    <x:mergeCell ref="B36:B42"/>
+    <x:mergeCell ref="B46:B48"/>
+    <x:mergeCell ref="B49:B51"/>
+    <x:mergeCell ref="B52:B53"/>
+    <x:mergeCell ref="B56:B58"/>
+    <x:mergeCell ref="B59:B64"/>
+    <x:mergeCell ref="B65:B66"/>
+    <x:mergeCell ref="B69:B74"/>
+    <x:mergeCell ref="B76:B77"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="H5:H76">
     <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="使用中"/>

--- a/docs/00_构建与版本/故障码/LTD故障代码统一表.xlsx
+++ b/docs/00_构建与版本/故障码/LTD故障代码统一表.xlsx
@@ -8632,3367 +8632,3400 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="24.75"/>
-  <x:cols>
-    <x:col min="1" max="1" width="4.875" style="42" customWidth="1"/>
-    <x:col min="2" max="2" width="7.875" style="43" customWidth="1"/>
-    <x:col min="3" max="3" width="13.875" style="43" customWidth="1"/>
-    <x:col min="4" max="4" width="37.125" style="43" customWidth="1"/>
-    <x:col min="5" max="5" width="47.875" style="43" customWidth="1"/>
-    <x:col min="6" max="6" width="35" style="43" customWidth="1"/>
-    <x:col min="7" max="7" width="9.383333206176758" hidden="1" customWidth="1"/>
-    <x:col min="8" max="8" width="23.75" hidden="1" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="44" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B1" s="45" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C1" s="45" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D1" s="45" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E1" s="45" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F1" s="45" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G1" s="46" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H1" s="47" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="66">
-      <x:c r="A2" s="48" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B2" s="66" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C2" s="66" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D2" s="65" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E2" s="65" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F2" s="65" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G2" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H2" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="66">
-      <x:c r="A3" s="48"/>
-      <x:c r="B3" s="66" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C3" s="66" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D3" s="65" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E3" s="65" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F3" s="65" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G3" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H3" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="66">
-      <x:c r="A4" s="48"/>
-      <x:c r="B4" s="66" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C4" s="66" t="str">
-        <x:v>电机驱动电流未建立</x:v>
-      </x:c>
-      <x:c r="D4" s="65" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E4" s="65" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F4" s="65" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G4" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H4" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="66">
-      <x:c r="A5" s="48"/>
-      <x:c r="B5" s="49" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="C5" s="49" t="str">
-        <x:v>电机驱动故障类型未知</x:v>
-      </x:c>
-      <x:c r="D5" s="50" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E5" s="50" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F5" s="50" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G5" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H5" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="66">
-      <x:c r="A6" s="48"/>
-      <x:c r="B6" s="66" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C6" s="66" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D6" s="65" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E6" s="65" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F6" s="65" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G6" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H6" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="66">
-      <x:c r="A7" s="48"/>
-      <x:c r="B7" s="49" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="C7" s="49" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D7" s="50" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E7" s="50" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F7" s="50" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G7" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H7" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="82.5">
-      <x:c r="A8" s="48"/>
-      <x:c r="B8" s="49" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C8" s="49" t="str">
-        <x:v>电机驱动内部升压不足</x:v>
-      </x:c>
-      <x:c r="D8" s="50" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E8" s="50" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F8" s="50" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G8" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H8" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="82.5">
-      <x:c r="A9" s="48"/>
-      <x:c r="B9" s="49" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C9" s="49" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D9" s="50" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E9" s="50" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F9" s="50" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G9" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H9" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="82.5">
-      <x:c r="A10" s="48"/>
-      <x:c r="B10" s="49" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="C10" s="49" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D10" s="50" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E10" s="50" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F10" s="50" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="G10" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H10" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="66">
-      <x:c r="A11" s="48"/>
-      <x:c r="B11" s="49" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C11" s="49" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D11" s="50" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E11" s="50" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F11" s="50" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G11" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H11" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="66">
-      <x:c r="A12" s="48"/>
-      <x:c r="B12" s="49" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C12" s="49" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D12" s="50" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E12" s="50" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="F12" s="50" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G12" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H12" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="82.5">
-      <x:c r="A13" s="48"/>
-      <x:c r="B13" s="49" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="C13" s="49" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D13" s="50" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E13" s="50" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="F13" s="50" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G13" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H13" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="82.5">
-      <x:c r="A14" s="48"/>
-      <x:c r="B14" s="49" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="C14" s="49" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D14" s="50" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E14" s="50" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="F14" s="50" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="G14" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H14" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="66">
-      <x:c r="A15" s="48"/>
-      <x:c r="B15" s="49" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C15" s="49" t="str">
-        <x:v>电机未按时停下</x:v>
-      </x:c>
-      <x:c r="D15" s="50" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E15" s="50" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F15" s="50" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="G15" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H15" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="99">
-      <x:c r="A16" s="48"/>
-      <x:c r="B16" s="52" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C16" s="52" t="str">
-        <x:v>电机未按时到位</x:v>
-      </x:c>
-      <x:c r="D16" s="53" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="E16" s="53" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="F16" s="53" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="G16" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H16" s="47" t="s">
-        <x:v>90</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="66">
-      <x:c r="A17" s="54" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="B17" s="66" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="C17" s="66" t="str">
-        <x:v>编码器没有有效位置数据</x:v>
-      </x:c>
-      <x:c r="D17" s="65" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="E17" s="65" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="F17" s="65" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G17" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H17" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="66">
-      <x:c r="A18" s="54"/>
-      <x:c r="B18" s="66" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="C18" s="66" t="str">
-        <x:v>编码器数据校验失败</x:v>
-      </x:c>
-      <x:c r="D18" s="65" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="E18" s="65" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="F18" s="65" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G18" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H18" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="82.5">
-      <x:c r="A19" s="54"/>
-      <x:c r="B19" s="52" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C19" s="52" t="str">
-        <x:v>编码器记录位移不足</x:v>
-      </x:c>
-      <x:c r="D19" s="53" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E19" s="53" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="F19" s="53" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G19" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H19" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="66">
-      <x:c r="A20" s="54"/>
-      <x:c r="B20" s="52" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C20" s="52" t="str">
-        <x:v>编码器位置记录不可用</x:v>
-      </x:c>
-      <x:c r="D20" s="53" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="E20" s="53" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="F20" s="53" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G20" s="55" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H20" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="66">
-      <x:c r="A21" s="54"/>
-      <x:c r="B21" s="52" t="str">
-        <x:v>12-6</x:v>
-      </x:c>
-      <x:c r="C21" s="52" t="str">
-        <x:v>编码器上电位置跳变</x:v>
-      </x:c>
-      <x:c r="D21" s="53" t="str">
-        <x:v>出现情况：开机连续取得3帧稳定位置后，与断电前保存的位置比较，位置变化超过允许范围。
-会有什么影响：断电前后的累计位置不能安全衔接，设备禁止普通运动，只允许人工确认后执行回零或零点标定重新建立位置基准。</x:v>
-      </x:c>
-      <x:c r="E21" s="53" t="str">
-        <x:v>• 断电期间机构或尺带被人为移动。
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="24.75"/>
+  <cols>
+    <col min="1" max="1" width="4.875" style="42" customWidth="1"/>
+    <col min="2" max="2" width="7.875" style="43" customWidth="1"/>
+    <col min="3" max="3" width="13.875" style="43" customWidth="1"/>
+    <col min="4" max="4" width="37.125" style="43" customWidth="1"/>
+    <col min="5" max="5" width="47.875" style="43" customWidth="1"/>
+    <col min="6" max="6" width="35" style="43" customWidth="1"/>
+    <col min="7" max="7" width="9.383333206176758" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="23.75" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="47" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" ht="66">
+      <c r="A2" s="48" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="66" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="66" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="65" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" ht="66">
+      <c r="A3" s="48"/>
+      <c r="B3" s="66" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="66" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="65" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="65" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="65" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" ht="66">
+      <c r="A4" s="48"/>
+      <c r="B4" s="66" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="66" t="str">
+        <v>电机驱动电流未建立</v>
+      </c>
+      <c r="D4" s="65" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" ht="66">
+      <c r="A5" s="48"/>
+      <c r="B5" s="49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="49" t="str">
+        <v>电机驱动故障类型未知</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="50" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" ht="66">
+      <c r="A6" s="48"/>
+      <c r="B6" s="66" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" ht="66">
+      <c r="A7" s="48"/>
+      <c r="B7" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="49" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="50" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="50" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" ht="82.5">
+      <c r="A8" s="48"/>
+      <c r="B8" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="49" t="str">
+        <v>电机驱动内部升压不足</v>
+      </c>
+      <c r="D8" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" ht="82.5">
+      <c r="A9" s="48"/>
+      <c r="B9" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="50" t="s">
+        <v>54</v>
+      </c>
+      <c r="E9" s="50" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="50" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" ht="82.5">
+      <c r="A10" s="48"/>
+      <c r="B10" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="49" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" ht="66">
+      <c r="A11" s="48"/>
+      <c r="B11" s="49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" s="50" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" ht="66">
+      <c r="A12" s="48"/>
+      <c r="B12" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" ht="82.5">
+      <c r="A13" s="48"/>
+      <c r="B13" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="49" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="50" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" s="50" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H13" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" ht="82.5">
+      <c r="A14" s="48"/>
+      <c r="B14" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="F14" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" ht="66">
+      <c r="A15" s="48"/>
+      <c r="B15" s="49" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="49" t="str">
+        <v>电机未按时停下</v>
+      </c>
+      <c r="D15" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="50" t="s">
+        <v>84</v>
+      </c>
+      <c r="F15" s="50" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16" ht="99">
+      <c r="A16" s="48"/>
+      <c r="B16" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="52" t="str">
+        <v>电机未按时到位</v>
+      </c>
+      <c r="D16" s="53" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" s="53" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="47" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" ht="66">
+      <c r="A17" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="66" t="str">
+        <v>编码器没有有效位置数据</v>
+      </c>
+      <c r="D17" s="65" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="65" t="s">
+        <v>94</v>
+      </c>
+      <c r="F17" s="65" t="s">
+        <v>95</v>
+      </c>
+      <c r="G17" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H17" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" ht="66">
+      <c r="A18" s="54"/>
+      <c r="B18" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="66" t="str">
+        <v>编码器数据校验失败</v>
+      </c>
+      <c r="D18" s="65" t="s">
+        <v>97</v>
+      </c>
+      <c r="E18" s="65" t="s">
+        <v>98</v>
+      </c>
+      <c r="F18" s="65" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H18" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" ht="82.5">
+      <c r="A19" s="54"/>
+      <c r="B19" s="52" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" s="52" t="str">
+        <v>编码器记录位移不足</v>
+      </c>
+      <c r="D19" s="53" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H19" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" ht="66">
+      <c r="A20" s="54"/>
+      <c r="B20" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="C20" s="52" t="str">
+        <v>编码器位置记录不可用</v>
+      </c>
+      <c r="D20" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="F20" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="G20" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="H20" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" ht="66">
+      <c r="A21" s="54"/>
+      <c r="B21" s="52" t="str">
+        <v>12-6</v>
+      </c>
+      <c r="C21" s="52" t="str">
+        <v>编码器上电位置跳变</v>
+      </c>
+      <c r="D21" s="53" t="str">
+        <v>出现情况：开机连续取得3帧稳定位置后，与断电前保存的位置比较，位置变化超过允许范围。
+会有什么影响：断电前后的累计位置不能安全衔接，设备禁止普通运动，只允许人工确认后执行回零或零点标定重新建立位置基准。</v>
+      </c>
+      <c r="E21" s="53" t="str">
+        <v>• 断电期间机构或尺带被人为移动。
 • 编码器、磁铁或固定件松动、偏移，更换主控板或编码器后没有重新回零。
-• 断电前位置未完整保存、存储记录异常，或上电初期位置反馈不稳定。</x:v>
-      </x:c>
-      <x:c r="F21" s="53" t="str">
-        <x:v>注意：不要按断电前位置直接继续运动。
+• 断电前位置未完整保存、存储记录异常，或上电初期位置反馈不稳定。</v>
+      </c>
+      <c r="F21" s="53" t="str">
+        <v>注意：不要按断电前位置直接继续运动。
 1. 重点检查：人工确认机构实际位置，检查编码器、磁铁、尺带和固定件。
 2. 处理完再看：执行回零或零点标定，重新建立位置基准。
-还是不行：检查位置保存记录和主控板。</x:v>
-      </x:c>
-      <x:c r="G21" s="51" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-      <x:c r="H21" s="47" t="str">
-        <x:v>CPU2共享故障｜协议34启用</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="82.5">
-      <x:c r="A22" s="54"/>
-      <x:c r="B22" s="52" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="C22" s="52" t="str">
-        <x:v>编码轮周长标定值过大</x:v>
-      </x:c>
-      <x:c r="D22" s="53" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="E22" s="53" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F22" s="53" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G22" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H22" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="66">
-      <x:c r="A23" s="54"/>
-      <x:c r="B23" s="52" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="C23" s="52" t="str">
-        <x:v>编码器角度计算超限</x:v>
-      </x:c>
-      <x:c r="D23" s="53" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="E23" s="53" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="F23" s="53" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G23" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H23" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="66">
-      <x:c r="A24" s="54"/>
-      <x:c r="B24" s="52" t="str">
-        <x:v>12-13</x:v>
-      </x:c>
-      <x:c r="C24" s="52" t="str">
-        <x:v>编码器角度线性异常</x:v>
-      </x:c>
-      <x:c r="D24" s="53" t="str">
-        <x:v>出现情况：调试查询发现编码器LIN线性度状态位持续置位。
-会有什么影响：当前策略仅保留原始状态和累计次数；LIN位本身不拒绝位置帧，也不触发12-13停机。</x:v>
-      </x:c>
-      <x:c r="E24" s="53" t="str">
-        <x:v>• 磁铁偏心、倾斜、安装间隙不合适，或编码器与磁铁固定件松动。
+还是不行：检查位置保存记录和主控板。</v>
+      </c>
+      <c r="G21" s="51" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H21" s="47" t="str">
+        <v>CPU2共享故障｜协议34启用</v>
+      </c>
+    </row>
+    <row r="22" ht="82.5">
+      <c r="A22" s="54"/>
+      <c r="B22" s="52" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="52" t="str">
+        <v>编码轮周长标定值过大</v>
+      </c>
+      <c r="D22" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="E22" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="F22" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H22" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" ht="66">
+      <c r="A23" s="54"/>
+      <c r="B23" s="52" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="52" t="str">
+        <v>编码器角度计算超限</v>
+      </c>
+      <c r="D23" s="53" t="s">
+        <v>109</v>
+      </c>
+      <c r="E23" s="53" t="s">
+        <v>110</v>
+      </c>
+      <c r="F23" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="G23" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="24" ht="66">
+      <c r="A24" s="54"/>
+      <c r="B24" s="52" t="str">
+        <v>12-13</v>
+      </c>
+      <c r="C24" s="52" t="str">
+        <v>编码器角度线性异常</v>
+      </c>
+      <c r="D24" s="53" t="str">
+        <v>出现情况：调试查询发现编码器LIN线性度状态位持续置位。
+会有什么影响：当前策略仅保留原始状态和累计次数；LIN位本身不拒绝位置帧，也不触发12-13停机。</v>
+      </c>
+      <c r="E24" s="53" t="str">
+        <v>• 磁铁偏心、倾斜、安装间隙不合适，或编码器与磁铁固定件松动。
 • 附近铁磁零件、金属碎屑或外部强磁场改变了磁场分布。
-• 编码器供电不稳、器件受损或安装面变形也可能持续触发。</x:v>
-      </x:c>
-      <x:c r="F24" s="53" t="str">
-        <x:v>当前程序不会主动报出12-13。
+• 编码器供电不稳、器件受损或安装面变形也可能持续触发。</v>
+      </c>
+      <c r="F24" s="53" t="str">
+        <v>当前程序不会主动报出12-13。
 1. 调试检查：通过ENC?查看LIN原始位、累计次数，并同时核对校验、OCF、COF、跳变和链路质量。
 2. 若LIN长期置位：检查磁铁与编码器同心度、安装间隙、固定件、供电及附近金属碎屑。
-3. 若同时出现位置跳变或其它编码器故障：按对应故障处理，必要时重新回零。</x:v>
-      </x:c>
-      <x:c r="G24" s="51" t="str">
-        <x:v>保留</x:v>
-      </x:c>
-      <x:c r="H24" s="47" t="str">
-        <x:v>CPU2/CPU3保留定义｜当前仅诊断统计</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="82.5">
-      <x:c r="A25" s="54"/>
-      <x:c r="B25" s="52" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="C25" s="52" t="str">
-        <x:v>编码器角度计算未完成</x:v>
-      </x:c>
-      <x:c r="D25" s="53" t="s">
-        <x:v>112</x:v>
-      </x:c>
-      <x:c r="E25" s="53" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="F25" s="53" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="G25" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H25" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="66">
-      <x:c r="A26" s="54"/>
-      <x:c r="B26" s="52" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="C26" s="52" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="D26" s="53" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="E26" s="53" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="F26" s="53" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="G26" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H26" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="82.5">
-      <x:c r="A27" s="54"/>
-      <x:c r="B27" s="52" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="C27" s="52" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D27" s="53" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="E27" s="53" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="F27" s="53" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="G27" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H27" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="82.5">
-      <x:c r="A28" s="54" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="B28" s="49" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="C28" s="49" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D28" s="50" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="E28" s="50" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="F28" s="50" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="G28" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H28" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="82.5">
-      <x:c r="A29" s="54"/>
-      <x:c r="B29" s="49" t="s">
-        <x:v>130</x:v>
-      </x:c>
-      <x:c r="C29" s="49" t="str">
-        <x:v>振动管频率异常</x:v>
-      </x:c>
-      <x:c r="D29" s="50" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="E29" s="50" t="s">
-        <x:v>132</x:v>
-      </x:c>
-      <x:c r="F29" s="50" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="G29" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H29" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="82.5">
-      <x:c r="A30" s="54"/>
-      <x:c r="B30" s="66" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="C30" s="66" t="s">
-        <x:v>134</x:v>
-      </x:c>
-      <x:c r="D30" s="65" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="E30" s="65" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="F30" s="65" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="G30" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H30" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="66">
-      <x:c r="A31" s="54"/>
-      <x:c r="B31" s="49" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="C31" s="49" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="D31" s="50" t="s">
-        <x:v>140</x:v>
-      </x:c>
-      <x:c r="E31" s="50" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="F31" s="50" t="s">
-        <x:v>142</x:v>
-      </x:c>
-      <x:c r="G31" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H31" s="47" t="s">
-        <x:v>143</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="66">
-      <x:c r="A32" s="54"/>
-      <x:c r="B32" s="49" t="s">
-        <x:v>144</x:v>
-      </x:c>
-      <x:c r="C32" s="49" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="D32" s="50" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="E32" s="50" t="s">
-        <x:v>147</x:v>
-      </x:c>
-      <x:c r="F32" s="50" t="s">
-        <x:v>148</x:v>
-      </x:c>
-      <x:c r="G32" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H32" s="47" t="s">
-        <x:v>149</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="66">
-      <x:c r="A33" s="54"/>
-      <x:c r="B33" s="49" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="C33" s="49" t="str">
-        <x:v>传感器内部通信校验失败</x:v>
-      </x:c>
-      <x:c r="D33" s="50" t="s">
-        <x:v>151</x:v>
-      </x:c>
-      <x:c r="E33" s="50" t="s">
-        <x:v>152</x:v>
-      </x:c>
-      <x:c r="F33" s="50" t="s">
-        <x:v>153</x:v>
-      </x:c>
-      <x:c r="G33" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H33" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="66">
-      <x:c r="A34" s="54"/>
-      <x:c r="B34" s="49" t="s">
-        <x:v>154</x:v>
-      </x:c>
-      <x:c r="C34" s="49" t="s">
-        <x:v>155</x:v>
-      </x:c>
-      <x:c r="D34" s="50" t="s">
-        <x:v>156</x:v>
-      </x:c>
-      <x:c r="E34" s="50" t="s">
-        <x:v>157</x:v>
-      </x:c>
-      <x:c r="F34" s="50" t="s">
-        <x:v>158</x:v>
-      </x:c>
-      <x:c r="G34" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H34" s="47" t="s">
-        <x:v>143</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="82.5">
-      <x:c r="A35" s="54"/>
-      <x:c r="B35" s="66" t="s">
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="C35" s="66" t="str">
-        <x:v>密度值超出有效范围</x:v>
-      </x:c>
-      <x:c r="D35" s="65" t="s">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="E35" s="65" t="s">
-        <x:v>161</x:v>
-      </x:c>
-      <x:c r="F35" s="65" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="G35" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H35" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="82.5">
-      <x:c r="A36" s="54"/>
-      <x:c r="B36" s="49" t="s">
-        <x:v>162</x:v>
-      </x:c>
-      <x:c r="C36" s="49" t="s">
-        <x:v>163</x:v>
-      </x:c>
-      <x:c r="D36" s="50" t="s">
-        <x:v>164</x:v>
-      </x:c>
-      <x:c r="E36" s="50" t="s">
-        <x:v>165</x:v>
-      </x:c>
-      <x:c r="F36" s="50" t="s">
-        <x:v>166</x:v>
-      </x:c>
-      <x:c r="G36" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H36" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="82.5">
-      <x:c r="A37" s="54"/>
-      <x:c r="B37" s="49" t="s">
-        <x:v>167</x:v>
-      </x:c>
-      <x:c r="C37" s="49" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="D37" s="50" t="s">
-        <x:v>169</x:v>
-      </x:c>
-      <x:c r="E37" s="50" t="s">
-        <x:v>170</x:v>
-      </x:c>
-      <x:c r="F37" s="50" t="s">
-        <x:v>171</x:v>
-      </x:c>
-      <x:c r="G37" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H37" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="66">
-      <x:c r="A38" s="54"/>
-      <x:c r="B38" s="49" t="s">
-        <x:v>172</x:v>
-      </x:c>
-      <x:c r="C38" s="49" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="D38" s="50" t="s">
-        <x:v>174</x:v>
-      </x:c>
-      <x:c r="E38" s="50" t="s">
-        <x:v>175</x:v>
-      </x:c>
-      <x:c r="F38" s="50" t="s">
-        <x:v>176</x:v>
-      </x:c>
-      <x:c r="G38" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H38" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="66">
-      <x:c r="A39" s="54"/>
-      <x:c r="B39" s="49" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="C39" s="49" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="D39" s="50" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="E39" s="50" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="F39" s="50" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="G39" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H39" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" ht="82.5">
-      <x:c r="A40" s="54"/>
-      <x:c r="B40" s="49" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="C40" s="49" t="s">
-        <x:v>183</x:v>
-      </x:c>
-      <x:c r="D40" s="50" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="E40" s="50" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="F40" s="50" t="s">
-        <x:v>186</x:v>
-      </x:c>
-      <x:c r="G40" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H40" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" ht="82.5">
-      <x:c r="A41" s="54"/>
-      <x:c r="B41" s="49" t="s">
-        <x:v>187</x:v>
-      </x:c>
-      <x:c r="C41" s="49" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="D41" s="50" t="s">
-        <x:v>189</x:v>
-      </x:c>
-      <x:c r="E41" s="50" t="s">
-        <x:v>190</x:v>
-      </x:c>
-      <x:c r="F41" s="50" t="s">
-        <x:v>191</x:v>
-      </x:c>
-      <x:c r="G41" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H41" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="82.5">
-      <x:c r="A42" s="54"/>
-      <x:c r="B42" s="49" t="s">
-        <x:v>192</x:v>
-      </x:c>
-      <x:c r="C42" s="49" t="s">
-        <x:v>193</x:v>
-      </x:c>
-      <x:c r="D42" s="50" t="s">
-        <x:v>194</x:v>
-      </x:c>
-      <x:c r="E42" s="50" t="s">
-        <x:v>195</x:v>
-      </x:c>
-      <x:c r="F42" s="50" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="G42" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H42" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" ht="66">
-      <x:c r="A43" s="54"/>
-      <x:c r="B43" s="49" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="C43" s="49" t="str">
-        <x:v>传感器配置批次不一致</x:v>
-      </x:c>
-      <x:c r="D43" s="50" t="s">
-        <x:v>198</x:v>
-      </x:c>
-      <x:c r="E43" s="50" t="s">
-        <x:v>199</x:v>
-      </x:c>
-      <x:c r="F43" s="50" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="G43" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H43" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" ht="82.5">
-      <x:c r="A44" s="54"/>
-      <x:c r="B44" s="49" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="C44" s="49" t="s">
-        <x:v>202</x:v>
-      </x:c>
-      <x:c r="D44" s="50" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="E44" s="50" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="F44" s="50" t="s">
-        <x:v>205</x:v>
-      </x:c>
-      <x:c r="G44" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H44" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" ht="82.5">
-      <x:c r="A45" s="54"/>
-      <x:c r="B45" s="49" t="s">
-        <x:v>206</x:v>
-      </x:c>
-      <x:c r="C45" s="49" t="s">
-        <x:v>207</x:v>
-      </x:c>
-      <x:c r="D45" s="50" t="s">
-        <x:v>208</x:v>
-      </x:c>
-      <x:c r="E45" s="50" t="s">
-        <x:v>209</x:v>
-      </x:c>
-      <x:c r="F45" s="50" t="s">
-        <x:v>210</x:v>
-      </x:c>
-      <x:c r="G45" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H45" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" ht="66">
-      <x:c r="A46" s="54"/>
-      <x:c r="B46" s="49" t="s">
-        <x:v>211</x:v>
-      </x:c>
-      <x:c r="C46" s="49" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="D46" s="50" t="s">
-        <x:v>213</x:v>
-      </x:c>
-      <x:c r="E46" s="50" t="s">
-        <x:v>214</x:v>
-      </x:c>
-      <x:c r="F46" s="50" t="s">
-        <x:v>215</x:v>
-      </x:c>
-      <x:c r="G46" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H46" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" ht="66">
-      <x:c r="A47" s="54"/>
-      <x:c r="B47" s="49" t="s">
-        <x:v>216</x:v>
-      </x:c>
-      <x:c r="C47" s="49" t="s">
-        <x:v>217</x:v>
-      </x:c>
-      <x:c r="D47" s="50" t="s">
-        <x:v>218</x:v>
-      </x:c>
-      <x:c r="E47" s="50" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="F47" s="50" t="s">
-        <x:v>220</x:v>
-      </x:c>
-      <x:c r="G47" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H47" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" ht="66">
-      <x:c r="A48" s="54"/>
-      <x:c r="B48" s="52" t="s">
-        <x:v>221</x:v>
-      </x:c>
-      <x:c r="C48" s="52" t="s">
-        <x:v>222</x:v>
-      </x:c>
-      <x:c r="D48" s="53" t="s">
-        <x:v>223</x:v>
-      </x:c>
-      <x:c r="E48" s="53" t="s">
-        <x:v>224</x:v>
-      </x:c>
-      <x:c r="F48" s="53" t="s">
-        <x:v>225</x:v>
-      </x:c>
-      <x:c r="G48" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H48" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" ht="82.5">
-      <x:c r="A49" s="54"/>
-      <x:c r="B49" s="52" t="s">
-        <x:v>226</x:v>
-      </x:c>
-      <x:c r="C49" s="52" t="str">
-        <x:v>传感器连接状态失效</x:v>
-      </x:c>
-      <x:c r="D49" s="53" t="s">
-        <x:v>227</x:v>
-      </x:c>
-      <x:c r="E49" s="53" t="s">
-        <x:v>228</x:v>
-      </x:c>
-      <x:c r="F49" s="53" t="s">
-        <x:v>229</x:v>
-      </x:c>
-      <x:c r="G49" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H49" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" ht="66">
-      <x:c r="A50" s="54"/>
-      <x:c r="B50" s="52" t="s">
-        <x:v>230</x:v>
-      </x:c>
-      <x:c r="C50" s="52" t="str">
-        <x:v>传感器应答序号不一致</x:v>
-      </x:c>
-      <x:c r="D50" s="53" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="E50" s="53" t="s">
-        <x:v>232</x:v>
-      </x:c>
-      <x:c r="F50" s="53" t="s">
-        <x:v>233</x:v>
-      </x:c>
-      <x:c r="G50" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H50" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" ht="82.5">
-      <x:c r="A51" s="54"/>
-      <x:c r="B51" s="52" t="s">
-        <x:v>234</x:v>
-      </x:c>
-      <x:c r="C51" s="52" t="str">
-        <x:v>传感器需要重新确认连接</x:v>
-      </x:c>
-      <x:c r="D51" s="53" t="s">
-        <x:v>235</x:v>
-      </x:c>
-      <x:c r="E51" s="53" t="s">
-        <x:v>236</x:v>
-      </x:c>
-      <x:c r="F51" s="53" t="s">
-        <x:v>237</x:v>
-      </x:c>
-      <x:c r="G51" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H51" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" ht="66">
-      <x:c r="A52" s="54"/>
-      <x:c r="B52" s="52" t="s">
-        <x:v>238</x:v>
-      </x:c>
-      <x:c r="C52" s="52" t="str">
-        <x:v>收到重复的传感器数据</x:v>
-      </x:c>
-      <x:c r="D52" s="53" t="s">
-        <x:v>239</x:v>
-      </x:c>
-      <x:c r="E52" s="53" t="s">
-        <x:v>240</x:v>
-      </x:c>
-      <x:c r="F52" s="53" t="s">
-        <x:v>241</x:v>
-      </x:c>
-      <x:c r="G52" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H52" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" ht="66">
-      <x:c r="A53" s="54"/>
-      <x:c r="B53" s="52" t="s">
-        <x:v>242</x:v>
-      </x:c>
-      <x:c r="C53" s="52" t="str">
-        <x:v>传感器不支持所需功能</x:v>
-      </x:c>
-      <x:c r="D53" s="53" t="s">
-        <x:v>243</x:v>
-      </x:c>
-      <x:c r="E53" s="53" t="s">
-        <x:v>244</x:v>
-      </x:c>
-      <x:c r="F53" s="53" t="s">
-        <x:v>245</x:v>
-      </x:c>
-      <x:c r="G53" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H53" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" ht="66">
-      <x:c r="A54" s="54"/>
-      <x:c r="B54" s="49" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="C54" s="49" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="D54" s="50" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="E54" s="50" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="F54" s="50" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="G54" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H54" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" ht="82.5">
-      <x:c r="A55" s="54"/>
-      <x:c r="B55" s="49" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="C55" s="49" t="str">
-        <x:v>传感器不接受当前参数</x:v>
-      </x:c>
-      <x:c r="D55" s="50" t="s">
-        <x:v>252</x:v>
-      </x:c>
-      <x:c r="E55" s="50" t="s">
-        <x:v>253</x:v>
-      </x:c>
-      <x:c r="F55" s="50" t="s">
-        <x:v>254</x:v>
-      </x:c>
-      <x:c r="G55" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H55" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" ht="66">
-      <x:c r="A56" s="54"/>
-      <x:c r="B56" s="49" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="C56" s="49" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="D56" s="50" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="E56" s="50" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="F56" s="50" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="G56" s="55" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H56" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" ht="82.5">
-      <x:c r="A57" s="54"/>
-      <x:c r="B57" s="49" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="C57" s="49" t="str">
-        <x:v>传感器当前模式不允许操作</x:v>
-      </x:c>
-      <x:c r="D57" s="50" t="s">
-        <x:v>261</x:v>
-      </x:c>
-      <x:c r="E57" s="50" t="s">
-        <x:v>262</x:v>
-      </x:c>
-      <x:c r="F57" s="50" t="s">
-        <x:v>263</x:v>
-      </x:c>
-      <x:c r="G57" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H57" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" ht="82.5">
-      <x:c r="A58" s="54"/>
-      <x:c r="B58" s="49" t="s">
-        <x:v>264</x:v>
-      </x:c>
-      <x:c r="C58" s="49" t="str">
-        <x:v>上一次传感器操作尚未完成</x:v>
-      </x:c>
-      <x:c r="D58" s="50" t="s">
-        <x:v>265</x:v>
-      </x:c>
-      <x:c r="E58" s="50" t="s">
-        <x:v>266</x:v>
-      </x:c>
-      <x:c r="F58" s="50" t="s">
-        <x:v>267</x:v>
-      </x:c>
-      <x:c r="G58" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H58" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" ht="66">
-      <x:c r="A59" s="54"/>
-      <x:c r="B59" s="49" t="s">
-        <x:v>268</x:v>
-      </x:c>
-      <x:c r="C59" s="49" t="s">
-        <x:v>269</x:v>
-      </x:c>
-      <x:c r="D59" s="50" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="E59" s="50" t="s">
-        <x:v>271</x:v>
-      </x:c>
-      <x:c r="F59" s="50" t="s">
-        <x:v>272</x:v>
-      </x:c>
-      <x:c r="G59" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H59" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" ht="66">
-      <x:c r="A60" s="54"/>
-      <x:c r="B60" s="49" t="s">
-        <x:v>273</x:v>
-      </x:c>
-      <x:c r="C60" s="49" t="s">
-        <x:v>274</x:v>
-      </x:c>
-      <x:c r="D60" s="50" t="s">
-        <x:v>275</x:v>
-      </x:c>
-      <x:c r="E60" s="50" t="s">
-        <x:v>276</x:v>
-      </x:c>
-      <x:c r="F60" s="50" t="s">
-        <x:v>277</x:v>
-      </x:c>
-      <x:c r="G60" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H60" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" ht="66">
-      <x:c r="A61" s="54"/>
-      <x:c r="B61" s="49" t="s">
-        <x:v>278</x:v>
-      </x:c>
-      <x:c r="C61" s="49" t="str">
-        <x:v>传感器采样序号异常</x:v>
-      </x:c>
-      <x:c r="D61" s="50" t="s">
-        <x:v>279</x:v>
-      </x:c>
-      <x:c r="E61" s="50" t="s">
-        <x:v>280</x:v>
-      </x:c>
-      <x:c r="F61" s="50" t="s">
-        <x:v>281</x:v>
-      </x:c>
-      <x:c r="G61" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H61" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" ht="66">
-      <x:c r="A62" s="54"/>
-      <x:c r="B62" s="49" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="C62" s="49" t="s">
-        <x:v>283</x:v>
-      </x:c>
-      <x:c r="D62" s="50" t="s">
-        <x:v>284</x:v>
-      </x:c>
-      <x:c r="E62" s="50" t="s">
-        <x:v>285</x:v>
-      </x:c>
-      <x:c r="F62" s="50" t="s">
-        <x:v>286</x:v>
-      </x:c>
-      <x:c r="G62" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H62" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" ht="66">
-      <x:c r="A63" s="54"/>
-      <x:c r="B63" s="49" t="s">
-        <x:v>287</x:v>
-      </x:c>
-      <x:c r="C63" s="49" t="s">
-        <x:v>288</x:v>
-      </x:c>
-      <x:c r="D63" s="50" t="s">
-        <x:v>289</x:v>
-      </x:c>
-      <x:c r="E63" s="50" t="s">
-        <x:v>290</x:v>
-      </x:c>
-      <x:c r="F63" s="50" t="s">
-        <x:v>291</x:v>
-      </x:c>
-      <x:c r="G63" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H63" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" ht="66">
-      <x:c r="A64" s="54"/>
-      <x:c r="B64" s="49" t="s">
-        <x:v>292</x:v>
-      </x:c>
-      <x:c r="C64" s="49" t="str">
-        <x:v>传感器周期上报重复启动</x:v>
-      </x:c>
-      <x:c r="D64" s="50" t="s">
-        <x:v>293</x:v>
-      </x:c>
-      <x:c r="E64" s="50" t="s">
-        <x:v>294</x:v>
-      </x:c>
-      <x:c r="F64" s="50" t="s">
-        <x:v>295</x:v>
-      </x:c>
-      <x:c r="G64" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H64" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" ht="82.5">
-      <x:c r="A65" s="54"/>
-      <x:c r="B65" s="49" t="s">
-        <x:v>296</x:v>
-      </x:c>
-      <x:c r="C65" s="49" t="s">
-        <x:v>297</x:v>
-      </x:c>
-      <x:c r="D65" s="50" t="s">
-        <x:v>298</x:v>
-      </x:c>
-      <x:c r="E65" s="50" t="s">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="F65" s="50" t="s">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="G65" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H65" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" ht="66">
-      <x:c r="A66" s="54" t="s">
-        <x:v>301</x:v>
-      </x:c>
-      <x:c r="B66" s="49" t="s">
-        <x:v>302</x:v>
-      </x:c>
-      <x:c r="C66" s="49" t="str">
-        <x:v>零点位置超出允许范围</x:v>
-      </x:c>
-      <x:c r="D66" s="50" t="s">
-        <x:v>303</x:v>
-      </x:c>
-      <x:c r="E66" s="50" t="s">
-        <x:v>304</x:v>
-      </x:c>
-      <x:c r="F66" s="50" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="G66" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H66" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" ht="99">
-      <x:c r="A67" s="54"/>
-      <x:c r="B67" s="49" t="s">
-        <x:v>306</x:v>
-      </x:c>
-      <x:c r="C67" s="49" t="str">
-        <x:v>陀螺仪基准不稳定</x:v>
-      </x:c>
-      <x:c r="D67" s="50" t="s">
-        <x:v>307</x:v>
-      </x:c>
-      <x:c r="E67" s="50" t="s">
-        <x:v>308</x:v>
-      </x:c>
-      <x:c r="F67" s="50" t="s">
-        <x:v>309</x:v>
-      </x:c>
-      <x:c r="G67" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H67" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" ht="66">
-      <x:c r="A68" s="54"/>
-      <x:c r="B68" s="49" t="s">
-        <x:v>310</x:v>
-      </x:c>
-      <x:c r="C68" s="49" t="s">
-        <x:v>311</x:v>
-      </x:c>
-      <x:c r="D68" s="50" t="s">
-        <x:v>312</x:v>
-      </x:c>
-      <x:c r="E68" s="50" t="s">
-        <x:v>313</x:v>
-      </x:c>
-      <x:c r="F68" s="50" t="s">
-        <x:v>314</x:v>
-      </x:c>
-      <x:c r="G68" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H68" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" ht="66">
-      <x:c r="A69" s="54"/>
-      <x:c r="B69" s="49" t="s">
-        <x:v>315</x:v>
-      </x:c>
-      <x:c r="C69" s="49" t="s">
-        <x:v>316</x:v>
-      </x:c>
-      <x:c r="D69" s="50" t="s">
-        <x:v>317</x:v>
-      </x:c>
-      <x:c r="E69" s="50" t="s">
-        <x:v>318</x:v>
-      </x:c>
-      <x:c r="F69" s="50" t="s">
-        <x:v>319</x:v>
-      </x:c>
-      <x:c r="G69" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H69" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" ht="66">
-      <x:c r="A70" s="54"/>
-      <x:c r="B70" s="49" t="s">
-        <x:v>320</x:v>
-      </x:c>
-      <x:c r="C70" s="49" t="str">
-        <x:v>电机到位偏差过大</x:v>
-      </x:c>
-      <x:c r="D70" s="50" t="s">
-        <x:v>321</x:v>
-      </x:c>
-      <x:c r="E70" s="50" t="s">
-        <x:v>322</x:v>
-      </x:c>
-      <x:c r="F70" s="50" t="s">
-        <x:v>323</x:v>
-      </x:c>
-      <x:c r="G70" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H70" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" ht="66">
-      <x:c r="A71" s="54"/>
-      <x:c r="B71" s="49" t="s">
-        <x:v>324</x:v>
-      </x:c>
-      <x:c r="C71" s="49" t="s">
-        <x:v>325</x:v>
-      </x:c>
-      <x:c r="D71" s="50" t="s">
-        <x:v>326</x:v>
-      </x:c>
-      <x:c r="E71" s="50" t="s">
-        <x:v>327</x:v>
-      </x:c>
-      <x:c r="F71" s="50" t="s">
-        <x:v>328</x:v>
-      </x:c>
-      <x:c r="G71" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H71" s="47" t="s">
-        <x:v>329</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" ht="82.5">
-      <x:c r="A72" s="54" t="s">
-        <x:v>330</x:v>
-      </x:c>
-      <x:c r="B72" s="49" t="s">
-        <x:v>331</x:v>
-      </x:c>
-      <x:c r="C72" s="49" t="str">
-        <x:v>上行找液位到达位置上限</x:v>
-      </x:c>
-      <x:c r="D72" s="50" t="s">
-        <x:v>332</x:v>
-      </x:c>
-      <x:c r="E72" s="50" t="s">
-        <x:v>333</x:v>
-      </x:c>
-      <x:c r="F72" s="50" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="G72" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H72" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" ht="82.5">
-      <x:c r="A73" s="54"/>
-      <x:c r="B73" s="49" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="C73" s="49" t="s">
-        <x:v>335</x:v>
-      </x:c>
-      <x:c r="D73" s="50" t="s">
-        <x:v>336</x:v>
-      </x:c>
-      <x:c r="E73" s="50" t="s">
-        <x:v>337</x:v>
-      </x:c>
-      <x:c r="F73" s="50" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="G73" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H73" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" ht="66">
-      <x:c r="A74" s="54"/>
-      <x:c r="B74" s="49" t="s">
-        <x:v>338</x:v>
-      </x:c>
-      <x:c r="C74" s="49" t="s">
-        <x:v>339</x:v>
-      </x:c>
-      <x:c r="D74" s="50" t="s">
-        <x:v>340</x:v>
-      </x:c>
-      <x:c r="E74" s="50" t="s">
-        <x:v>341</x:v>
-      </x:c>
-      <x:c r="F74" s="50" t="s">
-        <x:v>342</x:v>
-      </x:c>
-      <x:c r="G74" s="51" t="s">
-        <x:v>343</x:v>
-      </x:c>
-      <x:c r="H74" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" ht="82.5">
-      <x:c r="A75" s="54"/>
-      <x:c r="B75" s="49" t="s">
-        <x:v>344</x:v>
-      </x:c>
-      <x:c r="C75" s="49" t="s">
-        <x:v>345</x:v>
-      </x:c>
-      <x:c r="D75" s="50" t="s">
-        <x:v>346</x:v>
-      </x:c>
-      <x:c r="E75" s="50" t="s">
-        <x:v>347</x:v>
-      </x:c>
-      <x:c r="F75" s="50" t="s">
-        <x:v>348</x:v>
-      </x:c>
-      <x:c r="G75" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H75" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" ht="82.5">
-      <x:c r="A76" s="54"/>
-      <x:c r="B76" s="66" t="s">
-        <x:v>349</x:v>
-      </x:c>
-      <x:c r="C76" s="66" t="s">
-        <x:v>350</x:v>
-      </x:c>
-      <x:c r="D76" s="65" t="s">
-        <x:v>351</x:v>
-      </x:c>
-      <x:c r="E76" s="65" t="s">
-        <x:v>352</x:v>
-      </x:c>
-      <x:c r="F76" s="65" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="G76" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H76" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" ht="66">
-      <x:c r="A77" s="54"/>
-      <x:c r="B77" s="66" t="s">
-        <x:v>353</x:v>
-      </x:c>
-      <x:c r="C77" s="66" t="s">
-        <x:v>354</x:v>
-      </x:c>
-      <x:c r="D77" s="65" t="s">
-        <x:v>355</x:v>
-      </x:c>
-      <x:c r="E77" s="65" t="s">
-        <x:v>356</x:v>
-      </x:c>
-      <x:c r="F77" s="65" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="G77" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H77" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" ht="82.5">
-      <x:c r="A78" s="54"/>
-      <x:c r="B78" s="66" t="s">
-        <x:v>357</x:v>
-      </x:c>
-      <x:c r="C78" s="66" t="str">
-        <x:v>下行未找到罐底</x:v>
-      </x:c>
-      <x:c r="D78" s="65" t="s">
-        <x:v>358</x:v>
-      </x:c>
-      <x:c r="E78" s="65" t="s">
-        <x:v>359</x:v>
-      </x:c>
-      <x:c r="F78" s="65" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="G78" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H78" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" ht="66">
-      <x:c r="A79" s="54"/>
-      <x:c r="B79" s="66" t="s">
-        <x:v>360</x:v>
-      </x:c>
-      <x:c r="C79" s="66" t="str">
-        <x:v>上行未找到零点</x:v>
-      </x:c>
-      <x:c r="D79" s="65" t="s">
-        <x:v>361</x:v>
-      </x:c>
-      <x:c r="E79" s="65" t="s">
-        <x:v>362</x:v>
-      </x:c>
-      <x:c r="F79" s="65" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="G79" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H79" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" ht="82.5">
-      <x:c r="A80" s="54"/>
-      <x:c r="B80" s="52" t="s">
-        <x:v>363</x:v>
-      </x:c>
-      <x:c r="C80" s="52" t="s">
-        <x:v>364</x:v>
-      </x:c>
-      <x:c r="D80" s="53" t="s">
-        <x:v>365</x:v>
-      </x:c>
-      <x:c r="E80" s="53" t="s">
-        <x:v>366</x:v>
-      </x:c>
-      <x:c r="F80" s="53" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="G80" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H80" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" ht="82.5">
-      <x:c r="A81" s="54"/>
-      <x:c r="B81" s="52" t="s">
-        <x:v>367</x:v>
-      </x:c>
-      <x:c r="C81" s="52" t="s">
-        <x:v>368</x:v>
-      </x:c>
-      <x:c r="D81" s="53" t="s">
-        <x:v>369</x:v>
-      </x:c>
-      <x:c r="E81" s="53" t="s">
-        <x:v>370</x:v>
-      </x:c>
-      <x:c r="F81" s="53" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="G81" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H81" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" ht="66">
-      <x:c r="A82" s="54"/>
-      <x:c r="B82" s="52" t="s">
-        <x:v>371</x:v>
-      </x:c>
-      <x:c r="C82" s="52" t="s">
-        <x:v>372</x:v>
-      </x:c>
-      <x:c r="D82" s="53" t="s">
-        <x:v>373</x:v>
-      </x:c>
-      <x:c r="E82" s="53" t="s">
-        <x:v>374</x:v>
-      </x:c>
-      <x:c r="F82" s="53" t="s">
-        <x:v>305</x:v>
-      </x:c>
-      <x:c r="G82" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H82" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" ht="82.5">
-      <x:c r="A83" s="54"/>
-      <x:c r="B83" s="52" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="C83" s="52" t="s">
-        <x:v>376</x:v>
-      </x:c>
-      <x:c r="D83" s="53" t="s">
-        <x:v>377</x:v>
-      </x:c>
-      <x:c r="E83" s="53" t="s">
-        <x:v>378</x:v>
-      </x:c>
-      <x:c r="F83" s="53" t="s">
-        <x:v>379</x:v>
-      </x:c>
-      <x:c r="G83" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H83" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" ht="66">
-      <x:c r="A84" s="54"/>
-      <x:c r="B84" s="52" t="s">
-        <x:v>380</x:v>
-      </x:c>
-      <x:c r="C84" s="52" t="str">
-        <x:v>探底前未能离开罐底</x:v>
-      </x:c>
-      <x:c r="D84" s="53" t="s">
-        <x:v>381</x:v>
-      </x:c>
-      <x:c r="E84" s="53" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="F84" s="53" t="s">
-        <x:v>383</x:v>
-      </x:c>
-      <x:c r="G84" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H84" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" ht="82.5">
-      <x:c r="A85" s="54"/>
-      <x:c r="B85" s="52" t="s">
-        <x:v>384</x:v>
-      </x:c>
-      <x:c r="C85" s="52" t="s">
-        <x:v>385</x:v>
-      </x:c>
-      <x:c r="D85" s="53" t="s">
-        <x:v>386</x:v>
-      </x:c>
-      <x:c r="E85" s="53" t="s">
-        <x:v>387</x:v>
-      </x:c>
-      <x:c r="F85" s="53" t="s">
-        <x:v>388</x:v>
-      </x:c>
-      <x:c r="G85" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H85" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" ht="66">
-      <x:c r="A86" s="54"/>
-      <x:c r="B86" s="52" t="s">
-        <x:v>389</x:v>
-      </x:c>
-      <x:c r="C86" s="52" t="s">
-        <x:v>390</x:v>
-      </x:c>
-      <x:c r="D86" s="53" t="s">
-        <x:v>391</x:v>
-      </x:c>
-      <x:c r="E86" s="53" t="s">
-        <x:v>392</x:v>
-      </x:c>
-      <x:c r="F86" s="53" t="s">
-        <x:v>393</x:v>
-      </x:c>
-      <x:c r="G86" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H86" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" ht="66">
-      <x:c r="A87" s="54"/>
-      <x:c r="B87" s="52" t="s">
-        <x:v>394</x:v>
-      </x:c>
-      <x:c r="C87" s="52" t="s">
-        <x:v>395</x:v>
-      </x:c>
-      <x:c r="D87" s="53" t="s">
-        <x:v>396</x:v>
-      </x:c>
-      <x:c r="E87" s="53" t="s">
-        <x:v>397</x:v>
-      </x:c>
-      <x:c r="F87" s="53" t="s">
-        <x:v>398</x:v>
-      </x:c>
-      <x:c r="G87" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H87" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" ht="66">
-      <x:c r="A88" s="54"/>
-      <x:c r="B88" s="52" t="s">
-        <x:v>399</x:v>
-      </x:c>
-      <x:c r="C88" s="52" t="s">
-        <x:v>400</x:v>
-      </x:c>
-      <x:c r="D88" s="53" t="s">
-        <x:v>401</x:v>
-      </x:c>
-      <x:c r="E88" s="53" t="s">
-        <x:v>402</x:v>
-      </x:c>
-      <x:c r="F88" s="53" t="s">
-        <x:v>403</x:v>
-      </x:c>
-      <x:c r="G88" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H88" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" ht="82.5">
-      <x:c r="A89" s="54"/>
-      <x:c r="B89" s="52" t="s">
-        <x:v>404</x:v>
-      </x:c>
-      <x:c r="C89" s="52" t="s">
-        <x:v>405</x:v>
-      </x:c>
-      <x:c r="D89" s="53" t="s">
-        <x:v>406</x:v>
-      </x:c>
-      <x:c r="E89" s="53" t="s">
-        <x:v>407</x:v>
-      </x:c>
-      <x:c r="F89" s="53" t="s">
-        <x:v>408</x:v>
-      </x:c>
-      <x:c r="G89" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H89" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" ht="82.5">
-      <x:c r="A90" s="54" t="s">
-        <x:v>409</x:v>
-      </x:c>
-      <x:c r="B90" s="52" t="s">
-        <x:v>410</x:v>
-      </x:c>
-      <x:c r="C90" s="52" t="s">
-        <x:v>411</x:v>
-      </x:c>
-      <x:c r="D90" s="53" t="s">
-        <x:v>412</x:v>
-      </x:c>
-      <x:c r="E90" s="53" t="s">
-        <x:v>413</x:v>
-      </x:c>
-      <x:c r="F90" s="53" t="s">
-        <x:v>414</x:v>
-      </x:c>
-      <x:c r="G90" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H90" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" ht="66">
-      <x:c r="A91" s="54"/>
-      <x:c r="B91" s="52" t="s">
-        <x:v>415</x:v>
-      </x:c>
-      <x:c r="C91" s="52" t="s">
-        <x:v>416</x:v>
-      </x:c>
-      <x:c r="D91" s="53" t="s">
-        <x:v>417</x:v>
-      </x:c>
-      <x:c r="E91" s="53" t="s">
-        <x:v>418</x:v>
-      </x:c>
-      <x:c r="F91" s="53" t="s">
-        <x:v>419</x:v>
-      </x:c>
-      <x:c r="G91" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H91" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" ht="66">
-      <x:c r="A92" s="54"/>
-      <x:c r="B92" s="66" t="s">
-        <x:v>420</x:v>
-      </x:c>
-      <x:c r="C92" s="66" t="s">
-        <x:v>421</x:v>
-      </x:c>
-      <x:c r="D92" s="65" t="s">
-        <x:v>422</x:v>
-      </x:c>
-      <x:c r="E92" s="65" t="s">
-        <x:v>423</x:v>
-      </x:c>
-      <x:c r="F92" s="65" t="s">
-        <x:v>424</x:v>
-      </x:c>
-      <x:c r="G92" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H92" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" ht="66">
-      <x:c r="A93" s="54"/>
-      <x:c r="B93" s="52" t="s">
-        <x:v>425</x:v>
-      </x:c>
-      <x:c r="C93" s="52" t="s">
-        <x:v>426</x:v>
-      </x:c>
-      <x:c r="D93" s="53" t="s">
-        <x:v>427</x:v>
-      </x:c>
-      <x:c r="E93" s="53" t="s">
-        <x:v>428</x:v>
-      </x:c>
-      <x:c r="F93" s="53" t="s">
-        <x:v>429</x:v>
-      </x:c>
-      <x:c r="G93" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H93" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" ht="66">
-      <x:c r="A94" s="54"/>
-      <x:c r="B94" s="52" t="s">
-        <x:v>430</x:v>
-      </x:c>
-      <x:c r="C94" s="52" t="str">
-        <x:v>关键参数未设置</x:v>
-      </x:c>
-      <x:c r="D94" s="53" t="s">
-        <x:v>431</x:v>
-      </x:c>
-      <x:c r="E94" s="53" t="s">
-        <x:v>432</x:v>
-      </x:c>
-      <x:c r="F94" s="53" t="s">
-        <x:v>433</x:v>
-      </x:c>
-      <x:c r="G94" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H94" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" ht="66">
-      <x:c r="A95" s="54"/>
-      <x:c r="B95" s="52" t="s">
-        <x:v>434</x:v>
-      </x:c>
-      <x:c r="C95" s="52" t="s">
-        <x:v>435</x:v>
-      </x:c>
-      <x:c r="D95" s="53" t="s">
-        <x:v>436</x:v>
-      </x:c>
-      <x:c r="E95" s="53" t="s">
-        <x:v>437</x:v>
-      </x:c>
-      <x:c r="F95" s="53" t="s">
-        <x:v>438</x:v>
-      </x:c>
-      <x:c r="G95" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H95" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" ht="66">
-      <x:c r="A96" s="54"/>
-      <x:c r="B96" s="52" t="s">
-        <x:v>439</x:v>
-      </x:c>
-      <x:c r="C96" s="52" t="s">
-        <x:v>440</x:v>
-      </x:c>
-      <x:c r="D96" s="53" t="s">
-        <x:v>441</x:v>
-      </x:c>
-      <x:c r="E96" s="53" t="s">
-        <x:v>442</x:v>
-      </x:c>
-      <x:c r="F96" s="53" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="G96" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H96" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" ht="66">
-      <x:c r="A97" s="54"/>
-      <x:c r="B97" s="52" t="s">
-        <x:v>444</x:v>
-      </x:c>
-      <x:c r="C97" s="52" t="s">
-        <x:v>445</x:v>
-      </x:c>
-      <x:c r="D97" s="53" t="s">
-        <x:v>446</x:v>
-      </x:c>
-      <x:c r="E97" s="53" t="s">
-        <x:v>447</x:v>
-      </x:c>
-      <x:c r="F97" s="53" t="s">
-        <x:v>448</x:v>
-      </x:c>
-      <x:c r="G97" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H97" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" ht="66">
-      <x:c r="A98" s="54"/>
-      <x:c r="B98" s="52" t="s">
-        <x:v>449</x:v>
-      </x:c>
-      <x:c r="C98" s="52" t="s">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="D98" s="53" t="s">
-        <x:v>451</x:v>
-      </x:c>
-      <x:c r="E98" s="53" t="s">
-        <x:v>452</x:v>
-      </x:c>
-      <x:c r="F98" s="53" t="s">
-        <x:v>453</x:v>
-      </x:c>
-      <x:c r="G98" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H98" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" ht="82.5">
-      <x:c r="A99" s="54"/>
-      <x:c r="B99" s="52" t="s">
-        <x:v>454</x:v>
-      </x:c>
-      <x:c r="C99" s="52" t="s">
-        <x:v>455</x:v>
-      </x:c>
-      <x:c r="D99" s="53" t="s">
-        <x:v>456</x:v>
-      </x:c>
-      <x:c r="E99" s="53" t="s">
-        <x:v>457</x:v>
-      </x:c>
-      <x:c r="F99" s="53" t="s">
-        <x:v>458</x:v>
-      </x:c>
-      <x:c r="G99" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H99" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" ht="66">
-      <x:c r="A100" s="54" t="s">
-        <x:v>459</x:v>
-      </x:c>
-      <x:c r="B100" s="52" t="s">
-        <x:v>460</x:v>
-      </x:c>
-      <x:c r="C100" s="52" t="str">
-        <x:v>满载标定扭力超过上限</x:v>
-      </x:c>
-      <x:c r="D100" s="53" t="s">
-        <x:v>461</x:v>
-      </x:c>
-      <x:c r="E100" s="53" t="s">
-        <x:v>462</x:v>
-      </x:c>
-      <x:c r="F100" s="53" t="s">
-        <x:v>463</x:v>
-      </x:c>
-      <x:c r="G100" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H100" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" ht="82.5">
-      <x:c r="A101" s="54"/>
-      <x:c r="B101" s="52" t="s">
-        <x:v>464</x:v>
-      </x:c>
-      <x:c r="C101" s="52" t="str">
-        <x:v>满载标定扭力低于下限</x:v>
-      </x:c>
-      <x:c r="D101" s="53" t="s">
-        <x:v>465</x:v>
-      </x:c>
-      <x:c r="E101" s="53" t="s">
-        <x:v>466</x:v>
-      </x:c>
-      <x:c r="F101" s="53" t="s">
-        <x:v>463</x:v>
-      </x:c>
-      <x:c r="G101" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H101" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" ht="66">
-      <x:c r="A102" s="54"/>
-      <x:c r="B102" s="66" t="s">
-        <x:v>467</x:v>
-      </x:c>
-      <x:c r="C102" s="66" t="str">
-        <x:v>扭力变化超过保护值</x:v>
-      </x:c>
-      <x:c r="D102" s="65" t="s">
-        <x:v>468</x:v>
-      </x:c>
-      <x:c r="E102" s="65" t="s">
-        <x:v>469</x:v>
-      </x:c>
-      <x:c r="F102" s="65" t="s">
-        <x:v>463</x:v>
-      </x:c>
-      <x:c r="G102" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H102" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" ht="66">
-      <x:c r="A103" s="54"/>
-      <x:c r="B103" s="52" t="s">
-        <x:v>470</x:v>
-      </x:c>
-      <x:c r="C103" s="52" t="str">
-        <x:v>空载标定扭力偏离零点</x:v>
-      </x:c>
-      <x:c r="D103" s="53" t="s">
-        <x:v>471</x:v>
-      </x:c>
-      <x:c r="E103" s="53" t="s">
-        <x:v>472</x:v>
-      </x:c>
-      <x:c r="F103" s="53" t="s">
-        <x:v>463</x:v>
-      </x:c>
-      <x:c r="G103" s="55" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H103" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104" ht="82.5">
-      <x:c r="A104" s="54"/>
-      <x:c r="B104" s="52" t="s">
-        <x:v>473</x:v>
-      </x:c>
-      <x:c r="C104" s="52" t="s">
-        <x:v>474</x:v>
-      </x:c>
-      <x:c r="D104" s="53" t="s">
-        <x:v>475</x:v>
-      </x:c>
-      <x:c r="E104" s="53" t="s">
-        <x:v>476</x:v>
-      </x:c>
-      <x:c r="F104" s="53" t="s">
-        <x:v>477</x:v>
-      </x:c>
-      <x:c r="G104" s="51" t="s">
-        <x:v>343</x:v>
-      </x:c>
-      <x:c r="H104" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105" ht="66">
-      <x:c r="A105" s="54"/>
-      <x:c r="B105" s="66" t="s">
-        <x:v>478</x:v>
-      </x:c>
-      <x:c r="C105" s="66" t="s">
-        <x:v>479</x:v>
-      </x:c>
-      <x:c r="D105" s="65" t="s">
-        <x:v>480</x:v>
-      </x:c>
-      <x:c r="E105" s="65" t="s">
-        <x:v>481</x:v>
-      </x:c>
-      <x:c r="F105" s="65" t="s">
-        <x:v>463</x:v>
-      </x:c>
-      <x:c r="G105" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H105" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" ht="66">
-      <x:c r="A106" s="54" t="s">
-        <x:v>482</x:v>
-      </x:c>
-      <x:c r="B106" s="52" t="s">
-        <x:v>483</x:v>
-      </x:c>
-      <x:c r="C106" s="52" t="s">
-        <x:v>484</x:v>
-      </x:c>
-      <x:c r="D106" s="53" t="s">
-        <x:v>485</x:v>
-      </x:c>
-      <x:c r="E106" s="53" t="s">
-        <x:v>486</x:v>
-      </x:c>
-      <x:c r="F106" s="53" t="s">
-        <x:v>487</x:v>
-      </x:c>
-      <x:c r="G106" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H106" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" ht="66">
-      <x:c r="A107" s="54"/>
-      <x:c r="B107" s="52" t="s">
-        <x:v>488</x:v>
-      </x:c>
-      <x:c r="C107" s="52" t="str">
-        <x:v>无线滑环通信失败</x:v>
-      </x:c>
-      <x:c r="D107" s="53" t="s">
-        <x:v>489</x:v>
-      </x:c>
-      <x:c r="E107" s="53" t="s">
-        <x:v>490</x:v>
-      </x:c>
-      <x:c r="F107" s="53" t="s">
-        <x:v>491</x:v>
-      </x:c>
-      <x:c r="G107" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H107" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" ht="66">
-      <x:c r="A108" s="54"/>
-      <x:c r="B108" s="66" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="C108" s="66" t="str">
-        <x:v>无线配对信号不达标</x:v>
-      </x:c>
-      <x:c r="D108" s="65" t="s">
-        <x:v>493</x:v>
-      </x:c>
-      <x:c r="E108" s="65" t="s">
-        <x:v>494</x:v>
-      </x:c>
-      <x:c r="F108" s="65" t="s">
-        <x:v>491</x:v>
-      </x:c>
-      <x:c r="G108" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H108" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" ht="66">
-      <x:c r="A109" s="54"/>
-      <x:c r="B109" s="52" t="s">
-        <x:v>495</x:v>
-      </x:c>
-      <x:c r="C109" s="52" t="s">
-        <x:v>496</x:v>
-      </x:c>
-      <x:c r="D109" s="53" t="s">
-        <x:v>497</x:v>
-      </x:c>
-      <x:c r="E109" s="53" t="s">
-        <x:v>498</x:v>
-      </x:c>
-      <x:c r="F109" s="53" t="s">
-        <x:v>499</x:v>
-      </x:c>
-      <x:c r="G109" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H109" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" ht="66">
-      <x:c r="A110" s="54"/>
-      <x:c r="B110" s="66" t="s">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="C110" s="66" t="s">
-        <x:v>501</x:v>
-      </x:c>
-      <x:c r="D110" s="65" t="s">
-        <x:v>502</x:v>
-      </x:c>
-      <x:c r="E110" s="65" t="s">
-        <x:v>503</x:v>
-      </x:c>
-      <x:c r="F110" s="65" t="s">
-        <x:v>491</x:v>
-      </x:c>
-      <x:c r="G110" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H110" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" ht="66">
-      <x:c r="A111" s="54"/>
-      <x:c r="B111" s="52" t="s">
-        <x:v>504</x:v>
-      </x:c>
-      <x:c r="C111" s="52" t="s">
-        <x:v>505</x:v>
-      </x:c>
-      <x:c r="D111" s="53" t="s">
-        <x:v>506</x:v>
-      </x:c>
-      <x:c r="E111" s="53" t="s">
-        <x:v>507</x:v>
-      </x:c>
-      <x:c r="F111" s="53" t="s">
-        <x:v>508</x:v>
-      </x:c>
-      <x:c r="G111" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H111" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" ht="66">
-      <x:c r="A112" s="54"/>
-      <x:c r="B112" s="66" t="s">
-        <x:v>509</x:v>
-      </x:c>
-      <x:c r="C112" s="66" t="s">
-        <x:v>510</x:v>
-      </x:c>
-      <x:c r="D112" s="65" t="s">
-        <x:v>511</x:v>
-      </x:c>
-      <x:c r="E112" s="65" t="s">
-        <x:v>512</x:v>
-      </x:c>
-      <x:c r="F112" s="65" t="s">
-        <x:v>513</x:v>
-      </x:c>
-      <x:c r="G112" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H112" s="47" t="s">
-        <x:v>514</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" ht="82.5">
-      <x:c r="A113" s="54"/>
-      <x:c r="B113" s="52" t="s">
-        <x:v>515</x:v>
-      </x:c>
-      <x:c r="C113" s="52" t="str">
-        <x:v>无线扫描未发现设备</x:v>
-      </x:c>
-      <x:c r="D113" s="53" t="s">
-        <x:v>516</x:v>
-      </x:c>
-      <x:c r="E113" s="53" t="s">
-        <x:v>517</x:v>
-      </x:c>
-      <x:c r="F113" s="53" t="s">
-        <x:v>518</x:v>
-      </x:c>
-      <x:c r="G113" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H113" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" ht="82.5">
-      <x:c r="A114" s="54"/>
-      <x:c r="B114" s="52" t="s">
-        <x:v>519</x:v>
-      </x:c>
-      <x:c r="C114" s="52" t="s">
-        <x:v>520</x:v>
-      </x:c>
-      <x:c r="D114" s="53" t="s">
-        <x:v>521</x:v>
-      </x:c>
-      <x:c r="E114" s="53" t="s">
-        <x:v>522</x:v>
-      </x:c>
-      <x:c r="F114" s="53" t="s">
-        <x:v>523</x:v>
-      </x:c>
-      <x:c r="G114" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H114" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" ht="66">
-      <x:c r="A115" s="54"/>
-      <x:c r="B115" s="52" t="s">
-        <x:v>524</x:v>
-      </x:c>
-      <x:c r="C115" s="52" t="s">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="D115" s="53" t="s">
-        <x:v>526</x:v>
-      </x:c>
-      <x:c r="E115" s="53" t="s">
-        <x:v>527</x:v>
-      </x:c>
-      <x:c r="F115" s="53" t="s">
-        <x:v>528</x:v>
-      </x:c>
-      <x:c r="G115" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H115" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" ht="82.5">
-      <x:c r="A116" s="54"/>
-      <x:c r="B116" s="52" t="s">
-        <x:v>529</x:v>
-      </x:c>
-      <x:c r="C116" s="52" t="s">
-        <x:v>530</x:v>
-      </x:c>
-      <x:c r="D116" s="53" t="s">
-        <x:v>531</x:v>
-      </x:c>
-      <x:c r="E116" s="53" t="s">
-        <x:v>532</x:v>
-      </x:c>
-      <x:c r="F116" s="53" t="s">
-        <x:v>533</x:v>
-      </x:c>
-      <x:c r="G116" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H116" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" ht="66">
-      <x:c r="A117" s="54"/>
-      <x:c r="B117" s="52" t="s">
-        <x:v>534</x:v>
-      </x:c>
-      <x:c r="C117" s="52" t="s">
-        <x:v>535</x:v>
-      </x:c>
-      <x:c r="D117" s="53" t="s">
-        <x:v>536</x:v>
-      </x:c>
-      <x:c r="E117" s="53" t="s">
-        <x:v>537</x:v>
-      </x:c>
-      <x:c r="F117" s="53" t="s">
-        <x:v>538</x:v>
-      </x:c>
-      <x:c r="G117" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H117" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" ht="82.5">
-      <x:c r="A118" s="54"/>
-      <x:c r="B118" s="52" t="s">
-        <x:v>539</x:v>
-      </x:c>
-      <x:c r="C118" s="52" t="s">
-        <x:v>540</x:v>
-      </x:c>
-      <x:c r="D118" s="53" t="s">
-        <x:v>541</x:v>
-      </x:c>
-      <x:c r="E118" s="53" t="s">
-        <x:v>542</x:v>
-      </x:c>
-      <x:c r="F118" s="53" t="s">
-        <x:v>543</x:v>
-      </x:c>
-      <x:c r="G118" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H118" s="47" t="s">
-        <x:v>544</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" ht="82.5">
-      <x:c r="A119" s="54" t="s">
-        <x:v>545</x:v>
-      </x:c>
-      <x:c r="B119" s="52" t="s">
-        <x:v>546</x:v>
-      </x:c>
-      <x:c r="C119" s="52" t="s">
-        <x:v>547</x:v>
-      </x:c>
-      <x:c r="D119" s="53" t="s">
-        <x:v>548</x:v>
-      </x:c>
-      <x:c r="E119" s="53" t="s">
-        <x:v>549</x:v>
-      </x:c>
-      <x:c r="F119" s="53" t="s">
-        <x:v>550</x:v>
-      </x:c>
-      <x:c r="G119" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H119" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="120" ht="82.5">
-      <x:c r="A120" s="54"/>
-      <x:c r="B120" s="52" t="s">
-        <x:v>551</x:v>
-      </x:c>
-      <x:c r="C120" s="52" t="s">
-        <x:v>552</x:v>
-      </x:c>
-      <x:c r="D120" s="53" t="s">
-        <x:v>553</x:v>
-      </x:c>
-      <x:c r="E120" s="53" t="s">
-        <x:v>554</x:v>
-      </x:c>
-      <x:c r="F120" s="53" t="s">
-        <x:v>555</x:v>
-      </x:c>
-      <x:c r="G120" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H120" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="121" ht="82.5">
-      <x:c r="A121" s="54"/>
-      <x:c r="B121" s="52" t="s">
-        <x:v>556</x:v>
-      </x:c>
-      <x:c r="C121" s="52" t="s">
-        <x:v>557</x:v>
-      </x:c>
-      <x:c r="D121" s="53" t="s">
-        <x:v>558</x:v>
-      </x:c>
-      <x:c r="E121" s="53" t="s">
-        <x:v>559</x:v>
-      </x:c>
-      <x:c r="F121" s="53" t="s">
-        <x:v>560</x:v>
-      </x:c>
-      <x:c r="G121" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H121" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="122" ht="66">
-      <x:c r="A122" s="54"/>
-      <x:c r="B122" s="52" t="s">
-        <x:v>561</x:v>
-      </x:c>
-      <x:c r="C122" s="52" t="s">
-        <x:v>562</x:v>
-      </x:c>
-      <x:c r="D122" s="53" t="s">
-        <x:v>563</x:v>
-      </x:c>
-      <x:c r="E122" s="53" t="s">
-        <x:v>564</x:v>
-      </x:c>
-      <x:c r="F122" s="53" t="s">
-        <x:v>565</x:v>
-      </x:c>
-      <x:c r="G122" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H122" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="123" ht="66">
-      <x:c r="A123" s="54"/>
-      <x:c r="B123" s="66" t="s">
-        <x:v>566</x:v>
-      </x:c>
-      <x:c r="C123" s="66" t="s">
-        <x:v>567</x:v>
-      </x:c>
-      <x:c r="D123" s="65" t="s">
-        <x:v>568</x:v>
-      </x:c>
-      <x:c r="E123" s="65" t="s">
-        <x:v>569</x:v>
-      </x:c>
-      <x:c r="F123" s="65" t="s">
-        <x:v>570</x:v>
-      </x:c>
-      <x:c r="G123" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H123" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="124" ht="66">
-      <x:c r="A124" s="54"/>
-      <x:c r="B124" s="66" t="s">
-        <x:v>571</x:v>
-      </x:c>
-      <x:c r="C124" s="66" t="s">
-        <x:v>572</x:v>
-      </x:c>
-      <x:c r="D124" s="65" t="s">
-        <x:v>573</x:v>
-      </x:c>
-      <x:c r="E124" s="65" t="s">
-        <x:v>574</x:v>
-      </x:c>
-      <x:c r="F124" s="65" t="s">
-        <x:v>575</x:v>
-      </x:c>
-      <x:c r="G124" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H124" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="125" ht="66">
-      <x:c r="A125" s="54"/>
-      <x:c r="B125" s="52" t="s">
-        <x:v>576</x:v>
-      </x:c>
-      <x:c r="C125" s="52" t="str">
-        <x:v>主控与模拟量输出模块通信失败</x:v>
-      </x:c>
-      <x:c r="D125" s="53" t="s">
-        <x:v>577</x:v>
-      </x:c>
-      <x:c r="E125" s="53" t="s">
-        <x:v>578</x:v>
-      </x:c>
-      <x:c r="F125" s="53" t="s">
-        <x:v>579</x:v>
-      </x:c>
-      <x:c r="G125" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H125" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="126" ht="82.5">
-      <x:c r="A126" s="54"/>
-      <x:c r="B126" s="52" t="s">
-        <x:v>580</x:v>
-      </x:c>
-      <x:c r="C126" s="52" t="s">
-        <x:v>581</x:v>
-      </x:c>
-      <x:c r="D126" s="53" t="s">
-        <x:v>582</x:v>
-      </x:c>
-      <x:c r="E126" s="53" t="s">
-        <x:v>583</x:v>
-      </x:c>
-      <x:c r="F126" s="53" t="s">
-        <x:v>584</x:v>
-      </x:c>
-      <x:c r="G126" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H126" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="127" ht="82.5">
-      <x:c r="A127" s="54"/>
-      <x:c r="B127" s="52" t="s">
-        <x:v>585</x:v>
-      </x:c>
-      <x:c r="C127" s="52" t="s">
-        <x:v>586</x:v>
-      </x:c>
-      <x:c r="D127" s="53" t="s">
-        <x:v>587</x:v>
-      </x:c>
-      <x:c r="E127" s="53" t="s">
-        <x:v>588</x:v>
-      </x:c>
-      <x:c r="F127" s="53" t="s">
-        <x:v>589</x:v>
-      </x:c>
-      <x:c r="G127" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H127" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="128" ht="82.5">
-      <x:c r="A128" s="54"/>
-      <x:c r="B128" s="52" t="s">
-        <x:v>590</x:v>
-      </x:c>
-      <x:c r="C128" s="52" t="s">
-        <x:v>591</x:v>
-      </x:c>
-      <x:c r="D128" s="53" t="s">
-        <x:v>592</x:v>
-      </x:c>
-      <x:c r="E128" s="53" t="s">
-        <x:v>593</x:v>
-      </x:c>
-      <x:c r="F128" s="53" t="s">
-        <x:v>594</x:v>
-      </x:c>
-      <x:c r="G128" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H128" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="129" ht="82.5">
-      <x:c r="A129" s="54" t="s">
-        <x:v>595</x:v>
-      </x:c>
-      <x:c r="B129" s="52" t="s">
-        <x:v>596</x:v>
-      </x:c>
-      <x:c r="C129" s="52" t="str">
-        <x:v>内部数据空间不足</x:v>
-      </x:c>
-      <x:c r="D129" s="53" t="s">
-        <x:v>597</x:v>
-      </x:c>
-      <x:c r="E129" s="53" t="s">
-        <x:v>598</x:v>
-      </x:c>
-      <x:c r="F129" s="53" t="s">
-        <x:v>599</x:v>
-      </x:c>
-      <x:c r="G129" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H129" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="130" ht="99">
-      <x:c r="A130" s="54"/>
-      <x:c r="B130" s="52" t="s">
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="C130" s="52" t="s">
-        <x:v>601</x:v>
-      </x:c>
-      <x:c r="D130" s="53" t="s">
-        <x:v>602</x:v>
-      </x:c>
-      <x:c r="E130" s="53" t="s">
-        <x:v>603</x:v>
-      </x:c>
-      <x:c r="F130" s="53" t="s">
-        <x:v>604</x:v>
-      </x:c>
-      <x:c r="G130" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H130" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="131" ht="82.5">
-      <x:c r="A131" s="54"/>
-      <x:c r="B131" s="52" t="s">
-        <x:v>605</x:v>
-      </x:c>
-      <x:c r="C131" s="52" t="s">
-        <x:v>606</x:v>
-      </x:c>
-      <x:c r="D131" s="53" t="s">
-        <x:v>607</x:v>
-      </x:c>
-      <x:c r="E131" s="53" t="s">
-        <x:v>608</x:v>
-      </x:c>
-      <x:c r="F131" s="53" t="s">
-        <x:v>609</x:v>
-      </x:c>
-      <x:c r="G131" s="51" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H131" s="47" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="132" ht="115.5">
-      <x:c r="A132" s="56" t="s">
-        <x:v>610</x:v>
-      </x:c>
-      <x:c r="B132" s="66" t="s">
-        <x:v>611</x:v>
-      </x:c>
-      <x:c r="C132" s="66" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="D132" s="65" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="E132" s="65" t="s">
-        <x:v>614</x:v>
-      </x:c>
-      <x:c r="F132" s="65" t="s">
-        <x:v>615</x:v>
-      </x:c>
-      <x:c r="G132" s="57" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H132" s="58" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="133" ht="132">
-      <x:c r="A133" s="56"/>
-      <x:c r="B133" s="59" t="s">
-        <x:v>616</x:v>
-      </x:c>
-      <x:c r="C133" s="59" t="str">
-        <x:v>电源采样数据处理不及时</x:v>
-      </x:c>
-      <x:c r="D133" s="60" t="s">
-        <x:v>617</x:v>
-      </x:c>
-      <x:c r="E133" s="60" t="s">
-        <x:v>618</x:v>
-      </x:c>
-      <x:c r="F133" s="60" t="s">
-        <x:v>619</x:v>
-      </x:c>
-      <x:c r="G133" s="61" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H133" s="58" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="134" ht="132">
-      <x:c r="A134" s="56"/>
-      <x:c r="B134" s="59" t="s">
-        <x:v>620</x:v>
-      </x:c>
-      <x:c r="C134" s="59" t="str">
-        <x:v>电源采样传输意外停止</x:v>
-      </x:c>
-      <x:c r="D134" s="60" t="s">
-        <x:v>621</x:v>
-      </x:c>
-      <x:c r="E134" s="60" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="F134" s="60" t="s">
-        <x:v>623</x:v>
-      </x:c>
-      <x:c r="G134" s="61" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H134" s="58" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="135" ht="115.5">
-      <x:c r="A135" s="56"/>
-      <x:c r="B135" s="59" t="s">
-        <x:v>624</x:v>
-      </x:c>
-      <x:c r="C135" s="59" t="str">
-        <x:v>电源采样启动失败</x:v>
-      </x:c>
-      <x:c r="D135" s="60" t="s">
-        <x:v>625</x:v>
-      </x:c>
-      <x:c r="E135" s="60" t="s">
-        <x:v>626</x:v>
-      </x:c>
-      <x:c r="F135" s="60" t="s">
-        <x:v>627</x:v>
-      </x:c>
-      <x:c r="G135" s="61" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H135" s="58" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="136" ht="99">
-      <x:c r="A136" s="56"/>
-      <x:c r="B136" s="59" t="s">
-        <x:v>628</x:v>
-      </x:c>
-      <x:c r="C136" s="59" t="str">
-        <x:v>电源采样连续恢复失败</x:v>
-      </x:c>
-      <x:c r="D136" s="60" t="s">
-        <x:v>629</x:v>
-      </x:c>
-      <x:c r="E136" s="60" t="s">
-        <x:v>630</x:v>
-      </x:c>
-      <x:c r="F136" s="60" t="s">
-        <x:v>631</x:v>
-      </x:c>
-      <x:c r="G136" s="61" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H136" s="58" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="137" ht="165">
-      <x:c r="A137" s="56"/>
-      <x:c r="B137" s="69" t="s">
-        <x:v>632</x:v>
-      </x:c>
-      <x:c r="C137" s="69" t="s">
-        <x:v>633</x:v>
-      </x:c>
-      <x:c r="D137" s="68" t="s">
-        <x:v>634</x:v>
-      </x:c>
-      <x:c r="E137" s="68" t="s">
-        <x:v>635</x:v>
-      </x:c>
-      <x:c r="F137" s="68" t="s">
-        <x:v>636</x:v>
-      </x:c>
-      <x:c r="G137" s="61" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="H137" s="58" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A2:A16"/>
-    <x:mergeCell ref="A17:A27"/>
-    <x:mergeCell ref="A28:A65"/>
-    <x:mergeCell ref="A66:A71"/>
-    <x:mergeCell ref="A72:A89"/>
-    <x:mergeCell ref="A90:A99"/>
-    <x:mergeCell ref="A100:A105"/>
-    <x:mergeCell ref="A106:A118"/>
-    <x:mergeCell ref="A119:A128"/>
-    <x:mergeCell ref="A129:A131"/>
-    <x:mergeCell ref="A132:A137"/>
-  </x:mergeCells>
-  <x:conditionalFormatting sqref="G2:G73">
-    <x:cfRule type="containsText" dxfId="0" priority="1" operator="between" text="使用中">
-      <x:formula>NOT(ISERROR(SEARCH("使用中",G2)))</x:formula>
-    </x:cfRule>
-    <x:cfRule type="containsText" dxfId="1" priority="2" operator="between" text="保留">
-      <x:formula>NOT(ISERROR(SEARCH("保留",G2)))</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+3. 若同时出现位置跳变或其它编码器故障：按对应故障处理，必要时重新回零。</v>
+      </c>
+      <c r="G24" s="51" t="str">
+        <v>保留</v>
+      </c>
+      <c r="H24" s="47" t="str">
+        <v>CPU2/CPU3保留定义｜当前仅诊断统计</v>
+      </c>
+    </row>
+    <row r="25" ht="82.5">
+      <c r="A25" s="54"/>
+      <c r="B25" s="52" t="s">
+        <v>111</v>
+      </c>
+      <c r="C25" s="52" t="str">
+        <v>编码器角度计算未完成</v>
+      </c>
+      <c r="D25" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="E25" s="53" t="s">
+        <v>113</v>
+      </c>
+      <c r="F25" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="G25" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" ht="66">
+      <c r="A26" s="54"/>
+      <c r="B26" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="D26" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="E26" s="53" t="s">
+        <v>117</v>
+      </c>
+      <c r="F26" s="53" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" ht="82.5">
+      <c r="A27" s="54"/>
+      <c r="B27" s="52" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="52" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="F27" s="53" t="s">
+        <v>123</v>
+      </c>
+      <c r="G27" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" ht="82.5">
+      <c r="A28" s="54" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="49" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" s="49" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="50" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" s="50" t="s">
+        <v>128</v>
+      </c>
+      <c r="F28" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="G28" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" ht="82.5">
+      <c r="A29" s="54"/>
+      <c r="B29" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="C29" s="49" t="str">
+        <v>振动管频率异常</v>
+      </c>
+      <c r="D29" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" s="50" t="s">
+        <v>132</v>
+      </c>
+      <c r="F29" s="50" t="s">
+        <v>129</v>
+      </c>
+      <c r="G29" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" ht="82.5">
+      <c r="A30" s="54"/>
+      <c r="B30" s="66" t="s">
+        <v>133</v>
+      </c>
+      <c r="C30" s="66" t="s">
+        <v>134</v>
+      </c>
+      <c r="D30" s="65" t="s">
+        <v>135</v>
+      </c>
+      <c r="E30" s="65" t="s">
+        <v>136</v>
+      </c>
+      <c r="F30" s="65" t="s">
+        <v>137</v>
+      </c>
+      <c r="G30" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" ht="66">
+      <c r="A31" s="54"/>
+      <c r="B31" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" s="49" t="s">
+        <v>139</v>
+      </c>
+      <c r="D31" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" s="50" t="s">
+        <v>141</v>
+      </c>
+      <c r="F31" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="G31" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="47" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="32" ht="66">
+      <c r="A32" s="54"/>
+      <c r="B32" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="C32" s="49" t="s">
+        <v>145</v>
+      </c>
+      <c r="D32" s="50" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="F32" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="G32" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="47" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="33" ht="66">
+      <c r="A33" s="54"/>
+      <c r="B33" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" s="49" t="str">
+        <v>传感器内部通信校验失败</v>
+      </c>
+      <c r="D33" s="50" t="s">
+        <v>151</v>
+      </c>
+      <c r="E33" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="F33" s="50" t="s">
+        <v>153</v>
+      </c>
+      <c r="G33" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="34" ht="66">
+      <c r="A34" s="54"/>
+      <c r="B34" s="49" t="s">
+        <v>154</v>
+      </c>
+      <c r="C34" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="D34" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="E34" s="50" t="s">
+        <v>157</v>
+      </c>
+      <c r="F34" s="50" t="s">
+        <v>158</v>
+      </c>
+      <c r="G34" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="47" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" ht="82.5">
+      <c r="A35" s="54"/>
+      <c r="B35" s="66" t="s">
+        <v>159</v>
+      </c>
+      <c r="C35" s="66" t="str">
+        <v>密度值超出有效范围</v>
+      </c>
+      <c r="D35" s="65" t="s">
+        <v>160</v>
+      </c>
+      <c r="E35" s="65" t="s">
+        <v>161</v>
+      </c>
+      <c r="F35" s="65" t="s">
+        <v>129</v>
+      </c>
+      <c r="G35" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H35" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" ht="82.5">
+      <c r="A36" s="54"/>
+      <c r="B36" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="D36" s="50" t="s">
+        <v>164</v>
+      </c>
+      <c r="E36" s="50" t="s">
+        <v>165</v>
+      </c>
+      <c r="F36" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="G36" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H36" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" ht="82.5">
+      <c r="A37" s="54"/>
+      <c r="B37" s="49" t="s">
+        <v>167</v>
+      </c>
+      <c r="C37" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="D37" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="E37" s="50" t="s">
+        <v>170</v>
+      </c>
+      <c r="F37" s="50" t="s">
+        <v>171</v>
+      </c>
+      <c r="G37" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H37" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" ht="66">
+      <c r="A38" s="54"/>
+      <c r="B38" s="49" t="s">
+        <v>172</v>
+      </c>
+      <c r="C38" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="D38" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="E38" s="50" t="s">
+        <v>175</v>
+      </c>
+      <c r="F38" s="50" t="s">
+        <v>176</v>
+      </c>
+      <c r="G38" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H38" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" ht="66">
+      <c r="A39" s="54"/>
+      <c r="B39" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="C39" s="49" t="s">
+        <v>178</v>
+      </c>
+      <c r="D39" s="50" t="s">
+        <v>179</v>
+      </c>
+      <c r="E39" s="50" t="s">
+        <v>180</v>
+      </c>
+      <c r="F39" s="50" t="s">
+        <v>181</v>
+      </c>
+      <c r="G39" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H39" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" ht="82.5">
+      <c r="A40" s="54"/>
+      <c r="B40" s="49" t="s">
+        <v>182</v>
+      </c>
+      <c r="C40" s="49" t="s">
+        <v>183</v>
+      </c>
+      <c r="D40" s="50" t="s">
+        <v>184</v>
+      </c>
+      <c r="E40" s="50" t="s">
+        <v>185</v>
+      </c>
+      <c r="F40" s="50" t="s">
+        <v>186</v>
+      </c>
+      <c r="G40" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H40" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" ht="82.5">
+      <c r="A41" s="54"/>
+      <c r="B41" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="C41" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="D41" s="50" t="s">
+        <v>189</v>
+      </c>
+      <c r="E41" s="50" t="s">
+        <v>190</v>
+      </c>
+      <c r="F41" s="50" t="s">
+        <v>191</v>
+      </c>
+      <c r="G41" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H41" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" ht="82.5">
+      <c r="A42" s="54"/>
+      <c r="B42" s="49" t="s">
+        <v>192</v>
+      </c>
+      <c r="C42" s="49" t="s">
+        <v>193</v>
+      </c>
+      <c r="D42" s="50" t="s">
+        <v>194</v>
+      </c>
+      <c r="E42" s="50" t="s">
+        <v>195</v>
+      </c>
+      <c r="F42" s="50" t="s">
+        <v>196</v>
+      </c>
+      <c r="G42" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H42" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" ht="66">
+      <c r="A43" s="54"/>
+      <c r="B43" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="C43" s="49" t="str">
+        <v>传感器配置批次不一致</v>
+      </c>
+      <c r="D43" s="50" t="s">
+        <v>198</v>
+      </c>
+      <c r="E43" s="50" t="s">
+        <v>199</v>
+      </c>
+      <c r="F43" s="50" t="s">
+        <v>200</v>
+      </c>
+      <c r="G43" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H43" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" ht="82.5">
+      <c r="A44" s="54"/>
+      <c r="B44" s="49" t="s">
+        <v>201</v>
+      </c>
+      <c r="C44" s="49" t="s">
+        <v>202</v>
+      </c>
+      <c r="D44" s="50" t="s">
+        <v>203</v>
+      </c>
+      <c r="E44" s="50" t="s">
+        <v>204</v>
+      </c>
+      <c r="F44" s="50" t="s">
+        <v>205</v>
+      </c>
+      <c r="G44" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H44" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" ht="82.5">
+      <c r="A45" s="54"/>
+      <c r="B45" s="49" t="s">
+        <v>206</v>
+      </c>
+      <c r="C45" s="49" t="s">
+        <v>207</v>
+      </c>
+      <c r="D45" s="50" t="s">
+        <v>208</v>
+      </c>
+      <c r="E45" s="50" t="s">
+        <v>209</v>
+      </c>
+      <c r="F45" s="50" t="s">
+        <v>210</v>
+      </c>
+      <c r="G45" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H45" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" ht="66">
+      <c r="A46" s="54"/>
+      <c r="B46" s="49" t="s">
+        <v>211</v>
+      </c>
+      <c r="C46" s="49" t="s">
+        <v>212</v>
+      </c>
+      <c r="D46" s="50" t="s">
+        <v>213</v>
+      </c>
+      <c r="E46" s="50" t="s">
+        <v>214</v>
+      </c>
+      <c r="F46" s="50" t="s">
+        <v>215</v>
+      </c>
+      <c r="G46" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H46" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" ht="66">
+      <c r="A47" s="54"/>
+      <c r="B47" s="49" t="s">
+        <v>216</v>
+      </c>
+      <c r="C47" s="49" t="s">
+        <v>217</v>
+      </c>
+      <c r="D47" s="50" t="s">
+        <v>218</v>
+      </c>
+      <c r="E47" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="F47" s="50" t="s">
+        <v>220</v>
+      </c>
+      <c r="G47" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H47" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" ht="66">
+      <c r="A48" s="54"/>
+      <c r="B48" s="52" t="s">
+        <v>221</v>
+      </c>
+      <c r="C48" s="52" t="s">
+        <v>222</v>
+      </c>
+      <c r="D48" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="E48" s="53" t="s">
+        <v>224</v>
+      </c>
+      <c r="F48" s="53" t="s">
+        <v>225</v>
+      </c>
+      <c r="G48" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H48" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" ht="82.5">
+      <c r="A49" s="54"/>
+      <c r="B49" s="52" t="s">
+        <v>226</v>
+      </c>
+      <c r="C49" s="52" t="str">
+        <v>传感器连接状态失效</v>
+      </c>
+      <c r="D49" s="53" t="s">
+        <v>227</v>
+      </c>
+      <c r="E49" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="F49" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="G49" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H49" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" ht="66">
+      <c r="A50" s="54"/>
+      <c r="B50" s="52" t="s">
+        <v>230</v>
+      </c>
+      <c r="C50" s="52" t="str">
+        <v>传感器应答序号不一致</v>
+      </c>
+      <c r="D50" s="53" t="s">
+        <v>231</v>
+      </c>
+      <c r="E50" s="53" t="s">
+        <v>232</v>
+      </c>
+      <c r="F50" s="53" t="s">
+        <v>233</v>
+      </c>
+      <c r="G50" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H50" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" ht="82.5">
+      <c r="A51" s="54"/>
+      <c r="B51" s="52" t="s">
+        <v>234</v>
+      </c>
+      <c r="C51" s="52" t="str">
+        <v>传感器需要重新确认连接</v>
+      </c>
+      <c r="D51" s="53" t="s">
+        <v>235</v>
+      </c>
+      <c r="E51" s="53" t="s">
+        <v>236</v>
+      </c>
+      <c r="F51" s="53" t="s">
+        <v>237</v>
+      </c>
+      <c r="G51" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H51" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" ht="66">
+      <c r="A52" s="54"/>
+      <c r="B52" s="52" t="s">
+        <v>238</v>
+      </c>
+      <c r="C52" s="52" t="str">
+        <v>收到重复的传感器数据</v>
+      </c>
+      <c r="D52" s="53" t="s">
+        <v>239</v>
+      </c>
+      <c r="E52" s="53" t="s">
+        <v>240</v>
+      </c>
+      <c r="F52" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="G52" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H52" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" ht="66">
+      <c r="A53" s="54"/>
+      <c r="B53" s="52" t="s">
+        <v>242</v>
+      </c>
+      <c r="C53" s="52" t="str">
+        <v>传感器不支持所需功能</v>
+      </c>
+      <c r="D53" s="53" t="s">
+        <v>243</v>
+      </c>
+      <c r="E53" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="F53" s="53" t="s">
+        <v>245</v>
+      </c>
+      <c r="G53" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H53" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" ht="66">
+      <c r="A54" s="54"/>
+      <c r="B54" s="49" t="s">
+        <v>246</v>
+      </c>
+      <c r="C54" s="49" t="s">
+        <v>247</v>
+      </c>
+      <c r="D54" s="50" t="s">
+        <v>248</v>
+      </c>
+      <c r="E54" s="50" t="s">
+        <v>249</v>
+      </c>
+      <c r="F54" s="50" t="s">
+        <v>250</v>
+      </c>
+      <c r="G54" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H54" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" ht="82.5">
+      <c r="A55" s="54"/>
+      <c r="B55" s="49" t="s">
+        <v>251</v>
+      </c>
+      <c r="C55" s="49" t="str">
+        <v>传感器不接受当前参数</v>
+      </c>
+      <c r="D55" s="50" t="s">
+        <v>252</v>
+      </c>
+      <c r="E55" s="50" t="s">
+        <v>253</v>
+      </c>
+      <c r="F55" s="50" t="s">
+        <v>254</v>
+      </c>
+      <c r="G55" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H55" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="56" ht="66">
+      <c r="A56" s="54"/>
+      <c r="B56" s="49" t="s">
+        <v>255</v>
+      </c>
+      <c r="C56" s="49" t="s">
+        <v>256</v>
+      </c>
+      <c r="D56" s="50" t="s">
+        <v>257</v>
+      </c>
+      <c r="E56" s="50" t="s">
+        <v>258</v>
+      </c>
+      <c r="F56" s="50" t="s">
+        <v>259</v>
+      </c>
+      <c r="G56" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="H56" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="57" ht="82.5">
+      <c r="A57" s="54"/>
+      <c r="B57" s="49" t="s">
+        <v>260</v>
+      </c>
+      <c r="C57" s="49" t="str">
+        <v>传感器当前模式不允许操作</v>
+      </c>
+      <c r="D57" s="50" t="s">
+        <v>261</v>
+      </c>
+      <c r="E57" s="50" t="s">
+        <v>262</v>
+      </c>
+      <c r="F57" s="50" t="s">
+        <v>263</v>
+      </c>
+      <c r="G57" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H57" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" ht="82.5">
+      <c r="A58" s="54"/>
+      <c r="B58" s="49" t="s">
+        <v>264</v>
+      </c>
+      <c r="C58" s="49" t="str">
+        <v>上一次传感器操作尚未完成</v>
+      </c>
+      <c r="D58" s="50" t="s">
+        <v>265</v>
+      </c>
+      <c r="E58" s="50" t="s">
+        <v>266</v>
+      </c>
+      <c r="F58" s="50" t="s">
+        <v>267</v>
+      </c>
+      <c r="G58" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H58" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" ht="66">
+      <c r="A59" s="54"/>
+      <c r="B59" s="49" t="s">
+        <v>268</v>
+      </c>
+      <c r="C59" s="49" t="s">
+        <v>269</v>
+      </c>
+      <c r="D59" s="50" t="s">
+        <v>270</v>
+      </c>
+      <c r="E59" s="50" t="s">
+        <v>271</v>
+      </c>
+      <c r="F59" s="50" t="s">
+        <v>272</v>
+      </c>
+      <c r="G59" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H59" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" ht="66">
+      <c r="A60" s="54"/>
+      <c r="B60" s="49" t="s">
+        <v>273</v>
+      </c>
+      <c r="C60" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="D60" s="50" t="s">
+        <v>275</v>
+      </c>
+      <c r="E60" s="50" t="s">
+        <v>276</v>
+      </c>
+      <c r="F60" s="50" t="s">
+        <v>277</v>
+      </c>
+      <c r="G60" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H60" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="61" ht="66">
+      <c r="A61" s="54"/>
+      <c r="B61" s="49" t="s">
+        <v>278</v>
+      </c>
+      <c r="C61" s="49" t="str">
+        <v>传感器采样序号异常</v>
+      </c>
+      <c r="D61" s="50" t="s">
+        <v>279</v>
+      </c>
+      <c r="E61" s="50" t="s">
+        <v>280</v>
+      </c>
+      <c r="F61" s="50" t="s">
+        <v>281</v>
+      </c>
+      <c r="G61" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H61" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="62" ht="66">
+      <c r="A62" s="54"/>
+      <c r="B62" s="49" t="s">
+        <v>282</v>
+      </c>
+      <c r="C62" s="49" t="s">
+        <v>283</v>
+      </c>
+      <c r="D62" s="50" t="s">
+        <v>284</v>
+      </c>
+      <c r="E62" s="50" t="s">
+        <v>285</v>
+      </c>
+      <c r="F62" s="50" t="s">
+        <v>286</v>
+      </c>
+      <c r="G62" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H62" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63" ht="66">
+      <c r="A63" s="54"/>
+      <c r="B63" s="49" t="s">
+        <v>287</v>
+      </c>
+      <c r="C63" s="49" t="s">
+        <v>288</v>
+      </c>
+      <c r="D63" s="50" t="s">
+        <v>289</v>
+      </c>
+      <c r="E63" s="50" t="s">
+        <v>290</v>
+      </c>
+      <c r="F63" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="G63" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H63" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64" ht="66">
+      <c r="A64" s="54"/>
+      <c r="B64" s="49" t="s">
+        <v>292</v>
+      </c>
+      <c r="C64" s="49" t="str">
+        <v>传感器周期上报重复启动</v>
+      </c>
+      <c r="D64" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="E64" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="F64" s="50" t="s">
+        <v>295</v>
+      </c>
+      <c r="G64" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H64" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" ht="82.5">
+      <c r="A65" s="54"/>
+      <c r="B65" s="49" t="s">
+        <v>296</v>
+      </c>
+      <c r="C65" s="49" t="s">
+        <v>297</v>
+      </c>
+      <c r="D65" s="50" t="s">
+        <v>298</v>
+      </c>
+      <c r="E65" s="50" t="s">
+        <v>299</v>
+      </c>
+      <c r="F65" s="50" t="s">
+        <v>300</v>
+      </c>
+      <c r="G65" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H65" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66" ht="66">
+      <c r="A66" s="54" t="s">
+        <v>301</v>
+      </c>
+      <c r="B66" s="49" t="s">
+        <v>302</v>
+      </c>
+      <c r="C66" s="49" t="str">
+        <v>零点位置超出允许范围</v>
+      </c>
+      <c r="D66" s="50" t="s">
+        <v>303</v>
+      </c>
+      <c r="E66" s="50" t="s">
+        <v>304</v>
+      </c>
+      <c r="F66" s="50" t="s">
+        <v>305</v>
+      </c>
+      <c r="G66" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H66" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67" ht="99">
+      <c r="A67" s="54"/>
+      <c r="B67" s="49" t="s">
+        <v>306</v>
+      </c>
+      <c r="C67" s="49" t="str">
+        <v>陀螺仪基准不稳定</v>
+      </c>
+      <c r="D67" s="50" t="s">
+        <v>307</v>
+      </c>
+      <c r="E67" s="50" t="s">
+        <v>308</v>
+      </c>
+      <c r="F67" s="50" t="s">
+        <v>309</v>
+      </c>
+      <c r="G67" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H67" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68" ht="66">
+      <c r="A68" s="54"/>
+      <c r="B68" s="49" t="s">
+        <v>310</v>
+      </c>
+      <c r="C68" s="49" t="s">
+        <v>311</v>
+      </c>
+      <c r="D68" s="50" t="s">
+        <v>312</v>
+      </c>
+      <c r="E68" s="50" t="s">
+        <v>313</v>
+      </c>
+      <c r="F68" s="50" t="s">
+        <v>314</v>
+      </c>
+      <c r="G68" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H68" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" ht="66">
+      <c r="A69" s="54"/>
+      <c r="B69" s="49" t="s">
+        <v>315</v>
+      </c>
+      <c r="C69" s="49" t="s">
+        <v>316</v>
+      </c>
+      <c r="D69" s="50" t="s">
+        <v>317</v>
+      </c>
+      <c r="E69" s="50" t="s">
+        <v>318</v>
+      </c>
+      <c r="F69" s="50" t="s">
+        <v>319</v>
+      </c>
+      <c r="G69" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H69" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" ht="66">
+      <c r="A70" s="54"/>
+      <c r="B70" s="49" t="s">
+        <v>320</v>
+      </c>
+      <c r="C70" s="49" t="str">
+        <v>电机到位偏差过大</v>
+      </c>
+      <c r="D70" s="50" t="s">
+        <v>321</v>
+      </c>
+      <c r="E70" s="50" t="s">
+        <v>322</v>
+      </c>
+      <c r="F70" s="50" t="s">
+        <v>323</v>
+      </c>
+      <c r="G70" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H70" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="71" ht="66">
+      <c r="A71" s="54"/>
+      <c r="B71" s="49" t="s">
+        <v>324</v>
+      </c>
+      <c r="C71" s="49" t="s">
+        <v>325</v>
+      </c>
+      <c r="D71" s="50" t="s">
+        <v>326</v>
+      </c>
+      <c r="E71" s="50" t="s">
+        <v>327</v>
+      </c>
+      <c r="F71" s="50" t="s">
+        <v>328</v>
+      </c>
+      <c r="G71" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H71" s="47" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="72" ht="82.5">
+      <c r="A72" s="54" t="s">
+        <v>330</v>
+      </c>
+      <c r="B72" s="49" t="s">
+        <v>331</v>
+      </c>
+      <c r="C72" s="49" t="str">
+        <v>上行找液位到达位置上限</v>
+      </c>
+      <c r="D72" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="E72" s="50" t="s">
+        <v>333</v>
+      </c>
+      <c r="F72" s="50" t="s">
+        <v>305</v>
+      </c>
+      <c r="G72" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H72" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73" ht="82.5">
+      <c r="A73" s="54"/>
+      <c r="B73" s="49" t="s">
+        <v>334</v>
+      </c>
+      <c r="C73" s="49" t="s">
+        <v>335</v>
+      </c>
+      <c r="D73" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="E73" s="50" t="s">
+        <v>337</v>
+      </c>
+      <c r="F73" s="50" t="s">
+        <v>305</v>
+      </c>
+      <c r="G73" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H73" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" ht="66">
+      <c r="A74" s="54"/>
+      <c r="B74" s="49" t="s">
+        <v>338</v>
+      </c>
+      <c r="C74" s="49" t="s">
+        <v>339</v>
+      </c>
+      <c r="D74" s="50" t="s">
+        <v>340</v>
+      </c>
+      <c r="E74" s="50" t="s">
+        <v>341</v>
+      </c>
+      <c r="F74" s="50" t="s">
+        <v>342</v>
+      </c>
+      <c r="G74" s="51" t="s">
+        <v>343</v>
+      </c>
+      <c r="H74" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75" ht="82.5">
+      <c r="A75" s="54"/>
+      <c r="B75" s="49" t="s">
+        <v>344</v>
+      </c>
+      <c r="C75" s="49" t="s">
+        <v>345</v>
+      </c>
+      <c r="D75" s="50" t="s">
+        <v>346</v>
+      </c>
+      <c r="E75" s="50" t="s">
+        <v>347</v>
+      </c>
+      <c r="F75" s="50" t="s">
+        <v>348</v>
+      </c>
+      <c r="G75" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H75" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76" ht="82.5">
+      <c r="A76" s="54"/>
+      <c r="B76" s="66" t="s">
+        <v>349</v>
+      </c>
+      <c r="C76" s="66" t="s">
+        <v>350</v>
+      </c>
+      <c r="D76" s="65" t="s">
+        <v>351</v>
+      </c>
+      <c r="E76" s="65" t="s">
+        <v>352</v>
+      </c>
+      <c r="F76" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="G76" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H76" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77" ht="66">
+      <c r="A77" s="54"/>
+      <c r="B77" s="66" t="s">
+        <v>353</v>
+      </c>
+      <c r="C77" s="66" t="s">
+        <v>354</v>
+      </c>
+      <c r="D77" s="65" t="s">
+        <v>355</v>
+      </c>
+      <c r="E77" s="65" t="s">
+        <v>356</v>
+      </c>
+      <c r="F77" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="G77" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H77" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78" ht="82.5">
+      <c r="A78" s="54"/>
+      <c r="B78" s="66" t="s">
+        <v>357</v>
+      </c>
+      <c r="C78" s="66" t="str">
+        <v>下行未找到罐底</v>
+      </c>
+      <c r="D78" s="65" t="s">
+        <v>358</v>
+      </c>
+      <c r="E78" s="65" t="s">
+        <v>359</v>
+      </c>
+      <c r="F78" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="G78" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H78" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79" ht="66">
+      <c r="A79" s="54"/>
+      <c r="B79" s="66" t="s">
+        <v>360</v>
+      </c>
+      <c r="C79" s="66" t="str">
+        <v>上行未找到零点</v>
+      </c>
+      <c r="D79" s="65" t="s">
+        <v>361</v>
+      </c>
+      <c r="E79" s="65" t="s">
+        <v>362</v>
+      </c>
+      <c r="F79" s="65" t="s">
+        <v>305</v>
+      </c>
+      <c r="G79" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H79" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="80" ht="82.5">
+      <c r="A80" s="54"/>
+      <c r="B80" s="52" t="s">
+        <v>363</v>
+      </c>
+      <c r="C80" s="52" t="s">
+        <v>364</v>
+      </c>
+      <c r="D80" s="53" t="s">
+        <v>365</v>
+      </c>
+      <c r="E80" s="53" t="s">
+        <v>366</v>
+      </c>
+      <c r="F80" s="53" t="s">
+        <v>305</v>
+      </c>
+      <c r="G80" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H80" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81" ht="82.5">
+      <c r="A81" s="54"/>
+      <c r="B81" s="52" t="s">
+        <v>367</v>
+      </c>
+      <c r="C81" s="52" t="s">
+        <v>368</v>
+      </c>
+      <c r="D81" s="53" t="s">
+        <v>369</v>
+      </c>
+      <c r="E81" s="53" t="s">
+        <v>370</v>
+      </c>
+      <c r="F81" s="53" t="s">
+        <v>305</v>
+      </c>
+      <c r="G81" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H81" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82" ht="66">
+      <c r="A82" s="54"/>
+      <c r="B82" s="52" t="s">
+        <v>371</v>
+      </c>
+      <c r="C82" s="52" t="s">
+        <v>372</v>
+      </c>
+      <c r="D82" s="53" t="s">
+        <v>373</v>
+      </c>
+      <c r="E82" s="53" t="s">
+        <v>374</v>
+      </c>
+      <c r="F82" s="53" t="s">
+        <v>305</v>
+      </c>
+      <c r="G82" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H82" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83" ht="82.5">
+      <c r="A83" s="54"/>
+      <c r="B83" s="52" t="s">
+        <v>375</v>
+      </c>
+      <c r="C83" s="52" t="s">
+        <v>376</v>
+      </c>
+      <c r="D83" s="53" t="s">
+        <v>377</v>
+      </c>
+      <c r="E83" s="53" t="s">
+        <v>378</v>
+      </c>
+      <c r="F83" s="53" t="s">
+        <v>379</v>
+      </c>
+      <c r="G83" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H83" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="84" ht="66">
+      <c r="A84" s="54"/>
+      <c r="B84" s="52" t="s">
+        <v>380</v>
+      </c>
+      <c r="C84" s="52" t="str">
+        <v>探底前未能离开罐底</v>
+      </c>
+      <c r="D84" s="53" t="s">
+        <v>381</v>
+      </c>
+      <c r="E84" s="53" t="s">
+        <v>382</v>
+      </c>
+      <c r="F84" s="53" t="s">
+        <v>383</v>
+      </c>
+      <c r="G84" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H84" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="85" ht="82.5">
+      <c r="A85" s="54"/>
+      <c r="B85" s="52" t="s">
+        <v>384</v>
+      </c>
+      <c r="C85" s="52" t="s">
+        <v>385</v>
+      </c>
+      <c r="D85" s="53" t="s">
+        <v>386</v>
+      </c>
+      <c r="E85" s="53" t="s">
+        <v>387</v>
+      </c>
+      <c r="F85" s="53" t="s">
+        <v>388</v>
+      </c>
+      <c r="G85" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H85" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="86" ht="66">
+      <c r="A86" s="54"/>
+      <c r="B86" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="C86" s="52" t="s">
+        <v>390</v>
+      </c>
+      <c r="D86" s="53" t="s">
+        <v>391</v>
+      </c>
+      <c r="E86" s="53" t="s">
+        <v>392</v>
+      </c>
+      <c r="F86" s="53" t="s">
+        <v>393</v>
+      </c>
+      <c r="G86" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H86" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="87" ht="66">
+      <c r="A87" s="54"/>
+      <c r="B87" s="52" t="s">
+        <v>394</v>
+      </c>
+      <c r="C87" s="52" t="s">
+        <v>395</v>
+      </c>
+      <c r="D87" s="53" t="s">
+        <v>396</v>
+      </c>
+      <c r="E87" s="53" t="s">
+        <v>397</v>
+      </c>
+      <c r="F87" s="53" t="s">
+        <v>398</v>
+      </c>
+      <c r="G87" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H87" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="88" ht="66">
+      <c r="A88" s="54"/>
+      <c r="B88" s="52" t="s">
+        <v>399</v>
+      </c>
+      <c r="C88" s="52" t="s">
+        <v>400</v>
+      </c>
+      <c r="D88" s="53" t="s">
+        <v>401</v>
+      </c>
+      <c r="E88" s="53" t="s">
+        <v>402</v>
+      </c>
+      <c r="F88" s="53" t="s">
+        <v>403</v>
+      </c>
+      <c r="G88" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H88" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="89" ht="82.5">
+      <c r="A89" s="54"/>
+      <c r="B89" s="52" t="s">
+        <v>404</v>
+      </c>
+      <c r="C89" s="52" t="s">
+        <v>405</v>
+      </c>
+      <c r="D89" s="53" t="s">
+        <v>406</v>
+      </c>
+      <c r="E89" s="53" t="s">
+        <v>407</v>
+      </c>
+      <c r="F89" s="53" t="s">
+        <v>408</v>
+      </c>
+      <c r="G89" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H89" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="90" ht="82.5">
+      <c r="A90" s="54" t="s">
+        <v>409</v>
+      </c>
+      <c r="B90" s="52" t="s">
+        <v>410</v>
+      </c>
+      <c r="C90" s="52" t="s">
+        <v>411</v>
+      </c>
+      <c r="D90" s="53" t="s">
+        <v>412</v>
+      </c>
+      <c r="E90" s="53" t="s">
+        <v>413</v>
+      </c>
+      <c r="F90" s="53" t="s">
+        <v>414</v>
+      </c>
+      <c r="G90" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H90" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="91" ht="66">
+      <c r="A91" s="54"/>
+      <c r="B91" s="52" t="s">
+        <v>415</v>
+      </c>
+      <c r="C91" s="52" t="s">
+        <v>416</v>
+      </c>
+      <c r="D91" s="53" t="s">
+        <v>417</v>
+      </c>
+      <c r="E91" s="53" t="s">
+        <v>418</v>
+      </c>
+      <c r="F91" s="53" t="s">
+        <v>419</v>
+      </c>
+      <c r="G91" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H91" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="92" ht="66">
+      <c r="A92" s="54"/>
+      <c r="B92" s="66" t="s">
+        <v>420</v>
+      </c>
+      <c r="C92" s="66" t="s">
+        <v>421</v>
+      </c>
+      <c r="D92" s="65" t="s">
+        <v>422</v>
+      </c>
+      <c r="E92" s="65" t="s">
+        <v>423</v>
+      </c>
+      <c r="F92" s="65" t="s">
+        <v>424</v>
+      </c>
+      <c r="G92" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H92" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="93" ht="66">
+      <c r="A93" s="54"/>
+      <c r="B93" s="52" t="s">
+        <v>425</v>
+      </c>
+      <c r="C93" s="52" t="s">
+        <v>426</v>
+      </c>
+      <c r="D93" s="53" t="s">
+        <v>427</v>
+      </c>
+      <c r="E93" s="53" t="s">
+        <v>428</v>
+      </c>
+      <c r="F93" s="53" t="s">
+        <v>429</v>
+      </c>
+      <c r="G93" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H93" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94" ht="66">
+      <c r="A94" s="54"/>
+      <c r="B94" s="52" t="s">
+        <v>430</v>
+      </c>
+      <c r="C94" s="52" t="str">
+        <v>关键参数未设置</v>
+      </c>
+      <c r="D94" s="53" t="s">
+        <v>431</v>
+      </c>
+      <c r="E94" s="53" t="s">
+        <v>432</v>
+      </c>
+      <c r="F94" s="53" t="s">
+        <v>433</v>
+      </c>
+      <c r="G94" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H94" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="95" ht="66">
+      <c r="A95" s="54"/>
+      <c r="B95" s="52" t="s">
+        <v>434</v>
+      </c>
+      <c r="C95" s="52" t="s">
+        <v>435</v>
+      </c>
+      <c r="D95" s="53" t="s">
+        <v>436</v>
+      </c>
+      <c r="E95" s="53" t="s">
+        <v>437</v>
+      </c>
+      <c r="F95" s="53" t="s">
+        <v>438</v>
+      </c>
+      <c r="G95" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H95" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="96" ht="66">
+      <c r="A96" s="54"/>
+      <c r="B96" s="52" t="s">
+        <v>439</v>
+      </c>
+      <c r="C96" s="52" t="s">
+        <v>440</v>
+      </c>
+      <c r="D96" s="53" t="s">
+        <v>441</v>
+      </c>
+      <c r="E96" s="53" t="s">
+        <v>442</v>
+      </c>
+      <c r="F96" s="53" t="s">
+        <v>443</v>
+      </c>
+      <c r="G96" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H96" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="97" ht="66">
+      <c r="A97" s="54"/>
+      <c r="B97" s="52" t="s">
+        <v>444</v>
+      </c>
+      <c r="C97" s="52" t="s">
+        <v>445</v>
+      </c>
+      <c r="D97" s="53" t="s">
+        <v>446</v>
+      </c>
+      <c r="E97" s="53" t="s">
+        <v>447</v>
+      </c>
+      <c r="F97" s="53" t="s">
+        <v>448</v>
+      </c>
+      <c r="G97" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H97" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="98" ht="66">
+      <c r="A98" s="54"/>
+      <c r="B98" s="52" t="s">
+        <v>449</v>
+      </c>
+      <c r="C98" s="52" t="s">
+        <v>450</v>
+      </c>
+      <c r="D98" s="53" t="s">
+        <v>451</v>
+      </c>
+      <c r="E98" s="53" t="s">
+        <v>452</v>
+      </c>
+      <c r="F98" s="53" t="s">
+        <v>453</v>
+      </c>
+      <c r="G98" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H98" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="99" ht="82.5">
+      <c r="A99" s="54"/>
+      <c r="B99" s="52" t="s">
+        <v>454</v>
+      </c>
+      <c r="C99" s="52" t="s">
+        <v>455</v>
+      </c>
+      <c r="D99" s="53" t="s">
+        <v>456</v>
+      </c>
+      <c r="E99" s="53" t="s">
+        <v>457</v>
+      </c>
+      <c r="F99" s="53" t="s">
+        <v>458</v>
+      </c>
+      <c r="G99" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H99" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="100" ht="66">
+      <c r="A100" s="54" t="s">
+        <v>459</v>
+      </c>
+      <c r="B100" s="52" t="s">
+        <v>460</v>
+      </c>
+      <c r="C100" s="52" t="str">
+        <v>满载标定扭力超过上限</v>
+      </c>
+      <c r="D100" s="53" t="s">
+        <v>461</v>
+      </c>
+      <c r="E100" s="53" t="s">
+        <v>462</v>
+      </c>
+      <c r="F100" s="53" t="s">
+        <v>463</v>
+      </c>
+      <c r="G100" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H100" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="101" ht="82.5">
+      <c r="A101" s="54"/>
+      <c r="B101" s="52" t="s">
+        <v>464</v>
+      </c>
+      <c r="C101" s="52" t="str">
+        <v>满载标定扭力低于下限</v>
+      </c>
+      <c r="D101" s="53" t="s">
+        <v>465</v>
+      </c>
+      <c r="E101" s="53" t="s">
+        <v>466</v>
+      </c>
+      <c r="F101" s="53" t="s">
+        <v>463</v>
+      </c>
+      <c r="G101" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H101" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="102" ht="66">
+      <c r="A102" s="54"/>
+      <c r="B102" s="66" t="s">
+        <v>467</v>
+      </c>
+      <c r="C102" s="66" t="str">
+        <v>扭力变化超过保护值</v>
+      </c>
+      <c r="D102" s="65" t="s">
+        <v>468</v>
+      </c>
+      <c r="E102" s="65" t="s">
+        <v>469</v>
+      </c>
+      <c r="F102" s="65" t="s">
+        <v>463</v>
+      </c>
+      <c r="G102" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H102" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="103" ht="66">
+      <c r="A103" s="54"/>
+      <c r="B103" s="52" t="s">
+        <v>470</v>
+      </c>
+      <c r="C103" s="52" t="str">
+        <v>空载标定扭力偏离零点</v>
+      </c>
+      <c r="D103" s="53" t="s">
+        <v>471</v>
+      </c>
+      <c r="E103" s="53" t="s">
+        <v>472</v>
+      </c>
+      <c r="F103" s="53" t="s">
+        <v>463</v>
+      </c>
+      <c r="G103" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="H103" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="104" ht="82.5">
+      <c r="A104" s="54"/>
+      <c r="B104" s="52" t="s">
+        <v>473</v>
+      </c>
+      <c r="C104" s="52" t="s">
+        <v>474</v>
+      </c>
+      <c r="D104" s="53" t="s">
+        <v>475</v>
+      </c>
+      <c r="E104" s="53" t="s">
+        <v>476</v>
+      </c>
+      <c r="F104" s="53" t="s">
+        <v>477</v>
+      </c>
+      <c r="G104" s="51" t="s">
+        <v>343</v>
+      </c>
+      <c r="H104" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="105" ht="66">
+      <c r="A105" s="54"/>
+      <c r="B105" s="66" t="s">
+        <v>478</v>
+      </c>
+      <c r="C105" s="66" t="s">
+        <v>479</v>
+      </c>
+      <c r="D105" s="65" t="s">
+        <v>480</v>
+      </c>
+      <c r="E105" s="65" t="s">
+        <v>481</v>
+      </c>
+      <c r="F105" s="65" t="s">
+        <v>463</v>
+      </c>
+      <c r="G105" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H105" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="106" ht="66">
+      <c r="A106" s="54" t="s">
+        <v>482</v>
+      </c>
+      <c r="B106" s="52" t="s">
+        <v>483</v>
+      </c>
+      <c r="C106" s="52" t="s">
+        <v>484</v>
+      </c>
+      <c r="D106" s="53" t="s">
+        <v>485</v>
+      </c>
+      <c r="E106" s="53" t="s">
+        <v>486</v>
+      </c>
+      <c r="F106" s="53" t="s">
+        <v>487</v>
+      </c>
+      <c r="G106" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H106" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="107" ht="66">
+      <c r="A107" s="54"/>
+      <c r="B107" s="52" t="s">
+        <v>488</v>
+      </c>
+      <c r="C107" s="52" t="str">
+        <v>无线滑环通信失败</v>
+      </c>
+      <c r="D107" s="53" t="s">
+        <v>489</v>
+      </c>
+      <c r="E107" s="53" t="s">
+        <v>490</v>
+      </c>
+      <c r="F107" s="53" t="s">
+        <v>491</v>
+      </c>
+      <c r="G107" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H107" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="108" ht="66">
+      <c r="A108" s="54"/>
+      <c r="B108" s="66" t="s">
+        <v>492</v>
+      </c>
+      <c r="C108" s="66" t="str">
+        <v>无线配对信号不达标</v>
+      </c>
+      <c r="D108" s="65" t="s">
+        <v>493</v>
+      </c>
+      <c r="E108" s="65" t="s">
+        <v>494</v>
+      </c>
+      <c r="F108" s="65" t="s">
+        <v>491</v>
+      </c>
+      <c r="G108" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H108" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="109" ht="66">
+      <c r="A109" s="54"/>
+      <c r="B109" s="52" t="s">
+        <v>495</v>
+      </c>
+      <c r="C109" s="52" t="s">
+        <v>496</v>
+      </c>
+      <c r="D109" s="53" t="s">
+        <v>497</v>
+      </c>
+      <c r="E109" s="53" t="s">
+        <v>498</v>
+      </c>
+      <c r="F109" s="53" t="s">
+        <v>499</v>
+      </c>
+      <c r="G109" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H109" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="110" ht="66">
+      <c r="A110" s="54"/>
+      <c r="B110" s="66" t="s">
+        <v>500</v>
+      </c>
+      <c r="C110" s="66" t="s">
+        <v>501</v>
+      </c>
+      <c r="D110" s="65" t="s">
+        <v>502</v>
+      </c>
+      <c r="E110" s="65" t="s">
+        <v>503</v>
+      </c>
+      <c r="F110" s="65" t="s">
+        <v>491</v>
+      </c>
+      <c r="G110" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H110" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="111" ht="66">
+      <c r="A111" s="54"/>
+      <c r="B111" s="52" t="s">
+        <v>504</v>
+      </c>
+      <c r="C111" s="52" t="s">
+        <v>505</v>
+      </c>
+      <c r="D111" s="53" t="s">
+        <v>506</v>
+      </c>
+      <c r="E111" s="53" t="s">
+        <v>507</v>
+      </c>
+      <c r="F111" s="53" t="s">
+        <v>508</v>
+      </c>
+      <c r="G111" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H111" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="112" ht="66">
+      <c r="A112" s="54"/>
+      <c r="B112" s="66" t="s">
+        <v>509</v>
+      </c>
+      <c r="C112" s="66" t="s">
+        <v>510</v>
+      </c>
+      <c r="D112" s="65" t="s">
+        <v>511</v>
+      </c>
+      <c r="E112" s="65" t="s">
+        <v>512</v>
+      </c>
+      <c r="F112" s="65" t="s">
+        <v>513</v>
+      </c>
+      <c r="G112" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H112" s="47" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="113" ht="82.5">
+      <c r="A113" s="54"/>
+      <c r="B113" s="52" t="s">
+        <v>515</v>
+      </c>
+      <c r="C113" s="52" t="str">
+        <v>无线扫描未发现设备</v>
+      </c>
+      <c r="D113" s="53" t="s">
+        <v>516</v>
+      </c>
+      <c r="E113" s="53" t="s">
+        <v>517</v>
+      </c>
+      <c r="F113" s="53" t="s">
+        <v>518</v>
+      </c>
+      <c r="G113" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H113" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="114" ht="82.5">
+      <c r="A114" s="54"/>
+      <c r="B114" s="52" t="s">
+        <v>519</v>
+      </c>
+      <c r="C114" s="52" t="s">
+        <v>520</v>
+      </c>
+      <c r="D114" s="53" t="s">
+        <v>521</v>
+      </c>
+      <c r="E114" s="53" t="s">
+        <v>522</v>
+      </c>
+      <c r="F114" s="53" t="s">
+        <v>523</v>
+      </c>
+      <c r="G114" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H114" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="115" ht="66">
+      <c r="A115" s="54"/>
+      <c r="B115" s="52" t="s">
+        <v>524</v>
+      </c>
+      <c r="C115" s="52" t="s">
+        <v>525</v>
+      </c>
+      <c r="D115" s="53" t="s">
+        <v>526</v>
+      </c>
+      <c r="E115" s="53" t="s">
+        <v>527</v>
+      </c>
+      <c r="F115" s="53" t="s">
+        <v>528</v>
+      </c>
+      <c r="G115" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H115" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="116" ht="82.5">
+      <c r="A116" s="54"/>
+      <c r="B116" s="52" t="s">
+        <v>529</v>
+      </c>
+      <c r="C116" s="52" t="s">
+        <v>530</v>
+      </c>
+      <c r="D116" s="53" t="s">
+        <v>531</v>
+      </c>
+      <c r="E116" s="53" t="s">
+        <v>532</v>
+      </c>
+      <c r="F116" s="53" t="s">
+        <v>533</v>
+      </c>
+      <c r="G116" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H116" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="117" ht="66">
+      <c r="A117" s="54"/>
+      <c r="B117" s="52" t="s">
+        <v>534</v>
+      </c>
+      <c r="C117" s="52" t="s">
+        <v>535</v>
+      </c>
+      <c r="D117" s="53" t="s">
+        <v>536</v>
+      </c>
+      <c r="E117" s="53" t="s">
+        <v>537</v>
+      </c>
+      <c r="F117" s="53" t="s">
+        <v>538</v>
+      </c>
+      <c r="G117" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H117" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="118" ht="82.5">
+      <c r="A118" s="54"/>
+      <c r="B118" s="52" t="s">
+        <v>539</v>
+      </c>
+      <c r="C118" s="52" t="s">
+        <v>540</v>
+      </c>
+      <c r="D118" s="53" t="s">
+        <v>541</v>
+      </c>
+      <c r="E118" s="53" t="s">
+        <v>542</v>
+      </c>
+      <c r="F118" s="53" t="s">
+        <v>543</v>
+      </c>
+      <c r="G118" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H118" s="47" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="119" ht="82.5">
+      <c r="A119" s="54" t="s">
+        <v>545</v>
+      </c>
+      <c r="B119" s="52" t="s">
+        <v>546</v>
+      </c>
+      <c r="C119" s="52" t="s">
+        <v>547</v>
+      </c>
+      <c r="D119" s="53" t="s">
+        <v>548</v>
+      </c>
+      <c r="E119" s="53" t="s">
+        <v>549</v>
+      </c>
+      <c r="F119" s="53" t="s">
+        <v>550</v>
+      </c>
+      <c r="G119" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H119" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="120" ht="82.5">
+      <c r="A120" s="54"/>
+      <c r="B120" s="52" t="s">
+        <v>551</v>
+      </c>
+      <c r="C120" s="52" t="s">
+        <v>552</v>
+      </c>
+      <c r="D120" s="53" t="s">
+        <v>553</v>
+      </c>
+      <c r="E120" s="53" t="s">
+        <v>554</v>
+      </c>
+      <c r="F120" s="53" t="s">
+        <v>555</v>
+      </c>
+      <c r="G120" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H120" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="121" ht="82.5">
+      <c r="A121" s="54"/>
+      <c r="B121" s="52" t="s">
+        <v>556</v>
+      </c>
+      <c r="C121" s="52" t="s">
+        <v>557</v>
+      </c>
+      <c r="D121" s="53" t="s">
+        <v>558</v>
+      </c>
+      <c r="E121" s="53" t="s">
+        <v>559</v>
+      </c>
+      <c r="F121" s="53" t="s">
+        <v>560</v>
+      </c>
+      <c r="G121" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H121" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="122" ht="66">
+      <c r="A122" s="54"/>
+      <c r="B122" s="52" t="s">
+        <v>561</v>
+      </c>
+      <c r="C122" s="52" t="s">
+        <v>562</v>
+      </c>
+      <c r="D122" s="53" t="s">
+        <v>563</v>
+      </c>
+      <c r="E122" s="53" t="s">
+        <v>564</v>
+      </c>
+      <c r="F122" s="53" t="s">
+        <v>565</v>
+      </c>
+      <c r="G122" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H122" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="123" ht="66">
+      <c r="A123" s="54"/>
+      <c r="B123" s="66" t="s">
+        <v>566</v>
+      </c>
+      <c r="C123" s="66" t="s">
+        <v>567</v>
+      </c>
+      <c r="D123" s="65" t="s">
+        <v>568</v>
+      </c>
+      <c r="E123" s="65" t="s">
+        <v>569</v>
+      </c>
+      <c r="F123" s="65" t="s">
+        <v>570</v>
+      </c>
+      <c r="G123" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H123" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="124" ht="66">
+      <c r="A124" s="54"/>
+      <c r="B124" s="66" t="s">
+        <v>571</v>
+      </c>
+      <c r="C124" s="66" t="s">
+        <v>572</v>
+      </c>
+      <c r="D124" s="65" t="s">
+        <v>573</v>
+      </c>
+      <c r="E124" s="65" t="s">
+        <v>574</v>
+      </c>
+      <c r="F124" s="65" t="s">
+        <v>575</v>
+      </c>
+      <c r="G124" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H124" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="125" ht="66">
+      <c r="A125" s="54"/>
+      <c r="B125" s="52" t="s">
+        <v>576</v>
+      </c>
+      <c r="C125" s="52" t="str">
+        <v>主控与模拟量输出模块通信失败</v>
+      </c>
+      <c r="D125" s="53" t="s">
+        <v>577</v>
+      </c>
+      <c r="E125" s="53" t="s">
+        <v>578</v>
+      </c>
+      <c r="F125" s="53" t="s">
+        <v>579</v>
+      </c>
+      <c r="G125" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H125" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="126" ht="82.5">
+      <c r="A126" s="54"/>
+      <c r="B126" s="52" t="s">
+        <v>580</v>
+      </c>
+      <c r="C126" s="52" t="s">
+        <v>581</v>
+      </c>
+      <c r="D126" s="53" t="s">
+        <v>582</v>
+      </c>
+      <c r="E126" s="53" t="s">
+        <v>583</v>
+      </c>
+      <c r="F126" s="53" t="s">
+        <v>584</v>
+      </c>
+      <c r="G126" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H126" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="127" ht="82.5">
+      <c r="A127" s="54"/>
+      <c r="B127" s="52" t="s">
+        <v>585</v>
+      </c>
+      <c r="C127" s="52" t="s">
+        <v>586</v>
+      </c>
+      <c r="D127" s="53" t="s">
+        <v>587</v>
+      </c>
+      <c r="E127" s="53" t="s">
+        <v>588</v>
+      </c>
+      <c r="F127" s="53" t="s">
+        <v>589</v>
+      </c>
+      <c r="G127" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H127" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="128" ht="82.5">
+      <c r="A128" s="54"/>
+      <c r="B128" s="52" t="s">
+        <v>590</v>
+      </c>
+      <c r="C128" s="52" t="s">
+        <v>591</v>
+      </c>
+      <c r="D128" s="53" t="s">
+        <v>592</v>
+      </c>
+      <c r="E128" s="53" t="s">
+        <v>593</v>
+      </c>
+      <c r="F128" s="53" t="s">
+        <v>594</v>
+      </c>
+      <c r="G128" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H128" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="129" ht="82.5">
+      <c r="A129" s="54" t="s">
+        <v>595</v>
+      </c>
+      <c r="B129" s="52" t="s">
+        <v>596</v>
+      </c>
+      <c r="C129" s="52" t="str">
+        <v>内部数据空间不足</v>
+      </c>
+      <c r="D129" s="53" t="s">
+        <v>597</v>
+      </c>
+      <c r="E129" s="53" t="s">
+        <v>598</v>
+      </c>
+      <c r="F129" s="53" t="s">
+        <v>599</v>
+      </c>
+      <c r="G129" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H129" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="130" ht="99">
+      <c r="A130" s="54"/>
+      <c r="B130" s="52" t="s">
+        <v>600</v>
+      </c>
+      <c r="C130" s="52" t="s">
+        <v>601</v>
+      </c>
+      <c r="D130" s="53" t="s">
+        <v>602</v>
+      </c>
+      <c r="E130" s="53" t="s">
+        <v>603</v>
+      </c>
+      <c r="F130" s="53" t="s">
+        <v>604</v>
+      </c>
+      <c r="G130" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H130" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="131" ht="82.5">
+      <c r="A131" s="54"/>
+      <c r="B131" s="52" t="s">
+        <v>605</v>
+      </c>
+      <c r="C131" s="52" t="s">
+        <v>606</v>
+      </c>
+      <c r="D131" s="53" t="s">
+        <v>607</v>
+      </c>
+      <c r="E131" s="53" t="s">
+        <v>608</v>
+      </c>
+      <c r="F131" s="53" t="s">
+        <v>609</v>
+      </c>
+      <c r="G131" s="51" t="s">
+        <v>26</v>
+      </c>
+      <c r="H131" s="47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="132" ht="115.5">
+      <c r="A132" s="56" t="s">
+        <v>610</v>
+      </c>
+      <c r="B132" s="66" t="s">
+        <v>611</v>
+      </c>
+      <c r="C132" s="66" t="s">
+        <v>612</v>
+      </c>
+      <c r="D132" s="65" t="s">
+        <v>613</v>
+      </c>
+      <c r="E132" s="65" t="s">
+        <v>614</v>
+      </c>
+      <c r="F132" s="65" t="s">
+        <v>615</v>
+      </c>
+      <c r="G132" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="H132" s="58" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="133" ht="132">
+      <c r="A133" s="56"/>
+      <c r="B133" s="59" t="s">
+        <v>616</v>
+      </c>
+      <c r="C133" s="59" t="str">
+        <v>电源采样数据处理不及时</v>
+      </c>
+      <c r="D133" s="60" t="s">
+        <v>617</v>
+      </c>
+      <c r="E133" s="60" t="s">
+        <v>618</v>
+      </c>
+      <c r="F133" s="60" t="s">
+        <v>619</v>
+      </c>
+      <c r="G133" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="H133" s="58" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="134" ht="132">
+      <c r="A134" s="56"/>
+      <c r="B134" s="59" t="s">
+        <v>620</v>
+      </c>
+      <c r="C134" s="59" t="str">
+        <v>电源采样传输意外停止</v>
+      </c>
+      <c r="D134" s="60" t="s">
+        <v>621</v>
+      </c>
+      <c r="E134" s="60" t="s">
+        <v>622</v>
+      </c>
+      <c r="F134" s="60" t="s">
+        <v>623</v>
+      </c>
+      <c r="G134" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="H134" s="58" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="135" ht="115.5">
+      <c r="A135" s="56"/>
+      <c r="B135" s="59" t="s">
+        <v>624</v>
+      </c>
+      <c r="C135" s="59" t="str">
+        <v>电源采样启动失败</v>
+      </c>
+      <c r="D135" s="60" t="s">
+        <v>625</v>
+      </c>
+      <c r="E135" s="60" t="s">
+        <v>626</v>
+      </c>
+      <c r="F135" s="60" t="s">
+        <v>627</v>
+      </c>
+      <c r="G135" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="H135" s="58" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="136" ht="99">
+      <c r="A136" s="56"/>
+      <c r="B136" s="59" t="s">
+        <v>628</v>
+      </c>
+      <c r="C136" s="59" t="str">
+        <v>电源采样连续恢复失败</v>
+      </c>
+      <c r="D136" s="60" t="s">
+        <v>629</v>
+      </c>
+      <c r="E136" s="60" t="s">
+        <v>630</v>
+      </c>
+      <c r="F136" s="60" t="s">
+        <v>631</v>
+      </c>
+      <c r="G136" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="H136" s="58" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="137" ht="165">
+      <c r="A137" s="56"/>
+      <c r="B137" s="69" t="s">
+        <v>632</v>
+      </c>
+      <c r="C137" s="69" t="s">
+        <v>633</v>
+      </c>
+      <c r="D137" s="68" t="s">
+        <v>634</v>
+      </c>
+      <c r="E137" s="68" t="s">
+        <v>635</v>
+      </c>
+      <c r="F137" s="68" t="s">
+        <v>636</v>
+      </c>
+      <c r="G137" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="H137" s="58" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="138" ht="120" customHeight="1">
+      <c r="A138" t="str" s="56">
+        <v>测量过程</v>
+      </c>
+      <c r="B138" t="str" s="59">
+        <v>15-34</v>
+      </c>
+      <c r="C138" t="inlineStr" s="59">
+        <is>
+          <t>液位定时矫正失败</t>
+        </is>
+      </c>
+      <c r="D138" t="str" s="60">
+        <v>触发：周期更新无法取得可用基准或重新稳定，且无法有效返回当前液面；或连续3轮更新失败。
+影响：停止当前跟随，旧液位不再作为正常测量结果。</v>
+      </c>
+      <c r="E138" t="str" s="60">
+        <v>1、空气与油中频率区分不足，或固定目标已不在有效窗口内。
+2、液面持续变化，规定时间内不能完成稳定定位。
+3、可用旧基准不足或回退失败。</v>
+      </c>
+      <c r="F138" t="str" s="60">
+        <v>1、保存刷新前后频率、各阶段用时和失败记录。
+2、先检查探头、液面工况和运动空间，再停机核对液位方法及目标参数。
+3、排除原因后重新找液位；台架确认成功前保持周期刷新关闭。有具体通信或电机故障时先按对应故障处理。</v>
+      </c>
+      <c r="G138" t="str" s="61">
+        <v>使用中</v>
+      </c>
+      <c r="H138" t="str" s="58">
+        <v>CPU2 V1.43.0.0 / CPU3 V1.42.0.0起；共享协议36</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells>
+    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="A17:A27"/>
+    <mergeCell ref="A28:A65"/>
+    <mergeCell ref="A66:A71"/>
+    <mergeCell ref="A72:A89"/>
+    <mergeCell ref="A90:A99"/>
+    <mergeCell ref="A100:A105"/>
+    <mergeCell ref="A106:A118"/>
+    <mergeCell ref="A119:A128"/>
+    <mergeCell ref="A129:A131"/>
+    <mergeCell ref="A132:A137"/>
+  </mergeCells>
+  <conditionalFormatting sqref="G2:G73">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="between" text="使用中">
+      <formula>NOT(ISERROR(SEARCH("使用中",G2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="between" text="保留">
+      <formula>NOT(ISERROR(SEARCH("保留",G2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>

--- a/docs/00_构建与版本/故障码/LTD故障代码统一表.xlsx
+++ b/docs/00_构建与版本/故障码/LTD故障代码统一表.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2159" count="4495">
   <x:si>
     <x:t xml:space="preserve">设备故障代码及参数资料</x:t>
   </x:si>
@@ -7008,13 +7008,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="4">
+  <x:numFmts count="5">
     <x:numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <x:numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <x:numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <x:numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <x:numFmt numFmtId="200" formatCode="@"/>
   </x:numFmts>
-  <x:fonts count="50">
+  <x:fonts count="57">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -7287,8 +7288,44 @@
       <x:color rgb="FF7F6000"/>
       <x:name val="微软雅黑"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF222222"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF222222"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF9C2424"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF245B85"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF222222"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="52">
+  <x:fills count="57">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -7545,8 +7582,33 @@
         <x:fgColor rgb="FFF7FAFC"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF245B85"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF3F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF2F2F2"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="16">
+  <x:borders count="25">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -7716,6 +7778,111 @@
         <x:color theme="4"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color auto="1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color auto="1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DFE5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFB8C7D5"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DFE5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color auto="1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DFE5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color auto="1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color auto="1"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF96ADBE"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DFE5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFB8C7D5"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF96ADBE"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DFE5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color auto="1"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF96ADBE"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DFE5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB8C7D5"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color auto="1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color auto="1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DFE5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB8C7D5"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color auto="1"/>
+      </x:right>
+      <x:top style="medium">
+        <x:color rgb="FF96ADBE"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DFE5"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:bottom style="thin">
+        <x:color rgb="FFD7DFE5"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="50">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -7867,7 +8034,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="83">
+  <x:cellXfs count="181">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8094,6 +8261,292 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="51" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="52" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="22" fillId="52" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="52" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="52" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="48" fillId="52" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="52" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="52" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="24" fillId="52" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="23" fillId="52" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="25" fillId="52" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="26" fillId="52" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="52" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="52" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="27" fillId="52" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="28" fillId="52" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="49" fillId="52" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="53" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="53" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="53" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="53" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="53" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="53" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="53" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="53" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="53" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="53" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="53" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="53" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="50" fillId="52" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="50" fillId="52" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="50" fillId="52" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="54" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="51" fillId="52" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="51" fillId="52" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="51" fillId="55" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="51" fillId="55" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="54" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="51" fillId="55" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="51" fillId="55" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="52" fillId="52" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="52" fillId="52" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="56" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="50" fillId="56" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="56" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="56" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="51" fillId="56" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="52" fillId="55" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="52" fillId="55" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="50" fillId="52" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="52" fillId="55" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="52" fillId="55" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="52" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="50" fillId="52" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="50" fillId="54" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="51" fillId="52" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="51" fillId="52" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="51" fillId="55" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="51" fillId="55" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="52" fillId="55" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="52" fillId="55" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="54" fillId="54" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="55" fillId="54" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="51" fillId="50" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="56" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="51" fillId="50" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="51" fillId="53" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="53" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="50">
@@ -8546,8 +8999,8 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="15.633333206176758" customWidth="1"/>
-    <x:col min="2" max="2" width="90" customWidth="1"/>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="104" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28.5" customHeight="1">
@@ -8558,7 +9011,7 @@
     </x:row>
     <x:row r="2" ht="20.25" customHeight="1">
       <x:c r="A2" s="11" t="str">
-        <x:v>正式资料｜2026-08-14</x:v>
+        <x:v>正式资料 | 故障表核对日期：2026-09-07</x:v>
       </x:c>
       <x:c r="B2" s="11"/>
     </x:row>
@@ -8574,7 +9027,7 @@
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="31.5" customHeight="1">
+    <x:row r="5" ht="38" customHeight="1">
       <x:c r="A5" s="14" t="s">
         <x:v>3</x:v>
       </x:c>
@@ -8582,23 +9035,23 @@
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="31.5" customHeight="1">
+    <x:row r="6" ht="38" customHeight="1">
       <x:c r="A6" s="14" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="16" t="str">
-        <x:v>137项：135个主控单元共享故障，2个显示单元本机故障；其中使用中134项，保留3项。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="31.5" customHeight="1">
-      <x:c r="A7" s="14" t="s">
-        <x:v>6</x:v>
+        <x:v>主表137项：135个CPU2共享故障、2个CPU3本机故障；使用中134项、保留3项。12-17已归入主表。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="38" customHeight="1">
+      <x:c r="A7" s="14" t="str">
+        <x:v>故障表核对版本</x:v>
       </x:c>
       <x:c r="B7" s="16" t="str">
-        <x:v>适用于CPU2 V1.40.0.0、CPU3 V1.40.0.0及共享协议34；12-6、12-17为使用中，12-13保留定义与显示映射，LIN仅作ENC?诊断统计。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="31.5" customHeight="1">
+        <x:v>CPU2 V1.42.11.0、CPU3 V1.41.0.0、共享协议35。现场先核对实际固件版本，再按编号查表。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="38" customHeight="1">
       <x:c r="A8" s="14" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -8606,7 +9059,7 @@
         <x:v>8</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="31.5" customHeight="1">
+    <x:row r="9" ht="38" customHeight="1">
       <x:c r="A9" s="14" t="s">
         <x:v>9</x:v>
       </x:c>
@@ -8614,12 +9067,52 @@
         <x:v>10</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="31.5" customHeight="1">
+    <x:row r="10" ht="42" customHeight="1">
       <x:c r="A10" s="14" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B10" s="16" t="str">
-        <x:v>协议34在协议33口径上启用编码器上电位置跳变并新增运行位置跳变故障；12-13保留定义和显示映射，LIN及方向不一致仅作诊断统计。CPU2与CPU3必须保持共享协议版本匹配，现场记录按对应CPU2程序版本查询。</x:v>
+        <x:v>CPU2与CPU3应使用配套的共享协议。旧固件按对应历史资料查询；协议34起启用12-6、12-17，12-13仍保留定义，仅作诊断统计。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="38" customHeight="1">
+      <x:c r="A11" s="175" t="str">
+        <x:v>阅读说明</x:v>
+      </x:c>
+      <x:c r="B11" s="173" t="str">
+        <x:v>“故障原因”列列出的是可能原因，不代表某个部件已经确认损坏。先看故障说明，再按处理方法逐项排查。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="175" t="str">
+        <x:v>恢复操作</x:v>
+      </x:c>
+      <x:c r="B12" s="173" t="str">
+        <x:v>部分故障可按设置自动重试，取决于原操作、故障类型和恢复参数；不能把自动重试等同于已修复。涉及短路、堵转、过温、位置不可信时，先停机排查。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="175" t="str">
+        <x:v>重点标记</x:v>
+      </x:c>
+      <x:c r="B13" s="173" t="str">
+        <x:v>黄色底色、加粗编号和名称表示现场优先排查，不是发生率统计。红色编号和名称表示需先排除风险；灰色行表示保留码。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="42" customHeight="1">
+      <x:c r="A14" s="175" t="str">
+        <x:v>检修注意</x:v>
+      </x:c>
+      <x:c r="B14" s="173" t="str">
+        <x:v>检查接线或机构前，按现场规程停止操作并隔离能量。模拟输出检查应先与接收端协调。重启前保留必要日志；不得擅自恢复出厂、屏蔽保护或扩大运动边界。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="175" t="str">
+        <x:v>资料范围</x:v>
+      </x:c>
+      <x:c r="B15" s="173" t="str">
+        <x:v>本次更新故障主表、简介及新增码收录说明。设备参数、测量结果及历史页保持各自原有版本口径；文档核对不代替现场故障验证。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8635,3395 +9128,4184 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="24.75"/>
   <cols>
-    <col min="1" max="1" width="4.875" style="42" customWidth="1"/>
-    <col min="2" max="2" width="7.875" style="43" customWidth="1"/>
-    <col min="3" max="3" width="13.875" style="43" customWidth="1"/>
-    <col min="4" max="4" width="37.125" style="43" customWidth="1"/>
-    <col min="5" max="5" width="47.875" style="43" customWidth="1"/>
-    <col min="6" max="6" width="35" style="43" customWidth="1"/>
-    <col min="7" max="7" width="9.383333206176758" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="23.75" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="14" style="42" customWidth="1"/>
+    <col min="2" max="2" width="10" style="43" customWidth="1"/>
+    <col min="3" max="3" width="23" style="43" customWidth="1"/>
+    <col min="4" max="4" width="43" style="43" customWidth="1"/>
+    <col min="5" max="5" width="42" style="43" customWidth="1"/>
+    <col min="6" max="6" width="53" style="43" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1" s="45" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" s="47" t="s">
-        <v>19</v>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="127" t="str">
+        <v>类别</v>
+      </c>
+      <c r="B1" s="127" t="str">
+        <v>故障代码</v>
+      </c>
+      <c r="C1" s="127" t="str">
+        <v>故障名称</v>
+      </c>
+      <c r="D1" s="127" t="str">
+        <v>故障说明</v>
+      </c>
+      <c r="E1" s="127" t="str">
+        <v>故障原因</v>
+      </c>
+      <c r="F1" s="127" t="str">
+        <v>处理方法</v>
+      </c>
+      <c r="G1" s="128" t="str">
+        <v>状态</v>
+      </c>
+      <c r="H1" s="129" t="str">
+        <v>产生端/适用范围</v>
       </c>
     </row>
-    <row r="2" ht="66">
-      <c r="A2" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="66" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="66" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="65" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="65" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="47" t="s">
-        <v>27</v>
+    <row r="2" ht="76" customHeight="1">
+      <c r="A2" s="141" t="str">
+        <v>电机驱动</v>
+      </c>
+      <c r="B2" s="142" t="str">
+        <v>11-2</v>
+      </c>
+      <c r="C2" s="143" t="str">
+        <v>电机驱动通信异常</v>
+      </c>
+      <c r="D2" s="144" t="str">
+        <v>触发：主控板多次没能读取或下发电机驱动状态。
+影响：不能确认驱动器是否正常及运动参数是否生效，所以停止这次运动。</v>
+      </c>
+      <c r="E2" s="144" t="str">
+        <v>1、驱动板供电不稳，或主控与驱动板连接松动。
+2、电机启停干扰较强，或驱动板通信接口异常。</v>
+      </c>
+      <c r="F2" s="144" t="str">
+        <v>1、停止运动，检查驱动板供电和板间连接。
+2、观察故障是否总在电机启动时出现，确认驱动状态可以连续读到后再试运行。
+3、仍报错时保存驱动通信日志，再检查主控和驱动板。</v>
+      </c>
+      <c r="G2" s="145" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H2" s="146" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="3" ht="66">
-      <c r="A3" s="48"/>
-      <c r="B3" s="66" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="66" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="65" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" s="65" t="s">
-        <v>31</v>
-      </c>
-      <c r="F3" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="47" t="s">
-        <v>27</v>
+    <row r="3" ht="87" customHeight="1">
+      <c r="A3" s="136" t="str">
+        <v>电机驱动</v>
+      </c>
+      <c r="B3" s="139" t="str">
+        <v>11-3</v>
+      </c>
+      <c r="C3" s="140" t="str">
+        <v>电机驱动配置丢失</v>
+      </c>
+      <c r="D3" s="132" t="str">
+        <v>触发：设备仍可读取驱动器。
+影响：关键运动配置变为空值或与启动时不一致，当前电流、速度和运动保护不能确认，设备停止运动。</v>
+      </c>
+      <c r="E3" s="132" t="str">
+        <v>1、驱动板发生掉电或复位，原有运动设置丢失。
+2、供电接触不良、强干扰或驱动板异常。</v>
+      </c>
+      <c r="F3" s="132" t="str">
+        <v>1、停止操作，记录故障前是否发生掉电或重启。
+2、检查驱动供电和连接，排除问题后重新上电完成驱动初始化。
+3、确认设置不再丢失后短程试运行；再次丢失时检修驱动板。</v>
+      </c>
+      <c r="G3" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H3" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="4" ht="66">
-      <c r="A4" s="48"/>
-      <c r="B4" s="66" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="66" t="str">
+    <row r="4" ht="87" customHeight="1">
+      <c r="A4" s="136" t="str">
+        <v>电机驱动</v>
+      </c>
+      <c r="B4" s="139" t="str">
+        <v>11-4</v>
+      </c>
+      <c r="C4" s="140" t="str">
         <v>电机驱动电流未建立</v>
       </c>
-      <c r="D4" s="65" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="65" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="47" t="s">
-        <v>27</v>
+      <c r="D4" s="132" t="str">
+        <v>触发：设备能够与电机驱动器联系。
+影响：驱动输出未建立或驱动器尚未完成启动，电机不能按指令运动。</v>
+      </c>
+      <c r="E4" s="132" t="str">
+        <v>1、驱动供电或使能连接异常。
+2、驱动尚未就绪，或上次保护未解除。</v>
+      </c>
+      <c r="F4" s="132" t="str">
+        <v>1、停止运动，先检查是否同时出现过温、短路等驱动故障。
+2、检查驱动供电和使能连接，确认初始化完成。
+3、保护原因排除、驱动就绪后再短程测试，不要靠反复启动碰运气。</v>
+      </c>
+      <c r="G4" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H4" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="5" ht="66">
-      <c r="A5" s="48"/>
-      <c r="B5" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="49" t="str">
+    <row r="5" ht="87" customHeight="1">
+      <c r="A5" s="136" t="str">
+        <v>电机驱动</v>
+      </c>
+      <c r="B5" s="147" t="str">
+        <v>11-5</v>
+      </c>
+      <c r="C5" s="148" t="str">
         <v>电机驱动故障类型未知</v>
       </c>
-      <c r="D5" s="50" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="50" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="47" t="s">
-        <v>27</v>
+      <c r="D5" s="132" t="str">
+        <v>触发：驱动器报告有故障。
+影响：返回状态不属于设备已识别的过温、短路、断线或堵转等类型，不能进一步判断，设备停止运动。</v>
+      </c>
+      <c r="E5" s="132" t="str">
+        <v>1、驱动器返回了未能进一步分类的异常状态。
+2、可能与供电波动、间歇性接触不良或驱动板内部异常有关。</v>
+      </c>
+      <c r="F5" s="132" t="str">
+        <v>注意：先排除风险，再恢复操作。
+1、保持停机，先保存驱动器返回的原始状态。
+2、检查驱动供电、电机接线和机构是否卡阻。
+3、不要直接认定为某一种硬件损坏；由技术人员结合状态记录定位后再运行。</v>
+      </c>
+      <c r="G5" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H5" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="6" ht="66">
-      <c r="A6" s="48"/>
-      <c r="B6" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="66" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="65" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="65" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="47" t="s">
-        <v>27</v>
+    <row r="6" ht="87" customHeight="1">
+      <c r="A6" s="136" t="str">
+        <v>电机驱动</v>
+      </c>
+      <c r="B6" s="139" t="str">
+        <v>11-10</v>
+      </c>
+      <c r="C6" s="140" t="str">
+        <v>电机无有效位移</v>
+      </c>
+      <c r="D6" s="132" t="str">
+        <v>发出运动指令后，位置监测没有达到有效位移要求，这次动作失败。位置记录不能单独证明电机或尺带是否实际移动。</v>
+      </c>
+      <c r="E6" s="132" t="str">
+        <v>1、驱动没有正常执行运动，或点动条件不合适。
+2、机构、传动或位置反馈存在异常，需要结合实际运动确认。</v>
+      </c>
+      <c r="F6" s="132" t="str">
+        <v>1、停止重复启动，对照运动指令、位置记录和机构实际动作。
+2、检查驱动供电、运动距离及相关位置反馈。
+3、排除问题后做受控短程测试，确认实际运动与位置记录一致。</v>
+      </c>
+      <c r="G6" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H6" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="7" ht="66">
-      <c r="A7" s="48"/>
-      <c r="B7" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="50" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="50" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" s="47" t="s">
-        <v>27</v>
+    <row r="7" ht="87" customHeight="1">
+      <c r="A7" s="136" t="str">
+        <v>电机驱动</v>
+      </c>
+      <c r="B7" s="147" t="str">
+        <v>11-11</v>
+      </c>
+      <c r="C7" s="148" t="str">
+        <v>电机堵转</v>
+      </c>
+      <c r="D7" s="132" t="str">
+        <v>电机驱动器报告堵转状态，设备停止当前动作。这个码表示驱动器作出了堵转判定，还需要现场确认是机构卡住、负载过大还是驱动设置问题。</v>
+      </c>
+      <c r="E7" s="132" t="str">
+        <v>1、浮子、尺带、卷筒或导向机构卡住，或负载阻力过大。
+2、驱动力、速度等设置不合适，也可能触发驱动器的堵转判定。</v>
+      </c>
+      <c r="F7" s="132" t="str">
+        <v>注意：先排除风险，再恢复操作。
+1、不要反复强行启动，先停机并确认机构可以安全检查。
+2、检查浮子、尺带、卷筒和导向机构，再核对驱动设置。
+3、排除卡阻和设置问题后做短程测试；仍报错时保存驱动状态和运动日志。</v>
+      </c>
+      <c r="G7" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H7" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="8" ht="82.5">
-      <c r="A8" s="48"/>
-      <c r="B8" s="49" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="49" t="str">
+    <row r="8" ht="76" customHeight="1">
+      <c r="A8" s="136" t="str">
+        <v>电机驱动</v>
+      </c>
+      <c r="B8" s="133" t="str">
+        <v>11-16</v>
+      </c>
+      <c r="C8" s="132" t="str">
         <v>电机驱动内部升压不足</v>
       </c>
-      <c r="D8" s="50" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>51</v>
-      </c>
-      <c r="F8" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="47" t="s">
-        <v>27</v>
+      <c r="D8" s="132" t="str">
+        <v>触发：电机驱动器内部升压电源低于正常范围，驱动能力不足。
+影响：继续运行可能造成失步或停转。</v>
+      </c>
+      <c r="E8" s="132" t="str">
+        <v>1、驱动供电偏低，或启动时压降明显。
+2、端子接触不良、线路压降过大，或驱动板升压电路异常。</v>
+      </c>
+      <c r="F8" s="132" t="str">
+        <v>1、停止运动，测量驱动板输入端电压，重点观察启动瞬间。
+2、检查电源容量、端子和线缆，再检查机构负载。
+3、供电稳定后短程测试；输入正常仍报错时检修驱动板。</v>
+      </c>
+      <c r="G8" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H8" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="9" ht="82.5">
-      <c r="A9" s="48"/>
-      <c r="B9" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="50" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="50" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="50" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="47" t="s">
-        <v>27</v>
+    <row r="9" ht="87" customHeight="1">
+      <c r="A9" s="136" t="str">
+        <v>电机驱动</v>
+      </c>
+      <c r="B9" s="147" t="str">
+        <v>11-17</v>
+      </c>
+      <c r="C9" s="148" t="str">
+        <v>电机驱动过温关断</v>
+      </c>
+      <c r="D9" s="132" t="str">
+        <v>触发：电机驱动器温度已经达到保护上限并关闭输出，电机不能继续运行。
+影响：设备停止这次动作，避免驱动器和电机进一步受热损坏。</v>
+      </c>
+      <c r="E9" s="132" t="str">
+        <v>1、机构阻力或驱动电流偏大，连续运行时间过长。
+2、环境温度高、散热不良，或驱动板异常。</v>
+      </c>
+      <c r="F9" s="132" t="str">
+        <v>注意：先排除风险，再恢复操作。
+1、保持停机并等待冷却，不要反复上电强行运行。
+2、检查机构阻力、驱动电流设置和散热条件。
+3、温度恢复且原因排除后短程测试；很快再次过温时停用检修。</v>
+      </c>
+      <c r="G9" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H9" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="10" ht="82.5">
-      <c r="A10" s="48"/>
-      <c r="B10" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="D10" s="50" t="s">
-        <v>59</v>
-      </c>
-      <c r="E10" s="50" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="50" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="47" t="s">
-        <v>27</v>
+    <row r="10" ht="76" customHeight="1">
+      <c r="A10" s="136" t="str">
+        <v>电机驱动</v>
+      </c>
+      <c r="B10" s="133" t="str">
+        <v>11-18</v>
+      </c>
+      <c r="C10" s="132" t="str">
+        <v>电机整段运行超时</v>
+      </c>
+      <c r="D10" s="132" t="str">
+        <v>触发：设备连续运行时间超过这次运动允许上限。
+影响：还是没有完成整段运动，系统停止电机并结束这次操作。</v>
+      </c>
+      <c r="E10" s="132" t="str">
+        <v>1、运动距离、速度或允许时间不匹配。
+2、运行中有卡涩、打滑或驱动出力不足，导致动作迟迟不能完成。</v>
+      </c>
+      <c r="F10" s="132" t="str">
+        <v>1、停止运动，记录起点、目标位置、速度和已运行时间。
+2、检查尺带、卷筒及导向机构，核对距离和速度设置。
+3、排除原因后重新执行；不要仅放宽超时来掩盖机构问题。</v>
+      </c>
+      <c r="G10" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H10" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="11" ht="66">
-      <c r="A11" s="48"/>
-      <c r="B11" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="C11" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" s="50" t="s">
-        <v>64</v>
-      </c>
-      <c r="E11" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="F11" s="50" t="s">
-        <v>66</v>
-      </c>
-      <c r="G11" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="47" t="s">
-        <v>27</v>
+    <row r="11" ht="102" customHeight="1">
+      <c r="A11" s="136" t="str">
+        <v>电机驱动</v>
+      </c>
+      <c r="B11" s="147" t="str">
+        <v>11-19</v>
+      </c>
+      <c r="C11" s="148" t="str">
+        <v>电机相线短路</v>
+      </c>
+      <c r="D11" s="132" t="str">
+        <v>触发：驱动器检测到电机相线之间或相线对地存在短路，已停止输出。
+影响：继续送电可能损坏驱动器、电机或线缆。</v>
+      </c>
+      <c r="E11" s="132" t="str">
+        <v>1、电机线缆破损、端子进水或裸线搭接。
+2、电机绕组或驱动输出电路异常。</v>
+      </c>
+      <c r="F11" s="132" t="str">
+        <v>注意：先排除风险，再恢复操作。
+1、断电后检查相线、端子和绝缘，不要带故障继续送电。
+2、绝缘测试前按检修规程断开电子板，分别检查线缆和电机。
+3、确认没有短路后再接回驱动器测试；仍异常时检修驱动板。</v>
+      </c>
+      <c r="G11" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H11" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="12" ht="66">
-      <c r="A12" s="48"/>
-      <c r="B12" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" s="50" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="50" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="47" t="s">
-        <v>27</v>
+    <row r="12" ht="76" customHeight="1">
+      <c r="A12" s="136" t="str">
+        <v>电机驱动</v>
+      </c>
+      <c r="B12" s="147" t="str">
+        <v>11-20</v>
+      </c>
+      <c r="C12" s="148" t="str">
+        <v>电机相线断路</v>
+      </c>
+      <c r="D12" s="132" t="str">
+        <v>触发：驱动器检测到电机相线没有形成完整回路。
+影响：电机可能缺相、抖动或不能启动，设备停止运动。</v>
+      </c>
+      <c r="E12" s="132" t="str">
+        <v>1、相线断裂、端子松动或插头未插牢。
+2、电机绕组或驱动输出端异常。</v>
+      </c>
+      <c r="F12" s="132" t="str">
+        <v>注意：先排除风险，再恢复操作。
+1、断电后检查各相线和接插件是否松脱。
+2、按检修规程检查线缆与绕组连续性，排除间歇性断线。
+3、修复后低速短程测试；仍报错时检查驱动输出。</v>
+      </c>
+      <c r="G12" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H12" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="13" ht="82.5">
-      <c r="A13" s="48"/>
-      <c r="B13" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="50" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" s="50" t="s">
-        <v>75</v>
-      </c>
-      <c r="F13" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H13" s="47" t="s">
-        <v>27</v>
+    <row r="13" ht="87" customHeight="1">
+      <c r="A13" s="136" t="str">
+        <v>电机驱动</v>
+      </c>
+      <c r="B13" s="147" t="str">
+        <v>11-21</v>
+      </c>
+      <c r="C13" s="148" t="str">
+        <v>电机驱动过温预警</v>
+      </c>
+      <c r="D13" s="132" t="str">
+        <v>触发：电机驱动器温度已接近保护上限，虽然尚未完全关断，但继续运行可能很快触发停机。
+影响：设备中止这次动作以便检查散热和负载。</v>
+      </c>
+      <c r="E13" s="132" t="str">
+        <v>1、驱动电流、机构阻力或运行频次偏高。
+2、环境温度高，或散热通风不良。</v>
+      </c>
+      <c r="F13" s="132" t="str">
+        <v>注意：先排除风险，再恢复操作。
+1、暂停运行，检查驱动器温度，不要等到过温关断。
+2、检查机构阻力、电流设置及散热条件。
+3、冷却并排除原因后短程测试；短时间内再次预警时检修。</v>
+      </c>
+      <c r="G13" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H13" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="14" ht="82.5">
-      <c r="A14" s="48"/>
-      <c r="B14" s="49" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="D14" s="50" t="s">
-        <v>79</v>
-      </c>
-      <c r="E14" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="F14" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="G14" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="47" t="s">
-        <v>27</v>
+    <row r="14" ht="76" customHeight="1">
+      <c r="A14" s="136" t="str">
+        <v>电机驱动</v>
+      </c>
+      <c r="B14" s="133" t="str">
+        <v>11-22</v>
+      </c>
+      <c r="C14" s="132" t="str">
+        <v>电机驱动未初始化</v>
+      </c>
+      <c r="D14" s="132" t="str">
+        <v>触发：设备准备运动时发现电机驱动器尚未完成启动和基本设置。
+影响：当前电流、速度及保护条件不能确认，所以不执行运动。</v>
+      </c>
+      <c r="E14" s="132" t="str">
+        <v>1、驱动上电或初始化尚未完成。
+2、驱动供电不稳定，或启动时通信和配置失败。</v>
+      </c>
+      <c r="F14" s="132" t="str">
+        <v>1、停止下发运动命令，查看启动过程中的首个驱动故障。
+2、检查驱动供电和连接，排除问题后重新上电。
+3、确认初始化完成后再运行；不能完成时保存启动日志。</v>
+      </c>
+      <c r="G14" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H14" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="15" ht="66">
-      <c r="A15" s="48"/>
-      <c r="B15" s="49" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" s="49" t="str">
+    <row r="15" ht="76" customHeight="1">
+      <c r="A15" s="136" t="str">
+        <v>电机驱动</v>
+      </c>
+      <c r="B15" s="133" t="str">
+        <v>11-23</v>
+      </c>
+      <c r="C15" s="132" t="str">
         <v>电机未按时停下</v>
       </c>
-      <c r="D15" s="50" t="s">
-        <v>83</v>
-      </c>
-      <c r="E15" s="50" t="s">
-        <v>84</v>
-      </c>
-      <c r="F15" s="50" t="s">
-        <v>85</v>
-      </c>
-      <c r="G15" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H15" s="47" t="s">
-        <v>27</v>
+      <c r="D15" s="132" t="str">
+        <v>触发：设备已经发出停止指令，但在规定时间内仍检测到电机未停稳或位置仍在变化。
+影响：为防止结果在运动中被使用，这次动作失败。</v>
+      </c>
+      <c r="E15" s="132" t="str">
+        <v>1、驱动未能按时完成停止，或减速条件不合适。
+2、外力带动机构，或位置反馈仍在变化。</v>
+      </c>
+      <c r="F15" s="132" t="str">
+        <v>1、先确认机构实际是否已经停下，不要立即继续测量。
+2、记录停止前后的速度、位置和驱动状态，检查减速和传动。
+3、确认停止响应正常后再测试；仍不能停稳时停用检修。</v>
+      </c>
+      <c r="G15" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H15" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="16" ht="99">
-      <c r="A16" s="48"/>
-      <c r="B16" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="C16" s="52" t="str">
+    <row r="16" ht="87" customHeight="1">
+      <c r="A16" s="136" t="str">
+        <v>电机驱动</v>
+      </c>
+      <c r="B16" s="133" t="str">
+        <v>11-24</v>
+      </c>
+      <c r="C16" s="132" t="str">
         <v>电机未按时到位</v>
       </c>
-      <c r="D16" s="53" t="s">
-        <v>87</v>
-      </c>
-      <c r="E16" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="F16" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="G16" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="47" t="s">
-        <v>90</v>
+      <c r="D16" s="132" t="str">
+        <v>触发：设备执行首圈或局部周长标定等精确位置运动。
+影响：等待目标位置超过规定时间，实际位置还是没有进入允许偏差范围，所以停止这次动作。</v>
+      </c>
+      <c r="E16" s="132" t="str">
+        <v>1、精确位置运动中卡涩、打滑或位置反馈异常。
+2、目标位置、周长换算或到位条件不合适。</v>
+      </c>
+      <c r="F16" s="132" t="str">
+        <v>1、停止运动，记录目标位置、实际位置和等待时间。
+2、检查传动、位置反馈和周长参数，确认标定行程没有受阻。
+3、排除原因后重新执行该标定或定位，确认能够按时到位。</v>
+      </c>
+      <c r="G16" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H16" s="135" t="str">
+        <v>CPU2共享故障；精确位置运动/标定</v>
       </c>
     </row>
-    <row r="17" ht="66">
-      <c r="A17" s="54" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="66" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" s="66" t="str">
+    <row r="17" ht="87" customHeight="1">
+      <c r="A17" s="141" t="str">
+        <v>编码器</v>
+      </c>
+      <c r="B17" s="142" t="str">
+        <v>12-1</v>
+      </c>
+      <c r="C17" s="143" t="str">
         <v>编码器没有有效位置数据</v>
       </c>
-      <c r="D17" s="65" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="65" t="s">
-        <v>94</v>
-      </c>
-      <c r="F17" s="65" t="s">
-        <v>95</v>
-      </c>
-      <c r="G17" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H17" s="47" t="s">
-        <v>27</v>
+      <c r="D17" s="144" t="str">
+        <v>触发：设备没能启动编码器采集，或等待后还是没有收到有效的位置数据。
+影响：当前位置不能确认，相关运动被停止。</v>
+      </c>
+      <c r="E17" s="144" t="str">
+        <v>1、编码器供电、信号线或接插件异常。
+2、编码器未正常输出，或采集链路受到干扰。</v>
+      </c>
+      <c r="F17" s="144" t="str">
+        <v>1、停止相关运动，检查编码器供电和接线。
+2、查看位置数据是否能够连续取得，不能把固定旧值当作采集正常。
+3、仍无数据时检查采集链路；位置基准不可信时先重新建立基准。</v>
+      </c>
+      <c r="G17" s="145" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H17" s="146" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="18" ht="66">
-      <c r="A18" s="54"/>
-      <c r="B18" s="66" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" s="66" t="str">
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="136" t="str">
+        <v>编码器</v>
+      </c>
+      <c r="B18" s="139" t="str">
+        <v>12-2</v>
+      </c>
+      <c r="C18" s="140" t="str">
         <v>编码器数据校验失败</v>
       </c>
-      <c r="D18" s="65" t="s">
-        <v>97</v>
-      </c>
-      <c r="E18" s="65" t="s">
-        <v>98</v>
-      </c>
-      <c r="F18" s="65" t="s">
-        <v>95</v>
-      </c>
-      <c r="G18" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="47" t="s">
-        <v>27</v>
+      <c r="D18" s="132" t="str">
+        <v>触发：设备收到编码器位置数据。
+影响：完整性检查不通过，这次数据可能在传输中受到干扰，不能用于位置判断。</v>
+      </c>
+      <c r="E18" s="132" t="str">
+        <v>1、编码器信号线接触不良，或屏蔽接地不合适。
+2、供电波动、电机启停干扰，或编码器接口异常。</v>
+      </c>
+      <c r="F18" s="132" t="str">
+        <v>1、检查故障是否与电机启停同时出现。
+2、停机检查编码器连接、供电及信号线布置。
+3、确认连续采样不再校验失败后再运行；反复出现时保存编码器诊断记录。</v>
+      </c>
+      <c r="G18" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H18" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="19" ht="82.5">
-      <c r="A19" s="54"/>
-      <c r="B19" s="52" t="s">
-        <v>99</v>
-      </c>
-      <c r="C19" s="52" t="str">
+    <row r="19" ht="76" customHeight="1">
+      <c r="A19" s="136" t="str">
+        <v>编码器</v>
+      </c>
+      <c r="B19" s="133" t="str">
+        <v>12-3</v>
+      </c>
+      <c r="C19" s="132" t="str">
         <v>编码器记录位移不足</v>
       </c>
-      <c r="D19" s="53" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" s="53" t="s">
-        <v>101</v>
-      </c>
-      <c r="F19" s="53" t="s">
-        <v>95</v>
-      </c>
-      <c r="G19" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H19" s="47" t="s">
-        <v>27</v>
+      <c r="D19" s="132" t="str">
+        <v>触发：电机明显移动。
+影响：编码轮记录的尺带位移不足，或周长标定值低于允许下限，说明尺带或编码轮没有正常跟随运动。</v>
+      </c>
+      <c r="E19" s="132" t="str">
+        <v>1、尺带与编码轮打滑、压紧不足，或传动件松动。
+2、位置或周长设置不合适，标定时记录到的位移过小。</v>
+      </c>
+      <c r="F19" s="132" t="str">
+        <v>1、停止运动，核对电机动作和编码器记录位移是否一致。
+2、检查编码轮压紧、轮面、尺带和传动连接。
+3、排除打滑后再测试；若发生在周长标定中，按规定行程重新标定。</v>
+      </c>
+      <c r="G19" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H19" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="20" ht="66">
-      <c r="A20" s="54"/>
-      <c r="B20" s="52" t="s">
-        <v>102</v>
-      </c>
-      <c r="C20" s="52" t="str">
+    <row r="20" ht="102" customHeight="1">
+      <c r="A20" s="136" t="str">
+        <v>编码器</v>
+      </c>
+      <c r="B20" s="147" t="str">
+        <v>12-5</v>
+      </c>
+      <c r="C20" s="148" t="str">
         <v>编码器位置记录不可用</v>
       </c>
-      <c r="D20" s="53" t="s">
-        <v>103</v>
-      </c>
-      <c r="E20" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="F20" s="53" t="s">
-        <v>95</v>
-      </c>
-      <c r="G20" s="55" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="47" t="s">
-        <v>27</v>
+      <c r="D20" s="132" t="str">
+        <v>触发：开机时，设备检查到两份编码器位置记录都不可用，不能恢复断电前位置，已改用默认位置。
+影响：继续运动前必须确认实际位置。</v>
+      </c>
+      <c r="E20" s="132" t="str">
+        <v>1、首次使用或更换主控、存储部件后，还没有有效位置记录。
+2、掉电保存不完整，或位置存储记录损坏。</v>
+      </c>
+      <c r="F20" s="132" t="str">
+        <v>注意：先排除风险，再恢复操作。
+1、不要按默认位置直接继续运行，先确认机构实际位置。
+2、检查是否同时有掉电保存或存储故障，先处理这些问题。
+3、通过回零或零点标定重新建立位置，确认位置记录能保存后再恢复普通运动。</v>
+      </c>
+      <c r="G20" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H20" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="21" ht="66">
-      <c r="A21" s="54"/>
-      <c r="B21" s="52" t="str">
+    <row r="21" ht="87" customHeight="1">
+      <c r="A21" s="136" t="str">
+        <v>编码器</v>
+      </c>
+      <c r="B21" s="147" t="str">
         <v>12-6</v>
       </c>
-      <c r="C21" s="52" t="str">
+      <c r="C21" s="148" t="str">
         <v>编码器上电位置跳变</v>
       </c>
-      <c r="D21" s="53" t="str">
-        <v>出现情况：开机连续取得3帧稳定位置后，与断电前保存的位置比较，位置变化超过允许范围。
-会有什么影响：断电前后的累计位置不能安全衔接，设备禁止普通运动，只允许人工确认后执行回零或零点标定重新建立位置基准。</v>
-      </c>
-      <c r="E21" s="53" t="str">
-        <v>• 断电期间机构或尺带被人为移动。
-• 编码器、磁铁或固定件松动、偏移，更换主控板或编码器后没有重新回零。
-• 断电前位置未完整保存、存储记录异常，或上电初期位置反馈不稳定。</v>
-      </c>
-      <c r="F21" s="53" t="str">
-        <v>注意：不要按断电前位置直接继续运动。
-1. 重点检查：人工确认机构实际位置，检查编码器、磁铁、尺带和固定件。
-2. 处理完再看：执行回零或零点标定，重新建立位置基准。
-还是不行：检查位置保存记录和主控板。</v>
-      </c>
-      <c r="G21" s="51" t="str">
+      <c r="D21" s="132" t="str">
+        <v>触发：开机连续取得3帧稳定位置后，与断电前保存的位置比较，位置变化超过允许范围。
+影响：断电前后的累计位置不能安全衔接，设备禁止普通运动，只允许人工确认后执行回零或零点标定重新建立位置基准。</v>
+      </c>
+      <c r="E21" s="132" t="str">
+        <v>1、断电期间机构、尺带或磁铁位置发生变化。
+2、位置保存记录与实际位置不一致，或编码器安装松动。</v>
+      </c>
+      <c r="F21" s="132" t="str">
+        <v>注意：先排除风险，再恢复操作。
+1、不要按断电前位置继续运动，先人工确认机构位置。
+2、检查编码器、磁铁、尺带和固定件。
+3、排除问题后执行回零或零点标定，重新建立位置基准；反复出现时检查位置保存。</v>
+      </c>
+      <c r="G21" s="134" t="str">
         <v>使用中</v>
       </c>
-      <c r="H21" s="47" t="str">
-        <v>CPU2共享故障｜协议34启用</v>
+      <c r="H21" s="135" t="str">
+        <v>CPU2共享故障；协议34启用</v>
       </c>
     </row>
-    <row r="22" ht="82.5">
-      <c r="A22" s="54"/>
-      <c r="B22" s="52" t="s">
-        <v>105</v>
-      </c>
-      <c r="C22" s="52" t="str">
+    <row r="22" ht="76" customHeight="1">
+      <c r="A22" s="136" t="str">
+        <v>编码器</v>
+      </c>
+      <c r="B22" s="133" t="str">
+        <v>12-10</v>
+      </c>
+      <c r="C22" s="132" t="str">
         <v>编码轮周长标定值过大</v>
       </c>
-      <c r="D22" s="53" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="F22" s="53" t="s">
-        <v>95</v>
-      </c>
-      <c r="G22" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="47" t="s">
-        <v>27</v>
+      <c r="D22" s="132" t="str">
+        <v>周长标定得到的周长超过允许上限，本次标定不能采用。此码不用于表示运行中的相邻位置跳变，运行跳变请查12-17。</v>
+      </c>
+      <c r="E22" s="132" t="str">
+        <v>1、周长标定期间尺带或编码轮打滑、跳动，位移记录失真。
+2、周长换算参数或标定条件不正确。</v>
+      </c>
+      <c r="F22" s="132" t="str">
+        <v>1、停止重复标定，记录本次测得周长和允许范围。
+2、检查尺带、编码轮压紧、传动及相关周长参数。
+3、按规定流程重新标定；运行中突然跳变应另查12-17。</v>
+      </c>
+      <c r="G22" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H22" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="23" ht="66">
-      <c r="A23" s="54"/>
-      <c r="B23" s="52" t="s">
-        <v>108</v>
-      </c>
-      <c r="C23" s="52" t="str">
+    <row r="23" ht="76" customHeight="1">
+      <c r="A23" s="136" t="str">
+        <v>编码器</v>
+      </c>
+      <c r="B23" s="133" t="str">
+        <v>12-12</v>
+      </c>
+      <c r="C23" s="132" t="str">
         <v>编码器角度计算超限</v>
       </c>
-      <c r="D23" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="E23" s="53" t="s">
-        <v>110</v>
-      </c>
-      <c r="F23" s="53" t="s">
-        <v>95</v>
-      </c>
-      <c r="G23" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="47" t="s">
-        <v>27</v>
+      <c r="D23" s="132" t="str">
+        <v>触发：编码器报告内部角度计算超出有效范围。
+影响：当前角度不能换算为可靠位置，设备停止使用这次数据。</v>
+      </c>
+      <c r="E23" s="132" t="str">
+        <v>1、磁铁偏心、倾斜或间隙不合适。
+2、附近磁性物体、磁场变化，或编码器本体异常。</v>
+      </c>
+      <c r="F23" s="132" t="str">
+        <v>1、停机检查磁铁与编码器的同心度、间隙和固定情况。
+2、排除附近金属碎屑或异常磁场，并检查供电。
+3、确认角度状态和位置采样恢复正常后再运行。</v>
+      </c>
+      <c r="G23" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H23" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="24" ht="66">
-      <c r="A24" s="54"/>
-      <c r="B24" s="52" t="str">
+    <row r="24" ht="102" customHeight="1">
+      <c r="A24" s="149" t="str">
+        <v>编码器</v>
+      </c>
+      <c r="B24" s="150" t="str">
         <v>12-13</v>
       </c>
-      <c r="C24" s="52" t="str">
+      <c r="C24" s="149" t="str">
         <v>编码器角度线性异常</v>
       </c>
-      <c r="D24" s="53" t="str">
-        <v>出现情况：调试查询发现编码器LIN线性度状态位持续置位。
-会有什么影响：当前策略仅保留原始状态和累计次数；LIN位本身不拒绝位置帧，也不触发12-13停机。</v>
-      </c>
-      <c r="E24" s="53" t="str">
-        <v>• 磁铁偏心、倾斜、安装间隙不合适，或编码器与磁铁固定件松动。
-• 附近铁磁零件、金属碎屑或外部强磁场改变了磁场分布。
-• 编码器供电不稳、器件受损或安装面变形也可能持续触发。</v>
-      </c>
-      <c r="F24" s="53" t="str">
-        <v>当前程序不会主动报出12-13。
-1. 调试检查：通过ENC?查看LIN原始位、累计次数，并同时核对校验、OCF、COF、跳变和链路质量。
-2. 若LIN长期置位：检查磁铁与编码器同心度、安装间隙、固定件、供电及附近金属碎屑。
-3. 若同时出现位置跳变或其它编码器故障：按对应故障处理，必要时重新回零。</v>
-      </c>
-      <c r="G24" s="51" t="str">
+      <c r="D24" s="149" t="str">
+        <v>当前只保留编号和显示映射。编码器线性度状态用于诊断统计，本身不拒绝位置数据，也不触发12-13停机。</v>
+      </c>
+      <c r="E24" s="149" t="str">
+        <v>1、磁铁偏心、倾斜、间隙不合适，或固定件松动。
+2、附近铁磁零件、金属碎屑或磁场变化。</v>
+      </c>
+      <c r="F24" s="149" t="str">
+        <v>1、当前程序不会主动报出12-13，不要仅凭线性度诊断记录判定停机故障。
+2、由技术人员查看编码器线性度统计，同时检查安装和磁铁间隙。
+3、若同时出现位置跳变、校验或通信故障，按实际报出的故障处理。</v>
+      </c>
+      <c r="G24" s="153" t="str">
         <v>保留</v>
       </c>
-      <c r="H24" s="47" t="str">
-        <v>CPU2/CPU3保留定义｜当前仅诊断统计</v>
+      <c r="H24" s="152" t="str">
+        <v>CPU2/CPU3保留定义；当前仅诊断统计</v>
       </c>
     </row>
-    <row r="25" ht="82.5">
-      <c r="A25" s="54"/>
-      <c r="B25" s="52" t="s">
-        <v>111</v>
-      </c>
-      <c r="C25" s="52" t="str">
+    <row r="25" ht="76" customHeight="1">
+      <c r="A25" s="136" t="str">
+        <v>编码器</v>
+      </c>
+      <c r="B25" s="133" t="str">
+        <v>12-14</v>
+      </c>
+      <c r="C25" s="132" t="str">
         <v>编码器角度计算未完成</v>
       </c>
-      <c r="D25" s="53" t="s">
-        <v>112</v>
-      </c>
-      <c r="E25" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="F25" s="53" t="s">
-        <v>95</v>
-      </c>
-      <c r="G25" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H25" s="47" t="s">
-        <v>27</v>
+      <c r="D25" s="132" t="str">
+        <v>触发：编码器尚未完成内部角度测量，返回的位置没有达到可用状态。
+影响：设备不能确认当前位置。</v>
+      </c>
+      <c r="E25" s="132" t="str">
+        <v>1、编码器上电尚未稳定，或供电波动。
+2、磁铁位置不合适，或编码器内部角度测量异常。</v>
+      </c>
+      <c r="F25" s="132" t="str">
+        <v>1、等待编码器启动完成，观察是否仍持续报错。
+2、反复出现时停机检查供电、磁铁位置和间隙。
+3、确认角度计算状态正常、位置数据连续可用后再运行。</v>
+      </c>
+      <c r="G25" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H25" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="26" ht="66">
-      <c r="A26" s="54"/>
-      <c r="B26" s="52" t="s">
-        <v>114</v>
-      </c>
-      <c r="C26" s="52" t="s">
-        <v>115</v>
-      </c>
-      <c r="D26" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="F26" s="53" t="s">
-        <v>118</v>
-      </c>
-      <c r="G26" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H26" s="47" t="s">
-        <v>27</v>
+    <row r="26" ht="87" customHeight="1">
+      <c r="A26" s="136" t="str">
+        <v>编码器</v>
+      </c>
+      <c r="B26" s="133" t="str">
+        <v>12-15</v>
+      </c>
+      <c r="C26" s="132" t="str">
+        <v>编码器首个位置等待超时</v>
+      </c>
+      <c r="D26" s="132" t="str">
+        <v>触发：设备启动位置采集后，在允许时间内没有取得第一笔可用位置。
+影响：由于起始位置不能确认，相关运动和测量不能开始。</v>
+      </c>
+      <c r="E26" s="132" t="str">
+        <v>1、编码器没有供电或连接异常。
+2、持续返回无效状态，导致首笔位置一直不可用。</v>
+      </c>
+      <c r="F26" s="132" t="str">
+        <v>1、检查编码器供电、接线和磁铁安装。
+2、查看启动日志中是否先出现校验或角度状态异常，优先处理首个故障。
+3、重新启动位置采集，确认取得可靠起始位置后再执行运动。</v>
+      </c>
+      <c r="G26" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H26" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="27" ht="82.5">
-      <c r="A27" s="54"/>
-      <c r="B27" s="52" t="s">
-        <v>119</v>
-      </c>
-      <c r="C27" s="52" t="s">
-        <v>120</v>
-      </c>
-      <c r="D27" s="53" t="s">
-        <v>121</v>
-      </c>
-      <c r="E27" s="53" t="s">
-        <v>122</v>
-      </c>
-      <c r="F27" s="53" t="s">
-        <v>123</v>
-      </c>
-      <c r="G27" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="47" t="s">
-        <v>27</v>
+    <row r="27" ht="76" customHeight="1">
+      <c r="A27" s="136" t="str">
+        <v>编码器</v>
+      </c>
+      <c r="B27" s="133" t="str">
+        <v>12-16</v>
+      </c>
+      <c r="C27" s="132" t="str">
+        <v>编码轮周长标定异常</v>
+      </c>
+      <c r="D27" s="132" t="str">
+        <v>触发：周长标定完成后，计算结果超出允许范围或多次结果差异过大。
+影响：设备不能用这次结果换算尺带位置。</v>
+      </c>
+      <c r="E27" s="132" t="str">
+        <v>1、标定行程或条件不符合要求。
+2、尺带打滑、编码轮压紧不足，或位置记录不稳定。</v>
+      </c>
+      <c r="F27" s="132" t="str">
+        <v>1、停止重复标定，记录本次结果和标定行程。
+2、检查编码轮、尺带和位置反馈，核对标定方向及参数。
+3、按规定流程重新标定，确认结果有效后再用于位置换算。</v>
+      </c>
+      <c r="G27" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H27" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="28" ht="82.5">
-      <c r="A28" s="54" t="s">
-        <v>124</v>
-      </c>
-      <c r="B28" s="49" t="s">
-        <v>125</v>
-      </c>
-      <c r="C28" s="49" t="s">
-        <v>126</v>
-      </c>
-      <c r="D28" s="50" t="s">
-        <v>127</v>
-      </c>
-      <c r="E28" s="50" t="s">
-        <v>128</v>
-      </c>
-      <c r="F28" s="50" t="s">
-        <v>129</v>
-      </c>
-      <c r="G28" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="47" t="s">
-        <v>27</v>
+    <row r="28" ht="87" customHeight="1">
+      <c r="A28" s="136" t="str">
+        <v>编码器</v>
+      </c>
+      <c r="B28" s="154" t="str">
+        <v>12-17</v>
+      </c>
+      <c r="C28" s="155" t="str">
+        <v>编码器运行位置跳变</v>
+      </c>
+      <c r="D28" s="132" t="str">
+        <v>运行中连续3个候选位置增量超过按最大速度、采样间隔和编码轮周长计算的允许上限。异常增量不写入累计位置，当前运动停止。方向不一致仅作诊断统计，本身不触发此码。</v>
+      </c>
+      <c r="E28" s="132" t="str">
+        <v>1、编码器、磁铁或接插件松动，或信号受到干扰。
+2、尺带、编码轮异常跳动，或周长参数不正确。</v>
+      </c>
+      <c r="F28" s="132" t="str">
+        <v>注意：先排除风险，再恢复操作。
+1、停止运动并人工确认机构位置，不要直接继续原行程。
+2、检查磁铁、编码器、尺带压紧、连接和周长参数。
+3、位置基准不可信时先重新回零；确认位置可靠后再短程测试，仍报错时保存编码器诊断和运动日志。</v>
+      </c>
+      <c r="G28" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H28" s="135" t="str">
+        <v>CPU2共享故障；协议34起启用</v>
       </c>
     </row>
-    <row r="29" ht="82.5">
-      <c r="A29" s="54"/>
-      <c r="B29" s="49" t="s">
-        <v>130</v>
-      </c>
-      <c r="C29" s="49" t="str">
+    <row r="29" ht="87" customHeight="1">
+      <c r="A29" s="141" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B29" s="156" t="str">
+        <v>13-1</v>
+      </c>
+      <c r="C29" s="144" t="str">
+        <v>传感器数据校验失败</v>
+      </c>
+      <c r="D29" s="144" t="str">
+        <v>触发：传感器已经返回一组数据。
+影响：完整性检查不一致，这次温度、频率或密度数据可能在传输中受干扰，不能使用。</v>
+      </c>
+      <c r="E29" s="144" t="str">
+        <v>1、传感器供电或通信连接不稳。
+2、无线滑环链路干扰、丢字或混入旧数据。</v>
+      </c>
+      <c r="F29" s="144" t="str">
+        <v>1、保存报错前后的通信记录，确认是校验失败而不是完全无应答。
+2、检查传感器供电、接头和滑环链路。
+3、连续应答校验正常后再测量；反复出现时由技术人员对照原始报文。</v>
+      </c>
+      <c r="G29" s="145" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H29" s="146" t="str">
+        <v>CPU2共享故障</v>
+      </c>
+    </row>
+    <row r="30" ht="87" customHeight="1">
+      <c r="A30" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B30" s="133" t="str">
+        <v>13-2</v>
+      </c>
+      <c r="C30" s="132" t="str">
         <v>振动管频率异常</v>
       </c>
-      <c r="D29" s="50" t="s">
-        <v>131</v>
-      </c>
-      <c r="E29" s="50" t="s">
-        <v>132</v>
-      </c>
-      <c r="F29" s="50" t="s">
-        <v>129</v>
-      </c>
-      <c r="G29" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="47" t="s">
-        <v>27</v>
+      <c r="D30" s="132" t="str">
+        <v>液位或密度流程没有取得符合当前规则的频率，本次操作失败。液位流程中的0值表示尚未稳定，会继续等待；非零越界或无效频率按对应协议和流程报错。日志中的重试记录不等于最终停机。</v>
+      </c>
+      <c r="E30" s="132" t="str">
+        <v>1、振动信号异常，或探头附着物、气泡等使频率持续越界。
+2、供电、传感器模式或频率数据本身异常。</v>
+      </c>
+      <c r="F30" s="132" t="str">
+        <v>1、记录传感器型号、测量模式和故障前的频率。
+2、液位流程中的0值先按未稳定等待，不要直接当作损坏；非零异常需核对供电、探头状态和模式。
+3、异常排除后重新测量；仍报错时保存原始应答及重试日志。</v>
+      </c>
+      <c r="G30" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H30" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="30" ht="82.5">
-      <c r="A30" s="54"/>
-      <c r="B30" s="66" t="s">
-        <v>133</v>
-      </c>
-      <c r="C30" s="66" t="s">
-        <v>134</v>
-      </c>
-      <c r="D30" s="65" t="s">
-        <v>135</v>
-      </c>
-      <c r="E30" s="65" t="s">
-        <v>136</v>
-      </c>
-      <c r="F30" s="65" t="s">
-        <v>137</v>
-      </c>
-      <c r="G30" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="47" t="s">
-        <v>27</v>
+    <row r="31" ht="76" customHeight="1">
+      <c r="A31" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B31" s="139" t="str">
+        <v>13-3</v>
+      </c>
+      <c r="C31" s="140" t="str">
+        <v>传感器通信超时</v>
+      </c>
+      <c r="D31" s="132" t="str">
+        <v>触发：设备向密度或液位传感器发出请求后，在规定时间和重试次数内还是没有收到完整有效答复。
+影响：这次测量数据拿不到。</v>
+      </c>
+      <c r="E31" s="132" t="str">
+        <v>1、传感器无供电，或滑环主从链路未连接。
+2、接插件松动、无线信号受遮挡或配对对象不正确。</v>
+      </c>
+      <c r="F31" s="132" t="str">
+        <v>1、检查传感器是否上电，以及滑环主从机是否已连接。
+2、核对目标设备、接插件、天线和遮挡情况。
+3、确认能连续收到完整应答后再测量；仍超时则保存请求、应答和连接状态。</v>
+      </c>
+      <c r="G31" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H31" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="31" ht="66">
-      <c r="A31" s="54"/>
-      <c r="B31" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="C31" s="49" t="s">
-        <v>139</v>
-      </c>
-      <c r="D31" s="50" t="s">
-        <v>140</v>
-      </c>
-      <c r="E31" s="50" t="s">
-        <v>141</v>
-      </c>
-      <c r="F31" s="50" t="s">
-        <v>142</v>
-      </c>
-      <c r="G31" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H31" s="47" t="s">
-        <v>143</v>
+    <row r="32" ht="102" customHeight="1">
+      <c r="A32" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B32" s="133" t="str">
+        <v>13-5</v>
+      </c>
+      <c r="C32" s="132" t="str">
+        <v>传感器内部通信超时</v>
+      </c>
+      <c r="D32" s="132" t="str">
+        <v>触发：使用DSM传感器通信。
+影响：传感器明确返回内部测量处理单元无应答状态，当前温度、频率或密度数据不能使用。</v>
+      </c>
+      <c r="E32" s="132" t="str">
+        <v>1、DSM传感器内部测量单元未正常启动。
+2、内部供电、连接或测量板件异常。</v>
+      </c>
+      <c r="F32" s="132" t="str">
+        <v>1、先确认收到的是传感器内部超时应答，不要只查外部无线链路。
+2、检查传感器外部供电，按允许流程重新启动并观察自检。
+3、仍报错时记录型号、版本和应答，由厂家检查内部单元。</v>
+      </c>
+      <c r="G32" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H32" s="135" t="str">
+        <v>CPU2共享故障；DSM传感器</v>
       </c>
     </row>
-    <row r="32" ht="66">
-      <c r="A32" s="54"/>
-      <c r="B32" s="49" t="s">
-        <v>144</v>
-      </c>
-      <c r="C32" s="49" t="s">
-        <v>145</v>
-      </c>
-      <c r="D32" s="50" t="s">
-        <v>146</v>
-      </c>
-      <c r="E32" s="50" t="s">
-        <v>147</v>
-      </c>
-      <c r="F32" s="50" t="s">
-        <v>148</v>
-      </c>
-      <c r="G32" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H32" s="47" t="s">
-        <v>149</v>
+    <row r="33" ht="102" customHeight="1">
+      <c r="A33" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B33" s="133" t="str">
+        <v>13-14</v>
+      </c>
+      <c r="C33" s="132" t="str">
+        <v>传感器姿态角异常</v>
+      </c>
+      <c r="D33" s="132" t="str">
+        <v>触发：使用DSM或安全传感器协议。
+影响：传感器上报姿态数据无效，设备不能继续使用这次姿态信息进行测量判断。</v>
+      </c>
+      <c r="E33" s="132" t="str">
+        <v>1、传感器姿态测量或内部角度状态异常。
+2、探头安装松动、异常倾斜，或内部部件异常。</v>
+      </c>
+      <c r="F33" s="132" t="str">
+        <v>1、检查探头安装和活动空间，查看姿态数据能否正常更新。
+2、传感器仍报告姿态异常时，先检修姿态链路，不要只反复回零。
+3、姿态数据恢复有效后，再按当前测量流程建立所需基准。</v>
+      </c>
+      <c r="G33" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H33" s="135" t="str">
+        <v>CPU2共享故障；DSM/安全传感器</v>
       </c>
     </row>
-    <row r="33" ht="66">
-      <c r="A33" s="54"/>
-      <c r="B33" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="C33" s="49" t="str">
+    <row r="34" ht="76" customHeight="1">
+      <c r="A34" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B34" s="133" t="str">
+        <v>13-16</v>
+      </c>
+      <c r="C34" s="132" t="str">
         <v>传感器内部通信校验失败</v>
       </c>
-      <c r="D33" s="50" t="s">
-        <v>151</v>
-      </c>
-      <c r="E33" s="50" t="s">
-        <v>152</v>
-      </c>
-      <c r="F33" s="50" t="s">
-        <v>153</v>
-      </c>
-      <c r="G33" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H33" s="47" t="s">
-        <v>27</v>
+      <c r="D34" s="132" t="str">
+        <v>触发：传感器内部两个测量单元之间已交换数据。
+影响：内容确认不一致，这次频率、温度或密度结果被判为不可靠。</v>
+      </c>
+      <c r="E34" s="132" t="str">
+        <v>1、传感器内部数据交换受干扰或不同步。
+2、内部连接、供电或板件异常。</v>
+      </c>
+      <c r="F34" s="132" t="str">
+        <v>1、保存传感器返回的内部校验错误记录。
+2、检查外部供电，按允许流程重新启动后复测。
+3、持续出现时由厂家检查内部连接和板件，不要仅更换外部通信线。</v>
+      </c>
+      <c r="G34" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H34" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="34" ht="66">
-      <c r="A34" s="54"/>
-      <c r="B34" s="49" t="s">
-        <v>154</v>
-      </c>
-      <c r="C34" s="49" t="s">
-        <v>155</v>
-      </c>
-      <c r="D34" s="50" t="s">
-        <v>156</v>
-      </c>
-      <c r="E34" s="50" t="s">
-        <v>157</v>
-      </c>
-      <c r="F34" s="50" t="s">
-        <v>158</v>
-      </c>
-      <c r="G34" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H34" s="47" t="s">
-        <v>143</v>
+    <row r="35" ht="87" customHeight="1">
+      <c r="A35" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B35" s="133" t="str">
+        <v>13-21</v>
+      </c>
+      <c r="C35" s="132" t="str">
+        <v>传感器无谐振</v>
+      </c>
+      <c r="D35" s="132" t="str">
+        <v>触发：使用DSM传感器通信。
+影响：传感器明确返回未找到有效谐振点，设备不能使用这次频率数据判断液面或计算密度。</v>
+      </c>
+      <c r="E35" s="132" t="str">
+        <v>1、探头附着物、气泡或介质条件使振动异常。
+2、传感器供电、内部驱动或设置异常。</v>
+      </c>
+      <c r="F35" s="132" t="str">
+        <v>1、核对故障发生时探头所在位置和测量模式。
+2、按检修规程检查探头附着物和供电，不要为消除故障盲目下放探头。
+3、在已知正常条件下复测；仍返回无谐振时保存DSM应答并联系厂家。</v>
+      </c>
+      <c r="G35" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H35" s="135" t="str">
+        <v>CPU2共享故障；DSM传感器</v>
       </c>
     </row>
-    <row r="35" ht="82.5">
-      <c r="A35" s="54"/>
-      <c r="B35" s="66" t="s">
-        <v>159</v>
-      </c>
-      <c r="C35" s="66" t="str">
+    <row r="36" ht="87" customHeight="1">
+      <c r="A36" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B36" s="139" t="str">
+        <v>13-26</v>
+      </c>
+      <c r="C36" s="140" t="str">
         <v>密度值超出有效范围</v>
       </c>
-      <c r="D35" s="65" t="s">
-        <v>160</v>
-      </c>
-      <c r="E35" s="65" t="s">
-        <v>161</v>
-      </c>
-      <c r="F35" s="65" t="s">
-        <v>129</v>
-      </c>
-      <c r="G35" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H35" s="47" t="s">
-        <v>27</v>
+      <c r="D36" s="132" t="str">
+        <v>密度数据不可用，本次结果不采用。密度找液位流程连续读到密度小于等于0或大于3000 kg/m³时会报此码；0值可能来自尚未稳定的传感器，需要结合测量流程和原始状态判断。</v>
+      </c>
+      <c r="E36" s="132" t="str">
+        <v>1、有效密度测量条件未建立，或介质中气泡、附着物影响读数。
+2、传感器标定、温度或密度数据异常。</v>
+      </c>
+      <c r="F36" s="132" t="str">
+        <v>1、记录密度、温度、探头位置和传感器类型。
+2、0值也可能表示传感器尚未稳定，先结合协议状态和测点条件判断，不直接认定为硬件损坏。
+3、稳定液体点仍越界时核对标定和原始数据，不要通过放宽范围接受异常值。</v>
+      </c>
+      <c r="G36" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H36" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="36" ht="82.5">
-      <c r="A36" s="54"/>
-      <c r="B36" s="49" t="s">
-        <v>162</v>
-      </c>
-      <c r="C36" s="49" t="s">
-        <v>163</v>
-      </c>
-      <c r="D36" s="50" t="s">
-        <v>164</v>
-      </c>
-      <c r="E36" s="50" t="s">
-        <v>165</v>
-      </c>
-      <c r="F36" s="50" t="s">
-        <v>166</v>
-      </c>
-      <c r="G36" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H36" s="47" t="s">
-        <v>27</v>
+    <row r="37" ht="76" customHeight="1">
+      <c r="A37" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B37" s="133" t="str">
+        <v>13-27</v>
+      </c>
+      <c r="C37" s="132" t="str">
+        <v>传感器响应格式异常</v>
+      </c>
+      <c r="D37" s="132" t="str">
+        <v>触发：传感器已有答复。
+影响：答复的长度、开头、结尾、指令内容或数值格式与这次请求不一致，设备不能识别并舍弃该数据。</v>
+      </c>
+      <c r="E37" s="132" t="str">
+        <v>1、应答被截断、混入旧内容或通信受到干扰。
+2、传感器型号、协议或通信配置不配套。</v>
+      </c>
+      <c r="F37" s="132" t="str">
+        <v>1、保存当前请求和完整原始应答。
+2、检查传感器型号、协议配置及通信链路。
+3、确认应答与本次命令一致后再测量；持续异常时交由技术人员分析格式。</v>
+      </c>
+      <c r="G37" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H37" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="37" ht="82.5">
-      <c r="A37" s="54"/>
-      <c r="B37" s="49" t="s">
-        <v>167</v>
-      </c>
-      <c r="C37" s="49" t="s">
-        <v>168</v>
-      </c>
-      <c r="D37" s="50" t="s">
-        <v>169</v>
-      </c>
-      <c r="E37" s="50" t="s">
-        <v>170</v>
-      </c>
-      <c r="F37" s="50" t="s">
-        <v>171</v>
-      </c>
-      <c r="G37" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H37" s="47" t="s">
-        <v>27</v>
+    <row r="38" ht="76" customHeight="1">
+      <c r="A38" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B38" s="133" t="str">
+        <v>13-28</v>
+      </c>
+      <c r="C38" s="132" t="str">
+        <v>传感器供电异常</v>
+      </c>
+      <c r="D38" s="132" t="str">
+        <v>触发：传感器检测到自身供电低于或高于允许范围，测量电路可能不能稳定工作。
+影响：这次数据不使用。</v>
+      </c>
+      <c r="E38" s="132" t="str">
+        <v>1、传感器端供电过低、过高或启动时压降明显。
+2、线缆、端子、安全栅或传感器内部供电异常。</v>
+      </c>
+      <c r="F38" s="132" t="str">
+        <v>1、按现场电气规程测量传感器端实际供电。
+2、检查端子、线缆压降及安全栅等供电环节。
+3、电压回到该型号允许范围且稳定后再测量；仍报警时检修传感器。</v>
+      </c>
+      <c r="G38" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H38" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="38" ht="66">
-      <c r="A38" s="54"/>
-      <c r="B38" s="49" t="s">
-        <v>172</v>
-      </c>
-      <c r="C38" s="49" t="s">
-        <v>173</v>
-      </c>
-      <c r="D38" s="50" t="s">
-        <v>174</v>
-      </c>
-      <c r="E38" s="50" t="s">
-        <v>175</v>
-      </c>
-      <c r="F38" s="50" t="s">
-        <v>176</v>
-      </c>
-      <c r="G38" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H38" s="47" t="s">
-        <v>27</v>
+    <row r="39" ht="76" customHeight="1">
+      <c r="A39" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B39" s="133" t="str">
+        <v>13-29</v>
+      </c>
+      <c r="C39" s="132" t="str">
+        <v>姿态模块通信超时</v>
+      </c>
+      <c r="D39" s="132" t="str">
+        <v>触发：传感器内部姿态模块没有按时返回角度数据。
+影响：设备不能确认探头姿态，相关液面和罐底判断停止。</v>
+      </c>
+      <c r="E39" s="132" t="str">
+        <v>1、传感器内部姿态模块未就绪或停止响应。
+2、内部供电、连接或姿态模块异常。</v>
+      </c>
+      <c r="F39" s="132" t="str">
+        <v>1、确认是否只有角度通道无数据，保存传感器状态。
+2、检查传感器供电，按允许流程重新启动。
+3、角度数据仍不更新时联系厂家检查姿态模块；恢复前不要依赖姿态探底。</v>
+      </c>
+      <c r="G39" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H39" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="39" ht="66">
-      <c r="A39" s="54"/>
-      <c r="B39" s="49" t="s">
-        <v>177</v>
-      </c>
-      <c r="C39" s="49" t="s">
-        <v>178</v>
-      </c>
-      <c r="D39" s="50" t="s">
-        <v>179</v>
-      </c>
-      <c r="E39" s="50" t="s">
-        <v>180</v>
-      </c>
-      <c r="F39" s="50" t="s">
-        <v>181</v>
-      </c>
-      <c r="G39" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H39" s="47" t="s">
-        <v>27</v>
+    <row r="40" ht="76" customHeight="1">
+      <c r="A40" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B40" s="133" t="str">
+        <v>13-30</v>
+      </c>
+      <c r="C40" s="132" t="str">
+        <v>传感器自检失败</v>
+      </c>
+      <c r="D40" s="132" t="str">
+        <v>触发：传感器上电或测量前自检未通过，表示内部测量、存储、供电或关键部件存在异常。
+影响：设备不使用其数据。</v>
+      </c>
+      <c r="E40" s="132" t="str">
+        <v>1、传感器测量、存储、供电等自检项目未通过。
+2、部件异常或更换后配置不完整。</v>
+      </c>
+      <c r="F40" s="132" t="str">
+        <v>1、停止使用本次测量值，记录具体自检信息。
+2、检查外部供电和连接，再按允许流程重新启动等待自检。
+3、仍不通过时联系厂家，不要跳过自检继续测量。</v>
+      </c>
+      <c r="G40" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H40" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="40" ht="82.5">
-      <c r="A40" s="54"/>
-      <c r="B40" s="49" t="s">
-        <v>182</v>
-      </c>
-      <c r="C40" s="49" t="s">
-        <v>183</v>
-      </c>
-      <c r="D40" s="50" t="s">
-        <v>184</v>
-      </c>
-      <c r="E40" s="50" t="s">
-        <v>185</v>
-      </c>
-      <c r="F40" s="50" t="s">
-        <v>186</v>
-      </c>
-      <c r="G40" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H40" s="47" t="s">
-        <v>27</v>
+    <row r="41" ht="76" customHeight="1">
+      <c r="A41" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B41" s="133" t="str">
+        <v>13-31</v>
+      </c>
+      <c r="C41" s="132" t="str">
+        <v>传感器身份不匹配</v>
+      </c>
+      <c r="D41" s="132" t="str">
+        <v>触发：设备收到传感器应答。
+影响：传感器编号、型号或身份信息与当前设备保存的信息不一致，所以不使用这次数据。</v>
+      </c>
+      <c r="E41" s="132" t="str">
+        <v>1、接错传感器，或无线配到了邻近设备。
+2、更换传感器后，主控仍保留旧身份信息。</v>
+      </c>
+      <c r="F41" s="132" t="str">
+        <v>1、核对传感器实物型号、编号和当前连接对象。
+2、更换过传感器时，按调试流程重新确认连接和配置。
+3、身份一致后再测量；不要通过跳过身份检查继续使用。</v>
+      </c>
+      <c r="G41" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H41" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="41" ht="82.5">
-      <c r="A41" s="54"/>
-      <c r="B41" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="C41" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="D41" s="50" t="s">
-        <v>189</v>
-      </c>
-      <c r="E41" s="50" t="s">
-        <v>190</v>
-      </c>
-      <c r="F41" s="50" t="s">
-        <v>191</v>
-      </c>
-      <c r="G41" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H41" s="47" t="s">
-        <v>27</v>
+    <row r="42" ht="87" customHeight="1">
+      <c r="A42" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B42" s="133" t="str">
+        <v>13-32</v>
+      </c>
+      <c r="C42" s="132" t="str">
+        <v>传感器协议版本不兼容</v>
+      </c>
+      <c r="D42" s="132" t="str">
+        <v>触发：传感器使用的通信版本不在当前主控支持范围内。
+影响：双方不能按同一规则交换数据。</v>
+      </c>
+      <c r="E42" s="132" t="str">
+        <v>1、主控和传感器程序版本不配套。
+2、换入了不适配的传感器或固件。</v>
+      </c>
+      <c r="F42" s="132" t="str">
+        <v>1、记录主控及传感器的软件版本和型号。
+2、按配套说明确认兼容组合，由技术人员决定是否升级或恢复版本。
+3、版本确认通过后再建立连接，反复重启不能解决不兼容。</v>
+      </c>
+      <c r="G42" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H42" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="42" ht="82.5">
-      <c r="A42" s="54"/>
-      <c r="B42" s="49" t="s">
-        <v>192</v>
-      </c>
-      <c r="C42" s="49" t="s">
-        <v>193</v>
-      </c>
-      <c r="D42" s="50" t="s">
-        <v>194</v>
-      </c>
-      <c r="E42" s="50" t="s">
-        <v>195</v>
-      </c>
-      <c r="F42" s="50" t="s">
-        <v>196</v>
-      </c>
-      <c r="G42" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H42" s="47" t="s">
-        <v>27</v>
+    <row r="43" ht="76" customHeight="1">
+      <c r="A43" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B43" s="133" t="str">
+        <v>13-33</v>
+      </c>
+      <c r="C43" s="132" t="str">
+        <v>传感器模式未就绪</v>
+      </c>
+      <c r="D43" s="132" t="str">
+        <v>触发：已要求传感器进入指定测量模式。
+影响：传感器尚未完成准备，这次数据不能用于测量。</v>
+      </c>
+      <c r="E43" s="132" t="str">
+        <v>1、传感器尚在启动、自检或结束上一任务。
+2、模式切换未完成，或传感器状态异常。</v>
+      </c>
+      <c r="F43" s="132" t="str">
+        <v>1、停止重复下发命令，等待传感器完成当前准备。
+2、检查供电、通信和当前模式是否正确。
+3、模式就绪后再测量；长时间不就绪时保存状态和切换日志。</v>
+      </c>
+      <c r="G43" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H43" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="43" ht="66">
-      <c r="A43" s="54"/>
-      <c r="B43" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="C43" s="49" t="str">
+    <row r="44" ht="76" customHeight="1">
+      <c r="A44" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B44" s="133" t="str">
+        <v>13-34</v>
+      </c>
+      <c r="C44" s="132" t="str">
         <v>传感器配置批次不一致</v>
       </c>
-      <c r="D43" s="50" t="s">
-        <v>198</v>
-      </c>
-      <c r="E43" s="50" t="s">
-        <v>199</v>
-      </c>
-      <c r="F43" s="50" t="s">
-        <v>200</v>
-      </c>
-      <c r="G43" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H43" s="47" t="s">
-        <v>27</v>
+      <c r="D44" s="132" t="str">
+        <v>触发：主控记录的传感器配置批次与传感器当前配置批次不同。
+影响：说明连接建立后配置可能已变化。</v>
+      </c>
+      <c r="E44" s="132" t="str">
+        <v>1、连接期间传感器重启、配置被修改或部件被更换。
+2、主控保存的配置信息已经过期。</v>
+      </c>
+      <c r="F44" s="132" t="str">
+        <v>1、停止测量，确认是否有人修改参数或更换传感器。
+2、重新建立连接并读取当前配置，核对型号和参数。
+3、双方配置一致后再测量；无操作也反复变化时检查供电和存储。</v>
+      </c>
+      <c r="G44" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H44" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="44" ht="82.5">
-      <c r="A44" s="54"/>
-      <c r="B44" s="49" t="s">
-        <v>201</v>
-      </c>
-      <c r="C44" s="49" t="s">
-        <v>202</v>
-      </c>
-      <c r="D44" s="50" t="s">
-        <v>203</v>
-      </c>
-      <c r="E44" s="50" t="s">
-        <v>204</v>
-      </c>
-      <c r="F44" s="50" t="s">
-        <v>205</v>
-      </c>
-      <c r="G44" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H44" s="47" t="s">
-        <v>27</v>
+    <row r="45" ht="76" customHeight="1">
+      <c r="A45" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B45" s="133" t="str">
+        <v>13-35</v>
+      </c>
+      <c r="C45" s="132" t="str">
+        <v>传感器上报状态不一致</v>
+      </c>
+      <c r="D45" s="132" t="str">
+        <v>触发：主控记录的周期上报状态与传感器实际状态不一致。
+影响：不能确认后续数据是否连续有效。</v>
+      </c>
+      <c r="E45" s="132" t="str">
+        <v>1、周期上报启动或停止结果未同步。
+2、通信中断或传感器重启后，双方状态不一致。</v>
+      </c>
+      <c r="F45" s="132" t="str">
+        <v>1、停止本轮测量，查看周期上报的实际状态。
+2、检查供电和通信，重新建立连接并按流程启动测量。
+3、确认上报状态一致、连续收到新数据后再运行。</v>
+      </c>
+      <c r="G45" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H45" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="45" ht="82.5">
-      <c r="A45" s="54"/>
-      <c r="B45" s="49" t="s">
-        <v>206</v>
-      </c>
-      <c r="C45" s="49" t="s">
-        <v>207</v>
-      </c>
-      <c r="D45" s="50" t="s">
-        <v>208</v>
-      </c>
-      <c r="E45" s="50" t="s">
-        <v>209</v>
-      </c>
-      <c r="F45" s="50" t="s">
-        <v>210</v>
-      </c>
-      <c r="G45" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H45" s="47" t="s">
-        <v>27</v>
+    <row r="46" ht="76" customHeight="1">
+      <c r="A46" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B46" s="133" t="str">
+        <v>13-36</v>
+      </c>
+      <c r="C46" s="132" t="str">
+        <v>传感器数据过期</v>
+      </c>
+      <c r="D46" s="132" t="str">
+        <v>触发：设备仍保留上一笔传感器数据，但在允许时间内没有收到新的有效值。
+影响：旧数据不能代表当前介质状态，所以这次测量停止。</v>
+      </c>
+      <c r="E46" s="132" t="str">
+        <v>1、无线链路中断，或传感器停止上报。
+2、传感器忙碌、重启或供电不稳。</v>
+      </c>
+      <c r="F46" s="132" t="str">
+        <v>1、不要继续使用旧读数，检查采样时间或更新状态。
+2、检查供电、连接和周期上报是否仍在运行。
+3、重新连接后确认持续收到新样本；数值不变本身不能证明数据过期。</v>
+      </c>
+      <c r="G46" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H46" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="46" ht="66">
-      <c r="A46" s="54"/>
-      <c r="B46" s="49" t="s">
-        <v>211</v>
-      </c>
-      <c r="C46" s="49" t="s">
-        <v>212</v>
-      </c>
-      <c r="D46" s="50" t="s">
-        <v>213</v>
-      </c>
-      <c r="E46" s="50" t="s">
-        <v>214</v>
-      </c>
-      <c r="F46" s="50" t="s">
-        <v>215</v>
-      </c>
-      <c r="G46" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H46" s="47" t="s">
-        <v>27</v>
+    <row r="47" ht="76" customHeight="1">
+      <c r="A47" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B47" s="133" t="str">
+        <v>13-37</v>
+      </c>
+      <c r="C47" s="132" t="str">
+        <v>传感器温度超限</v>
+      </c>
+      <c r="D47" s="132" t="str">
+        <v>触发：传感器测得的自身或介质温度超出允许工作范围。
+影响：当前密度补偿和测量精度不能保证。</v>
+      </c>
+      <c r="E47" s="132" t="str">
+        <v>1、实际温度超出传感器允许工作范围。
+2、温度测量、连接或标定异常。</v>
+      </c>
+      <c r="F47" s="132" t="str">
+        <v>1、核对现场温度和该型号允许范围。
+2、超范围时先恢复适合的测量条件，不要只重启设备。
+3、现场温度正常但读数异常时，保存温度记录并检修传感器。</v>
+      </c>
+      <c r="G47" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H47" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="47" ht="66">
-      <c r="A47" s="54"/>
-      <c r="B47" s="49" t="s">
-        <v>216</v>
-      </c>
-      <c r="C47" s="49" t="s">
-        <v>217</v>
-      </c>
-      <c r="D47" s="50" t="s">
-        <v>218</v>
-      </c>
-      <c r="E47" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="F47" s="50" t="s">
-        <v>220</v>
-      </c>
-      <c r="G47" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H47" s="47" t="s">
-        <v>27</v>
+    <row r="48" ht="76" customHeight="1">
+      <c r="A48" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B48" s="133" t="str">
+        <v>13-38</v>
+      </c>
+      <c r="C48" s="132" t="str">
+        <v>传感器内部故障</v>
+      </c>
+      <c r="D48" s="132" t="str">
+        <v>触发：传感器明确报告内部故障。
+影响：这个故障不属于已单独编号的供电、姿态、通信、温度或自检问题，设备不使用这次数据。</v>
+      </c>
+      <c r="E48" s="132" t="str">
+        <v>1、传感器内部测量、存储或控制单元异常。
+2、供电波动、受潮或冲击等影响内部工作。</v>
+      </c>
+      <c r="F48" s="132" t="str">
+        <v>1、停止使用本次数据，保存传感器同时返回的详细状态。
+2、检查外部供电和连接，按允许流程重新启动复测。
+3、仍报错时按详细状态联系厂家，不要只凭该通用码指定更换部件。</v>
+      </c>
+      <c r="G48" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H48" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="48" ht="66">
-      <c r="A48" s="54"/>
-      <c r="B48" s="52" t="s">
-        <v>221</v>
-      </c>
-      <c r="C48" s="52" t="s">
-        <v>222</v>
-      </c>
-      <c r="D48" s="53" t="s">
-        <v>223</v>
-      </c>
-      <c r="E48" s="53" t="s">
-        <v>224</v>
-      </c>
-      <c r="F48" s="53" t="s">
-        <v>225</v>
-      </c>
-      <c r="G48" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H48" s="47" t="s">
-        <v>27</v>
+    <row r="49" ht="87" customHeight="1">
+      <c r="A49" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B49" s="133" t="str">
+        <v>13-39</v>
+      </c>
+      <c r="C49" s="132" t="str">
+        <v>传感器地址不匹配</v>
+      </c>
+      <c r="D49" s="132" t="str">
+        <v>触发：收到的应答来自非目标地址。
+影响：设备不能确认该数据属于当前连接的传感器。</v>
+      </c>
+      <c r="E49" s="132" t="str">
+        <v>1、目标地址设置不正确，或连接到了其它设备。
+2、链路中混入其它地址或旧请求的应答。</v>
+      </c>
+      <c r="F49" s="132" t="str">
+        <v>1、核对当前请求的目标地址、传感器地址和实际连接对象。
+2、排除地址冲突或错误配对，保存请求与应答。
+3、重新确认连接后再测量；广播应答由技术人员按对应协议核对。</v>
+      </c>
+      <c r="G49" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H49" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="49" ht="82.5">
-      <c r="A49" s="54"/>
-      <c r="B49" s="52" t="s">
-        <v>226</v>
-      </c>
-      <c r="C49" s="52" t="str">
+    <row r="50" ht="76" customHeight="1">
+      <c r="A50" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B50" s="133" t="str">
+        <v>13-40</v>
+      </c>
+      <c r="C50" s="132" t="str">
         <v>传感器连接状态失效</v>
       </c>
-      <c r="D49" s="53" t="s">
-        <v>227</v>
-      </c>
-      <c r="E49" s="53" t="s">
-        <v>228</v>
-      </c>
-      <c r="F49" s="53" t="s">
-        <v>229</v>
-      </c>
-      <c r="G49" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H49" s="47" t="s">
-        <v>27</v>
+      <c r="D50" s="132" t="str">
+        <v>触发：传感器不再认可当前连接。
+影响：后续命令和数据不能继续沿用原连接状态。</v>
+      </c>
+      <c r="E50" s="132" t="str">
+        <v>1、主控或传感器重启后，原连接状态失效。
+2、通信长时间中断，或传感器已经更换。</v>
+      </c>
+      <c r="F50" s="132" t="str">
+        <v>1、停止沿用当前测量数据，确认两端是否发生重启或更换。
+2、检查供电和链路，重新建立传感器连接。
+3、连接确认成功并取得新数据后重新测量。</v>
+      </c>
+      <c r="G50" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H50" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="50" ht="66">
-      <c r="A50" s="54"/>
-      <c r="B50" s="52" t="s">
-        <v>230</v>
-      </c>
-      <c r="C50" s="52" t="str">
+    <row r="51" ht="76" customHeight="1">
+      <c r="A51" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B51" s="133" t="str">
+        <v>13-41</v>
+      </c>
+      <c r="C51" s="132" t="str">
         <v>传感器应答序号不一致</v>
       </c>
-      <c r="D50" s="53" t="s">
-        <v>231</v>
-      </c>
-      <c r="E50" s="53" t="s">
-        <v>232</v>
-      </c>
-      <c r="F50" s="53" t="s">
-        <v>233</v>
-      </c>
-      <c r="G50" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H50" s="47" t="s">
-        <v>27</v>
+      <c r="D51" s="132" t="str">
+        <v>触发：传感器应答的先后编号与当前请求不一致。
+影响：可能存在丢失、乱序或旧应答混入。</v>
+      </c>
+      <c r="E51" s="132" t="str">
+        <v>1、旧应答晚到、丢包或应答顺序混乱。
+2、传感器重启后，请求和应答编号未同步。</v>
+      </c>
+      <c r="F51" s="132" t="str">
+        <v>1、停止重复下发，保存故障前后的请求与应答序号。
+2、检查链路延迟、供电和是否存在多端同时操作。
+3、重新建立连接后再测量；反复出现时交由技术人员分析通信记录。</v>
+      </c>
+      <c r="G51" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H51" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="51" ht="82.5">
-      <c r="A51" s="54"/>
-      <c r="B51" s="52" t="s">
-        <v>234</v>
-      </c>
-      <c r="C51" s="52" t="str">
+    <row r="52" ht="76" customHeight="1">
+      <c r="A52" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B52" s="133" t="str">
+        <v>13-42</v>
+      </c>
+      <c r="C52" s="132" t="str">
         <v>传感器需要重新确认连接</v>
       </c>
-      <c r="D51" s="53" t="s">
-        <v>235</v>
-      </c>
-      <c r="E51" s="53" t="s">
-        <v>236</v>
-      </c>
-      <c r="F51" s="53" t="s">
-        <v>237</v>
-      </c>
-      <c r="G51" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H51" s="47" t="s">
-        <v>27</v>
+      <c r="D52" s="132" t="str">
+        <v>触发：传感器拒绝继续使用当前连接。
+影响：要求主控重新完成身份和能力确认。</v>
+      </c>
+      <c r="E52" s="132" t="str">
+        <v>1、传感器重启或连接中断后，需要重新确认身份和能力。
+2、双方保存的连接状态不一致。</v>
+      </c>
+      <c r="F52" s="132" t="str">
+        <v>1、停止本轮操作，重新执行传感器连接确认。
+2、核对身份、能力和配置，不沿用旧测量值。
+3、连接成功后重新发起原操作；频繁发生时检查供电和掉线记录。</v>
+      </c>
+      <c r="G52" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H52" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="52" ht="66">
-      <c r="A52" s="54"/>
-      <c r="B52" s="52" t="s">
-        <v>238</v>
-      </c>
-      <c r="C52" s="52" t="str">
+    <row r="53" ht="76" customHeight="1">
+      <c r="A53" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B53" s="133" t="str">
+        <v>13-43</v>
+      </c>
+      <c r="C53" s="132" t="str">
         <v>收到重复的传感器数据</v>
       </c>
-      <c r="D52" s="53" t="s">
-        <v>239</v>
-      </c>
-      <c r="E52" s="53" t="s">
-        <v>240</v>
-      </c>
-      <c r="F52" s="53" t="s">
-        <v>241</v>
-      </c>
-      <c r="G52" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H52" s="47" t="s">
-        <v>27</v>
+      <c r="D53" s="132" t="str">
+        <v>触发：设备收到已经处理过的旧应答或重复数据，为避免误用旧测量结果。
+影响：这次数据被拒绝。</v>
+      </c>
+      <c r="E53" s="132" t="str">
+        <v>1、同一应答重复到达，或旧数据滞留。
+2、传感器编号未正常更新，或链路存在重发异常。</v>
+      </c>
+      <c r="F53" s="132" t="str">
+        <v>1、不采用本次重复数据，保存连续应答记录。
+2、检查无线链路和是否有重复操作。
+3、重新建立连接并取得新样本后再测量；持续重复时检查传感器和通信模块。</v>
+      </c>
+      <c r="G53" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H53" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="53" ht="66">
-      <c r="A53" s="54"/>
-      <c r="B53" s="52" t="s">
-        <v>242</v>
-      </c>
-      <c r="C53" s="52" t="str">
+    <row r="54" ht="76" customHeight="1">
+      <c r="A54" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B54" s="133" t="str">
+        <v>13-44</v>
+      </c>
+      <c r="C54" s="132" t="str">
         <v>传感器不支持所需功能</v>
       </c>
-      <c r="D53" s="53" t="s">
-        <v>243</v>
-      </c>
-      <c r="E53" s="53" t="s">
-        <v>244</v>
-      </c>
-      <c r="F53" s="53" t="s">
-        <v>245</v>
-      </c>
-      <c r="G53" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H53" s="47" t="s">
-        <v>27</v>
+      <c r="D54" s="132" t="str">
+        <v>触发：当前传感器没有设备所需的测量或维护能力。
+影响：相关功能不能执行。</v>
+      </c>
+      <c r="E54" s="132" t="str">
+        <v>1、传感器型号或版本不具备所需功能。
+2、更换传感器后没有重新确认能力。</v>
+      </c>
+      <c r="F54" s="132" t="str">
+        <v>1、核对传感器型号、软件版本和所选功能。
+2、按配套说明改用支持的功能，或由技术人员确认升级、更换方案。
+3、能力确认通过后再操作，不要强行跳过检查。</v>
+      </c>
+      <c r="G54" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H54" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="54" ht="66">
-      <c r="A54" s="54"/>
-      <c r="B54" s="49" t="s">
-        <v>246</v>
-      </c>
-      <c r="C54" s="49" t="s">
-        <v>247</v>
-      </c>
-      <c r="D54" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="E54" s="50" t="s">
-        <v>249</v>
-      </c>
-      <c r="F54" s="50" t="s">
-        <v>250</v>
-      </c>
-      <c r="G54" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H54" s="47" t="s">
-        <v>27</v>
+    <row r="55" ht="76" customHeight="1">
+      <c r="A55" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B55" s="133" t="str">
+        <v>13-45</v>
+      </c>
+      <c r="C55" s="132" t="str">
+        <v>传感器命令不支持</v>
+      </c>
+      <c r="D55" s="132" t="str">
+        <v>触发：传感器能够通信。
+影响：明确表示不认识或不支持这次操作命令。</v>
+      </c>
+      <c r="E55" s="132" t="str">
+        <v>1、所发命令不在传感器支持范围内。
+2、主控和传感器型号、协议或版本不配套。</v>
+      </c>
+      <c r="F55" s="132" t="str">
+        <v>1、记录被拒绝的操作及两端版本。
+2、确认该型号是否支持此命令，排除错误连接对象。
+3、按配套流程调整后再操作；不要持续重复发送同一不支持命令。</v>
+      </c>
+      <c r="G55" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H55" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="55" ht="82.5">
-      <c r="A55" s="54"/>
-      <c r="B55" s="49" t="s">
-        <v>251</v>
-      </c>
-      <c r="C55" s="49" t="str">
+    <row r="56" ht="76" customHeight="1">
+      <c r="A56" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B56" s="133" t="str">
+        <v>13-46</v>
+      </c>
+      <c r="C56" s="132" t="str">
         <v>传感器不接受当前参数</v>
       </c>
-      <c r="D55" s="50" t="s">
-        <v>252</v>
-      </c>
-      <c r="E55" s="50" t="s">
-        <v>253</v>
-      </c>
-      <c r="F55" s="50" t="s">
-        <v>254</v>
-      </c>
-      <c r="G55" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H55" s="47" t="s">
-        <v>27</v>
+      <c r="D56" s="132" t="str">
+        <v>触发：传感器识别了命令。
+影响：认为这次设置值或组合条件不允许，所以没有执行。</v>
+      </c>
+      <c r="E56" s="132" t="str">
+        <v>1、设置值超出传感器范围，或必要参数缺失。
+2、单位、模式或参数组合不符合传感器要求。</v>
+      </c>
+      <c r="F56" s="132" t="str">
+        <v>1、记录被拒绝的参数名称、数值和单位。
+2、对照该型号说明检查范围和组合，不盲目套用其它设备的默认值。
+3、修正并确认传感器接受设置后再测量。</v>
+      </c>
+      <c r="G56" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H56" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="56" ht="66">
-      <c r="A56" s="54"/>
-      <c r="B56" s="49" t="s">
-        <v>255</v>
-      </c>
-      <c r="C56" s="49" t="s">
-        <v>256</v>
-      </c>
-      <c r="D56" s="50" t="s">
-        <v>257</v>
-      </c>
-      <c r="E56" s="50" t="s">
-        <v>258</v>
-      </c>
-      <c r="F56" s="50" t="s">
-        <v>259</v>
-      </c>
-      <c r="G56" s="55" t="s">
-        <v>26</v>
-      </c>
-      <c r="H56" s="47" t="s">
-        <v>27</v>
+    <row r="57" ht="76" customHeight="1">
+      <c r="A57" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B57" s="133" t="str">
+        <v>13-47</v>
+      </c>
+      <c r="C57" s="132" t="str">
+        <v>传感器测量模式不一致</v>
+      </c>
+      <c r="D57" s="132" t="str">
+        <v>触发：传感器返回的数据属于另一种测量模式。
+影响：不能用于当前液位、密度或维护操作。</v>
+      </c>
+      <c r="E57" s="132" t="str">
+        <v>1、模式切换未完成，或旧模式数据仍在链路中。
+2、传感器复位后回到其它模式。</v>
+      </c>
+      <c r="F57" s="132" t="str">
+        <v>1、停止使用本次数据，核对需要的模式和实际返回模式。
+2、重新建立连接并按流程选择测量模式，等待就绪。
+3、收到对应模式的新数据后再测量；反复不一致时保存切换记录。</v>
+      </c>
+      <c r="G57" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H57" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="57" ht="82.5">
-      <c r="A57" s="54"/>
-      <c r="B57" s="49" t="s">
-        <v>260</v>
-      </c>
-      <c r="C57" s="49" t="str">
+    <row r="58" ht="76" customHeight="1">
+      <c r="A58" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B58" s="133" t="str">
+        <v>13-48</v>
+      </c>
+      <c r="C58" s="132" t="str">
         <v>传感器当前模式不允许操作</v>
       </c>
-      <c r="D57" s="50" t="s">
-        <v>261</v>
-      </c>
-      <c r="E57" s="50" t="s">
-        <v>262</v>
-      </c>
-      <c r="F57" s="50" t="s">
-        <v>263</v>
-      </c>
-      <c r="G57" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H57" s="47" t="s">
-        <v>27</v>
+      <c r="D58" s="132" t="str">
+        <v>触发：这次命令在传感器当前工作状态下被禁止。
+影响：需要先退出原状态或完成前一步操作。</v>
+      </c>
+      <c r="E58" s="132" t="str">
+        <v>1、传感器仍在自检、标定、保存或其它测量状态。
+2、当前操作顺序不符合该模式要求。</v>
+      </c>
+      <c r="F58" s="132" t="str">
+        <v>1、先完成或正常退出上一项操作。
+2、确认当前模式允许执行目标命令，再按正常顺序操作。
+3、仍被拒绝时保存模式和命令记录，交由技术人员确认。</v>
+      </c>
+      <c r="G58" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H58" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="58" ht="82.5">
-      <c r="A58" s="54"/>
-      <c r="B58" s="49" t="s">
-        <v>264</v>
-      </c>
-      <c r="C58" s="49" t="str">
+    <row r="59" ht="76" customHeight="1">
+      <c r="A59" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B59" s="133" t="str">
+        <v>13-49</v>
+      </c>
+      <c r="C59" s="132" t="str">
         <v>上一次传感器操作尚未完成</v>
       </c>
-      <c r="D58" s="50" t="s">
-        <v>265</v>
-      </c>
-      <c r="E58" s="50" t="s">
-        <v>266</v>
-      </c>
-      <c r="F58" s="50" t="s">
-        <v>267</v>
-      </c>
-      <c r="G58" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H58" s="47" t="s">
-        <v>27</v>
+      <c r="D59" s="132" t="str">
+        <v>触发：上一项传感器操作仍在处理中。
+影响：新命令暂时不能开始。</v>
+      </c>
+      <c r="E59" s="132" t="str">
+        <v>1、上一项操作尚未结束，新命令已到达。
+2、处理或应答延迟，导致完成状态尚未确认。</v>
+      </c>
+      <c r="F59" s="132" t="str">
+        <v>1、停止重复下发，先等待上一项操作完成。
+2、若超过正常等待时间，检查完成应答和通信链路。
+3、确认上一项已结束后再操作；状态无法确认时重新建立连接。</v>
+      </c>
+      <c r="G59" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H59" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="59" ht="66">
-      <c r="A59" s="54"/>
-      <c r="B59" s="49" t="s">
-        <v>268</v>
-      </c>
-      <c r="C59" s="49" t="s">
-        <v>269</v>
-      </c>
-      <c r="D59" s="50" t="s">
-        <v>270</v>
-      </c>
-      <c r="E59" s="50" t="s">
-        <v>271</v>
-      </c>
-      <c r="F59" s="50" t="s">
-        <v>272</v>
-      </c>
-      <c r="G59" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H59" s="47" t="s">
-        <v>27</v>
+    <row r="60" ht="76" customHeight="1">
+      <c r="A60" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B60" s="133" t="str">
+        <v>13-50</v>
+      </c>
+      <c r="C60" s="132" t="str">
+        <v>传感器设备忙</v>
+      </c>
+      <c r="D60" s="132" t="str">
+        <v>触发：传感器正在执行其它测量、保存或自检任务。
+影响：暂时不能接受这次操作。</v>
+      </c>
+      <c r="E60" s="132" t="str">
+        <v>1、传感器正在测量、自检、标定或保存。
+2、内部任务未正常结束，或供电不稳导致反复启动。</v>
+      </c>
+      <c r="F60" s="132" t="str">
+        <v>1、不要连续重复操作，先等待当前任务结束。
+2、长期忙碌时查看任务状态、供电和重启记录。
+3、按允许流程重新连接或重启；仍忙碌时保存状态联系厂家。</v>
+      </c>
+      <c r="G60" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H60" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="60" ht="66">
-      <c r="A60" s="54"/>
-      <c r="B60" s="49" t="s">
-        <v>273</v>
-      </c>
-      <c r="C60" s="49" t="s">
-        <v>274</v>
-      </c>
-      <c r="D60" s="50" t="s">
-        <v>275</v>
-      </c>
-      <c r="E60" s="50" t="s">
-        <v>276</v>
-      </c>
-      <c r="F60" s="50" t="s">
-        <v>277</v>
-      </c>
-      <c r="G60" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H60" s="47" t="s">
-        <v>27</v>
+    <row r="61" ht="76" customHeight="1">
+      <c r="A61" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B61" s="133" t="str">
+        <v>13-51</v>
+      </c>
+      <c r="C61" s="132" t="str">
+        <v>传感器参数校验失败</v>
+      </c>
+      <c r="D61" s="132" t="str">
+        <v>触发：传感器返回的参数内容不完整或校验不通过。
+影响：设备不会使用这次参数。</v>
+      </c>
+      <c r="E61" s="132" t="str">
+        <v>1、参数应答不完整，或传输受到干扰。
+2、传感器参数内容损坏，或双方参数格式不配套。</v>
+      </c>
+      <c r="F61" s="132" t="str">
+        <v>1、先重新读取参数，并保存失败应答。
+2、检查通信、供电和两端版本，核对已有有效参数备份。
+3、需要重新写入时只使用已确认的参数；读回校验正常后再测量。</v>
+      </c>
+      <c r="G61" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H61" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="61" ht="66">
-      <c r="A61" s="54"/>
-      <c r="B61" s="49" t="s">
-        <v>278</v>
-      </c>
-      <c r="C61" s="49" t="str">
+    <row r="62" ht="76" customHeight="1">
+      <c r="A62" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B62" s="133" t="str">
+        <v>13-52</v>
+      </c>
+      <c r="C62" s="132" t="str">
         <v>传感器采样序号异常</v>
       </c>
-      <c r="D61" s="50" t="s">
-        <v>279</v>
-      </c>
-      <c r="E61" s="50" t="s">
-        <v>280</v>
-      </c>
-      <c r="F61" s="50" t="s">
-        <v>281</v>
-      </c>
-      <c r="G61" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H61" s="47" t="s">
-        <v>27</v>
+      <c r="D62" s="132" t="str">
+        <v>触发：连续数据的采样编号没有按预期更新。
+影响：设备不能确认数据是否来自新的有效采样。</v>
+      </c>
+      <c r="E62" s="132" t="str">
+        <v>1、连续样本重复、丢失或延迟到达。
+2、传感器重启，或采样编号未按要求更新。</v>
+      </c>
+      <c r="F62" s="132" t="str">
+        <v>1、停止使用本轮连续数据，保存故障前后的采样编号。
+2、检查供电、通信和传感器重启记录。
+3、重新开始测量，确认采样编号按规则更新后再采用结果。</v>
+      </c>
+      <c r="G62" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H62" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="62" ht="66">
-      <c r="A62" s="54"/>
-      <c r="B62" s="49" t="s">
-        <v>282</v>
-      </c>
-      <c r="C62" s="49" t="s">
-        <v>283</v>
-      </c>
-      <c r="D62" s="50" t="s">
-        <v>284</v>
-      </c>
-      <c r="E62" s="50" t="s">
-        <v>285</v>
-      </c>
-      <c r="F62" s="50" t="s">
-        <v>286</v>
-      </c>
-      <c r="G62" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H62" s="47" t="s">
-        <v>27</v>
+    <row r="63" ht="76" customHeight="1">
+      <c r="A63" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B63" s="133" t="str">
+        <v>13-53</v>
+      </c>
+      <c r="C63" s="132" t="str">
+        <v>传感器周期上报意外停止</v>
+      </c>
+      <c r="D63" s="132" t="str">
+        <v>触发：周期测量已经启动。
+影响：传感器在未收到正常停止命令时停止了连续上报。</v>
+      </c>
+      <c r="E63" s="132" t="str">
+        <v>1、传感器供电中断、复位或自行退出测量。
+2、无线掉线或异常停止操作影响了上报。</v>
+      </c>
+      <c r="F63" s="132" t="str">
+        <v>1、停止依赖旧数据，检查供电、连接和停止原因。
+2、重新建立连接，按流程启动周期测量。
+3、确认连续收到新样本后再运行；再次中断时保存上报及重启记录。</v>
+      </c>
+      <c r="G63" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H63" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="63" ht="66">
-      <c r="A63" s="54"/>
-      <c r="B63" s="49" t="s">
-        <v>287</v>
-      </c>
-      <c r="C63" s="49" t="s">
-        <v>288</v>
-      </c>
-      <c r="D63" s="50" t="s">
-        <v>289</v>
-      </c>
-      <c r="E63" s="50" t="s">
-        <v>290</v>
-      </c>
-      <c r="F63" s="50" t="s">
-        <v>291</v>
-      </c>
-      <c r="G63" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H63" s="47" t="s">
-        <v>27</v>
+    <row r="64" ht="87" customHeight="1">
+      <c r="A64" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B64" s="133" t="str">
+        <v>13-54</v>
+      </c>
+      <c r="C64" s="132" t="str">
+        <v>传感器周期上报未启动</v>
+      </c>
+      <c r="D64" s="132" t="str">
+        <v>触发：设备准备读取连续数据。
+影响：传感器反馈周期上报尚未启动。</v>
+      </c>
+      <c r="E64" s="132" t="str">
+        <v>1、启动命令未成功执行，或传感器仍在其它模式。
+2、传感器启动后又复位，回到未上报状态。</v>
+      </c>
+      <c r="F64" s="132" t="str">
+        <v>1、核对启动应答和当前模式，不要直接等待不存在的数据流。
+2、按正常流程重新启动周期测量。
+3、确认启动成功且收到新样本后再测量；仍失败时检查供电和通信。</v>
+      </c>
+      <c r="G64" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H64" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="64" ht="66">
-      <c r="A64" s="54"/>
-      <c r="B64" s="49" t="s">
-        <v>292</v>
-      </c>
-      <c r="C64" s="49" t="str">
+    <row r="65" ht="76" customHeight="1">
+      <c r="A65" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B65" s="133" t="str">
+        <v>13-55</v>
+      </c>
+      <c r="C65" s="132" t="str">
         <v>传感器周期上报重复启动</v>
       </c>
-      <c r="D64" s="50" t="s">
-        <v>293</v>
-      </c>
-      <c r="E64" s="50" t="s">
-        <v>294</v>
-      </c>
-      <c r="F64" s="50" t="s">
-        <v>295</v>
-      </c>
-      <c r="G64" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H64" s="47" t="s">
-        <v>27</v>
+      <c r="D65" s="132" t="str">
+        <v>触发：设备再次要求启动周期上报。
+影响：传感器反馈该功能已经在运行，说明启动命令重复或状态不同步。</v>
+      </c>
+      <c r="E65" s="132" t="str">
+        <v>1、上一轮周期上报还在运行。
+2、启动应答丢失或重复操作，使双方状态不同步。</v>
+      </c>
+      <c r="F65" s="132" t="str">
+        <v>1、停止重复启动，先确认传感器是否已经在上报。
+2、需要重新开始时先正常停止上一轮，再按流程启动。
+3、确认本轮状态和新样本对应后再使用结果。</v>
+      </c>
+      <c r="G65" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H65" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="65" ht="82.5">
-      <c r="A65" s="54"/>
-      <c r="B65" s="49" t="s">
-        <v>296</v>
-      </c>
-      <c r="C65" s="49" t="s">
-        <v>297</v>
-      </c>
-      <c r="D65" s="50" t="s">
-        <v>298</v>
-      </c>
-      <c r="E65" s="50" t="s">
-        <v>299</v>
-      </c>
-      <c r="F65" s="50" t="s">
-        <v>300</v>
-      </c>
-      <c r="G65" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H65" s="47" t="s">
-        <v>27</v>
+    <row r="66" ht="76" customHeight="1">
+      <c r="A66" s="136" t="str">
+        <v>传感器与密度</v>
+      </c>
+      <c r="B66" s="133" t="str">
+        <v>13-56</v>
+      </c>
+      <c r="C66" s="132" t="str">
+        <v>传感器周期上报退出失败</v>
+      </c>
+      <c r="D66" s="132" t="str">
+        <v>触发：设备要求停止周期上报。
+影响：传感器没能正常退出，后续模式切换不能安全继续。</v>
+      </c>
+      <c r="E66" s="132" t="str">
+        <v>1、停止命令未执行完成，或传感器内部任务未退出。
+2、通信中断、供电波动或内部状态异常。</v>
+      </c>
+      <c r="F66" s="132" t="str">
+        <v>1、暂停后续模式切换，先确认停止命令及应答。
+2、按允许流程重新停止或重新建立连接。
+3、确认周期上报已退出后再切换模式；仍失败时保存记录联系检修。</v>
+      </c>
+      <c r="G66" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H66" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="66" ht="66">
-      <c r="A66" s="54" t="s">
-        <v>301</v>
-      </c>
-      <c r="B66" s="49" t="s">
-        <v>302</v>
-      </c>
-      <c r="C66" s="49" t="str">
+    <row r="67" ht="76" customHeight="1">
+      <c r="A67" s="141" t="str">
+        <v>零点与位置检测</v>
+      </c>
+      <c r="B67" s="156" t="str">
+        <v>14-9</v>
+      </c>
+      <c r="C67" s="144" t="str">
         <v>零点位置超出允许范围</v>
       </c>
-      <c r="D66" s="50" t="s">
-        <v>303</v>
-      </c>
-      <c r="E66" s="50" t="s">
-        <v>304</v>
-      </c>
-      <c r="F66" s="50" t="s">
-        <v>305</v>
-      </c>
-      <c r="G66" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H66" s="47" t="s">
-        <v>27</v>
+      <c r="D67" s="144" t="str">
+        <v>触发：粗找、精找或回零完成后，尺带位置仍偏离设定零点超过允许值。
+影响：设备不能把当前位置作为可靠零点。</v>
+      </c>
+      <c r="E67" s="144" t="str">
+        <v>1、零点、周长或位置基准设置不正确。
+2、尺带打滑、机构异常或位置反馈失真。</v>
+      </c>
+      <c r="F67" s="144" t="str">
+        <v>1、停止重复找零，记录本次最终位置及允许范围。
+2、检查零点机构、尺带、编码器和相关参数。
+3、排除原因后重新回零或零点标定，确认最终位置在允许范围内。</v>
+      </c>
+      <c r="G67" s="145" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H67" s="146" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="67" ht="99">
-      <c r="A67" s="54"/>
-      <c r="B67" s="49" t="s">
-        <v>306</v>
-      </c>
-      <c r="C67" s="49" t="str">
-        <v>陀螺仪基准不稳定</v>
-      </c>
-      <c r="D67" s="50" t="s">
-        <v>307</v>
-      </c>
-      <c r="E67" s="50" t="s">
-        <v>308</v>
-      </c>
-      <c r="F67" s="50" t="s">
-        <v>309</v>
-      </c>
-      <c r="G67" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H67" s="47" t="s">
-        <v>27</v>
+    <row r="68" ht="102" customHeight="1">
+      <c r="A68" s="136" t="str">
+        <v>零点与位置检测</v>
+      </c>
+      <c r="B68" s="133" t="str">
+        <v>14-11</v>
+      </c>
+      <c r="C68" s="132" t="str">
+        <v>陀螺仪基准无效或不稳定</v>
+      </c>
+      <c r="D68" s="132" t="str">
+        <v>用于角度探底的姿态基准不可用，或回零后建立基准时5次采样中任一轴的最大、最小角度差超过2°。基准在回零后的采样位置建立，不要求探头接触罐底。</v>
+      </c>
+      <c r="E68" s="132" t="str">
+        <v>1、建立基准时探头晃动，或姿态读数变化过大。
+2、基准没有成功建立或已经失效，姿态部件安装也可能松动。</v>
+      </c>
+      <c r="F68" s="132" t="str">
+        <v>1、停止相关测量，检查探头是否还在晃动、姿态安装是否牢固。
+2、确认角度数据有效后，按回零流程重新建立基准，不要求把探头压在罐底。
+3、确认基准建立成功、采样波动符合要求后再探底；仍失败时保存角度采样日志。</v>
+      </c>
+      <c r="G68" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H68" s="135" t="str">
+        <v>CPU2共享故障；角度探底；屏幕名称仍为“陀螺仪基准不稳定”</v>
       </c>
     </row>
-    <row r="68" ht="66">
-      <c r="A68" s="54"/>
-      <c r="B68" s="49" t="s">
-        <v>310</v>
-      </c>
-      <c r="C68" s="49" t="s">
-        <v>311</v>
-      </c>
-      <c r="D68" s="50" t="s">
-        <v>312</v>
-      </c>
-      <c r="E68" s="50" t="s">
-        <v>313</v>
-      </c>
-      <c r="F68" s="50" t="s">
-        <v>314</v>
-      </c>
-      <c r="G68" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H68" s="47" t="s">
-        <v>27</v>
+    <row r="69" ht="102" customHeight="1">
+      <c r="A69" s="136" t="str">
+        <v>零点与位置检测</v>
+      </c>
+      <c r="B69" s="147" t="str">
+        <v>14-12</v>
+      </c>
+      <c r="C69" s="148" t="str">
+        <v>当前位置数据无效</v>
+      </c>
+      <c r="D69" s="132" t="str">
+        <v>触发：设备在准备运动、判断到位或提交结果时没有取得可靠当前位置。
+影响：不能确认机构所处位置，所以停止这次动作。</v>
+      </c>
+      <c r="E69" s="132" t="str">
+        <v>1、位置采集或位置记录不可用。
+2、尺带、编码器或零点基准异常。</v>
+      </c>
+      <c r="F69" s="132" t="str">
+        <v>注意：先排除风险，再恢复操作。
+1、停止运动，先确认机构实际位置，不依赖当前无效读数。
+2、检查是否同时存在编码器、掉电保存或零点故障，先处理对应原因。
+3、重新建立可靠位置基准后再执行运动或测量。</v>
+      </c>
+      <c r="G69" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H69" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="69" ht="66">
-      <c r="A69" s="54"/>
-      <c r="B69" s="49" t="s">
-        <v>315</v>
-      </c>
-      <c r="C69" s="49" t="s">
-        <v>316</v>
-      </c>
-      <c r="D69" s="50" t="s">
-        <v>317</v>
-      </c>
-      <c r="E69" s="50" t="s">
-        <v>318</v>
-      </c>
-      <c r="F69" s="50" t="s">
-        <v>319</v>
-      </c>
-      <c r="G69" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H69" s="47" t="s">
-        <v>27</v>
+    <row r="70" ht="76" customHeight="1">
+      <c r="A70" s="136" t="str">
+        <v>零点与位置检测</v>
+      </c>
+      <c r="B70" s="133" t="str">
+        <v>14-13</v>
+      </c>
+      <c r="C70" s="132" t="str">
+        <v>运动越过目标位置</v>
+      </c>
+      <c r="D70" s="132" t="str">
+        <v>触发：电机运行过程中实际位置已越过目标且未在允许范围内停下。
+影响：设备判断这次到位失败并停止运动。</v>
+      </c>
+      <c r="E70" s="132" t="str">
+        <v>1、停止响应或减速条件不合适。
+2、位置反馈、尺带传动或位置参数异常。</v>
+      </c>
+      <c r="F70" s="132" t="str">
+        <v>1、停止运动，记录目标位置、实际位置和速度。
+2、检查制动响应、传动和位置反馈，再核对运动参数。
+3、在安全行程内做低速短程测试，确认不再越过目标后恢复使用。</v>
+      </c>
+      <c r="G70" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H70" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="70" ht="66">
-      <c r="A70" s="54"/>
-      <c r="B70" s="49" t="s">
-        <v>320</v>
-      </c>
-      <c r="C70" s="49" t="str">
+    <row r="71" ht="76" customHeight="1">
+      <c r="A71" s="136" t="str">
+        <v>零点与位置检测</v>
+      </c>
+      <c r="B71" s="133" t="str">
+        <v>14-14</v>
+      </c>
+      <c r="C71" s="132" t="str">
         <v>电机到位偏差过大</v>
       </c>
-      <c r="D70" s="50" t="s">
-        <v>321</v>
-      </c>
-      <c r="E70" s="50" t="s">
-        <v>322</v>
-      </c>
-      <c r="F70" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="G70" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H70" s="47" t="s">
-        <v>27</v>
+      <c r="D71" s="132" t="str">
+        <v>触发：电机已经停稳。
+影响：最终位置与目标位置的差值超过允许范围，设备不把这次运动视为到位。</v>
+      </c>
+      <c r="E71" s="132" t="str">
+        <v>1、机构卡涩、打滑或驱动力不足。
+2、周长换算、目标值或位置反馈异常。</v>
+      </c>
+      <c r="F71" s="132" t="str">
+        <v>1、确认已经停稳，记录目标与实际位置的差值。
+2、检查尺带、编码轮及运动参数，不只放宽允许偏差。
+3、修复或按需重新标定后测试，确认到位偏差符合要求。</v>
+      </c>
+      <c r="G71" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H71" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="71" ht="66">
-      <c r="A71" s="54"/>
-      <c r="B71" s="49" t="s">
-        <v>324</v>
-      </c>
-      <c r="C71" s="49" t="s">
-        <v>325</v>
-      </c>
-      <c r="D71" s="50" t="s">
-        <v>326</v>
-      </c>
-      <c r="E71" s="50" t="s">
-        <v>327</v>
-      </c>
-      <c r="F71" s="50" t="s">
-        <v>328</v>
-      </c>
-      <c r="G71" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H71" s="47" t="s">
-        <v>329</v>
+    <row r="72" ht="102" customHeight="1">
+      <c r="A72" s="136" t="str">
+        <v>零点与位置检测</v>
+      </c>
+      <c r="B72" s="133" t="str">
+        <v>14-15</v>
+      </c>
+      <c r="C72" s="132" t="str">
+        <v>结果提交时电机未停</v>
+      </c>
+      <c r="D72" s="132" t="str">
+        <v>触发：SI测量结果提交前，设备记录的电机状态不是停止，这次结果不提交。
+影响：这个故障表示运行状态记录未停止，不直接说明机构仍在移动。</v>
+      </c>
+      <c r="E72" s="132" t="str">
+        <v>1、结果提交时，设备仍记录为上行或下行。
+2、停止流程未完成，或异常退出后运动状态未更新。</v>
+      </c>
+      <c r="F72" s="132" t="str">
+        <v>1、先确认机构实际是否停止，再查看设备记录的电机状态。
+2、机构已停但状态未恢复时，保存停止前后的日志交技术人员检查。
+3、状态恢复正常后重新执行测量；不要把未提交结果当成本次有效结果。</v>
+      </c>
+      <c r="G72" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H72" s="135" t="str">
+        <v>CPU2共享故障；SI结果提交</v>
       </c>
     </row>
-    <row r="72" ht="82.5">
-      <c r="A72" s="54" t="s">
-        <v>330</v>
-      </c>
-      <c r="B72" s="49" t="s">
-        <v>331</v>
-      </c>
-      <c r="C72" s="49" t="str">
+    <row r="73" ht="76" customHeight="1">
+      <c r="A73" s="141" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B73" s="156" t="str">
+        <v>15-6</v>
+      </c>
+      <c r="C73" s="144" t="str">
         <v>上行找液位到达位置上限</v>
       </c>
-      <c r="D72" s="50" t="s">
-        <v>332</v>
-      </c>
-      <c r="E72" s="50" t="s">
-        <v>333</v>
-      </c>
-      <c r="F72" s="50" t="s">
-        <v>305</v>
-      </c>
-      <c r="G72" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H72" s="47" t="s">
-        <v>27</v>
+      <c r="D73" s="144" t="str">
+        <v>触发：向上搜索液位。
+影响：浮子或探头已到达罐高上限还是没有识别到液面，为防止越界，设备停止测量。</v>
+      </c>
+      <c r="E73" s="144" t="str">
+        <v>1、实际液面不在当前可搜索范围内。
+2、罐高、起始位置或位置换算不准，或液面信号未被识别。</v>
+      </c>
+      <c r="F73" s="144" t="str">
+        <v>1、停止继续上行，核对现场液位和当前搜索范围。
+2、检查罐高、零点、位置显示及液面信号。
+3、确认液面在允许范围内后重新搜索，不要盲目扩大上限。</v>
+      </c>
+      <c r="G73" s="145" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H73" s="146" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="73" ht="82.5">
-      <c r="A73" s="54"/>
-      <c r="B73" s="49" t="s">
-        <v>334</v>
-      </c>
-      <c r="C73" s="49" t="s">
-        <v>335</v>
-      </c>
-      <c r="D73" s="50" t="s">
-        <v>336</v>
-      </c>
-      <c r="E73" s="50" t="s">
-        <v>337</v>
-      </c>
-      <c r="F73" s="50" t="s">
-        <v>305</v>
-      </c>
-      <c r="G73" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H73" s="47" t="s">
-        <v>27</v>
+    <row r="74" ht="76" customHeight="1">
+      <c r="A74" s="136" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B74" s="133" t="str">
+        <v>15-15</v>
+      </c>
+      <c r="C74" s="132" t="str">
+        <v>液位变化过快</v>
+      </c>
+      <c r="D74" s="132" t="str">
+        <v>触发：跟随液位时，传感器信号连续偏离目标范围。
+影响：设备判断液面变化速度超出跟随能力，不能稳定测量。</v>
+      </c>
+      <c r="E74" s="132" t="str">
+        <v>1、进出料或液面波动较快，超过当前跟随能力。
+2、机构跟随不畅，或气泡、附着物使信号快速变化。</v>
+      </c>
+      <c r="F74" s="132" t="str">
+        <v>1、先核对现场是否正在快速进出料或液面剧烈波动。
+2、检查频率变化、实际运动和跟随设置，排除卡涩及信号异常。
+3、条件恢复适合测量后重新找液位，再进入跟随。</v>
+      </c>
+      <c r="G74" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H74" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="74" ht="66">
-      <c r="A74" s="54"/>
-      <c r="B74" s="49" t="s">
-        <v>338</v>
-      </c>
-      <c r="C74" s="49" t="s">
-        <v>339</v>
-      </c>
-      <c r="D74" s="50" t="s">
-        <v>340</v>
-      </c>
-      <c r="E74" s="50" t="s">
-        <v>341</v>
-      </c>
-      <c r="F74" s="50" t="s">
-        <v>342</v>
-      </c>
-      <c r="G74" s="51" t="s">
-        <v>343</v>
-      </c>
-      <c r="H74" s="47" t="s">
-        <v>27</v>
+    <row r="75" ht="76" customHeight="1">
+      <c r="A75" s="149" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B75" s="150" t="str">
+        <v>15-16</v>
+      </c>
+      <c r="C75" s="149" t="str">
+        <v>实高偏差过大</v>
+      </c>
+      <c r="D75" s="149" t="str">
+        <v>当前保留编号，程序不会主动报出。</v>
+      </c>
+      <c r="E75" s="149" t="str">
+        <v>1、当前保留码，不作现行故障原因判断。</v>
+      </c>
+      <c r="F75" s="149" t="str">
+        <v>1、当前设备不会主动报出；旧设备日志请按对应固件历史资料查询。</v>
+      </c>
+      <c r="G75" s="153" t="str">
+        <v>保留</v>
+      </c>
+      <c r="H75" s="152" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="75" ht="82.5">
-      <c r="A75" s="54"/>
-      <c r="B75" s="49" t="s">
-        <v>344</v>
-      </c>
-      <c r="C75" s="49" t="s">
-        <v>345</v>
-      </c>
-      <c r="D75" s="50" t="s">
-        <v>346</v>
-      </c>
-      <c r="E75" s="50" t="s">
-        <v>347</v>
-      </c>
-      <c r="F75" s="50" t="s">
-        <v>348</v>
-      </c>
-      <c r="G75" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H75" s="47" t="s">
-        <v>27</v>
+    <row r="76" ht="76" customHeight="1">
+      <c r="A76" s="136" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B76" s="133" t="str">
+        <v>15-17</v>
+      </c>
+      <c r="C76" s="132" t="str">
+        <v>密度找液位超时</v>
+      </c>
+      <c r="D76" s="132" t="str">
+        <v>触发：设备使用密度变化寻找液面。
+影响：经过规定时间和多次调整还是没有获得稳定的空气与液体分界，当前搜索结束。</v>
+      </c>
+      <c r="E76" s="132" t="str">
+        <v>1、泡沫、气泡或乳化层使空气与液体的密度变化不清楚。
+2、传感器未稳定，或搜索位置、运动条件不合适。</v>
+      </c>
+      <c r="F76" s="132" t="str">
+        <v>1、记录搜索起止位置、密度和超时前的动作。
+2、核对液面是否在范围内，检查探头状态及实际运动。
+3、液面和读数稳定后重新搜索；持续超时需分析过程日志，不只延长时间。</v>
+      </c>
+      <c r="G76" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H76" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="76" ht="82.5">
-      <c r="A76" s="54"/>
-      <c r="B76" s="66" t="s">
-        <v>349</v>
-      </c>
-      <c r="C76" s="66" t="s">
-        <v>350</v>
-      </c>
-      <c r="D76" s="65" t="s">
-        <v>351</v>
-      </c>
-      <c r="E76" s="65" t="s">
-        <v>352</v>
-      </c>
-      <c r="F76" s="65" t="s">
-        <v>305</v>
-      </c>
-      <c r="G76" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H76" s="47" t="s">
-        <v>27</v>
+    <row r="77" ht="87" customHeight="1">
+      <c r="A77" s="136" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B77" s="139" t="str">
+        <v>15-18</v>
+      </c>
+      <c r="C77" s="140" t="str">
+        <v>下行未找到液位</v>
+      </c>
+      <c r="D77" s="132" t="str">
+        <v>触发：向下搜索液面时已经进入盲区或到达下限。
+影响：还是没有识别到由空气进入液体的稳定变化，设备停止下行。</v>
+      </c>
+      <c r="E77" s="132" t="str">
+        <v>1、液位低于可测下限，或搜索范围设置不正确。
+2、传感器未识别入液，或实际下行与位置记录不符。</v>
+      </c>
+      <c r="F77" s="132" t="str">
+        <v>1、停止继续下放，确认现场液位及盲区。
+2、核对罐高、零点和搜索下限，检查入液时频率或密度变化。
+3、确认位置及信号正常后重新搜索；液面在盲区内时不能靠扩大行程解决。</v>
+      </c>
+      <c r="G77" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H77" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="77" ht="66">
-      <c r="A77" s="54"/>
-      <c r="B77" s="66" t="s">
-        <v>353</v>
-      </c>
-      <c r="C77" s="66" t="s">
-        <v>354</v>
-      </c>
-      <c r="D77" s="65" t="s">
-        <v>355</v>
-      </c>
-      <c r="E77" s="65" t="s">
-        <v>356</v>
-      </c>
-      <c r="F77" s="65" t="s">
-        <v>305</v>
-      </c>
-      <c r="G77" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H77" s="47" t="s">
-        <v>27</v>
+    <row r="78" ht="76" customHeight="1">
+      <c r="A78" s="136" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B78" s="139" t="str">
+        <v>15-19</v>
+      </c>
+      <c r="C78" s="140" t="str">
+        <v>上行未找到液位</v>
+      </c>
+      <c r="D78" s="132" t="str">
+        <v>触发：向上搜索液面或重新启用液位测量后。
+影响：还是没有识别到由液体进入空气的稳定变化，设备不能确认液面位置。</v>
+      </c>
+      <c r="E78" s="132" t="str">
+        <v>1、液面超出上行搜索范围。
+2、信号未稳定，或尺带打滑使位置显示与实际不符。</v>
+      </c>
+      <c r="F78" s="132" t="str">
+        <v>1、确认探头是否实际向上移动、是否经过液面。
+2、核对罐高和起始位置，检查液面附近的信号变化。
+3、位置及信号恢复正常后重新搜索，不要继续无边界上行。</v>
+      </c>
+      <c r="G78" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H78" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="78" ht="82.5">
-      <c r="A78" s="54"/>
-      <c r="B78" s="66" t="s">
-        <v>357</v>
-      </c>
-      <c r="C78" s="66" t="str">
+    <row r="79" ht="87" customHeight="1">
+      <c r="A79" s="136" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B79" s="139" t="str">
+        <v>15-20</v>
+      </c>
+      <c r="C79" s="140" t="str">
         <v>下行未找到罐底</v>
       </c>
-      <c r="D78" s="65" t="s">
-        <v>358</v>
-      </c>
-      <c r="E78" s="65" t="s">
-        <v>359</v>
-      </c>
-      <c r="F78" s="65" t="s">
-        <v>305</v>
-      </c>
-      <c r="G78" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H78" s="47" t="s">
-        <v>27</v>
+      <c r="D79" s="132" t="str">
+        <v>下行到达允许边界，或精找越过预计范围，仍未确认可靠罐底，本次探底失败。应按当前使用的称重或角度探底方式检查。</v>
+      </c>
+      <c r="E79" s="132" t="str">
+        <v>1、探头未在允许范围内形成可靠触底信号。
+2、罐高、位置或探底设置不准，或检测通道、机构存在异常。</v>
+      </c>
+      <c r="F79" s="132" t="str">
+        <v>1、停止继续下探，记录最后位置和当前探底方式。
+2、称重探底检查受力数据，角度探底检查姿态基准；同时核对尺带和行程。
+3、排除问题并确认允许范围后重新探底，不要仅扩大下行范围。</v>
+      </c>
+      <c r="G79" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H79" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="79" ht="66">
-      <c r="A79" s="54"/>
-      <c r="B79" s="66" t="s">
-        <v>360</v>
-      </c>
-      <c r="C79" s="66" t="str">
+    <row r="80" ht="76" customHeight="1">
+      <c r="A80" s="136" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B80" s="139" t="str">
+        <v>15-21</v>
+      </c>
+      <c r="C80" s="140" t="str">
         <v>上行未找到零点</v>
       </c>
-      <c r="D79" s="65" t="s">
-        <v>361</v>
-      </c>
-      <c r="E79" s="65" t="s">
-        <v>362</v>
-      </c>
-      <c r="F79" s="65" t="s">
-        <v>305</v>
-      </c>
-      <c r="G79" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="47" t="s">
-        <v>27</v>
+      <c r="D80" s="132" t="str">
+        <v>触发：从罐底向上精确回零。
+影响：移动已经超过允许零点范围，扭力还是没有恢复到离底特征，设备不能确认浮子已离开罐底。</v>
+      </c>
+      <c r="E80" s="132" t="str">
+        <v>1、上行后离底或零点特征没有恢复。
+2、机构吸附、卡涩，或扭力基准及位置记录异常。</v>
+      </c>
+      <c r="F80" s="132" t="str">
+        <v>1、停止反复上拉，检查浮子、尺带和导向机构。
+2、核对上行实际位移、扭力变化和零点相关设置。
+3、排除卡阻并确认离底响应正常后，再按流程回零。</v>
+      </c>
+      <c r="G80" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H80" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="80" ht="82.5">
-      <c r="A80" s="54"/>
-      <c r="B80" s="52" t="s">
-        <v>363</v>
-      </c>
-      <c r="C80" s="52" t="s">
-        <v>364</v>
-      </c>
-      <c r="D80" s="53" t="s">
-        <v>365</v>
-      </c>
-      <c r="E80" s="53" t="s">
-        <v>366</v>
-      </c>
-      <c r="F80" s="53" t="s">
-        <v>305</v>
-      </c>
-      <c r="G80" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H80" s="47" t="s">
-        <v>27</v>
+    <row r="81" ht="76" customHeight="1">
+      <c r="A81" s="136" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B81" s="133" t="str">
+        <v>15-22</v>
+      </c>
+      <c r="C81" s="132" t="str">
+        <v>下行未找到水位</v>
+      </c>
+      <c r="D81" s="132" t="str">
+        <v>触发：向下搜索水层时已经接近零点或经过多次粗找、精找。
+影响：还是没有找到稳定的油水分界，设备停止测量。</v>
+      </c>
+      <c r="E81" s="132" t="str">
+        <v>1、水层不在可测范围内，或水层过薄、乳化明显。
+2、水位探头、标定值或运动位置异常。</v>
+      </c>
+      <c r="F81" s="132" t="str">
+        <v>1、核对现场是否存在可测水层及预计水位。
+2、检查水位电容变化、探头附着物、标定值和搜索范围。
+3、条件满足后重新测水；不要把未找到水位直接当作水位为零。</v>
+      </c>
+      <c r="G81" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H81" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="81" ht="82.5">
-      <c r="A81" s="54"/>
-      <c r="B81" s="52" t="s">
-        <v>367</v>
-      </c>
-      <c r="C81" s="52" t="s">
-        <v>368</v>
-      </c>
-      <c r="D81" s="53" t="s">
-        <v>369</v>
-      </c>
-      <c r="E81" s="53" t="s">
-        <v>370</v>
-      </c>
-      <c r="F81" s="53" t="s">
-        <v>305</v>
-      </c>
-      <c r="G81" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H81" s="47" t="s">
-        <v>27</v>
+    <row r="82" ht="76" customHeight="1">
+      <c r="A82" s="136" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B82" s="133" t="str">
+        <v>15-23</v>
+      </c>
+      <c r="C82" s="132" t="str">
+        <v>密度测量无有效点</v>
+      </c>
+      <c r="D82" s="132" t="str">
+        <v>触发：密度分布测量没有生成可用测点，或全部测点完成后仍没有得到一组有效密度值。
+影响：不能形成测量结果。</v>
+      </c>
+      <c r="E82" s="132" t="str">
+        <v>1、测点没有得到可采用的液体密度。
+2、测量范围、点距或位置不合适，或传感器各点均未稳定。</v>
+      </c>
+      <c r="F82" s="132" t="str">
+        <v>1、查看各测点的位置、读数和被舍弃原因。
+2、确认测点落在有效液体范围内，检查传感器状态和运动到位。
+3、修正条件后重新测量，确认有有效点再使用平均结果。</v>
+      </c>
+      <c r="G82" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H82" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="82" ht="66">
-      <c r="A82" s="54"/>
-      <c r="B82" s="52" t="s">
-        <v>371</v>
-      </c>
-      <c r="C82" s="52" t="s">
-        <v>372</v>
-      </c>
-      <c r="D82" s="53" t="s">
-        <v>373</v>
-      </c>
-      <c r="E82" s="53" t="s">
-        <v>374</v>
-      </c>
-      <c r="F82" s="53" t="s">
-        <v>305</v>
-      </c>
-      <c r="G82" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H82" s="47" t="s">
-        <v>27</v>
+    <row r="83" ht="76" customHeight="1">
+      <c r="A83" s="136" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B83" s="133" t="str">
+        <v>15-24</v>
+      </c>
+      <c r="C83" s="132" t="str">
+        <v>密度测量未找到油面</v>
+      </c>
+      <c r="D83" s="132" t="str">
+        <v>触发：密度分布测量已经到达最高测点还是没有确认进入空气，或全过程没有得到可用于判定液面的有效液体点。
+影响：设备不能确定油面。</v>
+      </c>
+      <c r="E83" s="132" t="str">
+        <v>1、分布测量范围没有跨过实际油面。
+2、没有可用液体点，或液面附近密度信号不可靠。</v>
+      </c>
+      <c r="F83" s="132" t="str">
+        <v>1、核对最高测点、现场油面和有效液体点记录。
+2、检查测量范围、罐高、位置及液面附近的密度变化。
+3、确认范围和信号能覆盖油面后重新测量，不沿用未确认的油面结果。</v>
+      </c>
+      <c r="G83" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H83" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="83" ht="82.5">
-      <c r="A83" s="54"/>
-      <c r="B83" s="52" t="s">
-        <v>375</v>
-      </c>
-      <c r="C83" s="52" t="s">
-        <v>376</v>
-      </c>
-      <c r="D83" s="53" t="s">
-        <v>377</v>
-      </c>
-      <c r="E83" s="53" t="s">
-        <v>378</v>
-      </c>
-      <c r="F83" s="53" t="s">
-        <v>379</v>
-      </c>
-      <c r="G83" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H83" s="47" t="s">
-        <v>27</v>
+    <row r="84" ht="87" customHeight="1">
+      <c r="A84" s="136" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B84" s="133" t="str">
+        <v>15-25</v>
+      </c>
+      <c r="C84" s="132" t="str">
+        <v>频率找液位超时</v>
+      </c>
+      <c r="D84" s="132" t="str">
+        <v>触发：设备使用振动频率变化寻找液面。
+影响：经过规定时间还是不能稳定区分空气和液体，当前搜索结束。</v>
+      </c>
+      <c r="E84" s="132" t="str">
+        <v>1、液面附近频率尚未稳定，或空气、液体差异不清楚。
+2、起始位置、运动或搜索条件不合适。</v>
+      </c>
+      <c r="F84" s="132" t="str">
+        <v>1、保存超时前的频率、位置和搜索动作。
+2、检查液面是否在搜索范围内，核对探头状态及空气、液体频率。
+3、条件恢复后重新找液位；0值未稳定应与通信失败、非零越界分开排查。</v>
+      </c>
+      <c r="G84" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H84" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="84" ht="66">
-      <c r="A84" s="54"/>
-      <c r="B84" s="52" t="s">
-        <v>380</v>
-      </c>
-      <c r="C84" s="52" t="str">
+    <row r="85" ht="87" customHeight="1">
+      <c r="A85" s="136" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B85" s="133" t="str">
+        <v>15-26</v>
+      </c>
+      <c r="C85" s="132" t="str">
         <v>探底前未能离开罐底</v>
       </c>
-      <c r="D84" s="53" t="s">
-        <v>381</v>
-      </c>
-      <c r="E84" s="53" t="s">
-        <v>382</v>
-      </c>
-      <c r="F84" s="53" t="s">
-        <v>383</v>
-      </c>
-      <c r="G84" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H84" s="47" t="s">
-        <v>27</v>
+      <c r="D85" s="132" t="str">
+        <v>触发：开始粗找罐底前。
+影响：设备尝试先向上释放受力，但在允许距离内还是没有确认浮子已经离开罐底或卡阻位置。</v>
+      </c>
+      <c r="E85" s="132" t="str">
+        <v>1、浮子受吸附或机构卡涩，上行后仍有触底特征。
+2、受力基准、释放条件或位置反馈异常。</v>
+      </c>
+      <c r="F85" s="132" t="str">
+        <v>1、停止继续下探，先确认上行动作是否实际发生。
+2、检查浮子、尺带和导向机构，核对上行位移与受力变化。
+3、确认能可靠离底并恢复正常基准后再探底，不要盲目增加拉力。</v>
+      </c>
+      <c r="G85" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H85" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="85" ht="82.5">
-      <c r="A85" s="54"/>
-      <c r="B85" s="52" t="s">
-        <v>384</v>
-      </c>
-      <c r="C85" s="52" t="s">
-        <v>385</v>
-      </c>
-      <c r="D85" s="53" t="s">
-        <v>386</v>
-      </c>
-      <c r="E85" s="53" t="s">
-        <v>387</v>
-      </c>
-      <c r="F85" s="53" t="s">
-        <v>388</v>
-      </c>
-      <c r="G85" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H85" s="47" t="s">
-        <v>27</v>
+    <row r="86" ht="76" customHeight="1">
+      <c r="A86" s="136" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B86" s="133" t="str">
+        <v>15-27</v>
+      </c>
+      <c r="C86" s="132" t="str">
+        <v>未设置罐高标定值</v>
+      </c>
+      <c r="D86" s="132" t="str">
+        <v>触发：执行罐高标定。
+影响：设备发现标定罐高为零，不能用真实罐高修正测量结果。</v>
+      </c>
+      <c r="E86" s="132" t="str">
+        <v>1、罐高标定真值未录入，或参数恢复后丢失。
+2、当前选用的罐体配置不正确。</v>
+      </c>
+      <c r="F86" s="132" t="str">
+        <v>1、核对当前储罐和真实罐高，确认单位。
+2、录入并保存已确认的标定值，再执行罐高标定。
+3、若保存后又变为零，先检查参数存储故障。</v>
+      </c>
+      <c r="G86" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H86" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="86" ht="66">
-      <c r="A86" s="54"/>
-      <c r="B86" s="52" t="s">
-        <v>389</v>
-      </c>
-      <c r="C86" s="52" t="s">
-        <v>390</v>
-      </c>
-      <c r="D86" s="53" t="s">
-        <v>391</v>
-      </c>
-      <c r="E86" s="53" t="s">
-        <v>392</v>
-      </c>
-      <c r="F86" s="53" t="s">
-        <v>393</v>
-      </c>
-      <c r="G86" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H86" s="47" t="s">
-        <v>27</v>
+    <row r="87" ht="76" customHeight="1">
+      <c r="A87" s="136" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B87" s="133" t="str">
+        <v>15-28</v>
+      </c>
+      <c r="C87" s="132" t="str">
+        <v>未设置水位标定值</v>
+      </c>
+      <c r="D87" s="132" t="str">
+        <v>触发：执行水位标定。
+影响：设备发现水位真值为零，不能计算水位测量基准。</v>
+      </c>
+      <c r="E87" s="132" t="str">
+        <v>1、水位标定真值未录入，或恢复参数后未重新设置。
+2、选择了错误的罐体或标定项目。</v>
+      </c>
+      <c r="F87" s="132" t="str">
+        <v>1、确认现场实测水位、单位及本次标定项目。
+2、输入已确认的真值并保存，再执行水位标定。
+3、没有可靠真值时先停止标定，不为消除故障随意填写数值。</v>
+      </c>
+      <c r="G87" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H87" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="87" ht="66">
-      <c r="A87" s="54"/>
-      <c r="B87" s="52" t="s">
-        <v>394</v>
-      </c>
-      <c r="C87" s="52" t="s">
-        <v>395</v>
-      </c>
-      <c r="D87" s="53" t="s">
-        <v>396</v>
-      </c>
-      <c r="E87" s="53" t="s">
-        <v>397</v>
-      </c>
-      <c r="F87" s="53" t="s">
-        <v>398</v>
-      </c>
-      <c r="G87" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H87" s="47" t="s">
-        <v>27</v>
+    <row r="88" ht="87" customHeight="1">
+      <c r="A88" s="136" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B88" s="133" t="str">
+        <v>15-29</v>
+      </c>
+      <c r="C88" s="132" t="str">
+        <v>密度测点规划失败</v>
+      </c>
+      <c r="D88" s="132" t="str">
+        <v>触发：设备根据液位、罐高、起止位置、测量间距和点数生成密度测点。
+影响：发现范围为空、顺序冲突或不能形成任何有效测点。</v>
+      </c>
+      <c r="E88" s="132" t="str">
+        <v>1、起止位置、点距、点数或盲区组合不合理。
+2、液位、罐高或可用测量范围尚未有效。</v>
+      </c>
+      <c r="F88" s="132" t="str">
+        <v>1、记录本次起止位置、间距、点数和罐高。
+2、核对单位、位置基准及范围，确认至少能形成一个允许测点。
+3、修正参数或先取得有效液位后重新启动，不通过强行增加点数绕过检查。</v>
+      </c>
+      <c r="G88" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H88" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="88" ht="66">
-      <c r="A88" s="54"/>
-      <c r="B88" s="52" t="s">
-        <v>399</v>
-      </c>
-      <c r="C88" s="52" t="s">
-        <v>400</v>
-      </c>
-      <c r="D88" s="53" t="s">
-        <v>401</v>
-      </c>
-      <c r="E88" s="53" t="s">
-        <v>402</v>
-      </c>
-      <c r="F88" s="53" t="s">
-        <v>403</v>
-      </c>
-      <c r="G88" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="47" t="s">
-        <v>27</v>
+    <row r="89" ht="76" customHeight="1">
+      <c r="A89" s="136" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B89" s="133" t="str">
+        <v>15-30</v>
+      </c>
+      <c r="C89" s="132" t="str">
+        <v>罐高测量结果无效</v>
+      </c>
+      <c r="D89" s="132" t="str">
+        <v>触发：探底流程结束后没有得到大于零的有效实高。
+影响：设备不能完成罐高修正。</v>
+      </c>
+      <c r="E89" s="132" t="str">
+        <v>1、探底结果或位置基准不可用。
+2、尺带打滑、周长换算或罐高相关设置异常。</v>
+      </c>
+      <c r="F89" s="132" t="str">
+        <v>1、不要保存本次无效实高，先检查探底和位置日志。
+2、确认零点、实际触底位置和位置记录可靠。
+3、重新探底得到有效实高后再标定罐高；仍异常时交技术人员分析。</v>
+      </c>
+      <c r="G89" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H89" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="89" ht="82.5">
-      <c r="A89" s="54"/>
-      <c r="B89" s="52" t="s">
-        <v>404</v>
-      </c>
-      <c r="C89" s="52" t="s">
-        <v>405</v>
-      </c>
-      <c r="D89" s="53" t="s">
-        <v>406</v>
-      </c>
-      <c r="E89" s="53" t="s">
-        <v>407</v>
-      </c>
-      <c r="F89" s="53" t="s">
-        <v>408</v>
-      </c>
-      <c r="G89" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="47" t="s">
-        <v>27</v>
+    <row r="90" ht="76" customHeight="1">
+      <c r="A90" s="136" t="str">
+        <v>测量过程</v>
+      </c>
+      <c r="B90" s="133" t="str">
+        <v>15-31</v>
+      </c>
+      <c r="C90" s="132" t="str">
+        <v>水位标定计算结果越界</v>
+      </c>
+      <c r="D90" s="132" t="str">
+        <v>触发：根据当前缆长和水位真值计算出的水位罐高小于等于零或超过500米。
+影响：设备拒绝保存该结果。</v>
+      </c>
+      <c r="E90" s="132" t="str">
+        <v>1、水位真值、缆长或单位填写错误。
+2、零点和位置换算不准确。</v>
+      </c>
+      <c r="F90" s="132" t="str">
+        <v>1、核对水位真值的单位及当前缆长。
+2、检查零点、编码轮周长和实际水位位置。
+3、修正并重新定位后再标定，确认结果在允许范围内再采用。</v>
+      </c>
+      <c r="G90" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H90" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="90" ht="82.5">
-      <c r="A90" s="54" t="s">
-        <v>409</v>
-      </c>
-      <c r="B90" s="52" t="s">
-        <v>410</v>
-      </c>
-      <c r="C90" s="52" t="s">
-        <v>411</v>
-      </c>
-      <c r="D90" s="53" t="s">
-        <v>412</v>
-      </c>
-      <c r="E90" s="53" t="s">
-        <v>413</v>
-      </c>
-      <c r="F90" s="53" t="s">
-        <v>414</v>
-      </c>
-      <c r="G90" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H90" s="47" t="s">
-        <v>27</v>
+    <row r="91" ht="87" customHeight="1">
+      <c r="A91" s="141" t="str">
+        <v>参数与存储</v>
+      </c>
+      <c r="B91" s="156" t="str">
+        <v>17-1</v>
+      </c>
+      <c r="C91" s="144" t="str">
+        <v>参数存储访问失败</v>
+      </c>
+      <c r="D91" s="144" t="str">
+        <v>触发：设备不能从两份参数记录中取得可用内容。
+影响：不属于未初始化、大小、版本或完整性校验等已明确原因。</v>
+      </c>
+      <c r="E91" s="144" t="str">
+        <v>1、参数存储器访问或供电异常。
+2、主板连接、干扰或存储器故障。</v>
+      </c>
+      <c r="F91" s="144" t="str">
+        <v>1、先记录现有参数和报错过程，不要立即恢复出厂。
+2、检查主板供电和存储器；读取到的异常参数不能当作可靠备份。
+3、访问恢复后用已核实的参数重新配置并验证保存，仍失败时检修主板。</v>
+      </c>
+      <c r="G91" s="145" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H91" s="146" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="91" ht="66">
-      <c r="A91" s="54"/>
-      <c r="B91" s="52" t="s">
-        <v>415</v>
-      </c>
-      <c r="C91" s="52" t="s">
-        <v>416</v>
-      </c>
-      <c r="D91" s="53" t="s">
-        <v>417</v>
-      </c>
-      <c r="E91" s="53" t="s">
-        <v>418</v>
-      </c>
-      <c r="F91" s="53" t="s">
-        <v>419</v>
-      </c>
-      <c r="G91" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H91" s="47" t="s">
-        <v>27</v>
+    <row r="92" ht="87" customHeight="1">
+      <c r="A92" s="136" t="str">
+        <v>参数与存储</v>
+      </c>
+      <c r="B92" s="133" t="str">
+        <v>17-2</v>
+      </c>
+      <c r="C92" s="132" t="str">
+        <v>参数未初始化</v>
+      </c>
+      <c r="D92" s="132" t="str">
+        <v>触发：开机时两份参数记录都没有初始化标志。
+影响：设备判断从未保存过有效参数，已改用出厂参数启动。</v>
+      </c>
+      <c r="E92" s="132" t="str">
+        <v>1、首次使用或更换主板、存储器后未完成参数保存。
+2、存储内容被清空，或初始化写入未完成。</v>
+      </c>
+      <c r="F92" s="132" t="str">
+        <v>1、确认是否为新机、换板或恢复参数后的首次启动。
+2、按现场配置重新设置并保存参数，不直接用出厂值开始测量。
+3、在安全停机条件下重新上电复查，确认参数完整保留后再调试。</v>
+      </c>
+      <c r="G92" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H92" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="92" ht="66">
-      <c r="A92" s="54"/>
-      <c r="B92" s="66" t="s">
-        <v>420</v>
-      </c>
-      <c r="C92" s="66" t="s">
-        <v>421</v>
-      </c>
-      <c r="D92" s="65" t="s">
-        <v>422</v>
-      </c>
-      <c r="E92" s="65" t="s">
-        <v>423</v>
-      </c>
-      <c r="F92" s="65" t="s">
-        <v>424</v>
-      </c>
-      <c r="G92" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H92" s="47" t="s">
-        <v>27</v>
+    <row r="93" ht="76" customHeight="1">
+      <c r="A93" s="136" t="str">
+        <v>参数与存储</v>
+      </c>
+      <c r="B93" s="139" t="str">
+        <v>17-5</v>
+      </c>
+      <c r="C93" s="140" t="str">
+        <v>参数值超出范围</v>
+      </c>
+      <c r="D93" s="132" t="str">
+        <v>触发：当前设置值、目标位置或测量计划超出设备允许范围。
+影响：继续执行可能越界或得不到有效结果，设备拒绝这次操作。</v>
+      </c>
+      <c r="E93" s="132" t="str">
+        <v>1、参数、目标位置或测量数量超出允许范围。
+2、单位、小数位或位置基准使用错误。</v>
+      </c>
+      <c r="F93" s="132" t="str">
+        <v>1、查看被拒绝的参数或目标值，核对单位和范围。
+2、涉及运动时同时确认当前位置、罐高和盲区。
+3、修正后重新操作，不通过放宽安全边界消除报错。</v>
+      </c>
+      <c r="G93" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H93" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="93" ht="66">
-      <c r="A93" s="54"/>
-      <c r="B93" s="52" t="s">
-        <v>425</v>
-      </c>
-      <c r="C93" s="52" t="s">
-        <v>426</v>
-      </c>
-      <c r="D93" s="53" t="s">
-        <v>427</v>
-      </c>
-      <c r="E93" s="53" t="s">
-        <v>428</v>
-      </c>
-      <c r="F93" s="53" t="s">
-        <v>429</v>
-      </c>
-      <c r="G93" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="47" t="s">
-        <v>27</v>
+    <row r="94" ht="87" customHeight="1">
+      <c r="A94" s="136" t="str">
+        <v>参数与存储</v>
+      </c>
+      <c r="B94" s="133" t="str">
+        <v>17-6</v>
+      </c>
+      <c r="C94" s="132" t="str">
+        <v>参数完整性校验失败</v>
+      </c>
+      <c r="D94" s="132" t="str">
+        <v>触发：开机时参数记录的基本信息可以识别，但保存内容确认不一致，另一份备份也不可用。
+影响：设备改用出厂参数启动，原参数不可信。</v>
+      </c>
+      <c r="E94" s="132" t="str">
+        <v>1、保存过程中掉电，或两份参数记录都不完整。
+2、供电、干扰或存储器异常。</v>
+      </c>
+      <c r="F94" s="132" t="str">
+        <v>1、不要直接依赖启动后的出厂参数，先核对可靠的现场参数备份。
+2、检查供电和存储状态，再恢复已确认的配置。
+3、保存后重新读取并复查；再次校验失败时停用检修存储器。</v>
+      </c>
+      <c r="G94" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H94" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="94" ht="66">
-      <c r="A94" s="54"/>
-      <c r="B94" s="52" t="s">
-        <v>430</v>
-      </c>
-      <c r="C94" s="52" t="str">
+    <row r="95" ht="76" customHeight="1">
+      <c r="A95" s="136" t="str">
+        <v>参数与存储</v>
+      </c>
+      <c r="B95" s="133" t="str">
+        <v>17-7</v>
+      </c>
+      <c r="C95" s="132" t="str">
         <v>关键参数未设置</v>
       </c>
-      <c r="D94" s="53" t="s">
-        <v>431</v>
-      </c>
-      <c r="E94" s="53" t="s">
-        <v>432</v>
-      </c>
-      <c r="F94" s="53" t="s">
-        <v>433</v>
-      </c>
-      <c r="G94" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="47" t="s">
-        <v>27</v>
+      <c r="D95" s="132" t="str">
+        <v>触发：这个功能所需的关键设备参数尚未设置或内容为空。
+影响：设备不能确定运动范围、测量条件或部件类型，所以拒绝执行。</v>
+      </c>
+      <c r="E95" s="132" t="str">
+        <v>1、首次调试、换板或恢复参数后漏填必要项目。
+2、更换设备类型后，原配置不再满足当前功能。</v>
+      </c>
+      <c r="F95" s="132" t="str">
+        <v>1、根据当前功能和日志定位缺少的参数。
+2、核对罐高、零点、传感器类型等相关设置，只补入已确认的值。
+3、保存并重新读取确认后，再执行原功能。</v>
+      </c>
+      <c r="G95" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H95" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="95" ht="66">
-      <c r="A95" s="54"/>
-      <c r="B95" s="52" t="s">
-        <v>434</v>
-      </c>
-      <c r="C95" s="52" t="s">
-        <v>435</v>
-      </c>
-      <c r="D95" s="53" t="s">
-        <v>436</v>
-      </c>
-      <c r="E95" s="53" t="s">
-        <v>437</v>
-      </c>
-      <c r="F95" s="53" t="s">
-        <v>438</v>
-      </c>
-      <c r="G95" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H95" s="47" t="s">
-        <v>27</v>
+    <row r="96" ht="87" customHeight="1">
+      <c r="A96" s="136" t="str">
+        <v>参数与存储</v>
+      </c>
+      <c r="B96" s="133" t="str">
+        <v>17-8</v>
+      </c>
+      <c r="C96" s="132" t="str">
+        <v>参数组合冲突</v>
+      </c>
+      <c r="D96" s="132" t="str">
+        <v>触发：单个参数可能都在允许范围内。
+影响：多个参数组合后出现起止顺序、上下限、距离或数量互相矛盾，设备拒绝执行。</v>
+      </c>
+      <c r="E96" s="132" t="str">
+        <v>1、起止位置、上下限、间距或点数组合互相矛盾。
+2、罐高、液位或零点采用了不同位置基准。</v>
+      </c>
+      <c r="F96" s="132" t="str">
+        <v>1、把相关参数一起核对，不只检查单个数值是否超限。
+2、确认单位、位置基准和上下限顺序，再检查点距与数量是否适合范围。
+3、修正并保存后重新操作，保留发生冲突的原参数供追查。</v>
+      </c>
+      <c r="G96" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H96" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="96" ht="66">
-      <c r="A96" s="54"/>
-      <c r="B96" s="52" t="s">
-        <v>439</v>
-      </c>
-      <c r="C96" s="52" t="s">
-        <v>440</v>
-      </c>
-      <c r="D96" s="53" t="s">
-        <v>441</v>
-      </c>
-      <c r="E96" s="53" t="s">
-        <v>442</v>
-      </c>
-      <c r="F96" s="53" t="s">
-        <v>443</v>
-      </c>
-      <c r="G96" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H96" s="47" t="s">
-        <v>27</v>
+    <row r="97" ht="87" customHeight="1">
+      <c r="A97" s="136" t="str">
+        <v>参数与存储</v>
+      </c>
+      <c r="B97" s="133" t="str">
+        <v>17-9</v>
+      </c>
+      <c r="C97" s="132" t="str">
+        <v>当前配置不支持此功能</v>
+      </c>
+      <c r="D97" s="132" t="str">
+        <v>触发：已选择的传感器、设备类型或工作模式不具备这次功能所需条件。
+影响：继续执行不能得到有效结果。</v>
+      </c>
+      <c r="E97" s="132" t="str">
+        <v>1、当前传感器、设备类型或模式不支持所选功能。
+2、更换部件后配置未同步。</v>
+      </c>
+      <c r="F97" s="132" t="str">
+        <v>1、核对实际安装型号、当前模式和功能要求。
+2、配置选错时按实物修正；硬件本身不支持时停止使用该功能。
+3、需升级或换件时按配套方案处理，不能只修改型号参数冒充支持。</v>
+      </c>
+      <c r="G97" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H97" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="97" ht="66">
-      <c r="A97" s="54"/>
-      <c r="B97" s="52" t="s">
-        <v>444</v>
-      </c>
-      <c r="C97" s="52" t="s">
-        <v>445</v>
-      </c>
-      <c r="D97" s="53" t="s">
-        <v>446</v>
-      </c>
-      <c r="E97" s="53" t="s">
-        <v>447</v>
-      </c>
-      <c r="F97" s="53" t="s">
-        <v>448</v>
-      </c>
-      <c r="G97" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H97" s="47" t="s">
-        <v>27</v>
+    <row r="98" ht="76" customHeight="1">
+      <c r="A98" s="136" t="str">
+        <v>参数与存储</v>
+      </c>
+      <c r="B98" s="133" t="str">
+        <v>17-10</v>
+      </c>
+      <c r="C98" s="132" t="str">
+        <v>参数存储结构不匹配</v>
+      </c>
+      <c r="D98" s="132" t="str">
+        <v>触发：存储器中的参数记录长度与当前程序要求不同。
+影响：设备不能按当前格式读取原参数。</v>
+      </c>
+      <c r="E98" s="132" t="str">
+        <v>1、当前程序要求的参数结构与存储记录长度不同。
+2、升级、换板或存储损坏导致旧记录不适用。</v>
+      </c>
+      <c r="F98" s="132" t="str">
+        <v>1、记录当前程序版本和升级、换板经过。
+2、查参数兼容说明，并核对已有可靠的现场参数备份。
+3、按批准流程迁移或重新配置，保存和读回验证正常后再运行。</v>
+      </c>
+      <c r="G98" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H98" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="98" ht="66">
-      <c r="A98" s="54"/>
-      <c r="B98" s="52" t="s">
-        <v>449</v>
-      </c>
-      <c r="C98" s="52" t="s">
-        <v>450</v>
-      </c>
-      <c r="D98" s="53" t="s">
-        <v>451</v>
-      </c>
-      <c r="E98" s="53" t="s">
-        <v>452</v>
-      </c>
-      <c r="F98" s="53" t="s">
-        <v>453</v>
-      </c>
-      <c r="G98" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H98" s="47" t="s">
-        <v>27</v>
+    <row r="99" ht="76" customHeight="1">
+      <c r="A99" s="136" t="str">
+        <v>参数与存储</v>
+      </c>
+      <c r="B99" s="133" t="str">
+        <v>17-11</v>
+      </c>
+      <c r="C99" s="132" t="str">
+        <v>参数存储版本不匹配</v>
+      </c>
+      <c r="D99" s="132" t="str">
+        <v>触发：参数记录的版本标记与当前程序要求不同。
+影响：设备不能确认旧参数是否可以直接使用。</v>
+      </c>
+      <c r="E99" s="132" t="str">
+        <v>1、程序升级或降级后，仍保存着另一版本的参数。
+2、换板或存储版本标记异常。</v>
+      </c>
+      <c r="F99" s="132" t="str">
+        <v>1、核对程序版本、参数版本及升级说明。
+2、先保留原参数资料，由技术人员确认能否迁移。
+3、按配套流程恢复参数并验证，不直接套用另一版本的参数文件。</v>
+      </c>
+      <c r="G99" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H99" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="99" ht="82.5">
-      <c r="A99" s="54"/>
-      <c r="B99" s="52" t="s">
-        <v>454</v>
-      </c>
-      <c r="C99" s="52" t="s">
-        <v>455</v>
-      </c>
-      <c r="D99" s="53" t="s">
-        <v>456</v>
-      </c>
-      <c r="E99" s="53" t="s">
-        <v>457</v>
-      </c>
-      <c r="F99" s="53" t="s">
-        <v>458</v>
-      </c>
-      <c r="G99" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="47" t="s">
-        <v>27</v>
+    <row r="100" ht="76" customHeight="1">
+      <c r="A100" s="136" t="str">
+        <v>参数与存储</v>
+      </c>
+      <c r="B100" s="133" t="str">
+        <v>17-12</v>
+      </c>
+      <c r="C100" s="132" t="str">
+        <v>参数写入后校验失败</v>
+      </c>
+      <c r="D100" s="132" t="str">
+        <v>触发：设备保存参数后重新读取两份记录，发现至少一份无效或与刚写入的内容不一致。
+影响：不能确认保存成功。</v>
+      </c>
+      <c r="E100" s="132" t="str">
+        <v>1、保存时供电不稳或写入过程受到干扰。
+2、存储器或板上连接异常。</v>
+      </c>
+      <c r="F100" s="132" t="str">
+        <v>1、不要把本次操作当作保存成功，先记录待保存参数。
+2、检查供电和存储器，再保存一次并重新读取核对。
+3、仍不一致时停用检修，不能依赖重启后可能丢失的设置。</v>
+      </c>
+      <c r="G100" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H100" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="100" ht="66">
-      <c r="A100" s="54" t="s">
-        <v>459</v>
-      </c>
-      <c r="B100" s="52" t="s">
-        <v>460</v>
-      </c>
-      <c r="C100" s="52" t="str">
+    <row r="101" ht="87" customHeight="1">
+      <c r="A101" s="141" t="str">
+        <v>扭力检测</v>
+      </c>
+      <c r="B101" s="156" t="str">
+        <v>18-1</v>
+      </c>
+      <c r="C101" s="144" t="str">
         <v>满载标定扭力超过上限</v>
       </c>
-      <c r="D100" s="53" t="s">
-        <v>461</v>
-      </c>
-      <c r="E100" s="53" t="s">
-        <v>462</v>
-      </c>
-      <c r="F100" s="53" t="s">
-        <v>463</v>
-      </c>
-      <c r="G100" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H100" s="47" t="s">
-        <v>27</v>
+      <c r="D101" s="144" t="str">
+        <v>触发：满载标定时扭力值高于允许上限。
+影响：说明当前载荷、安装或传感器零点不符合标定要求，满载标定无效。</v>
+      </c>
+      <c r="E101" s="144" t="str">
+        <v>1、标定载荷或机构阻力偏大。
+2、空载基准、安装受力或称重部件异常。</v>
+      </c>
+      <c r="F101" s="144" t="str">
+        <v>1、停止标定，确认使用的是规定载荷，不要继续加重。
+2、检查浮子和传动有无卡阻，再核对空载基准及安装受力。
+3、载荷和读数正常后重新标定；仍超限时记录原始扭力值检修。</v>
+      </c>
+      <c r="G101" s="145" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H101" s="146" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="101" ht="82.5">
-      <c r="A101" s="54"/>
-      <c r="B101" s="52" t="s">
-        <v>464</v>
-      </c>
-      <c r="C101" s="52" t="str">
+    <row r="102" ht="76" customHeight="1">
+      <c r="A102" s="136" t="str">
+        <v>扭力检测</v>
+      </c>
+      <c r="B102" s="133" t="str">
+        <v>18-2</v>
+      </c>
+      <c r="C102" s="132" t="str">
         <v>满载标定扭力低于下限</v>
       </c>
-      <c r="D101" s="53" t="s">
-        <v>465</v>
-      </c>
-      <c r="E101" s="53" t="s">
-        <v>466</v>
-      </c>
-      <c r="F101" s="53" t="s">
-        <v>463</v>
-      </c>
-      <c r="G101" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H101" s="47" t="s">
-        <v>27</v>
+      <c r="D102" s="132" t="str">
+        <v>触发：满载标定时扭力值低于允许下限。
+影响：说明加载不足、传感器未正确受力或信号未正常传递，满载标定无效。</v>
+      </c>
+      <c r="E102" s="132" t="str">
+        <v>1、规定载荷没有正确传到称重部件。
+2、钢丝松弛、受力方向或空载基准异常。</v>
+      </c>
+      <c r="F102" s="132" t="str">
+        <v>1、确认标定载荷已正确加载，机构没有托住或分担载荷。
+2、检查钢丝、传动和安装受力，再核对空载基准。
+3、受力和读数正常后重新标定，不通过随意增加载荷补偿异常。</v>
+      </c>
+      <c r="G102" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H102" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="102" ht="66">
-      <c r="A102" s="54"/>
-      <c r="B102" s="66" t="s">
-        <v>467</v>
-      </c>
-      <c r="C102" s="66" t="str">
+    <row r="103" ht="102" customHeight="1">
+      <c r="A103" s="136" t="str">
+        <v>扭力检测</v>
+      </c>
+      <c r="B103" s="154" t="str">
+        <v>18-3</v>
+      </c>
+      <c r="C103" s="155" t="str">
         <v>扭力变化超过保护值</v>
       </c>
-      <c r="D102" s="65" t="s">
-        <v>468</v>
-      </c>
-      <c r="E102" s="65" t="s">
-        <v>469</v>
-      </c>
-      <c r="F102" s="65" t="s">
-        <v>463</v>
-      </c>
-      <c r="G102" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H102" s="47" t="s">
-        <v>27</v>
+      <c r="D103" s="132" t="str">
+        <v>触发：运动中扭力相对稳定基准突然升高或降低并超过保护值。
+影响：设备判断浮子、钢丝或导向机构可能碰撞、卡阻或失去受力，立即停止运动。</v>
+      </c>
+      <c r="E103" s="132" t="str">
+        <v>1、运动中碰撞、卡阻或突然失去受力。
+2、液体冲击、机构晃动或扭力信号突变。</v>
+      </c>
+      <c r="F103" s="132" t="str">
+        <v>注意：先排除风险，再恢复操作。
+1、停止运动，不要连续尝试同一方向。
+2、检查浮子、尺带、钢丝和导向机构，对照故障前后的扭力变化。
+3、确认无卡阻、受力恢复正常后再短程测试；反复触发时保存运动和扭力日志。</v>
+      </c>
+      <c r="G103" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H103" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="103" ht="66">
-      <c r="A103" s="54"/>
-      <c r="B103" s="52" t="s">
-        <v>470</v>
-      </c>
-      <c r="C103" s="52" t="str">
+    <row r="104" ht="76" customHeight="1">
+      <c r="A104" s="136" t="str">
+        <v>扭力检测</v>
+      </c>
+      <c r="B104" s="133" t="str">
+        <v>18-4</v>
+      </c>
+      <c r="C104" s="132" t="str">
         <v>空载标定扭力偏离零点</v>
       </c>
-      <c r="D103" s="53" t="s">
-        <v>471</v>
-      </c>
-      <c r="E103" s="53" t="s">
-        <v>472</v>
-      </c>
-      <c r="F103" s="53" t="s">
-        <v>463</v>
-      </c>
-      <c r="G103" s="55" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" s="47" t="s">
-        <v>27</v>
+      <c r="D104" s="132" t="str">
+        <v>触发：空载标定时扭力偏离零点超过允许范围。
+影响：当前零点不稳定，后续碰撞和罐底判断可能失准。</v>
+      </c>
+      <c r="E104" s="132" t="str">
+        <v>1、空载标定时机构仍有载荷或预紧力。
+2、称重零点漂移、安装或信号异常。</v>
+      </c>
+      <c r="F104" s="132" t="str">
+        <v>1、先确认真正满足空载标定条件，不要带载反复清零。
+2、检查预紧、安装和读数稳定性。
+3、空载读数恢复合理后重新标定；仍偏离时记录原始值并检修称重部件。</v>
+      </c>
+      <c r="G104" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H104" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="104" ht="82.5">
-      <c r="A104" s="54"/>
-      <c r="B104" s="52" t="s">
-        <v>473</v>
-      </c>
-      <c r="C104" s="52" t="s">
-        <v>474</v>
-      </c>
-      <c r="D104" s="53" t="s">
-        <v>475</v>
-      </c>
-      <c r="E104" s="53" t="s">
-        <v>476</v>
-      </c>
-      <c r="F104" s="53" t="s">
-        <v>477</v>
-      </c>
-      <c r="G104" s="51" t="s">
-        <v>343</v>
-      </c>
-      <c r="H104" s="47" t="s">
-        <v>27</v>
+    <row r="105" ht="76" customHeight="1">
+      <c r="A105" s="149" t="str">
+        <v>扭力检测</v>
+      </c>
+      <c r="B105" s="150" t="str">
+        <v>18-5</v>
+      </c>
+      <c r="C105" s="149" t="str">
+        <v>扭力传感器饱和</v>
+      </c>
+      <c r="D105" s="149" t="str">
+        <v>当前保留编号，程序不会主动报出。</v>
+      </c>
+      <c r="E105" s="149" t="str">
+        <v>1、当前保留码，不作现行故障原因判断。</v>
+      </c>
+      <c r="F105" s="149" t="str">
+        <v>1、当前设备不会主动报出；旧设备日志请按对应固件历史资料查询。</v>
+      </c>
+      <c r="G105" s="153" t="str">
+        <v>保留</v>
+      </c>
+      <c r="H105" s="152" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="105" ht="66">
-      <c r="A105" s="54"/>
-      <c r="B105" s="66" t="s">
-        <v>478</v>
-      </c>
-      <c r="C105" s="66" t="s">
-        <v>479</v>
-      </c>
-      <c r="D105" s="65" t="s">
-        <v>480</v>
-      </c>
-      <c r="E105" s="65" t="s">
-        <v>481</v>
-      </c>
-      <c r="F105" s="65" t="s">
-        <v>463</v>
-      </c>
-      <c r="G105" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H105" s="47" t="s">
-        <v>27</v>
+    <row r="106" ht="87" customHeight="1">
+      <c r="A106" s="136" t="str">
+        <v>扭力检测</v>
+      </c>
+      <c r="B106" s="139" t="str">
+        <v>18-6</v>
+      </c>
+      <c r="C106" s="140" t="str">
+        <v>扭力通信无响应</v>
+      </c>
+      <c r="D106" s="132" t="str">
+        <v>触发：设备连续一秒未收到新的有效扭力数据。
+影响：不能继续进行载荷、碰撞或罐底判断，相关运动被停止。</v>
+      </c>
+      <c r="E106" s="132" t="str">
+        <v>1、扭力模块无供电，或通信连接松动、断线。
+2、模块重启、受干扰或停止发送数据。</v>
+      </c>
+      <c r="F106" s="132" t="str">
+        <v>1、停止依赖扭力判断的运动，检查模块供电和通信连接。
+2、确认收到的扭力样本持续更新，不能只看屏幕是否还有一个数值。
+3、数据更新恢复后再执行操作；仍无新样本时保存通信记录并检修模块。</v>
+      </c>
+      <c r="G106" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H106" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="106" ht="66">
-      <c r="A106" s="54" t="s">
-        <v>482</v>
-      </c>
-      <c r="B106" s="52" t="s">
-        <v>483</v>
-      </c>
-      <c r="C106" s="52" t="s">
-        <v>484</v>
-      </c>
-      <c r="D106" s="53" t="s">
-        <v>485</v>
-      </c>
-      <c r="E106" s="53" t="s">
-        <v>486</v>
-      </c>
-      <c r="F106" s="53" t="s">
-        <v>487</v>
-      </c>
-      <c r="G106" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H106" s="47" t="s">
-        <v>27</v>
+    <row r="107" ht="87" customHeight="1">
+      <c r="A107" s="141" t="str">
+        <v>设备通信链路</v>
+      </c>
+      <c r="B107" s="156" t="str">
+        <v>20-1</v>
+      </c>
+      <c r="C107" s="144" t="str">
+        <v>串口传输异常</v>
+      </c>
+      <c r="D107" s="144" t="str">
+        <v>触发：主控板与传感器或无线模块交换数据。
+影响：发送或接收没能启动、传输中断，或数据未在规定时间内发完，当前通信中止。</v>
+      </c>
+      <c r="E107" s="144" t="str">
+        <v>1、串口发送或接收启动失败、中断或超时。
+2、模块、通信接口或主控运行状态异常。</v>
+      </c>
+      <c r="F107" s="144" t="str">
+        <v>1、记录发生在传感器还是无线模块通信，以及当时的操作。
+2、检查对应模块供电、连接和是否异常重启。
+3、链路恢复后单独测试通信；持续出现时保存传输日志定位接口。</v>
+      </c>
+      <c r="G107" s="145" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H107" s="146" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="107" ht="66">
-      <c r="A107" s="54"/>
-      <c r="B107" s="52" t="s">
-        <v>488</v>
-      </c>
-      <c r="C107" s="52" t="str">
+    <row r="108" ht="76" customHeight="1">
+      <c r="A108" s="136" t="str">
+        <v>设备通信链路</v>
+      </c>
+      <c r="B108" s="133" t="str">
+        <v>20-2</v>
+      </c>
+      <c r="C108" s="132" t="str">
         <v>无线滑环通信失败</v>
       </c>
-      <c r="D107" s="53" t="s">
-        <v>489</v>
-      </c>
-      <c r="E107" s="53" t="s">
-        <v>490</v>
-      </c>
-      <c r="F107" s="53" t="s">
-        <v>491</v>
-      </c>
-      <c r="G107" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H107" s="47" t="s">
-        <v>27</v>
+      <c r="D108" s="132" t="str">
+        <v>触发：主控板与无线滑环模块之间的指令或状态查询未完成。
+影响：设备不能继续配对、连接或传感器通信。</v>
+      </c>
+      <c r="E108" s="132" t="str">
+        <v>1、主控与无线滑环模块之间的查询或设置失败。
+2、模块供电、连接、模式或接口异常。</v>
+      </c>
+      <c r="F108" s="132" t="str">
+        <v>1、先检查主控能否正常查询本机无线模块。
+2、核对模块供电、板间连接和工作模式，再检查主从链路。
+3、查询与连接均正常后再测量；仍失败时保存模块应答。</v>
+      </c>
+      <c r="G108" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H108" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="108" ht="66">
-      <c r="A108" s="54"/>
-      <c r="B108" s="66" t="s">
-        <v>492</v>
-      </c>
-      <c r="C108" s="66" t="str">
+    <row r="109" ht="76" customHeight="1">
+      <c r="A109" s="136" t="str">
+        <v>设备通信链路</v>
+      </c>
+      <c r="B109" s="139" t="str">
+        <v>20-3</v>
+      </c>
+      <c r="C109" s="140" t="str">
         <v>无线配对信号不达标</v>
       </c>
-      <c r="D108" s="65" t="s">
-        <v>493</v>
-      </c>
-      <c r="E108" s="65" t="s">
-        <v>494</v>
-      </c>
-      <c r="F108" s="65" t="s">
-        <v>491</v>
-      </c>
-      <c r="G108" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H108" s="47" t="s">
-        <v>27</v>
+      <c r="D109" s="132" t="str">
+        <v>触发：无线配对或链路检查。
+影响：接收信号低于设定要求，连接容易掉线或重复传输，设备不继续建立稳定链路。</v>
+      </c>
+      <c r="E109" s="132" t="str">
+        <v>1、目标设备距离较远、天线受遮挡或金属屏蔽较强。
+2、天线连接或现场无线干扰影响信号。</v>
+      </c>
+      <c r="F109" s="132" t="str">
+        <v>1、核对目标设备及信号强度记录。
+2、按安装要求检查天线、距离和遮挡，排除明显干扰。
+3、信号达到要求后再配对；不要只降低判定要求连接不可靠链路。</v>
+      </c>
+      <c r="G109" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H109" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="109" ht="66">
-      <c r="A109" s="54"/>
-      <c r="B109" s="52" t="s">
-        <v>495</v>
-      </c>
-      <c r="C109" s="52" t="s">
-        <v>496</v>
-      </c>
-      <c r="D109" s="53" t="s">
-        <v>497</v>
-      </c>
-      <c r="E109" s="53" t="s">
-        <v>498</v>
-      </c>
-      <c r="F109" s="53" t="s">
-        <v>499</v>
-      </c>
-      <c r="G109" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H109" s="47" t="s">
-        <v>27</v>
+    <row r="110" ht="87" customHeight="1">
+      <c r="A110" s="136" t="str">
+        <v>设备通信链路</v>
+      </c>
+      <c r="B110" s="133" t="str">
+        <v>20-4</v>
+      </c>
+      <c r="C110" s="132" t="str">
+        <v>无线主机通信超时</v>
+      </c>
+      <c r="D110" s="132" t="str">
+        <v>触发：无线主机没能发送指令或没有按时答复，或没有处于主机模式。
+影响：扫描、配对和连接不能继续。</v>
+      </c>
+      <c r="E110" s="132" t="str">
+        <v>1、无线主机未供电、未启动或连接异常。
+2、模块未应答，或本机通信受到干扰。</v>
+      </c>
+      <c r="F110" s="132" t="str">
+        <v>1、检查本机无线主机供电和与主控的连接。
+2、确认模块启动后能答复查询，不要先把问题归到远端传感器。
+3、连续查询正常后再配对；仍超时则检查主机模块和接口。</v>
+      </c>
+      <c r="G110" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H110" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="110" ht="66">
-      <c r="A110" s="54"/>
-      <c r="B110" s="66" t="s">
-        <v>500</v>
-      </c>
-      <c r="C110" s="66" t="s">
-        <v>501</v>
-      </c>
-      <c r="D110" s="65" t="s">
-        <v>502</v>
-      </c>
-      <c r="E110" s="65" t="s">
-        <v>503</v>
-      </c>
-      <c r="F110" s="65" t="s">
-        <v>491</v>
-      </c>
-      <c r="G110" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H110" s="47" t="s">
-        <v>27</v>
+    <row r="111" ht="76" customHeight="1">
+      <c r="A111" s="136" t="str">
+        <v>设备通信链路</v>
+      </c>
+      <c r="B111" s="139" t="str">
+        <v>20-5</v>
+      </c>
+      <c r="C111" s="140" t="str">
+        <v>无线从机未连接</v>
+      </c>
+      <c r="D111" s="132" t="str">
+        <v>触发：无线主机可以正常工作。
+影响：未发现或未连接到目标从机，传感器无线链路尚未建立。</v>
+      </c>
+      <c r="E111" s="132" t="str">
+        <v>1、无线从机未上电、距离或信号条件不合适。
+2、配对对象不正确，或原连接已断开。</v>
+      </c>
+      <c r="F111" s="132" t="str">
+        <v>1、确认目标从机上电并处于可连接状态。
+2、核对主从设备身份、名称、天线和连接状态。
+3、重新连接成功后再测量；频繁掉线时检查供电和现场信号。</v>
+      </c>
+      <c r="G111" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H111" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="111" ht="66">
-      <c r="A111" s="54"/>
-      <c r="B111" s="52" t="s">
-        <v>504</v>
-      </c>
-      <c r="C111" s="52" t="s">
-        <v>505</v>
-      </c>
-      <c r="D111" s="53" t="s">
-        <v>506</v>
-      </c>
-      <c r="E111" s="53" t="s">
-        <v>507</v>
-      </c>
-      <c r="F111" s="53" t="s">
-        <v>508</v>
-      </c>
-      <c r="G111" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H111" s="47" t="s">
-        <v>27</v>
+    <row r="112" ht="76" customHeight="1">
+      <c r="A112" s="136" t="str">
+        <v>设备通信链路</v>
+      </c>
+      <c r="B112" s="133" t="str">
+        <v>20-6</v>
+      </c>
+      <c r="C112" s="132" t="str">
+        <v>无线响应格式异常</v>
+      </c>
+      <c r="D112" s="132" t="str">
+        <v>触发：无线模块有答复。
+影响：工作模式、连接状态、目标设备、信号强度或扫描结果不完整或不符合预期，设备不能确认链路状态。</v>
+      </c>
+      <c r="E112" s="132" t="str">
+        <v>1、无线模块应答被截断、受到干扰或混入旧内容。
+2、模块型号、版本或当前模式不符合预期。</v>
+      </c>
+      <c r="F112" s="132" t="str">
+        <v>1、保存模块查询命令和原始应答。
+2、检查供电、连接、型号及模式，再单独查询状态。
+3、应答恢复完整后再配对；持续异常时由技术人员核对模块协议。</v>
+      </c>
+      <c r="G112" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H112" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="112" ht="66">
-      <c r="A112" s="54"/>
-      <c r="B112" s="66" t="s">
-        <v>509</v>
-      </c>
-      <c r="C112" s="66" t="s">
-        <v>510</v>
-      </c>
-      <c r="D112" s="65" t="s">
-        <v>511</v>
-      </c>
-      <c r="E112" s="65" t="s">
-        <v>512</v>
-      </c>
-      <c r="F112" s="65" t="s">
-        <v>513</v>
-      </c>
-      <c r="G112" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H112" s="47" t="s">
-        <v>514</v>
+    <row r="113" ht="87" customHeight="1">
+      <c r="A113" s="136" t="str">
+        <v>设备通信链路</v>
+      </c>
+      <c r="B113" s="139" t="str">
+        <v>20-7</v>
+      </c>
+      <c r="C113" s="140" t="str">
+        <v>主控单元通信超时</v>
+      </c>
+      <c r="D113" s="132" t="str">
+        <v>触发：显示板连续多次没有收到主控板的完整有效答复。
+影响：设备状态、测量结果和参数不能同步，屏幕按通信中断处理。</v>
+      </c>
+      <c r="E113" s="132" t="str">
+        <v>1、显示板与主控板连接或供电异常。
+2、主控重启、接口异常，或两端程序不配套。</v>
+      </c>
+      <c r="F113" s="132" t="str">
+        <v>1、不要把屏幕旧数据当作当前状态，先确认主控实际是否运行。
+2、检查两块板的供电、内部通信连接和配套版本。
+3、确认状态和结果持续同步后再操作；仍超时时保存两端启动及通信日志。</v>
+      </c>
+      <c r="G113" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H113" s="135" t="str">
+        <v>CPU3本机故障；CPU2通信</v>
       </c>
     </row>
-    <row r="113" ht="82.5">
-      <c r="A113" s="54"/>
-      <c r="B113" s="52" t="s">
-        <v>515</v>
-      </c>
-      <c r="C113" s="52" t="str">
+    <row r="114" ht="76" customHeight="1">
+      <c r="A114" s="136" t="str">
+        <v>设备通信链路</v>
+      </c>
+      <c r="B114" s="133" t="str">
+        <v>20-8</v>
+      </c>
+      <c r="C114" s="132" t="str">
         <v>无线扫描未发现设备</v>
       </c>
-      <c r="D113" s="53" t="s">
-        <v>516</v>
-      </c>
-      <c r="E113" s="53" t="s">
-        <v>517</v>
-      </c>
-      <c r="F113" s="53" t="s">
-        <v>518</v>
-      </c>
-      <c r="G113" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H113" s="47" t="s">
-        <v>27</v>
+      <c r="D114" s="132" t="str">
+        <v>触发：无线主机完成扫描，但没有发现任何可连接设备。
+影响：当前不能进入按信号或名称选择目标的步骤。</v>
+      </c>
+      <c r="E114" s="132" t="str">
+        <v>1、目标从机未上电或不在可扫描范围内。
+2、从机模式、连接占用、天线或遮挡条件异常。</v>
+      </c>
+      <c r="F114" s="132" t="str">
+        <v>1、确认目标从机已经上电且允许被连接。
+2、核对天线、距离、遮挡及是否被其它主机占用。
+3、调整后重新扫描，找到目标再配对，不随意选择其它设备。</v>
+      </c>
+      <c r="G114" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H114" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="114" ht="82.5">
-      <c r="A114" s="54"/>
-      <c r="B114" s="52" t="s">
-        <v>519</v>
-      </c>
-      <c r="C114" s="52" t="s">
-        <v>520</v>
-      </c>
-      <c r="D114" s="53" t="s">
-        <v>521</v>
-      </c>
-      <c r="E114" s="53" t="s">
-        <v>522</v>
-      </c>
-      <c r="F114" s="53" t="s">
-        <v>523</v>
-      </c>
-      <c r="G114" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H114" s="47" t="s">
-        <v>27</v>
+    <row r="115" ht="76" customHeight="1">
+      <c r="A115" s="136" t="str">
+        <v>设备通信链路</v>
+      </c>
+      <c r="B115" s="133" t="str">
+        <v>20-9</v>
+      </c>
+      <c r="C115" s="132" t="str">
+        <v>无线名称重复</v>
+      </c>
+      <c r="D115" s="132" t="str">
+        <v>触发：扫描结果中发现两个或更多设备使用同一个目标名称。
+影响：设备不能确定应该连接哪一个，所以取消配对。</v>
+      </c>
+      <c r="E115" s="132" t="str">
+        <v>1、多台设备使用相同名称。
+2、更换模块后未设置唯一名称，或邻近同名设备进入扫描范围。</v>
+      </c>
+      <c r="F115" s="132" t="str">
+        <v>1、核对同名设备的实际身份。
+2、按现场协调安排为目标设置唯一名称，不擅自关闭其它运行设备。
+3、重新扫描，确认只匹配正确目标后再连接。</v>
+      </c>
+      <c r="G115" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H115" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="115" ht="66">
-      <c r="A115" s="54"/>
-      <c r="B115" s="52" t="s">
-        <v>524</v>
-      </c>
-      <c r="C115" s="52" t="s">
-        <v>525</v>
-      </c>
-      <c r="D115" s="53" t="s">
-        <v>526</v>
-      </c>
-      <c r="E115" s="53" t="s">
-        <v>527</v>
-      </c>
-      <c r="F115" s="53" t="s">
-        <v>528</v>
-      </c>
-      <c r="G115" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H115" s="47" t="s">
-        <v>27</v>
+    <row r="116" ht="76" customHeight="1">
+      <c r="A116" s="136" t="str">
+        <v>设备通信链路</v>
+      </c>
+      <c r="B116" s="133" t="str">
+        <v>20-10</v>
+      </c>
+      <c r="C116" s="132" t="str">
+        <v>无线名称无效</v>
+      </c>
+      <c r="D116" s="132" t="str">
+        <v>触发：输入或保存的无线设备名称为空、过长或含有当前模块不能接受的格式。
+影响：设备不开始按名称配对。</v>
+      </c>
+      <c r="E116" s="132" t="str">
+        <v>1、目标名称未填写、过长或格式不符合模块要求。
+2、名称保存异常或复制时带入多余字符。</v>
+      </c>
+      <c r="F116" s="132" t="str">
+        <v>1、核对当前保存名称及该模块允许格式。
+2、按实际目标输入唯一、合规的名称并保存。
+3、重新读取确认名称正确后再配对；再次丢失时检查参数保存。</v>
+      </c>
+      <c r="G116" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H116" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="116" ht="82.5">
-      <c r="A116" s="54"/>
-      <c r="B116" s="52" t="s">
-        <v>529</v>
-      </c>
-      <c r="C116" s="52" t="s">
-        <v>530</v>
-      </c>
-      <c r="D116" s="53" t="s">
-        <v>531</v>
-      </c>
-      <c r="E116" s="53" t="s">
-        <v>532</v>
-      </c>
-      <c r="F116" s="53" t="s">
-        <v>533</v>
-      </c>
-      <c r="G116" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H116" s="47" t="s">
-        <v>27</v>
+    <row r="117" ht="76" customHeight="1">
+      <c r="A117" s="136" t="str">
+        <v>设备通信链路</v>
+      </c>
+      <c r="B117" s="133" t="str">
+        <v>20-11</v>
+      </c>
+      <c r="C117" s="132" t="str">
+        <v>无线模块非主机模式</v>
+      </c>
+      <c r="D117" s="132" t="str">
+        <v>触发：准备扫描或配对时发现本机无线模块没有工作在主机模式。
+影响：不能主动搜索和连接从机。</v>
+      </c>
+      <c r="E117" s="132" t="str">
+        <v>1、本机模块设置成从机或其它模式。
+2、更换模块后未配置，或模式设置未保存。</v>
+      </c>
+      <c r="F117" s="132" t="str">
+        <v>1、确认主从模块安装位置，避免把远端从机改成主机。
+2、按调试流程将本机模块设置为主机并保存。
+3、重新查询确认模式正确后再扫描；重启后丢失时检查模块保存。</v>
+      </c>
+      <c r="G117" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H117" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="117" ht="66">
-      <c r="A117" s="54"/>
-      <c r="B117" s="52" t="s">
-        <v>534</v>
-      </c>
-      <c r="C117" s="52" t="s">
-        <v>535</v>
-      </c>
-      <c r="D117" s="53" t="s">
-        <v>536</v>
-      </c>
-      <c r="E117" s="53" t="s">
-        <v>537</v>
-      </c>
-      <c r="F117" s="53" t="s">
-        <v>538</v>
-      </c>
-      <c r="G117" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H117" s="47" t="s">
-        <v>27</v>
+    <row r="118" ht="76" customHeight="1">
+      <c r="A118" s="136" t="str">
+        <v>设备通信链路</v>
+      </c>
+      <c r="B118" s="133" t="str">
+        <v>20-12</v>
+      </c>
+      <c r="C118" s="132" t="str">
+        <v>无线名称未找到</v>
+      </c>
+      <c r="D118" s="132" t="str">
+        <v>触发：无线扫描已经发现一个或多个候选设备。
+影响：其中没有任何设备的名称与指定目标完全一致。</v>
+      </c>
+      <c r="E118" s="132" t="str">
+        <v>1、目标名称与实际从机名称不一致。
+2、目标未上电、超出范围，或更换后名称未同步。</v>
+      </c>
+      <c r="F118" s="132" t="str">
+        <v>1、核对扫描到的设备和目标从机的实际名称。
+2、逐项检查字符、大小写和编号，确认目标已上电。
+3、修正名称或恢复目标可见状态后重新扫描配对。</v>
+      </c>
+      <c r="G118" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H118" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="118" ht="82.5">
-      <c r="A118" s="54"/>
-      <c r="B118" s="52" t="s">
-        <v>539</v>
-      </c>
-      <c r="C118" s="52" t="s">
-        <v>540</v>
-      </c>
-      <c r="D118" s="53" t="s">
-        <v>541</v>
-      </c>
-      <c r="E118" s="53" t="s">
-        <v>542</v>
-      </c>
-      <c r="F118" s="53" t="s">
-        <v>543</v>
-      </c>
-      <c r="G118" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H118" s="47" t="s">
-        <v>544</v>
+    <row r="119" ht="87" customHeight="1">
+      <c r="A119" s="136" t="str">
+        <v>设备通信链路</v>
+      </c>
+      <c r="B119" s="133" t="str">
+        <v>20-13</v>
+      </c>
+      <c r="C119" s="132" t="str">
+        <v>分布结果读取失败</v>
+      </c>
+      <c r="D119" s="132" t="str">
+        <v>触发：显示板与主控板仍能通信。
+影响：连续三轮读取分布测量点阵时，完成计数、测点数量、结果来源或完成锁存前后不一致，不能确认本轮结果完整，所以不发布完成状态。</v>
+      </c>
+      <c r="E119" s="132" t="str">
+        <v>1、读取期间测量结果被更新、开始新一轮测量或主控重启。
+2、两端通信不稳或版本不配套。</v>
+      </c>
+      <c r="F119" s="132" t="str">
+        <v>1、暂不采用本轮分布结果，避免同时切换或重复启动测量。
+2、检查主控与显示通信、两端版本和测量切换记录。
+3、重新执行完整测量，确认点数及完成状态一致后再使用结果；仍失败时保存同步日志。</v>
+      </c>
+      <c r="G119" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H119" s="135" t="str">
+        <v>CPU3本机故障；分布结果同步</v>
       </c>
     </row>
-    <row r="119" ht="82.5">
-      <c r="A119" s="54" t="s">
-        <v>545</v>
-      </c>
-      <c r="B119" s="52" t="s">
-        <v>546</v>
-      </c>
-      <c r="C119" s="52" t="s">
-        <v>547</v>
-      </c>
-      <c r="D119" s="53" t="s">
-        <v>548</v>
-      </c>
-      <c r="E119" s="53" t="s">
-        <v>549</v>
-      </c>
-      <c r="F119" s="53" t="s">
-        <v>550</v>
-      </c>
-      <c r="G119" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H119" s="47" t="s">
-        <v>27</v>
+    <row r="120" ht="87" customHeight="1">
+      <c r="A120" s="141" t="str">
+        <v>模拟输出与自检</v>
+      </c>
+      <c r="B120" s="156" t="str">
+        <v>21-2</v>
+      </c>
+      <c r="C120" s="144" t="str">
+        <v>模拟量输出初始化失败</v>
+      </c>
+      <c r="D120" s="144" t="str">
+        <v>触发：开机建立模拟量输出。
+影响：芯片复位、基本配置或状态确认未完成，四至二十毫安输出不能保证正确。</v>
+      </c>
+      <c r="E120" s="144" t="str">
+        <v>1、模拟输出部件供电、复位或初始配置失败。
+2、板间连接、输出回路或器件异常。</v>
+      </c>
+      <c r="F120" s="144" t="str">
+        <v>1、先通知使用该信号的控制端，确认后续检查不会引起误动作。
+2、检查输出部件供电、连接和回路，保存启动故障阶段。
+3、初始化正常后实测输出电流并核对接收端，再恢复使用。</v>
+      </c>
+      <c r="G120" s="145" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H120" s="146" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="120" ht="82.5">
-      <c r="A120" s="54"/>
-      <c r="B120" s="52" t="s">
-        <v>551</v>
-      </c>
-      <c r="C120" s="52" t="s">
-        <v>552</v>
-      </c>
-      <c r="D120" s="53" t="s">
-        <v>553</v>
-      </c>
-      <c r="E120" s="53" t="s">
-        <v>554</v>
-      </c>
-      <c r="F120" s="53" t="s">
-        <v>555</v>
-      </c>
-      <c r="G120" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H120" s="47" t="s">
-        <v>27</v>
+    <row r="121" ht="76" customHeight="1">
+      <c r="A121" s="136" t="str">
+        <v>模拟输出与自检</v>
+      </c>
+      <c r="B121" s="133" t="str">
+        <v>21-6</v>
+      </c>
+      <c r="C121" s="132" t="str">
+        <v>模拟量输出配置校验失败</v>
+      </c>
+      <c r="D121" s="132" t="str">
+        <v>触发：设备写入模拟量输出配置后，再次确认发现结果不一致。
+影响：当前输出范围和控制方式不能确认。</v>
+      </c>
+      <c r="E121" s="132" t="str">
+        <v>1、写入配置与读回内容不一致。
+2、供电波动、通信干扰或输出部件复位。</v>
+      </c>
+      <c r="F121" s="132" t="str">
+        <v>1、暂停依赖该输出，记录本次配置及校验结果。
+2、检查输出部件供电和连接，再按流程重新配置。
+3、读回配置一致并实测电流正确后再恢复使用。</v>
+      </c>
+      <c r="G121" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H121" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="121" ht="82.5">
-      <c r="A121" s="54"/>
-      <c r="B121" s="52" t="s">
-        <v>556</v>
-      </c>
-      <c r="C121" s="52" t="s">
-        <v>557</v>
-      </c>
-      <c r="D121" s="53" t="s">
-        <v>558</v>
-      </c>
-      <c r="E121" s="53" t="s">
-        <v>559</v>
-      </c>
-      <c r="F121" s="53" t="s">
-        <v>560</v>
-      </c>
-      <c r="G121" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H121" s="47" t="s">
-        <v>27</v>
+    <row r="122" ht="76" customHeight="1">
+      <c r="A122" s="136" t="str">
+        <v>模拟输出与自检</v>
+      </c>
+      <c r="B122" s="133" t="str">
+        <v>21-9</v>
+      </c>
+      <c r="C122" s="132" t="str">
+        <v>模拟输出内部通信异常</v>
+      </c>
+      <c r="D122" s="132" t="str">
+        <v>触发：模拟输出部件报告内部数据交换异常。
+影响：设备不能确认电流设置和诊断状态是否可靠。</v>
+      </c>
+      <c r="E122" s="132" t="str">
+        <v>1、模拟输出部件内部通信或供电异常。
+2、干扰、板上连接或器件异常。</v>
+      </c>
+      <c r="F122" s="132" t="str">
+        <v>1、通知接收端不要依赖当前电流值。
+2、记录内部故障状态，检查供电、连接和接地。
+3、内部诊断恢复正常后实测电流；仍报错时检修输出部件。</v>
+      </c>
+      <c r="G122" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H122" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="122" ht="66">
-      <c r="A122" s="54"/>
-      <c r="B122" s="52" t="s">
-        <v>561</v>
-      </c>
-      <c r="C122" s="52" t="s">
-        <v>562</v>
-      </c>
-      <c r="D122" s="53" t="s">
-        <v>563</v>
-      </c>
-      <c r="E122" s="53" t="s">
-        <v>564</v>
-      </c>
-      <c r="F122" s="53" t="s">
-        <v>565</v>
-      </c>
-      <c r="G122" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H122" s="47" t="s">
-        <v>27</v>
+    <row r="123" ht="87" customHeight="1">
+      <c r="A123" s="136" t="str">
+        <v>模拟输出与自检</v>
+      </c>
+      <c r="B123" s="133" t="str">
+        <v>21-10</v>
+      </c>
+      <c r="C123" s="132" t="str">
+        <v>模拟输出电流过高</v>
+      </c>
+      <c r="D123" s="132" t="str">
+        <v>触发：模拟输出部件检测到环路电流高于允许范围，实际输出可能超过目标值。
+影响：设备不能保证四至二十毫安信号正确。</v>
+      </c>
+      <c r="E123" s="132" t="str">
+        <v>1、回路接线、供电或负载配置错误。
+2、输出部件或接收端异常。</v>
+      </c>
+      <c r="F123" s="132" t="str">
+        <v>1、先协调接收端，再按规程停用并检查回路，避免错误电流引起动作。
+2、核对接线、负载和供电，使用合适仪表检查实际电流。
+3、排除原因并确认设定值、实测值和接收值一致后再恢复使用。</v>
+      </c>
+      <c r="G123" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H123" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="123" ht="66">
-      <c r="A123" s="54"/>
-      <c r="B123" s="66" t="s">
-        <v>566</v>
-      </c>
-      <c r="C123" s="66" t="s">
-        <v>567</v>
-      </c>
-      <c r="D123" s="65" t="s">
-        <v>568</v>
-      </c>
-      <c r="E123" s="65" t="s">
-        <v>569</v>
-      </c>
-      <c r="F123" s="65" t="s">
-        <v>570</v>
-      </c>
-      <c r="G123" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H123" s="47" t="s">
-        <v>27</v>
+    <row r="124" ht="76" customHeight="1">
+      <c r="A124" s="136" t="str">
+        <v>模拟输出与自检</v>
+      </c>
+      <c r="B124" s="139" t="str">
+        <v>21-11</v>
+      </c>
+      <c r="C124" s="140" t="str">
+        <v>模拟输出电流过低或断环</v>
+      </c>
+      <c r="D124" s="132" t="str">
+        <v>触发：模拟输出部件检测到环路电流低于目标范围，常见于回路开路、负载未接通或供电不足。
+影响：四至二十毫安信号不可信。</v>
+      </c>
+      <c r="E124" s="132" t="str">
+        <v>1、回路断线、接反、端子松动或未供电。
+2、负载过大、线路压降或输出部件异常。</v>
+      </c>
+      <c r="F124" s="132" t="str">
+        <v>1、协调接收端后检查回路是否闭合、极性是否正确。
+2、测量回路供电，核对负载和端子。
+3、修复后实测电流并与目标值、接收端读数核对。</v>
+      </c>
+      <c r="G124" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H124" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="124" ht="66">
-      <c r="A124" s="54"/>
-      <c r="B124" s="66" t="s">
-        <v>571</v>
-      </c>
-      <c r="C124" s="66" t="s">
-        <v>572</v>
-      </c>
-      <c r="D124" s="65" t="s">
-        <v>573</v>
-      </c>
-      <c r="E124" s="65" t="s">
-        <v>574</v>
-      </c>
-      <c r="F124" s="65" t="s">
-        <v>575</v>
-      </c>
-      <c r="G124" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H124" s="47" t="s">
-        <v>27</v>
+    <row r="125" ht="87" customHeight="1">
+      <c r="A125" s="136" t="str">
+        <v>模拟输出与自检</v>
+      </c>
+      <c r="B125" s="139" t="str">
+        <v>21-12</v>
+      </c>
+      <c r="C125" s="140" t="str">
+        <v>模拟输出环路电压不足</v>
+      </c>
+      <c r="D125" s="132" t="str">
+        <v>触发：模拟输出环路可用电压低于正常工作要求。
+影响：输出部件可能不能把电流稳定到目标值。</v>
+      </c>
+      <c r="E125" s="132" t="str">
+        <v>1、回路电源偏低，或线路、端子压降过大。
+2、负载总阻值过大，输出余量不足。</v>
+      </c>
+      <c r="F125" s="132" t="str">
+        <v>1、核对回路电源及接收设备的连接方式。
+2、按规程测量设备端电压，检查端子、线路和负载总阻值。
+3、恢复规定工作条件后核对输出电流，不能只确认回路已经接通。</v>
+      </c>
+      <c r="G125" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H125" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="125" ht="66">
-      <c r="A125" s="54"/>
-      <c r="B125" s="52" t="s">
-        <v>576</v>
-      </c>
-      <c r="C125" s="52" t="str">
+    <row r="126" ht="76" customHeight="1">
+      <c r="A126" s="136" t="str">
+        <v>模拟输出与自检</v>
+      </c>
+      <c r="B126" s="133" t="str">
+        <v>21-13</v>
+      </c>
+      <c r="C126" s="132" t="str">
         <v>主控与模拟量输出模块通信失败</v>
       </c>
-      <c r="D125" s="53" t="s">
-        <v>577</v>
-      </c>
-      <c r="E125" s="53" t="s">
-        <v>578</v>
-      </c>
-      <c r="F125" s="53" t="s">
-        <v>579</v>
-      </c>
-      <c r="G125" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H125" s="47" t="s">
-        <v>27</v>
+      <c r="D126" s="132" t="str">
+        <v>触发：主控板向模拟输出部件传送设置或读取状态时没有完成。
+影响：当前输出值和诊断结果不能确认。</v>
+      </c>
+      <c r="E126" s="132" t="str">
+        <v>1、主控与模拟输出部件通信未完成。
+2、部件供电、板上连接或接口异常。</v>
+      </c>
+      <c r="F126" s="132" t="str">
+        <v>1、记录发生在初始化、设置输出还是读取状态阶段。
+2、检查输出部件供电和主控连接，暂停依赖当前输出。
+3、通信及诊断恢复后实测电流，确认正确再交回接收端使用。</v>
+      </c>
+      <c r="G126" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H126" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="126" ht="82.5">
-      <c r="A126" s="54"/>
-      <c r="B126" s="52" t="s">
-        <v>580</v>
-      </c>
-      <c r="C126" s="52" t="s">
-        <v>581</v>
-      </c>
-      <c r="D126" s="53" t="s">
-        <v>582</v>
-      </c>
-      <c r="E126" s="53" t="s">
-        <v>583</v>
-      </c>
-      <c r="F126" s="53" t="s">
-        <v>584</v>
-      </c>
-      <c r="G126" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H126" s="47" t="s">
-        <v>27</v>
+    <row r="127" ht="76" customHeight="1">
+      <c r="A127" s="136" t="str">
+        <v>模拟输出与自检</v>
+      </c>
+      <c r="B127" s="133" t="str">
+        <v>21-14</v>
+      </c>
+      <c r="C127" s="132" t="str">
+        <v>模拟输出操作冲突</v>
+      </c>
+      <c r="D127" s="132" t="str">
+        <v>触发：模拟输出部件正在处理上一项设置或诊断操作，新的访问不能安全开始。
+影响：设备中止这次操作。</v>
+      </c>
+      <c r="E127" s="132" t="str">
+        <v>1、上一项模拟输出访问还未结束。
+2、访问未正常收尾，或内部任务竞争。</v>
+      </c>
+      <c r="F127" s="132" t="str">
+        <v>1、停止连续调整输出，记录触发操作。
+2、等待前一项完成后再单独测试；持续冲突时保存日志。
+3、由技术人员确认访问状态恢复，实测输出正确后再使用。</v>
+      </c>
+      <c r="G127" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H127" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="127" ht="82.5">
-      <c r="A127" s="54"/>
-      <c r="B127" s="52" t="s">
-        <v>585</v>
-      </c>
-      <c r="C127" s="52" t="s">
-        <v>586</v>
-      </c>
-      <c r="D127" s="53" t="s">
-        <v>587</v>
-      </c>
-      <c r="E127" s="53" t="s">
-        <v>588</v>
-      </c>
-      <c r="F127" s="53" t="s">
-        <v>589</v>
-      </c>
-      <c r="G127" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H127" s="47" t="s">
-        <v>27</v>
+    <row r="128" ht="76" customHeight="1">
+      <c r="A128" s="136" t="str">
+        <v>模拟输出与自检</v>
+      </c>
+      <c r="B128" s="133" t="str">
+        <v>21-15</v>
+      </c>
+      <c r="C128" s="132" t="str">
+        <v>模拟输出过温关断</v>
+      </c>
+      <c r="D128" s="132" t="str">
+        <v>触发：模拟输出部件温度达到保护上限并关闭输出。
+影响：四至二十毫安信号可能中断或回到保护状态。</v>
+      </c>
+      <c r="E128" s="132" t="str">
+        <v>1、模拟输出部件温度过高，散热或工作条件不合适。
+2、回路异常或器件故障导致发热。</v>
+      </c>
+      <c r="F128" s="132" t="str">
+        <v>1、通知接收端并停用该输出，等待冷却。
+2、检查环境、散热、回路供电和负载。
+3、原因排除、温度及电流恢复正常后再使用；再次关断时检修。</v>
+      </c>
+      <c r="G128" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H128" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="128" ht="82.5">
-      <c r="A128" s="54"/>
-      <c r="B128" s="52" t="s">
-        <v>590</v>
-      </c>
-      <c r="C128" s="52" t="s">
-        <v>591</v>
-      </c>
-      <c r="D128" s="53" t="s">
-        <v>592</v>
-      </c>
-      <c r="E128" s="53" t="s">
-        <v>593</v>
-      </c>
-      <c r="F128" s="53" t="s">
-        <v>594</v>
-      </c>
-      <c r="G128" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H128" s="47" t="s">
-        <v>27</v>
+    <row r="129" ht="76" customHeight="1">
+      <c r="A129" s="136" t="str">
+        <v>模拟输出与自检</v>
+      </c>
+      <c r="B129" s="133" t="str">
+        <v>21-16</v>
+      </c>
+      <c r="C129" s="132" t="str">
+        <v>模拟输出过温预警</v>
+      </c>
+      <c r="D129" s="132" t="str">
+        <v>触发：模拟输出部件温度已接近保护上限。
+影响：继续工作可能触发关断并影响四至二十毫安信号。</v>
+      </c>
+      <c r="E129" s="132" t="str">
+        <v>1、环境温度高或散热不良。
+2、回路工作条件不合适，或器件发热异常。</v>
+      </c>
+      <c r="F129" s="132" t="str">
+        <v>1、检查部件温度，提醒接收端存在输出关断风险。
+2、核对回路供电、负载和散热条件。
+3、温度恢复后核对输出电流；预警反复出现时停用检修。</v>
+      </c>
+      <c r="G129" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H129" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="129" ht="82.5">
-      <c r="A129" s="54" t="s">
-        <v>595</v>
-      </c>
-      <c r="B129" s="52" t="s">
-        <v>596</v>
-      </c>
-      <c r="C129" s="52" t="str">
+    <row r="130" ht="87" customHeight="1">
+      <c r="A130" s="141" t="str">
+        <v>系统与软件</v>
+      </c>
+      <c r="B130" s="156" t="str">
+        <v>22-1</v>
+      </c>
+      <c r="C130" s="144" t="str">
         <v>内部数据空间不足</v>
       </c>
-      <c r="D129" s="53" t="s">
-        <v>597</v>
-      </c>
-      <c r="E129" s="53" t="s">
-        <v>598</v>
-      </c>
-      <c r="F129" s="53" t="s">
-        <v>599</v>
-      </c>
-      <c r="G129" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H129" s="47" t="s">
-        <v>27</v>
+      <c r="D130" s="144" t="str">
+        <v>触发：设备准备保存、接收或整理这次数据。
+影响：发现可用空间不足以容纳完整内容，为防止数据被截断或覆盖而中止操作。</v>
+      </c>
+      <c r="E130" s="144" t="str">
+        <v>1、数据长度或测点数量超过当前处理容量。
+2、异常输入、配置不配套或内部容量处理异常。</v>
+      </c>
+      <c r="F130" s="144" t="str">
+        <v>1、记录触发功能、数据量和相关参数。
+2、仅在参数允许范围内调整测点数量，不随意删除历史数据或恢复出厂。
+3、仍失败时保存日志交技术人员定位数据来源和容量限制。</v>
+      </c>
+      <c r="G130" s="145" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H130" s="146" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="130" ht="99">
-      <c r="A130" s="54"/>
-      <c r="B130" s="52" t="s">
-        <v>600</v>
-      </c>
-      <c r="C130" s="52" t="s">
-        <v>601</v>
-      </c>
-      <c r="D130" s="53" t="s">
-        <v>602</v>
-      </c>
-      <c r="E130" s="53" t="s">
-        <v>603</v>
-      </c>
-      <c r="F130" s="53" t="s">
-        <v>604</v>
-      </c>
-      <c r="G130" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H130" s="47" t="s">
-        <v>27</v>
+    <row r="131" ht="76" customHeight="1">
+      <c r="A131" s="136" t="str">
+        <v>系统与软件</v>
+      </c>
+      <c r="B131" s="133" t="str">
+        <v>22-2</v>
+      </c>
+      <c r="C131" s="132" t="str">
+        <v>内部执行条件异常</v>
+      </c>
+      <c r="D131" s="132" t="str">
+        <v>触发：设备内部准备执行某项动作时发现必要对象、方向、数量或前置状态不完整。
+影响：继续运行可能产生错误动作，所以中止。</v>
+      </c>
+      <c r="E131" s="132" t="str">
+        <v>1、操作所需的对象、方向、数量或前置状态不完整。
+2、前一流程异常退出，或内部执行状态异常。</v>
+      </c>
+      <c r="F131" s="132" t="str">
+        <v>1、停止重复操作，记录前一步动作和本次命令。
+2、核对该功能需要的配置和前置状态。
+3、正常操作仍复现时保存日志交技术人员检查，不直接归咎于现场操作。</v>
+      </c>
+      <c r="G131" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H131" s="135" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="131" ht="82.5">
-      <c r="A131" s="54"/>
-      <c r="B131" s="52" t="s">
-        <v>605</v>
-      </c>
-      <c r="C131" s="52" t="s">
-        <v>606</v>
-      </c>
-      <c r="D131" s="53" t="s">
-        <v>607</v>
-      </c>
-      <c r="E131" s="53" t="s">
-        <v>608</v>
-      </c>
-      <c r="F131" s="53" t="s">
-        <v>609</v>
-      </c>
-      <c r="G131" s="51" t="s">
-        <v>26</v>
-      </c>
-      <c r="H131" s="47" t="s">
-        <v>27</v>
+    <row r="132" ht="87" customHeight="1">
+      <c r="A132" s="136" t="str">
+        <v>系统与软件</v>
+      </c>
+      <c r="B132" s="133" t="str">
+        <v>22-3</v>
+      </c>
+      <c r="C132" s="132" t="str">
+        <v>内部计算结果异常</v>
+      </c>
+      <c r="D132" s="132" t="str">
+        <v>触发：设备根据当前位置、距离、比例或测量数据计算控制结果。
+影响：得到超出可表示范围或不能使用的结果，这次动作被取消。</v>
+      </c>
+      <c r="E132" s="132" t="str">
+        <v>1、位置、比例、距离或测量输入异常。
+2、换算参数不合理，或程序计算边界问题。</v>
+      </c>
+      <c r="F132" s="132" t="str">
+        <v>1、记录触发时的位置、目标、比例和测量数据。
+2、核对单位、周长及标定值，不使用无法确认的计算结果。
+3、修正已确认的输入问题后再测试；仍异常时交技术人员分析计算过程。</v>
+      </c>
+      <c r="G132" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H132" s="157" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="132" ht="115.5">
-      <c r="A132" s="56" t="s">
-        <v>610</v>
-      </c>
-      <c r="B132" s="66" t="s">
-        <v>611</v>
-      </c>
-      <c r="C132" s="66" t="s">
-        <v>612</v>
-      </c>
-      <c r="D132" s="65" t="s">
-        <v>613</v>
-      </c>
-      <c r="E132" s="65" t="s">
-        <v>614</v>
-      </c>
-      <c r="F132" s="65" t="s">
-        <v>615</v>
-      </c>
-      <c r="G132" s="57" t="s">
-        <v>26</v>
-      </c>
-      <c r="H132" s="58" t="s">
-        <v>27</v>
+    <row r="133" ht="117" customHeight="1">
+      <c r="A133" s="141" t="str">
+        <v>整机供电与电源监控</v>
+      </c>
+      <c r="B133" s="158" t="str">
+        <v>23-1</v>
+      </c>
+      <c r="C133" s="159" t="str">
+        <v>整机24 V欠压</v>
+      </c>
+      <c r="D133" s="144" t="str">
+        <v>触发：电源监控确认整机24V供电已经低于20V安全值。
+影响：设备会停止当前动作，并进入低压保护，避免电压继续下降时位置和参数来不及保存。</v>
+      </c>
+      <c r="E133" s="144" t="str">
+        <v>1、24 V电源容量不足，或大负载启动时压降明显。
+2、端子松动、线缆压降过大，或负载异常。</v>
+      </c>
+      <c r="F133" s="144" t="str">
+        <v>注意：先排除风险，再恢复操作。
+1、保持停机，不反复启动电机；先确认现场供电和机构安全。
+2、测量设备24 V输入，检查电源容量、端子、线缆和负载。
+3、供电和电源监控恢复正常后，确认位置可信再重新发起操作；出现23-6时先处理位置保存。</v>
+      </c>
+      <c r="G133" s="145" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H133" s="160" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="133" ht="132">
-      <c r="A133" s="56"/>
-      <c r="B133" s="59" t="s">
-        <v>616</v>
-      </c>
-      <c r="C133" s="59" t="str">
+    <row r="134" ht="87" customHeight="1">
+      <c r="A134" s="136" t="str">
+        <v>整机供电与电源监控</v>
+      </c>
+      <c r="B134" s="133" t="str">
+        <v>23-2</v>
+      </c>
+      <c r="C134" s="132" t="str">
         <v>电源采样数据处理不及时</v>
       </c>
-      <c r="D133" s="60" t="s">
-        <v>617</v>
-      </c>
-      <c r="E133" s="60" t="s">
-        <v>618</v>
-      </c>
-      <c r="F133" s="60" t="s">
-        <v>619</v>
-      </c>
-      <c r="G133" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="H133" s="58" t="s">
-        <v>27</v>
+      <c r="D134" s="132" t="str">
+        <v>触发：24V电压采样来不及处理，新的数据把前面的数据顶掉了。
+影响：设备不能确定这段时间的电压数据是不是最新的，会停止使用这次采样结果。</v>
+      </c>
+      <c r="E134" s="132" t="str">
+        <v>1、电压采样处理不及时，或主控运行状态异常。
+2、现场干扰或采样链路异常，需要结合日志定位。</v>
+      </c>
+      <c r="F134" s="132" t="str">
+        <v>1、停止相关操作，保存采样故障和恢复记录。
+2、检查24 V供电及故障时的系统负载，观察采样能否恢复更新。
+3、监控恢复正常并确认位置可靠后再操作；反复出现时检查主控采样处理。</v>
+      </c>
+      <c r="G134" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H134" s="157" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="134" ht="132">
-      <c r="A134" s="56"/>
-      <c r="B134" s="59" t="s">
-        <v>620</v>
-      </c>
-      <c r="C134" s="59" t="str">
+    <row r="135" ht="76" customHeight="1">
+      <c r="A135" s="136" t="str">
+        <v>整机供电与电源监控</v>
+      </c>
+      <c r="B135" s="133" t="str">
+        <v>23-3</v>
+      </c>
+      <c r="C135" s="132" t="str">
         <v>电源采样传输意外停止</v>
       </c>
-      <c r="D134" s="60" t="s">
-        <v>621</v>
-      </c>
-      <c r="E134" s="60" t="s">
-        <v>622</v>
-      </c>
-      <c r="F134" s="60" t="s">
-        <v>623</v>
-      </c>
-      <c r="G134" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="H134" s="58" t="s">
-        <v>27</v>
+      <c r="D135" s="132" t="str">
+        <v>触发：24V电压采样的数据传输意外停了。
+影响：已有的电压数据可能已经过期，设备不能继续把旧数据当成当前电压。</v>
+      </c>
+      <c r="E135" s="132" t="str">
+        <v>1、电压采样传输被打断，或采样链路异常。
+2、干扰、主控运行或硬件状态异常。</v>
+      </c>
+      <c r="F135" s="132" t="str">
+        <v>1、停止相关操作，不把旧电压当作当前值。
+2、检查24 V供电，记录采样停止及恢复情况。
+3、采样连续更新且电源监控恢复后再操作；重复停止时检修采样链路。</v>
+      </c>
+      <c r="G135" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H135" s="157" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="135" ht="115.5">
-      <c r="A135" s="56"/>
-      <c r="B135" s="59" t="s">
-        <v>624</v>
-      </c>
-      <c r="C135" s="59" t="str">
+    <row r="136" ht="76" customHeight="1">
+      <c r="A136" s="136" t="str">
+        <v>整机供电与电源监控</v>
+      </c>
+      <c r="B136" s="133" t="str">
+        <v>23-4</v>
+      </c>
+      <c r="C136" s="132" t="str">
         <v>电源采样启动失败</v>
       </c>
-      <c r="D135" s="60" t="s">
-        <v>625</v>
-      </c>
-      <c r="E135" s="60" t="s">
-        <v>626</v>
-      </c>
-      <c r="F135" s="60" t="s">
-        <v>627</v>
-      </c>
-      <c r="G135" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="H135" s="58" t="s">
-        <v>27</v>
+      <c r="D136" s="132" t="str">
+        <v>触发：设备启动24V电源监控后，5ms内没有拿到第一笔有效电压数据。
+影响：设备暂时不能判断整机供电是否正常，电源保护也不能正常开始工作。</v>
+      </c>
+      <c r="E136" s="132" t="str">
+        <v>1、电压采样未启动，或启动后没有有效数据。
+2、主控供电、采样输入或内部时钟异常。</v>
+      </c>
+      <c r="F136" s="132" t="str">
+        <v>1、先确认设备24 V输入正常，保存启动日志。
+2、由技术人员检查电源监控启动及采样回路。
+3、确认启动时取得有效电压且持续更新后再运行；未恢复时不要依赖电源保护。</v>
+      </c>
+      <c r="G136" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H136" s="157" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="136" ht="99">
-      <c r="A136" s="56"/>
-      <c r="B136" s="59" t="s">
-        <v>628</v>
-      </c>
-      <c r="C136" s="59" t="str">
+    <row r="137" ht="102" customHeight="1">
+      <c r="A137" s="136" t="str">
+        <v>整机供电与电源监控</v>
+      </c>
+      <c r="B137" s="147" t="str">
+        <v>23-5</v>
+      </c>
+      <c r="C137" s="148" t="str">
         <v>电源采样连续恢复失败</v>
       </c>
-      <c r="D136" s="60" t="s">
-        <v>629</v>
-      </c>
-      <c r="E136" s="60" t="s">
-        <v>630</v>
-      </c>
-      <c r="F136" s="60" t="s">
-        <v>631</v>
-      </c>
-      <c r="G136" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="H136" s="58" t="s">
-        <v>27</v>
+      <c r="D137" s="132" t="str">
+        <v>触发：24V电源监控出问题后，设备已经连续尝试恢复3次，但都没有成功。
+影响：设备不能继续确认24V供电状态，会停止当前动作并保留故障。</v>
+      </c>
+      <c r="E137" s="132" t="str">
+        <v>1、电源采样故障持续存在，自动恢复未成功。
+2、供电、采样输入、主控硬件或内部运行异常。</v>
+      </c>
+      <c r="F137" s="132" t="str">
+        <v>注意：先排除风险，再恢复操作。
+1、保持停机，保存连续恢复失败的记录，不反复发起运动。
+2、检查24 V供电、采样回路和主控状态。
+3、检修后确认监控持续正常，再按流程重新发起操作；仅故障文字消失不代表已经恢复。</v>
+      </c>
+      <c r="G137" s="134" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H137" s="157" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="137" ht="165">
-      <c r="A137" s="56"/>
-      <c r="B137" s="69" t="s">
-        <v>632</v>
-      </c>
-      <c r="C137" s="69" t="s">
-        <v>633</v>
-      </c>
-      <c r="D137" s="68" t="s">
-        <v>634</v>
-      </c>
-      <c r="E137" s="68" t="s">
-        <v>635</v>
-      </c>
-      <c r="F137" s="68" t="s">
-        <v>636</v>
-      </c>
-      <c r="G137" s="61" t="s">
-        <v>26</v>
-      </c>
-      <c r="H137" s="58" t="s">
-        <v>27</v>
+    <row r="138" ht="117" customHeight="1">
+      <c r="A138" s="163" t="str">
+        <v>整机供电与电源监控</v>
+      </c>
+      <c r="B138" s="168" t="str">
+        <v>23-6</v>
+      </c>
+      <c r="C138" s="169" t="str">
+        <v>掉电位置保存失败</v>
+      </c>
+      <c r="D138" s="161" t="str">
+        <v>触发：设备检测到真实掉电，但编码器位置和掉电记录没有可靠保存，或重新上电后发现保存记录不完整。
+影响：断电前的位置可能不可信，重新运动前必须先确认设备实际位置。</v>
+      </c>
+      <c r="E138" s="161" t="str">
+        <v>1、掉电过快，或后备储能及电源保持时间不足。
+2、位置记录、存储校验或保存标记不完整。</v>
+      </c>
+      <c r="F138" s="161" t="str">
+        <v>注意：先排除风险，再恢复操作。
+1、不要按断电前位置继续运动，先人工确认机构实际位置。
+2、检查是否伴随编码器或存储故障，由技术人员检查掉电保持和保存记录。
+3、排除原因后回零或重新标定位置，确认保存和读回正常；不要反复制造掉电试验。</v>
+      </c>
+      <c r="G138" s="161" t="str">
+        <v>使用中</v>
+      </c>
+      <c r="H138" s="161" t="str">
+        <v>CPU2共享故障</v>
       </c>
     </row>
-    <row r="138" ht="120" customHeight="1">
-      <c r="A138" t="str" s="56">
+    <row r="139" ht="120" customHeight="1">
+      <c r="A139" t="str" s="136">
         <v>测量过程</v>
       </c>
-      <c r="B138" t="str" s="59">
+      <c r="B139" t="str" s="133">
         <v>15-34</v>
       </c>
-      <c r="C138" t="inlineStr" s="59">
+      <c r="C139" t="inlineStr" s="132">
         <is>
           <t>液位定时矫正失败</t>
         </is>
       </c>
-      <c r="D138" t="str" s="60">
+      <c r="D139" t="str" s="132">
         <v>触发：周期更新无法取得可用基准或重新稳定，且无法有效返回当前液面；或连续3轮更新失败。
 影响：停止当前跟随，旧液位不再作为正常测量结果。</v>
       </c>
-      <c r="E138" t="str" s="60">
+      <c r="E139" t="str" s="132">
         <v>1、空气与油中频率区分不足，或固定目标已不在有效窗口内。
 2、液面持续变化，规定时间内不能完成稳定定位。
 3、可用旧基准不足或回退失败。</v>
       </c>
-      <c r="F138" t="str" s="60">
+      <c r="F139" t="str" s="132">
         <v>1、保存刷新前后频率、各阶段用时和失败记录。
 2、先检查探头、液面工况和运动空间，再停机核对液位方法及目标参数。
 3、排除原因后重新找液位；台架确认成功前保持周期刷新关闭。有具体通信或电机故障时先按对应故障处理。</v>
       </c>
-      <c r="G138" t="str" s="61">
+      <c r="G139" t="str" s="134">
         <v>使用中</v>
       </c>
-      <c r="H138" t="str" s="58">
-        <v>CPU2 V1.43.0.0 / CPU3 V1.42.0.0起；共享协议36</v>
+      <c r="H139" t="str" s="157">
+        <v>协议36开发源码新增；首个正式固件组合待发布</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells>
-    <mergeCell ref="A2:A16"/>
-    <mergeCell ref="A17:A27"/>
-    <mergeCell ref="A28:A65"/>
-    <mergeCell ref="A66:A71"/>
-    <mergeCell ref="A72:A89"/>
-    <mergeCell ref="A90:A99"/>
-    <mergeCell ref="A100:A105"/>
-    <mergeCell ref="A106:A118"/>
-    <mergeCell ref="A119:A128"/>
-    <mergeCell ref="A129:A131"/>
-    <mergeCell ref="A132:A137"/>
-  </mergeCells>
-  <conditionalFormatting sqref="G2:G73">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="between" text="使用中">
-      <formula>NOT(ISERROR(SEARCH("使用中",G2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="2" operator="between" text="保留">
-      <formula>NOT(ISERROR(SEARCH("保留",G2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
+  <autoFilter ref="A1:H139"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -29126,19 +30408,19 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="42" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="24" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" customWidth="1"/>
+    <x:col min="2" max="2" width="10" customWidth="1"/>
+    <x:col min="3" max="3" width="23" customWidth="1"/>
+    <x:col min="4" max="4" width="43" customWidth="1"/>
+    <x:col min="5" max="5" width="42" customWidth="1"/>
+    <x:col min="6" max="6" width="53" customWidth="1"/>
+    <x:col min="7" max="7" width="10" customWidth="1"/>
+    <x:col min="8" max="8" width="30" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="72" t="str">
-        <x:v>协议34新增故障代码</x:v>
+        <x:v>协议34新增故障收录说明</x:v>
       </x:c>
       <x:c r="B1" s="72"/>
       <x:c r="C1" s="72"/>
@@ -29148,63 +30430,56 @@
       <x:c r="G1" s="72"/>
       <x:c r="H1" s="72"/>
     </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="77" t="str">
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="180" t="str">
         <x:v>类别</x:v>
       </x:c>
-      <x:c r="B2" s="77" t="str">
+      <x:c r="B2" s="180" t="str">
         <x:v>故障代码</x:v>
       </x:c>
-      <x:c r="C2" s="77" t="str">
+      <x:c r="C2" s="180" t="str">
         <x:v>故障名称</x:v>
       </x:c>
-      <x:c r="D2" s="77" t="str">
+      <x:c r="D2" s="180" t="str">
         <x:v>故障说明</x:v>
       </x:c>
-      <x:c r="E2" s="77" t="str">
+      <x:c r="E2" s="180" t="str">
         <x:v>故障原因</x:v>
       </x:c>
-      <x:c r="F2" s="77" t="str">
+      <x:c r="F2" s="180" t="str">
         <x:v>处理方法</x:v>
       </x:c>
-      <x:c r="G2" s="77" t="str">
+      <x:c r="G2" s="180" t="str">
         <x:v>状态</x:v>
       </x:c>
-      <x:c r="H2" s="77" t="str">
+      <x:c r="H2" s="180" t="str">
         <x:v>适用范围</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="150" customHeight="1">
-      <x:c r="A3" s="82" t="str">
+    <x:row r="3" ht="100" customHeight="1">
+      <x:c r="A3" s="177" t="str">
         <x:v>编码器</x:v>
       </x:c>
-      <x:c r="B3" s="82" t="str">
-        <x:v>12-17</x:v>
-      </x:c>
-      <x:c r="C3" s="82" t="str">
-        <x:v>编码器运行位置跳变</x:v>
-      </x:c>
-      <x:c r="D3" s="82" t="str">
-        <x:v>出现情况：运行中连续3个编码器候选增量超过按20 m/min极限、实际采样间隔和编码轮周长计算的动态物理上限。
-会有什么影响：异常读数不会写入累计位置，设备停止当前运动，避免位置突然越过罐高或运动边界。
-说明：方向不一致当前只在ENC?累计诊断，本身不触发12-17。</x:v>
-      </x:c>
-      <x:c r="E3" s="82" t="str">
-        <x:v>• 编码器或磁铁松动、瞬间偏移，信号线接触不良或电机启停干扰造成异常角度。
-• 尺带打滑、编码轮跳动，使位置反馈出现不可能的瞬时增量。
-• 编码轮周长参数明显不正确，也可能使正常速度被换算成异常增量。</x:v>
-      </x:c>
-      <x:c r="F3" s="82" t="str">
-        <x:v>1. 先处理：停止运动并人工确认机构实际位置。
-2. 重点检查：检查编码器、磁铁、线缆、尺带、编码轮压紧和周长参数。
-3. 处理完再看：重新上电后低速短程试运行，并查看ENC?中的候选增量、物理上限、间隔、拒绝原因和方向不一致统计。
-还是不行：保存故障前后的ENC?和运动日志交由技术人员分析。</x:v>
-      </x:c>
-      <x:c r="G3" s="82" t="str">
-        <x:v>使用中</x:v>
-      </x:c>
-      <x:c r="H3" s="82" t="str">
-        <x:v>CPU2共享故障｜协议34新增</x:v>
+      <x:c r="B3" s="177" t="str">
+        <x:v>已并入主表</x:v>
+      </x:c>
+      <x:c r="C3" s="177" t="str">
+        <x:v>12-17 编码器运行位置跳变</x:v>
+      </x:c>
+      <x:c r="D3" s="177" t="str">
+        <x:v>2026-09-07起，完整说明、可能原因和处理方法统一在“故障代码”页查询。</x:v>
+      </x:c>
+      <x:c r="E3" s="177" t="str">
+        <x:v>本页只保留收录记录，不再重复维护故障内容。</x:v>
+      </x:c>
+      <x:c r="F3" s="177" t="str">
+        <x:v>到主表按故障代码12-17筛选。</x:v>
+      </x:c>
+      <x:c r="G3" s="177" t="str">
+        <x:v>收录记录</x:v>
+      </x:c>
+      <x:c r="H3" s="177" t="str">
+        <x:v>协议34起启用</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
